--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -142,11 +142,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>HighProAmnesia</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>OrangePunchMimosa</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>HighProAmnesia</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>OrangePunchMimosa</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -14471,12 +14471,12 @@
       <c r="A104" s="2" t="inlineStr"/>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>— at issue —</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="D104" s="5">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -14503,71 +14503,75 @@
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>P060362</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr"/>
+          <t>N/A — no P batch assigned</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>— all three on the CNP certificate —</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
+          <t>Ident A + Ident B + Foreign matter</t>
+        </is>
+      </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N104" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060362|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("GG1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0020</t>
+          <t>iCoA-PP-2025-0003</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>11.03.2025</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>20.01.2025</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>11.03.2025</t>
         </is>
       </c>
       <c r="S104" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060362|I",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("GG1024|I",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>CNP ППК26111</t>
+          <t>Conforms</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>CNP ППК26111</t>
+          <t>Conforms</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>CNP ППК26111</t>
+          <t>Conforms</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>ППК26111, (30.06.2026) [CNP]</t>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
@@ -14587,12 +14591,12 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>P060362|I</t>
-        </is>
-      </c>
-      <c r="AB104" s="9" t="inlineStr">
-        <is>
-          <t>not needed — CNP covers A, B and foreign matter</t>
+          <t>GG1024|I</t>
+        </is>
+      </c>
+      <c r="AB104" s="8" t="inlineStr">
+        <is>
+          <t>not yet issuable — not in icoa_register.py — the register numbers the series and does not carry this round</t>
         </is>
       </c>
     </row>
@@ -14632,17 +14636,17 @@
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>BSS1024_01/2</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P050142</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
@@ -14656,31 +14660,31 @@
         </is>
       </c>
       <c r="N105" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("GG1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0003</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050142|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>11.03.2025</t>
+          <t>30.09.2025</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
         <is>
-          <t>20.01.2025</t>
+          <t>— not given —</t>
         </is>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>11.03.2025</t>
+          <t>30.09.2025</t>
         </is>
       </c>
       <c r="S105" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("GG1024|I",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050142|I",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T105" s="2" t="inlineStr">
@@ -14720,7 +14724,7 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>GG1024|I</t>
+          <t>P050142|I</t>
         </is>
       </c>
       <c r="AB105" s="8" t="inlineStr">
@@ -14765,17 +14769,17 @@
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>BSS1024_01/2</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>P050142</t>
+          <t>P060102</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -14789,7 +14793,7 @@
         </is>
       </c>
       <c r="N106" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050142|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060102|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O106" s="6" t="inlineStr">
@@ -14799,21 +14803,21 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>30.09.2025</t>
+          <t>16.02.2026</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>— not given —</t>
+          <t>08.01.2026</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>30.09.2025</t>
+          <t>16.02.2026</t>
         </is>
       </c>
       <c r="S106" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050142|I",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060102|I",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T106" s="2" t="inlineStr">
@@ -14853,7 +14857,7 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>P050142|I</t>
+          <t>P060102|I</t>
         </is>
       </c>
       <c r="AB106" s="8" t="inlineStr">
@@ -14898,17 +14902,17 @@
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>GRC102501</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>P060102</t>
+          <t>P060142</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
@@ -14922,7 +14926,7 @@
         </is>
       </c>
       <c r="N107" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060102|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060142|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O107" s="6" t="inlineStr">
@@ -14932,21 +14936,21 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>16.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>08.01.2026</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>16.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="S107" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060102|I",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060142|I",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T107" s="2" t="inlineStr">
@@ -14966,7 +14970,7 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+          <t>051-6-K-26, (04.03.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
@@ -14986,7 +14990,7 @@
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>P060102|I</t>
+          <t>P060142|I</t>
         </is>
       </c>
       <c r="AB107" s="8" t="inlineStr">
@@ -15021,7 +15025,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -15031,17 +15035,17 @@
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>GRC102501</t>
+          <t>JD112501＊</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>P060142</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -15055,31 +15059,31 @@
         </is>
       </c>
       <c r="N108" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060142|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O108" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("JD112501|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0015</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>— not on the list —</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>— not on the list —</t>
         </is>
       </c>
       <c r="S108" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060142|I",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("JD112501|I",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T108" s="2" t="inlineStr">
@@ -15099,7 +15103,7 @@
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>051-6-K-26, (04.03.2026) [FHM-K]</t>
+          <t>ППК26065, (11.05.2026) [CNP]</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
@@ -15119,12 +15123,12 @@
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>P060142|I</t>
+          <t>JD112501|I</t>
         </is>
       </c>
       <c r="AB108" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — not in icoa_register.py — the register numbers the series and does not carry this round</t>
+          <t>not yet issuable — no packaging date on the list</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15158,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -15164,75 +15168,71 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>JD112501＊</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>Jelly Donutz</t>
-        </is>
-      </c>
+          <t>P060362</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
         </is>
       </c>
-      <c r="M109" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
         </is>
       </c>
       <c r="N109" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("JD112501|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060362|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0015</t>
+          <t>iCoA-PP-2026-0020</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>23.05.2026</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>— not on the list —</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>— not on the list —</t>
+          <t>23.05.2026</t>
         </is>
       </c>
       <c r="S109" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("JD112501|I",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060362|I",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>Conforms</t>
+          <t>CNP ППК26111</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
         <is>
-          <t>Conforms</t>
+          <t>CNP ППК26111</t>
         </is>
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>Conforms</t>
+          <t>CNP ППК26111</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>ППК26065, (11.05.2026) [CNP]</t>
+          <t>ППК26111, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="X109" s="2" t="inlineStr">
@@ -15252,12 +15252,12 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>JD112501|I</t>
+          <t>P060362|I</t>
         </is>
       </c>
       <c r="AB109" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — no packaging date on the list</t>
+          <t>not yet issuable — not in the release register — icoa_register.py builds from it and has no testing history for this batch to number; the batch has to be entered there first</t>
         </is>
       </c>
     </row>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
@@ -22527,7 +22527,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L167" s="2" t="inlineStr">
@@ -23016,8 +23016,9 @@
         </is>
       </c>
     </row>
+    <row r="168"/>
     <row r="169" ht="110" customHeight="1">
-      <c r="A169" s="10" t="inlineStr">
+      <c r="A169" s="9" t="inlineStr">
         <is>
           <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 03.06.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 03.06.2026; a RETEST is dated at its own sampling, which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
         </is>
@@ -23511,7 +23512,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>HighProAmnesia</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -23607,7 +23608,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>OrangePunchMimosa</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
@@ -24829,7 +24830,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -25299,7 +25300,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -25393,7 +25394,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -29143,7 +29144,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -29515,7 +29516,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -29609,7 +29610,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -29703,7 +29704,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -31393,7 +31394,7 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>HighProAmnesia</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -31581,7 +31582,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>OrangePunchMimosa</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -32905,7 +32906,7 @@
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
@@ -33191,7 +33192,7 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="O108" s="6" t="inlineStr">
@@ -34235,7 +34236,7 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
@@ -37157,7 +37158,7 @@
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
@@ -37625,7 +37626,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="O155" s="6" t="inlineStr">
@@ -37815,7 +37816,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="O157" s="6" t="inlineStr">
@@ -37911,7 +37912,7 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="O158" s="6" t="inlineStr">
@@ -37945,8 +37946,9 @@
         </is>
       </c>
     </row>
+    <row r="159"/>
     <row r="160" ht="150" customHeight="1">
-      <c r="A160" s="10" t="inlineStr">
+      <c r="A160" s="9" t="inlineStr">
         <is>
           <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #9 — only the retest 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
@@ -38067,7 +38069,7 @@
           <t>CJ1024</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>listed as 'CJ1024 - R&amp;D'</t>
         </is>
@@ -38104,7 +38106,7 @@
           <t>GG1024</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>listed as 'GG1024- R&amp;D'</t>
         </is>
@@ -38141,7 +38143,7 @@
           <t>OPM1024</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>listed as 'OPM1024- R&amp;D'</t>
         </is>
@@ -38178,7 +38180,7 @@
           <t>BG1024</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>listed as 'BG1024- R&amp;D'</t>
         </is>
@@ -38215,7 +38217,7 @@
           <t>BSS1024</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>listed as 'BSS1024- R&amp;D'</t>
         </is>
@@ -38252,7 +38254,7 @@
           <t>HPA1024</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>listed as 'HPA1024- R&amp;D'</t>
         </is>
@@ -38293,7 +38295,7 @@
           <t>GG1024_01</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>packaging: year 2025 inferred (not printed)</t>
         </is>
@@ -38334,7 +38336,7 @@
           <t>GP0824_01</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>packaging: year 2025 inferred (not printed)</t>
         </is>
@@ -38375,7 +38377,7 @@
           <t>OMP1024_01</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -38412,7 +38414,7 @@
           <t>MB0824_04</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -38449,7 +38451,7 @@
           <t>GG1024_02</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -38486,7 +38488,7 @@
           <t>GP0824_02</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -38523,7 +38525,7 @@
           <t>HPA1024_01</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -38560,7 +38562,7 @@
           <t>OPM1024_02</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -38597,7 +38599,7 @@
           <t>BSS1024_01/1</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>packaging: year 2025 inferred (not printed)</t>
         </is>
@@ -38642,7 +38644,7 @@
           <t>BSS1024_01/2</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>harvest: no date given; packaging: year 2025 inferred (not printed)</t>
         </is>
@@ -38683,7 +38685,7 @@
           <t>GP0824_03</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>packaging: year 2025 inferred (not printed)</t>
         </is>
@@ -38724,7 +38726,7 @@
           <t>OPM1024_03</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -38761,7 +38763,7 @@
           <t>MB0824_05</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>packaging: year 2025 inferred (not printed)</t>
         </is>
@@ -38802,7 +38804,7 @@
           <t>OPM052501</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>packaging: year 2025 inferred (not printed)</t>
         </is>
@@ -38847,7 +38849,7 @@
           <t>GP052501</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>harvest: no date given</t>
         </is>
@@ -38888,7 +38890,7 @@
           <t>CJ052501/01</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -38925,7 +38927,7 @@
           <t>CJ052501/02</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -38962,7 +38964,7 @@
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -38999,7 +39001,7 @@
           <t>BSS052501</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -39036,7 +39038,7 @@
           <t>GP062501</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -39073,7 +39075,7 @@
           <t>— not on the tracker —</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -39110,7 +39112,7 @@
           <t>— not on the tracker —</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -39147,7 +39149,7 @@
           <t>CJ062501/1</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -39184,7 +39186,7 @@
           <t>CJ062501/2</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -39221,7 +39223,7 @@
           <t>CJ072501</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -39258,7 +39260,7 @@
           <t>PM072501</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -39295,7 +39297,7 @@
           <t>WC072501</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr"/>
+      <c r="J34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -39332,7 +39334,7 @@
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -39369,7 +39371,7 @@
           <t>GP072501/1</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>harvest: printed 11-13-11.2025, read as 11-13.11.2025</t>
         </is>
@@ -39410,7 +39412,7 @@
           <t>GP072501/2</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -39447,7 +39449,7 @@
           <t>GP082501/1</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr"/>
+      <c r="J38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -39484,7 +39486,7 @@
           <t>GP082501/2</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -39521,7 +39523,7 @@
           <t>WC082501</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr"/>
+      <c r="J40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -39558,7 +39560,7 @@
           <t>CJ082501/1</t>
         </is>
       </c>
-      <c r="J41" s="9" t="inlineStr"/>
+      <c r="J41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -39595,7 +39597,7 @@
           <t>CJ082501/2</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr"/>
+      <c r="J42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -39632,7 +39634,7 @@
           <t>PM092501</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -39669,7 +39671,7 @@
           <t>AB092501</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr"/>
+      <c r="J44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -39706,7 +39708,7 @@
           <t>SJ0925021</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -39743,7 +39745,7 @@
           <t>CJ092501</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr"/>
+      <c r="J46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -39780,7 +39782,7 @@
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -39817,7 +39819,7 @@
           <t>GP092501</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr"/>
+      <c r="J48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -39854,7 +39856,7 @@
           <t>— not on the tracker —</t>
         </is>
       </c>
-      <c r="J49" s="9" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -39891,7 +39893,7 @@
           <t>— not on the tracker —</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr"/>
+      <c r="J50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -39928,7 +39930,7 @@
           <t>GRC102501</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -39965,7 +39967,7 @@
           <t>WED102501</t>
         </is>
       </c>
-      <c r="J52" s="9" t="inlineStr"/>
+      <c r="J52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -40002,7 +40004,7 @@
           <t>— not on the tracker —</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr"/>
+      <c r="J53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -40039,7 +40041,7 @@
           <t>GRC102501</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr"/>
+      <c r="J54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -40076,7 +40078,7 @@
           <t>SJ102501</t>
         </is>
       </c>
-      <c r="J55" s="9" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -40113,7 +40115,7 @@
           <t>KC102501</t>
         </is>
       </c>
-      <c r="J56" s="9" t="inlineStr"/>
+      <c r="J56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -40150,7 +40152,7 @@
           <t>J31102501</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -40187,7 +40189,7 @@
           <t>J31112501</t>
         </is>
       </c>
-      <c r="J58" s="9" t="inlineStr"/>
+      <c r="J58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -40224,7 +40226,7 @@
           <t>SJ112501</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -40261,7 +40263,7 @@
           <t>OPM112501</t>
         </is>
       </c>
-      <c r="J60" s="9" t="inlineStr"/>
+      <c r="J60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -40298,7 +40300,7 @@
           <t>PM112501</t>
         </is>
       </c>
-      <c r="J61" s="9" t="inlineStr"/>
+      <c r="J61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -40335,7 +40337,7 @@
           <t>JD112501</t>
         </is>
       </c>
-      <c r="J62" s="9" t="inlineStr"/>
+      <c r="J62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -40372,7 +40374,7 @@
           <t>OPM122501</t>
         </is>
       </c>
-      <c r="J63" s="9" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -40409,7 +40411,7 @@
           <t>GG112501</t>
         </is>
       </c>
-      <c r="J64" s="9" t="inlineStr"/>
+      <c r="J64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -40446,7 +40448,7 @@
           <t>J31122501</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr"/>
+      <c r="J65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -40483,7 +40485,7 @@
           <t>CC112501</t>
         </is>
       </c>
-      <c r="J66" s="9" t="inlineStr"/>
+      <c r="J66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -40520,7 +40522,7 @@
           <t>SCR112501</t>
         </is>
       </c>
-      <c r="J67" s="9" t="inlineStr"/>
+      <c r="J67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -40557,7 +40559,7 @@
           <t>FB112501</t>
         </is>
       </c>
-      <c r="J68" s="9" t="inlineStr"/>
+      <c r="J68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -40594,7 +40596,7 @@
           <t>GG012601＊</t>
         </is>
       </c>
-      <c r="J69" s="9" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -40631,7 +40633,7 @@
           <t>JD012601＊</t>
         </is>
       </c>
-      <c r="J70" s="9" t="inlineStr"/>
+      <c r="J70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -40668,7 +40670,7 @@
           <t>FB012601_1</t>
         </is>
       </c>
-      <c r="J71" s="9" t="inlineStr"/>
+      <c r="J71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -40705,7 +40707,7 @@
           <t>CC012601/1</t>
         </is>
       </c>
-      <c r="J72" s="9" t="inlineStr"/>
+      <c r="J72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -40742,7 +40744,7 @@
           <t>SCR012601*</t>
         </is>
       </c>
-      <c r="J73" s="9" t="inlineStr"/>
+      <c r="J73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -40779,7 +40781,7 @@
           <t>FB012602*</t>
         </is>
       </c>
-      <c r="J74" s="9" t="inlineStr"/>
+      <c r="J74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -40816,7 +40818,7 @@
           <t>JD012603</t>
         </is>
       </c>
-      <c r="J75" s="9" t="inlineStr"/>
+      <c r="J75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -40853,7 +40855,7 @@
           <t>— not on the tracker —</t>
         </is>
       </c>
-      <c r="J76" s="9" t="inlineStr"/>
+      <c r="J76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -40890,7 +40892,7 @@
           <t>SCR012603</t>
         </is>
       </c>
-      <c r="J77" s="9" t="inlineStr"/>
+      <c r="J77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -40927,7 +40929,7 @@
           <t>FB012603V</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr"/>
+      <c r="J78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -40964,7 +40966,7 @@
           <t>GG012603</t>
         </is>
       </c>
-      <c r="J79" s="9" t="inlineStr"/>
+      <c r="J79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -41001,7 +41003,7 @@
           <t>JD012603</t>
         </is>
       </c>
-      <c r="J80" s="9" t="inlineStr"/>
+      <c r="J80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -41038,7 +41040,7 @@
           <t>JD012603</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr"/>
+      <c r="J81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -41075,7 +41077,7 @@
           <t>FB012603</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr"/>
+      <c r="J82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -41112,7 +41114,7 @@
           <t>SCR022601</t>
         </is>
       </c>
-      <c r="J83" s="9" t="inlineStr"/>
+      <c r="J83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -41149,7 +41151,7 @@
           <t>FB032601</t>
         </is>
       </c>
-      <c r="J84" s="9" t="inlineStr"/>
+      <c r="J84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -41186,7 +41188,7 @@
           <t>GG032601</t>
         </is>
       </c>
-      <c r="J85" s="9" t="inlineStr"/>
+      <c r="J85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -41223,7 +41225,7 @@
           <t>— not on the tracker —</t>
         </is>
       </c>
-      <c r="J86" s="9" t="inlineStr"/>
+      <c r="J86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -41260,7 +41262,7 @@
           <t>JD022601</t>
         </is>
       </c>
-      <c r="J87" s="9" t="inlineStr"/>
+      <c r="J87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -41297,7 +41299,7 @@
           <t>— not on the tracker —</t>
         </is>
       </c>
-      <c r="J88" s="9" t="inlineStr"/>
+      <c r="J88" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -41319,7 +41321,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v26 on 05.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v26 on 14.09.2026</t>
         </is>
       </c>
     </row>
@@ -41340,7 +41342,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v26.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v26.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -52472,7 +52472,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v31 on 15.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v32 on 15.09.2026</t>
         </is>
       </c>
     </row>
@@ -52493,7 +52493,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v31.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v32.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -52472,7 +52472,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v32 on 15.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v33 on 15.09.2026</t>
         </is>
       </c>
     </row>
@@ -52493,7 +52493,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v32.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v33.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -56063,7 +56063,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v34 on 15.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v35 on 15.09.2026</t>
         </is>
       </c>
     </row>
@@ -56084,7 +56084,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v34.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v35.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -56063,7 +56063,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v35 on 15.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v35 on 16.09.2026</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -56063,7 +56063,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v35 on 16.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v36 on 15.09.2026</t>
         </is>
       </c>
     </row>
@@ -56084,7 +56084,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v35.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v36.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -56063,7 +56063,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v36 on 15.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v36 on 16.09.2026</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -55529,7 +55529,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v37 on 16.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v38 on 16.09.2026</t>
         </is>
       </c>
     </row>
@@ -55550,7 +55550,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v37.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v38.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -36046,7 +36046,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>051-1-K/26</t>
+          <t>051-1-К/26</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
@@ -36179,7 +36179,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>051-3-K/26</t>
+          <t>051-3-К/26</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
@@ -36312,7 +36312,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>051-4-K/26</t>
+          <t>051-4-К/26</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
@@ -36445,7 +36445,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>051-6-K/26</t>
+          <t>051-6-К/26</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
@@ -36578,7 +36578,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>051-2-K/26</t>
+          <t>051-2-К/26</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
@@ -36711,7 +36711,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>051-5-K/26</t>
+          <t>051-5-К/26</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
@@ -55529,7 +55529,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v38 on 16.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v39 on 16.09.2026</t>
         </is>
       </c>
     </row>
@@ -55550,7 +55550,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v38.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v39.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="iCoA Register" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CoQ Register" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Batch Dates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iCoA Register" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoQ Register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch Dates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29998,12 +29998,14 @@
           <t>n/a — initial certificate</t>
         </is>
       </c>
-      <c r="V5" s="9" t="n">
-        <v>13.34</v>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP_26-004</t>
+          <t>—</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -30023,17 +30025,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-III_v.01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AB5" s="11" t="inlineStr">
         <is>
-          <t>for review — new specification required</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AC5" s="10" t="inlineStr">
         <is>
-          <t>new specification required — 13.34 % is in no window of GG (nearest 13.77 – 16.22); nominal and tolerance to define, numeral III</t>
+          <t>no Total THC result on this certificate</t>
         </is>
       </c>
     </row>
@@ -33743,7 +33745,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>PP CoA #027 / ППК25370</t>
+          <t>ППК25370</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
@@ -33876,7 +33878,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>PP CoA #018 / ППК25378</t>
+          <t>ППК25378</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
@@ -34009,7 +34011,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>PP CoA #019 / ППК25379</t>
+          <t>ППК25379</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
@@ -34142,7 +34144,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>PP CoA #020 / ППК25380</t>
+          <t>ППК25380</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
@@ -34275,7 +34277,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>PP CoA #021 / ППК25381</t>
+          <t>ППК25381</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
@@ -34940,7 +34942,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>PP CoA #037 / ППК26005</t>
+          <t>ППК26005</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
@@ -35639,7 +35641,7 @@
       </c>
       <c r="AC47" s="10" t="inlineStr">
         <is>
-          <t>strain not in the potency specification of 15.09.2026</t>
+          <t>no Total THC result on this certificate</t>
         </is>
       </c>
     </row>
@@ -43656,12 +43658,12 @@
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>12.00 ± 0.95 (I)</t>
+          <t>12.00 ± 1.20 (I)</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>11.05 – 12.94 %</t>
+          <t>10.80 – 13.19 %</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr">
@@ -43676,7 +43678,7 @@
       </c>
       <c r="AB107" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_ACC-I_v.01 (was ACC_THC12 : CBD1, 10.80 – 13.20 %); now ACC_THC12 : CBD1 11.05 – 12.94 %</t>
+          <t>for review — replaces the issued QCSP_001_ACC-I_v.01 (was ACC_THC12 : CBD1, 10.80 – 13.20 %); now ACC_THC12 : CBD1 10.80 – 13.19 %</t>
         </is>
       </c>
       <c r="AC107" s="11" t="inlineStr"/>
@@ -51444,34 +51446,30 @@
       </c>
       <c r="X166" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26.00 ± 2.60 (I)</t>
         </is>
       </c>
       <c r="Y166" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23.40 – 28.59 %</t>
         </is>
       </c>
       <c r="Z166" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WED_THC26 : CBD1</t>
         </is>
       </c>
       <c r="AA166" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>QCSP_001_WED-I_v.01</t>
         </is>
       </c>
       <c r="AB166" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC166" s="10" t="inlineStr">
-        <is>
-          <t>strain not in the potency specification of 15.09.2026</t>
-        </is>
-      </c>
+          <t>for review — new</t>
+        </is>
+      </c>
+      <c r="AC166" s="11" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2">
@@ -55793,7 +55791,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v41 on 16.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v42 on 17.09.2026</t>
         </is>
       </c>
     </row>
@@ -55814,7 +55812,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v41.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v42.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -248,8 +248,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="iCoA_Register" displayName="iCoA_Register" ref="A1:AB214" headerRowCount="1">
-  <autoFilter ref="A1:AB214"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="iCoA_Register" displayName="iCoA_Register" ref="A1:AB216" headerRowCount="1">
+  <autoFilter ref="A1:AB216"/>
   <tableColumns count="28">
     <tableColumn id="1" name="No."/>
     <tableColumn id="2" name="iCoA code"/>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB216"/>
+  <dimension ref="A1:AB218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14557,7 +14557,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>retest 1</t>
+          <t>retest 2</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -14586,7 +14586,7 @@
         </is>
       </c>
       <c r="N104" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050212|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050212|R2",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O104" s="6" t="inlineStr">
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="S104" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050212|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050212|R2",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T104" s="2" t="inlineStr">
@@ -14650,12 +14650,12 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>P050212|R</t>
+          <t>P050212|R2</t>
         </is>
       </c>
       <c r="AB104" s="7" t="inlineStr">
         <is>
-          <t>registered — retest 1 · Tranche 1 (sampled 21–24.07.2026), tested 21.07.2026, issued 27.07.2026</t>
+          <t>registered — retest 2 · Tranche 1 (sampled 21–24.07.2026), tested 21.07.2026, issued 27.07.2026</t>
         </is>
       </c>
     </row>
@@ -17620,7 +17620,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>retest 1</t>
+          <t>retest 2</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="N127" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050222|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050222|R2",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O127" s="6" t="inlineStr">
@@ -17673,7 +17673,7 @@
         </is>
       </c>
       <c r="S127" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050222|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050222|R2",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T127" s="2" t="inlineStr">
@@ -17713,12 +17713,12 @@
       </c>
       <c r="AA127" s="2" t="inlineStr">
         <is>
-          <t>P050222|R</t>
+          <t>P050222|R2</t>
         </is>
       </c>
       <c r="AB127" s="7" t="inlineStr">
         <is>
-          <t>registered — retest 1 · Tranche 2 (sampled 12–14.08.2026), tested 12.08.2026, issued 17.08.2026</t>
+          <t>registered — retest 2 · Tranche 2 (sampled 12–14.08.2026), tested 12.08.2026, issued 17.08.2026</t>
         </is>
       </c>
     </row>
@@ -25595,7 +25595,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -25605,17 +25605,17 @@
       </c>
       <c r="I187" s="3" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>CJ062501/1</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>P060432</t>
+          <t>P050222</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L187" s="2" t="inlineStr">
@@ -25629,7 +25629,7 @@
         </is>
       </c>
       <c r="N187" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060432|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050222|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O187" s="6" t="inlineStr">
@@ -25639,31 +25639,31 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>30.06.2027</t>
+          <t>24.11.2026</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
         <is>
-          <t>04.05.2026</t>
+          <t>23.09.2025</t>
         </is>
       </c>
       <c r="R187" s="2" t="inlineStr">
         <is>
-          <t>15.06.2026 (the issuance plan's basis: 30.06.2026)</t>
+          <t>24.11.2025 – 25.11.2025</t>
         </is>
       </c>
       <c r="S187" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060432|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050222|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T187" s="2" t="inlineStr">
         <is>
-          <t>CNP ППК26112</t>
+          <t>Conforms</t>
         </is>
       </c>
       <c r="U187" s="2" t="inlineStr">
         <is>
-          <t>CNP ППК26112</t>
+          <t>Conforms</t>
         </is>
       </c>
       <c r="V187" s="2" t="inlineStr">
@@ -25673,17 +25673,17 @@
       </c>
       <c r="W187" s="2" t="inlineStr">
         <is>
-          <t>227-24-K-26, (11.09.2026) [FHM-K]</t>
+          <t>220-3-K-26, (25.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X187" s="2" t="inlineStr">
         <is>
-          <t>227-24-K-26, (11.09.2026) [FHM-K]</t>
+          <t>220-3-K-26, (25.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>— pending —</t>
+          <t>220-3-M-26, (11.09.2026) [FHM-M]</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="AA187" s="2" t="inlineStr">
         <is>
-          <t>P060432|R</t>
+          <t>P050222|R</t>
         </is>
       </c>
       <c r="AB187" s="7" t="inlineStr">
@@ -25728,7 +25728,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -25738,17 +25738,17 @@
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>FB012603V</t>
+          <t>CJ062501/2</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>P060392</t>
+          <t>P050212</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="N188" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060392|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050212|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O188" s="6" t="inlineStr">
@@ -25772,31 +25772,31 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>30.06.2027</t>
+          <t>24.01.2027</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
         <is>
-          <t>29.04.2026</t>
+          <t>23.09.2025 – 24.09.2025</t>
         </is>
       </c>
       <c r="R188" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026 (the issuance plan's basis: 30.06.2026)</t>
+          <t>18.11.2025 – 24.11.2025 (the issuance plan's basis: 24.01.2026)</t>
         </is>
       </c>
       <c r="S188" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060392|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050212|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T188" s="2" t="inlineStr">
         <is>
-          <t>CNP ППК26110</t>
+          <t>Conforms</t>
         </is>
       </c>
       <c r="U188" s="2" t="inlineStr">
         <is>
-          <t>CNP ППК26110</t>
+          <t>Conforms</t>
         </is>
       </c>
       <c r="V188" s="2" t="inlineStr">
@@ -25806,17 +25806,17 @@
       </c>
       <c r="W188" s="2" t="inlineStr">
         <is>
-          <t>227-23-K-26, (11.09.2026) [FHM-K]</t>
+          <t>197-4-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X188" s="2" t="inlineStr">
         <is>
-          <t>227-23-K-26, (11.09.2026) [FHM-K]</t>
+          <t>197-4-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y188" s="2" t="inlineStr">
         <is>
-          <t>— pending —</t>
+          <t>197-4-M-26, (10.08.2026) [FHM-M]</t>
         </is>
       </c>
       <c r="Z188" s="2" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="AA188" s="2" t="inlineStr">
         <is>
-          <t>P060392|R</t>
+          <t>P050212|R</t>
         </is>
       </c>
       <c r="AB188" s="7" t="inlineStr">
@@ -25871,12 +25871,12 @@
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>P060292</t>
+          <t>P060432</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -25895,7 +25895,7 @@
         </is>
       </c>
       <c r="N189" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060292|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060432|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O189" s="6" t="inlineStr">
@@ -25905,31 +25905,31 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>11.05.2027</t>
+          <t>30.06.2027</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
         <is>
-          <t>25.03.2026</t>
+          <t>04.05.2026</t>
         </is>
       </c>
       <c r="R189" s="2" t="inlineStr">
         <is>
-          <t>19.05.2026 (the issuance plan's basis: 11.05.2026)</t>
+          <t>15.06.2026 (the issuance plan's basis: 30.06.2026)</t>
         </is>
       </c>
       <c r="S189" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060292|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060432|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T189" s="2" t="inlineStr">
         <is>
-          <t>Conforms</t>
+          <t>CNP ППК26112</t>
         </is>
       </c>
       <c r="U189" s="2" t="inlineStr">
         <is>
-          <t>Conforms</t>
+          <t>CNP ППК26112</t>
         </is>
       </c>
       <c r="V189" s="2" t="inlineStr">
@@ -25939,12 +25939,12 @@
       </c>
       <c r="W189" s="2" t="inlineStr">
         <is>
-          <t>227-22-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-24-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>227-22-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-24-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
@@ -25959,7 +25959,7 @@
       </c>
       <c r="AA189" s="2" t="inlineStr">
         <is>
-          <t>P060292|R</t>
+          <t>P060432|R</t>
         </is>
       </c>
       <c r="AB189" s="7" t="inlineStr">
@@ -26004,17 +26004,17 @@
       </c>
       <c r="I190" s="3" t="inlineStr">
         <is>
-          <t>GG012601＊</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>P060302</t>
+          <t>P060392</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="N190" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060302|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060392|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O190" s="6" t="inlineStr">
@@ -26038,31 +26038,31 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>11.05.2027</t>
+          <t>30.06.2027</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
         <is>
-          <t>27.03.2026</t>
+          <t>29.04.2026</t>
         </is>
       </c>
       <c r="R190" s="2" t="inlineStr">
         <is>
-          <t>20.05.2026 (the issuance plan's basis: 11.05.2026)</t>
+          <t>23.05.2026 (the issuance plan's basis: 30.06.2026)</t>
         </is>
       </c>
       <c r="S190" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060302|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060392|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T190" s="2" t="inlineStr">
         <is>
-          <t>Conforms</t>
+          <t>CNP ППК26110</t>
         </is>
       </c>
       <c r="U190" s="2" t="inlineStr">
         <is>
-          <t>Conforms</t>
+          <t>CNP ППК26110</t>
         </is>
       </c>
       <c r="V190" s="2" t="inlineStr">
@@ -26072,12 +26072,12 @@
       </c>
       <c r="W190" s="2" t="inlineStr">
         <is>
-          <t>227-21-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-23-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>227-21-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-23-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="AA190" s="2" t="inlineStr">
         <is>
-          <t>P060302|R</t>
+          <t>P060392|R</t>
         </is>
       </c>
       <c r="AB190" s="7" t="inlineStr">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -26137,17 +26137,17 @@
       </c>
       <c r="I191" s="3" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>P060252</t>
+          <t>P060292</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L191" s="2" t="inlineStr">
@@ -26161,7 +26161,7 @@
         </is>
       </c>
       <c r="N191" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060252|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060292|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O191" s="6" t="inlineStr">
@@ -26181,11 +26181,11 @@
       </c>
       <c r="R191" s="2" t="inlineStr">
         <is>
-          <t>05.05.2026 (the issuance plan's basis: 11.05.2026)</t>
+          <t>19.05.2026 (the issuance plan's basis: 11.05.2026)</t>
         </is>
       </c>
       <c r="S191" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060252|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060292|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T191" s="2" t="inlineStr">
@@ -26205,12 +26205,12 @@
       </c>
       <c r="W191" s="2" t="inlineStr">
         <is>
-          <t>227-20-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-22-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>227-20-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-22-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
@@ -26225,7 +26225,7 @@
       </c>
       <c r="AA191" s="2" t="inlineStr">
         <is>
-          <t>P060252|R</t>
+          <t>P060292|R</t>
         </is>
       </c>
       <c r="AB191" s="7" t="inlineStr">
@@ -26260,7 +26260,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -26270,17 +26270,17 @@
       </c>
       <c r="I192" s="3" t="inlineStr">
         <is>
-          <t>J31112501</t>
+          <t>GG012601＊</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>P060202</t>
+          <t>P060302</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
@@ -26294,7 +26294,7 @@
         </is>
       </c>
       <c r="N192" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060202|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060302|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O192" s="6" t="inlineStr">
@@ -26304,21 +26304,21 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>09.04.2027</t>
+          <t>11.05.2027</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
         <is>
-          <t>26.01.2026</t>
+          <t>27.03.2026</t>
         </is>
       </c>
       <c r="R192" s="2" t="inlineStr">
         <is>
-          <t>17.04.2026 (the issuance plan's basis: 09.04.2026)</t>
+          <t>20.05.2026 (the issuance plan's basis: 11.05.2026)</t>
         </is>
       </c>
       <c r="S192" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060202|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060302|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T192" s="2" t="inlineStr">
@@ -26338,12 +26338,12 @@
       </c>
       <c r="W192" s="2" t="inlineStr">
         <is>
-          <t>227-14-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-21-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>227-14-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-21-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="AA192" s="2" t="inlineStr">
         <is>
-          <t>P060202|R</t>
+          <t>P060302|R</t>
         </is>
       </c>
       <c r="AB192" s="7" t="inlineStr">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -26403,17 +26403,17 @@
       </c>
       <c r="I193" s="3" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>GG112501</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>P060262</t>
+          <t>P060252</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
@@ -26427,7 +26427,7 @@
         </is>
       </c>
       <c r="N193" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060262|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060252|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O193" s="6" t="inlineStr">
@@ -26437,21 +26437,21 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>23.04.2027</t>
+          <t>11.05.2027</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>25.03.2026</t>
         </is>
       </c>
       <c r="R193" s="2" t="inlineStr">
         <is>
-          <t>14.05.2026 (the issuance plan's basis: 23.04.2026)</t>
+          <t>05.05.2026 (the issuance plan's basis: 11.05.2026)</t>
         </is>
       </c>
       <c r="S193" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060262|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060252|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T193" s="2" t="inlineStr">
@@ -26471,19 +26471,19 @@
       </c>
       <c r="W193" s="2" t="inlineStr">
         <is>
-          <t>— retest assay not yet on file —</t>
+          <t>227-20-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
+          <t>227-20-K-26, (11.09.2026) [FHM-K]</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr">
+        <is>
           <t>— pending —</t>
         </is>
       </c>
-      <c r="Y193" s="2" t="inlineStr">
-        <is>
-          <t>— pending —</t>
-        </is>
-      </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
           <t>#8, #9, #11, #12 from the initial testing</t>
@@ -26491,7 +26491,7 @@
       </c>
       <c r="AA193" s="2" t="inlineStr">
         <is>
-          <t>P060262|R</t>
+          <t>P060252|R</t>
         </is>
       </c>
       <c r="AB193" s="7" t="inlineStr">
@@ -26526,7 +26526,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -26536,17 +26536,17 @@
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>JD012601＊</t>
+          <t>J31112501</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>P060312</t>
+          <t>P060202</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
@@ -26560,7 +26560,7 @@
         </is>
       </c>
       <c r="N194" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060312|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060202|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O194" s="6" t="inlineStr">
@@ -26570,21 +26570,21 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>11.05.2027</t>
+          <t>09.04.2027</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
         <is>
-          <t>27.03.2026</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="R194" s="2" t="inlineStr">
         <is>
-          <t>21.05.2026 (the issuance plan's basis: 11.05.2026)</t>
+          <t>17.04.2026 (the issuance plan's basis: 09.04.2026)</t>
         </is>
       </c>
       <c r="S194" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060312|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060202|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T194" s="2" t="inlineStr">
@@ -26604,12 +26604,12 @@
       </c>
       <c r="W194" s="2" t="inlineStr">
         <is>
-          <t>227-15-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-14-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>227-15-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-14-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
@@ -26624,7 +26624,7 @@
       </c>
       <c r="AA194" s="2" t="inlineStr">
         <is>
-          <t>P060312|R</t>
+          <t>P060202|R</t>
         </is>
       </c>
       <c r="AB194" s="7" t="inlineStr">
@@ -26659,7 +26659,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -26669,17 +26669,17 @@
       </c>
       <c r="I195" s="3" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>P060222</t>
+          <t>P060262</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="L195" s="2" t="inlineStr">
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="N195" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060222|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060262|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O195" s="6" t="inlineStr">
@@ -26703,21 +26703,21 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>05.03.2027</t>
+          <t>23.04.2027</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
         <is>
-          <t>05.02.2026</t>
+          <t>04.03.2026</t>
         </is>
       </c>
       <c r="R195" s="2" t="inlineStr">
         <is>
-          <t>24.04.2026 (the issuance plan's basis: 05.03.2026)</t>
+          <t>14.05.2026 (the issuance plan's basis: 23.04.2026)</t>
         </is>
       </c>
       <c r="S195" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060222|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060262|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T195" s="2" t="inlineStr">
@@ -26737,12 +26737,12 @@
       </c>
       <c r="W195" s="2" t="inlineStr">
         <is>
-          <t>227-10-K-26, (11.09.2026) [FHM-K]</t>
+          <t>— retest assay not yet on file —</t>
         </is>
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>227-10-K-26, (11.09.2026) [FHM-K]</t>
+          <t>— pending —</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="AA195" s="2" t="inlineStr">
         <is>
-          <t>P060222|R</t>
+          <t>P060262|R</t>
         </is>
       </c>
       <c r="AB195" s="7" t="inlineStr">
@@ -26802,17 +26802,17 @@
       </c>
       <c r="I196" s="3" t="inlineStr">
         <is>
-          <t>SCR012601*</t>
+          <t>JD012601＊</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>P060342</t>
+          <t>P060312</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
@@ -26826,7 +26826,7 @@
         </is>
       </c>
       <c r="N196" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060342|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060312|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O196" s="6" t="inlineStr">
@@ -26836,21 +26836,21 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>25.05.2027</t>
+          <t>11.05.2027</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
         <is>
-          <t>16.04.2026</t>
+          <t>27.03.2026</t>
         </is>
       </c>
       <c r="R196" s="2" t="inlineStr">
         <is>
-          <t>25.05.2026</t>
+          <t>21.05.2026 (the issuance plan's basis: 11.05.2026)</t>
         </is>
       </c>
       <c r="S196" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060342|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060312|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T196" s="2" t="inlineStr">
@@ -26870,12 +26870,12 @@
       </c>
       <c r="W196" s="2" t="inlineStr">
         <is>
-          <t>227-8-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-15-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>227-8-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-15-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="AA196" s="2" t="inlineStr">
         <is>
-          <t>P060342|R</t>
+          <t>P060312|R</t>
         </is>
       </c>
       <c r="AB196" s="7" t="inlineStr">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -26935,17 +26935,17 @@
       </c>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>P060442</t>
+          <t>P060222</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L197" s="2" t="inlineStr">
@@ -26959,7 +26959,7 @@
         </is>
       </c>
       <c r="N197" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060442|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060222|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O197" s="6" t="inlineStr">
@@ -26969,31 +26969,31 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>06.07.2027</t>
+          <t>05.03.2027</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
         <is>
-          <t>13.05.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="R197" s="2" t="inlineStr">
         <is>
-          <t>18.06.2026 (the issuance plan's basis: 06.07.2026)</t>
+          <t>24.04.2026 (the issuance plan's basis: 05.03.2026)</t>
         </is>
       </c>
       <c r="S197" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060442|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060222|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T197" s="2" t="inlineStr">
         <is>
-          <t>CNP ППК26116</t>
+          <t>Conforms</t>
         </is>
       </c>
       <c r="U197" s="2" t="inlineStr">
         <is>
-          <t>CNP ППК26116</t>
+          <t>Conforms</t>
         </is>
       </c>
       <c r="V197" s="2" t="inlineStr">
@@ -27003,12 +27003,12 @@
       </c>
       <c r="W197" s="2" t="inlineStr">
         <is>
-          <t>227-7-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-10-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>227-7-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-10-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="AA197" s="2" t="inlineStr">
         <is>
-          <t>P060442|R</t>
+          <t>P060222|R</t>
         </is>
       </c>
       <c r="AB197" s="7" t="inlineStr">
@@ -27058,7 +27058,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -27068,17 +27068,17 @@
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>SJ102501</t>
+          <t>SCR012601*</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>P060162</t>
+          <t>P060342</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="N198" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060162|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060342|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O198" s="6" t="inlineStr">
@@ -27102,21 +27102,21 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>04.03.2027</t>
+          <t>25.05.2027</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>16.04.2026</t>
         </is>
       </c>
       <c r="R198" s="2" t="inlineStr">
         <is>
-          <t>09.03.2026 (the issuance plan's basis: 04.03.2026)</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="S198" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060162|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060342|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T198" s="2" t="inlineStr">
@@ -27136,12 +27136,12 @@
       </c>
       <c r="W198" s="2" t="inlineStr">
         <is>
-          <t>227-6-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-8-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>227-6-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-8-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
@@ -27156,7 +27156,7 @@
       </c>
       <c r="AA198" s="2" t="inlineStr">
         <is>
-          <t>P060162|R</t>
+          <t>P060342|R</t>
         </is>
       </c>
       <c r="AB198" s="7" t="inlineStr">
@@ -27180,10 +27180,10 @@
         </is>
       </c>
       <c r="D199" s="5" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="F199" s="5">
         <f>IFERROR(INDEX('Batch Dates'!$G:$G,MATCH(J199,'Batch Dates'!$C:$C,0)),IFERROR(INDEX('Batch Dates'!$G:$G,MATCH(I199,'Batch Dates'!$B:$B,0)),""))</f>
@@ -27191,7 +27191,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -27201,17 +27201,17 @@
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>AB092501</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>P060052</t>
+          <t>P060442</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>Apple and Banana</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L199" s="2" t="inlineStr">
@@ -27225,7 +27225,7 @@
         </is>
       </c>
       <c r="N199" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060052|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060442|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O199" s="6" t="inlineStr">
@@ -27235,31 +27235,31 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20.02.2027</t>
+          <t>06.07.2027</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
         <is>
-          <t>11.12.2025</t>
+          <t>13.05.2026</t>
         </is>
       </c>
       <c r="R199" s="2" t="inlineStr">
         <is>
-          <t>30.01.2026 (the issuance plan's basis: 20.02.2026)</t>
+          <t>18.06.2026 (the issuance plan's basis: 06.07.2026)</t>
         </is>
       </c>
       <c r="S199" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060052|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060442|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T199" s="2" t="inlineStr">
         <is>
-          <t>Conforms</t>
+          <t>CNP ППК26116</t>
         </is>
       </c>
       <c r="U199" s="2" t="inlineStr">
         <is>
-          <t>Conforms</t>
+          <t>CNP ППК26116</t>
         </is>
       </c>
       <c r="V199" s="2" t="inlineStr">
@@ -27269,12 +27269,12 @@
       </c>
       <c r="W199" s="2" t="inlineStr">
         <is>
-          <t>227-30-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-7-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>227-30-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-7-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="AA199" s="2" t="inlineStr">
         <is>
-          <t>P060052|R</t>
+          <t>P060442|R</t>
         </is>
       </c>
       <c r="AB199" s="7" t="inlineStr">
         <is>
-          <t>registered — retest 1, issued 01.09.2026</t>
+          <t>registered — retest 1, issued 31.08.2026</t>
         </is>
       </c>
     </row>
@@ -27313,10 +27313,10 @@
         </is>
       </c>
       <c r="D200" s="5" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="F200" s="5">
         <f>IFERROR(INDEX('Batch Dates'!$G:$G,MATCH(J200,'Batch Dates'!$C:$C,0)),IFERROR(INDEX('Batch Dates'!$G:$G,MATCH(I200,'Batch Dates'!$B:$B,0)),""))</f>
@@ -27334,17 +27334,17 @@
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
-          <t>BSS1024_01/1</t>
+          <t>SJ102501</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>P050122</t>
+          <t>P060162</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
@@ -27358,7 +27358,7 @@
         </is>
       </c>
       <c r="N200" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050122|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060162|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O200" s="6" t="inlineStr">
@@ -27368,21 +27368,21 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>04.03.2027</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
         <is>
-          <t>04.06.2025 – 05.06.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="R200" s="2" t="inlineStr">
         <is>
-          <t>01.09.2025 – 09.09.2025 (the issuance plan's basis: 10.07.2025)</t>
+          <t>09.03.2026 (the issuance plan's basis: 04.03.2026)</t>
         </is>
       </c>
       <c r="S200" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050122|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060162|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T200" s="2" t="inlineStr">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="W200" s="2" t="inlineStr">
         <is>
-          <t>227-29-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-6-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>227-29-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-6-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
@@ -27422,12 +27422,12 @@
       </c>
       <c r="AA200" s="2" t="inlineStr">
         <is>
-          <t>P050122|R</t>
+          <t>P060162|R</t>
         </is>
       </c>
       <c r="AB200" s="7" t="inlineStr">
         <is>
-          <t>registered — retest 1, issued 01.09.2026</t>
+          <t>registered — retest 1, issued 31.08.2026</t>
         </is>
       </c>
     </row>
@@ -27467,17 +27467,17 @@
       </c>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>BSS1024_01/2</t>
+          <t>AB092501</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>P050142</t>
+          <t>P060052</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Apple and Banana</t>
         </is>
       </c>
       <c r="L201" s="2" t="inlineStr">
@@ -27491,7 +27491,7 @@
         </is>
       </c>
       <c r="N201" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050142|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060052|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O201" s="6" t="inlineStr">
@@ -27501,21 +27501,21 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>20.02.2027</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
         <is>
-          <t>— not given —</t>
+          <t>11.12.2025</t>
         </is>
       </c>
       <c r="R201" s="2" t="inlineStr">
         <is>
-          <t>30.09.2025</t>
+          <t>30.01.2026 (the issuance plan's basis: 20.02.2026)</t>
         </is>
       </c>
       <c r="S201" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050142|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060052|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T201" s="2" t="inlineStr">
@@ -27535,12 +27535,12 @@
       </c>
       <c r="W201" s="2" t="inlineStr">
         <is>
-          <t>227-1-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-30-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>227-1-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-30-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
@@ -27555,7 +27555,7 @@
       </c>
       <c r="AA201" s="2" t="inlineStr">
         <is>
-          <t>P050142|R</t>
+          <t>P060052|R</t>
         </is>
       </c>
       <c r="AB201" s="7" t="inlineStr">
@@ -27600,17 +27600,17 @@
       </c>
       <c r="I202" s="3" t="inlineStr">
         <is>
-          <t>CJ052501/02</t>
+          <t>BSS1024_01/1</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>P050172</t>
+          <t>P050122</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="N202" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050172|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050122|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O202" s="6" t="inlineStr">
@@ -27634,21 +27634,21 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>04.06.2025 – 05.06.2025</t>
         </is>
       </c>
       <c r="R202" s="2" t="inlineStr">
         <is>
-          <t>01.10.2025 – 02.10.2025 (the issuance plan's basis: 17.09.2025)</t>
+          <t>01.09.2025 – 09.09.2025 (the issuance plan's basis: 10.07.2025)</t>
         </is>
       </c>
       <c r="S202" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050172|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050122|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T202" s="2" t="inlineStr">
@@ -27668,12 +27668,12 @@
       </c>
       <c r="W202" s="2" t="inlineStr">
         <is>
-          <t>227-28-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-29-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X202" s="2" t="inlineStr">
         <is>
-          <t>227-28-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-29-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y202" s="2" t="inlineStr">
@@ -27688,7 +27688,7 @@
       </c>
       <c r="AA202" s="2" t="inlineStr">
         <is>
-          <t>P050172|R</t>
+          <t>P050122|R</t>
         </is>
       </c>
       <c r="AB202" s="7" t="inlineStr">
@@ -27733,17 +27733,17 @@
       </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
-          <t>CJ072501</t>
+          <t>BSS1024_01/2</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>P050252</t>
+          <t>P050142</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="L203" s="2" t="inlineStr">
@@ -27757,7 +27757,7 @@
         </is>
       </c>
       <c r="N203" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050252|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050142|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O203" s="6" t="inlineStr">
@@ -27767,21 +27767,21 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>02.12.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
         <is>
-          <t>27.10.2025</t>
+          <t>— not given —</t>
         </is>
       </c>
       <c r="R203" s="2" t="inlineStr">
         <is>
-          <t>27.11.2025 – 28.11.2025 (the issuance plan's basis: 02.12.2025)</t>
+          <t>30.09.2025</t>
         </is>
       </c>
       <c r="S203" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050252|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050142|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T203" s="2" t="inlineStr">
@@ -27801,12 +27801,12 @@
       </c>
       <c r="W203" s="2" t="inlineStr">
         <is>
-          <t>227-27-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-1-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X203" s="2" t="inlineStr">
         <is>
-          <t>227-27-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-1-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y203" s="2" t="inlineStr">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="AA203" s="2" t="inlineStr">
         <is>
-          <t>P050252|R</t>
+          <t>P050142|R</t>
         </is>
       </c>
       <c r="AB203" s="7" t="inlineStr">
@@ -27866,12 +27866,12 @@
       </c>
       <c r="I204" s="3" t="inlineStr">
         <is>
-          <t>CJ1024</t>
+          <t>CJ052501/02</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P050172</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -27890,7 +27890,7 @@
         </is>
       </c>
       <c r="N204" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("CJ1024|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050172|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O204" s="6" t="inlineStr">
@@ -27900,21 +27900,21 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>27.02.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
         <is>
-          <t>20.01.2025</t>
+          <t>20.08.2025</t>
         </is>
       </c>
       <c r="R204" s="2" t="inlineStr">
         <is>
-          <t>03.03.2025 (the issuance plan's basis: 27.02.2025)</t>
+          <t>01.10.2025 – 02.10.2025 (the issuance plan's basis: 17.09.2025)</t>
         </is>
       </c>
       <c r="S204" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("CJ1024|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050172|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T204" s="2" t="inlineStr">
@@ -27934,12 +27934,12 @@
       </c>
       <c r="W204" s="2" t="inlineStr">
         <is>
-          <t>227-26-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-28-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X204" s="2" t="inlineStr">
         <is>
-          <t>227-26-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-28-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y204" s="2" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="AA204" s="2" t="inlineStr">
         <is>
-          <t>CJ1024|R</t>
+          <t>P050172|R</t>
         </is>
       </c>
       <c r="AB204" s="7" t="inlineStr">
@@ -27999,17 +27999,17 @@
       </c>
       <c r="I205" s="3" t="inlineStr">
         <is>
-          <t>GG1024_02</t>
+          <t>CJ072501</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>P050012</t>
+          <t>P050252</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L205" s="2" t="inlineStr">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="N205" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050012|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050252|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O205" s="6" t="inlineStr">
@@ -28033,21 +28033,21 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>30.05.2026</t>
+          <t>02.12.2026</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
         <is>
-          <t>14.04.2025 – 15.04.2025</t>
+          <t>27.10.2025</t>
         </is>
       </c>
       <c r="R205" s="2" t="inlineStr">
         <is>
-          <t>11.06.2025 – 16.06.2025 (the issuance plan's basis: 30.05.2025)</t>
+          <t>27.11.2025 – 28.11.2025 (the issuance plan's basis: 02.12.2025)</t>
         </is>
       </c>
       <c r="S205" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050012|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050252|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T205" s="2" t="inlineStr">
@@ -28067,12 +28067,12 @@
       </c>
       <c r="W205" s="2" t="inlineStr">
         <is>
-          <t>227-19-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-27-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X205" s="2" t="inlineStr">
         <is>
-          <t>227-19-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-27-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y205" s="2" t="inlineStr">
@@ -28087,7 +28087,7 @@
       </c>
       <c r="AA205" s="2" t="inlineStr">
         <is>
-          <t>P050012|R</t>
+          <t>P050252|R</t>
         </is>
       </c>
       <c r="AB205" s="7" t="inlineStr">
@@ -28127,22 +28127,22 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>retest 2</t>
+          <t>retest 1</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr">
         <is>
-          <t>GP062501</t>
+          <t>CJ1024</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>P050202</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L206" s="2" t="inlineStr">
@@ -28156,7 +28156,7 @@
         </is>
       </c>
       <c r="N206" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050202|R2",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("CJ1024|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O206" s="6" t="inlineStr">
@@ -28166,21 +28166,21 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>11.05.2027</t>
+          <t>27.02.2026</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
         <is>
-          <t>15.09.2025 – 17.09.2025</t>
+          <t>20.01.2025</t>
         </is>
       </c>
       <c r="R206" s="2" t="inlineStr">
         <is>
-          <t>30.10.2025 – 07.11.2025 (the issuance plan's basis: 11.05.2026)</t>
+          <t>03.03.2025 (the issuance plan's basis: 27.02.2025)</t>
         </is>
       </c>
       <c r="S206" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050202|R2",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("CJ1024|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T206" s="2" t="inlineStr">
@@ -28200,12 +28200,12 @@
       </c>
       <c r="W206" s="2" t="inlineStr">
         <is>
-          <t>227-18-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-26-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X206" s="2" t="inlineStr">
         <is>
-          <t>227-18-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-26-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y206" s="2" t="inlineStr">
@@ -28220,12 +28220,12 @@
       </c>
       <c r="AA206" s="2" t="inlineStr">
         <is>
-          <t>P050202|R2</t>
+          <t>CJ1024|R</t>
         </is>
       </c>
       <c r="AB206" s="7" t="inlineStr">
         <is>
-          <t>registered — retest 2, issued 01.09.2026</t>
+          <t>registered — retest 1, issued 01.09.2026</t>
         </is>
       </c>
     </row>
@@ -28265,17 +28265,17 @@
       </c>
       <c r="I207" s="3" t="inlineStr">
         <is>
-          <t>GP072501/1</t>
+          <t>GG1024_02</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>P050292</t>
+          <t>P050012</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L207" s="2" t="inlineStr">
@@ -28289,7 +28289,7 @@
         </is>
       </c>
       <c r="N207" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050292|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050012|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O207" s="6" t="inlineStr">
@@ -28299,21 +28299,21 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>21.01.2027</t>
+          <t>30.05.2026</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
         <is>
-          <t>11.11.2025 – 13.11.2025</t>
+          <t>14.04.2025 – 15.04.2025</t>
         </is>
       </c>
       <c r="R207" s="2" t="inlineStr">
         <is>
-          <t>15.12.2025 – 21.12.2025 (the issuance plan's basis: 21.01.2026)</t>
+          <t>11.06.2025 – 16.06.2025 (the issuance plan's basis: 30.05.2025)</t>
         </is>
       </c>
       <c r="S207" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050292|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050012|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T207" s="2" t="inlineStr">
@@ -28333,12 +28333,12 @@
       </c>
       <c r="W207" s="2" t="inlineStr">
         <is>
-          <t>227-17-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-19-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X207" s="2" t="inlineStr">
         <is>
-          <t>227-17-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-19-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y207" s="2" t="inlineStr">
@@ -28353,7 +28353,7 @@
       </c>
       <c r="AA207" s="2" t="inlineStr">
         <is>
-          <t>P050292|R</t>
+          <t>P050012|R</t>
         </is>
       </c>
       <c r="AB207" s="7" t="inlineStr">
@@ -28393,17 +28393,17 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>retest 1</t>
+          <t>retest 2</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>GP0824_01</t>
+          <t>GP062501</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>P050102</t>
+          <t>P050202</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -28422,7 +28422,7 @@
         </is>
       </c>
       <c r="N208" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050102|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050202|R2",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O208" s="6" t="inlineStr">
@@ -28432,21 +28432,21 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>17.04.2026</t>
+          <t>11.05.2027</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
         <is>
-          <t>20.03.2025 – 21.03.2025</t>
+          <t>15.09.2025 – 17.09.2025</t>
         </is>
       </c>
       <c r="R208" s="2" t="inlineStr">
         <is>
-          <t>05.08.2025 – 07.08.2025 (the issuance plan's basis: 17.04.2025)</t>
+          <t>30.10.2025 – 07.11.2025 (the issuance plan's basis: 11.05.2026)</t>
         </is>
       </c>
       <c r="S208" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050102|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050202|R2",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T208" s="2" t="inlineStr">
@@ -28466,12 +28466,12 @@
       </c>
       <c r="W208" s="2" t="inlineStr">
         <is>
-          <t>227-2-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-18-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X208" s="2" t="inlineStr">
         <is>
-          <t>227-2-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-18-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y208" s="2" t="inlineStr">
@@ -28486,12 +28486,12 @@
       </c>
       <c r="AA208" s="2" t="inlineStr">
         <is>
-          <t>P050102|R</t>
+          <t>P050202|R2</t>
         </is>
       </c>
       <c r="AB208" s="7" t="inlineStr">
         <is>
-          <t>registered — retest 1, issued 01.09.2026</t>
+          <t>registered — retest 2, issued 01.09.2026</t>
         </is>
       </c>
     </row>
@@ -28531,17 +28531,17 @@
       </c>
       <c r="I209" s="3" t="inlineStr">
         <is>
-          <t>GRC102501</t>
+          <t>GP072501/1</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>P060142</t>
+          <t>P050292</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L209" s="2" t="inlineStr">
@@ -28555,7 +28555,7 @@
         </is>
       </c>
       <c r="N209" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060142|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050292|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O209" s="6" t="inlineStr">
@@ -28565,21 +28565,21 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>23.02.2027</t>
+          <t>21.01.2027</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
         <is>
-          <t>09.01.2026</t>
+          <t>11.11.2025 – 13.11.2025</t>
         </is>
       </c>
       <c r="R209" s="2" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>15.12.2025 – 21.12.2025 (the issuance plan's basis: 21.01.2026)</t>
         </is>
       </c>
       <c r="S209" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060142|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050292|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T209" s="2" t="inlineStr">
@@ -28599,12 +28599,12 @@
       </c>
       <c r="W209" s="2" t="inlineStr">
         <is>
-          <t>227-16-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-17-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X209" s="2" t="inlineStr">
         <is>
-          <t>227-16-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-17-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y209" s="2" t="inlineStr">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="AA209" s="2" t="inlineStr">
         <is>
-          <t>P060142|R</t>
+          <t>P050292|R</t>
         </is>
       </c>
       <c r="AB209" s="7" t="inlineStr">
@@ -28664,17 +28664,17 @@
       </c>
       <c r="I210" s="3" t="inlineStr">
         <is>
-          <t>MB0824_04</t>
+          <t>GP0824_01</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>P050032</t>
+          <t>P050102</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L210" s="2" t="inlineStr">
@@ -28688,7 +28688,7 @@
         </is>
       </c>
       <c r="N210" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050032|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050102|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O210" s="6" t="inlineStr">
@@ -28698,21 +28698,21 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>07.05.2026</t>
+          <t>17.04.2026</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
         <is>
-          <t>02.04.2025 – 03.04.2025</t>
+          <t>20.03.2025 – 21.03.2025</t>
         </is>
       </c>
       <c r="R210" s="2" t="inlineStr">
         <is>
-          <t>16.06.2025 – 19.06.2025 (the issuance plan's basis: 07.05.2025)</t>
+          <t>05.08.2025 – 07.08.2025 (the issuance plan's basis: 17.04.2025)</t>
         </is>
       </c>
       <c r="S210" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050032|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050102|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T210" s="2" t="inlineStr">
@@ -28732,12 +28732,12 @@
       </c>
       <c r="W210" s="2" t="inlineStr">
         <is>
-          <t>227-12-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-2-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X210" s="2" t="inlineStr">
         <is>
-          <t>227-12-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-2-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y210" s="2" t="inlineStr">
@@ -28752,7 +28752,7 @@
       </c>
       <c r="AA210" s="2" t="inlineStr">
         <is>
-          <t>P050032|R</t>
+          <t>P050102|R</t>
         </is>
       </c>
       <c r="AB210" s="7" t="inlineStr">
@@ -28797,17 +28797,17 @@
       </c>
       <c r="I211" s="3" t="inlineStr">
         <is>
-          <t>OPM052501</t>
+          <t>GRC102501</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>P050132</t>
+          <t>P060142</t>
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="L211" s="2" t="inlineStr">
@@ -28821,7 +28821,7 @@
         </is>
       </c>
       <c r="N211" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050132|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060142|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O211" s="6" t="inlineStr">
@@ -28831,21 +28831,21 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>23.02.2027</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
         <is>
-          <t>11.08.2025 – 13.08.2025</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="R211" s="2" t="inlineStr">
         <is>
-          <t>09.09.2025 – 15.09.2025 (the issuance plan's basis: 05.09.2025)</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="S211" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050132|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060142|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T211" s="2" t="inlineStr">
@@ -28865,12 +28865,12 @@
       </c>
       <c r="W211" s="2" t="inlineStr">
         <is>
-          <t>227-11-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-16-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X211" s="2" t="inlineStr">
         <is>
-          <t>227-11-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-16-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y211" s="2" t="inlineStr">
@@ -28885,7 +28885,7 @@
       </c>
       <c r="AA211" s="2" t="inlineStr">
         <is>
-          <t>P050132|R</t>
+          <t>P060142|R</t>
         </is>
       </c>
       <c r="AB211" s="7" t="inlineStr">
@@ -28930,17 +28930,17 @@
       </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>MB0824_04</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>P050272</t>
+          <t>P050032</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="L212" s="2" t="inlineStr">
@@ -28954,7 +28954,7 @@
         </is>
       </c>
       <c r="N212" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050272|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050032|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O212" s="6" t="inlineStr">
@@ -28964,21 +28964,21 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>21.01.2027</t>
+          <t>07.05.2026</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
         <is>
-          <t>27.10.2025</t>
+          <t>02.04.2025 – 03.04.2025</t>
         </is>
       </c>
       <c r="R212" s="2" t="inlineStr">
         <is>
-          <t>02.12.2025 – 03.12.2025 (the issuance plan's basis: 21.01.2026)</t>
+          <t>16.06.2025 – 19.06.2025 (the issuance plan's basis: 07.05.2025)</t>
         </is>
       </c>
       <c r="S212" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050272|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050032|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T212" s="2" t="inlineStr">
@@ -28998,12 +28998,12 @@
       </c>
       <c r="W212" s="2" t="inlineStr">
         <is>
-          <t>227-9-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-12-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X212" s="2" t="inlineStr">
         <is>
-          <t>227-9-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-12-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y212" s="2" t="inlineStr">
@@ -29018,7 +29018,7 @@
       </c>
       <c r="AA212" s="2" t="inlineStr">
         <is>
-          <t>P050272|R</t>
+          <t>P050032|R</t>
         </is>
       </c>
       <c r="AB212" s="7" t="inlineStr">
@@ -29063,17 +29063,17 @@
       </c>
       <c r="I213" s="3" t="inlineStr">
         <is>
-          <t>WC072501</t>
+          <t>OPM052501</t>
         </is>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>P050262</t>
+          <t>P050132</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L213" s="2" t="inlineStr">
@@ -29087,7 +29087,7 @@
         </is>
       </c>
       <c r="N213" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050262|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050132|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O213" s="6" t="inlineStr">
@@ -29097,21 +29097,21 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>02.12.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
         <is>
-          <t>27.10.2025 – 28.10.2025</t>
+          <t>11.08.2025 – 13.08.2025</t>
         </is>
       </c>
       <c r="R213" s="2" t="inlineStr">
         <is>
-          <t>01.12.2025 (the issuance plan's basis: 02.12.2025)</t>
+          <t>09.09.2025 – 15.09.2025 (the issuance plan's basis: 05.09.2025)</t>
         </is>
       </c>
       <c r="S213" s="5">
-        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050262|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050132|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
       <c r="T213" s="2" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="W213" s="2" t="inlineStr">
         <is>
-          <t>227-3-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-11-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X213" s="2" t="inlineStr">
         <is>
-          <t>227-3-K-26, (11.09.2026) [FHM-K]</t>
+          <t>227-11-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="Y213" s="2" t="inlineStr">
@@ -29151,7 +29151,7 @@
       </c>
       <c r="AA213" s="2" t="inlineStr">
         <is>
-          <t>P050262|R</t>
+          <t>P050132|R</t>
         </is>
       </c>
       <c r="AB213" s="7" t="inlineStr">
@@ -29196,106 +29196,372 @@
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
+          <t>PM072501</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>P050272</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Permanent Market</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>Ident A + Ident B + Foreign matter</t>
+        </is>
+      </c>
+      <c r="M214" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N214" s="2">
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050272|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O214" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>21.01.2027</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2025</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>02.12.2025 – 03.12.2025 (the issuance plan's basis: 21.01.2026)</t>
+        </is>
+      </c>
+      <c r="S214" s="5">
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050272|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <v/>
+      </c>
+      <c r="T214" s="2" t="inlineStr">
+        <is>
+          <t>Conforms</t>
+        </is>
+      </c>
+      <c r="U214" s="2" t="inlineStr">
+        <is>
+          <t>Conforms</t>
+        </is>
+      </c>
+      <c r="V214" s="2" t="inlineStr">
+        <is>
+          <t>Conforms</t>
+        </is>
+      </c>
+      <c r="W214" s="2" t="inlineStr">
+        <is>
+          <t>227-9-K-26, (11.09.2026) [FHM-K]</t>
+        </is>
+      </c>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>227-9-K-26, (11.09.2026) [FHM-K]</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr">
+        <is>
+          <t>— pending —</t>
+        </is>
+      </c>
+      <c r="Z214" s="2" t="inlineStr">
+        <is>
+          <t>#8, #9, #11, #12 from the initial testing</t>
+        </is>
+      </c>
+      <c r="AA214" s="2" t="inlineStr">
+        <is>
+          <t>P050272|R</t>
+        </is>
+      </c>
+      <c r="AB214" s="7" t="inlineStr">
+        <is>
+          <t>registered — retest 1, issued 01.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>iCoA-PP_26-214</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E215" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F215" s="5">
+        <f>IFERROR(INDEX('Batch Dates'!$G:$G,MATCH(J215,'Batch Dates'!$C:$C,0)),IFERROR(INDEX('Batch Dates'!$G:$G,MATCH(I215,'Batch Dates'!$B:$B,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>retest 1</t>
+        </is>
+      </c>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>WC072501</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>P050262</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>Ident A + Ident B + Foreign matter</t>
+        </is>
+      </c>
+      <c r="M215" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N215" s="2">
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050262|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O215" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>02.12.2026</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>27.10.2025 – 28.10.2025</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>01.12.2025 (the issuance plan's basis: 02.12.2025)</t>
+        </is>
+      </c>
+      <c r="S215" s="5">
+        <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P050262|R",'CoQ Register'!$S:$S,0)),"")</f>
+        <v/>
+      </c>
+      <c r="T215" s="2" t="inlineStr">
+        <is>
+          <t>Conforms</t>
+        </is>
+      </c>
+      <c r="U215" s="2" t="inlineStr">
+        <is>
+          <t>Conforms</t>
+        </is>
+      </c>
+      <c r="V215" s="2" t="inlineStr">
+        <is>
+          <t>Conforms</t>
+        </is>
+      </c>
+      <c r="W215" s="2" t="inlineStr">
+        <is>
+          <t>227-3-K-26, (11.09.2026) [FHM-K]</t>
+        </is>
+      </c>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>227-3-K-26, (11.09.2026) [FHM-K]</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr">
+        <is>
+          <t>— pending —</t>
+        </is>
+      </c>
+      <c r="Z215" s="2" t="inlineStr">
+        <is>
+          <t>#8, #9, #11, #12 from the initial testing</t>
+        </is>
+      </c>
+      <c r="AA215" s="2" t="inlineStr">
+        <is>
+          <t>P050262|R</t>
+        </is>
+      </c>
+      <c r="AB215" s="7" t="inlineStr">
+        <is>
+          <t>registered — retest 1, issued 01.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>iCoA-PP_26-215</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E216" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F216" s="5">
+        <f>IFERROR(INDEX('Batch Dates'!$G:$G,MATCH(J216,'Batch Dates'!$C:$C,0)),IFERROR(INDEX('Batch Dates'!$G:$G,MATCH(I216,'Batch Dates'!$B:$B,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>retest 1</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr">
+        <is>
           <t>WED102501</t>
         </is>
       </c>
-      <c r="J214" s="2" t="inlineStr">
+      <c r="J216" s="2" t="inlineStr">
         <is>
           <t>P060102</t>
         </is>
       </c>
-      <c r="K214" s="2" t="inlineStr">
+      <c r="K216" s="2" t="inlineStr">
         <is>
           <t>Wedding Cake</t>
         </is>
       </c>
-      <c r="L214" s="2" t="inlineStr">
+      <c r="L216" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
         </is>
       </c>
-      <c r="M214" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N214" s="2">
+      <c r="M216" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N216" s="2">
         <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060102|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
-      <c r="O214" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P214" s="2" t="inlineStr">
+      <c r="O216" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr">
         <is>
           <t>16.02.2027</t>
         </is>
       </c>
-      <c r="Q214" s="2" t="inlineStr">
+      <c r="Q216" s="2" t="inlineStr">
         <is>
           <t>08.01.2026</t>
         </is>
       </c>
-      <c r="R214" s="2" t="inlineStr">
+      <c r="R216" s="2" t="inlineStr">
         <is>
           <t>16.02.2026</t>
         </is>
       </c>
-      <c r="S214" s="5">
+      <c r="S216" s="5">
         <f>IFERROR(INDEX('CoQ Register'!$D:$D,MATCH("P060102|R",'CoQ Register'!$S:$S,0)),"")</f>
         <v/>
       </c>
-      <c r="T214" s="2" t="inlineStr">
-        <is>
-          <t>Conforms</t>
-        </is>
-      </c>
-      <c r="U214" s="2" t="inlineStr">
-        <is>
-          <t>Conforms</t>
-        </is>
-      </c>
-      <c r="V214" s="2" t="inlineStr">
-        <is>
-          <t>Conforms</t>
-        </is>
-      </c>
-      <c r="W214" s="2" t="inlineStr">
+      <c r="T216" s="2" t="inlineStr">
+        <is>
+          <t>Conforms</t>
+        </is>
+      </c>
+      <c r="U216" s="2" t="inlineStr">
+        <is>
+          <t>Conforms</t>
+        </is>
+      </c>
+      <c r="V216" s="2" t="inlineStr">
+        <is>
+          <t>Conforms</t>
+        </is>
+      </c>
+      <c r="W216" s="2" t="inlineStr">
         <is>
           <t>227-4-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
-      <c r="X214" s="2" t="inlineStr">
+      <c r="X216" s="2" t="inlineStr">
         <is>
           <t>227-4-K-26, (11.09.2026) [FHM-K]</t>
         </is>
       </c>
-      <c r="Y214" s="2" t="inlineStr">
+      <c r="Y216" s="2" t="inlineStr">
         <is>
           <t>— pending —</t>
         </is>
       </c>
-      <c r="Z214" s="2" t="inlineStr">
+      <c r="Z216" s="2" t="inlineStr">
         <is>
           <t>#8, #9, #11, #12 from the initial testing</t>
         </is>
       </c>
-      <c r="AA214" s="2" t="inlineStr">
+      <c r="AA216" s="2" t="inlineStr">
         <is>
           <t>P060102|R</t>
         </is>
       </c>
-      <c r="AB214" s="7" t="inlineStr">
+      <c r="AB216" s="7" t="inlineStr">
         <is>
           <t>registered — retest 1, issued 01.09.2026</t>
         </is>
       </c>
     </row>
-    <row r="215"/>
-    <row r="216" ht="110" customHeight="1">
-      <c r="A216" s="8" t="inlineStr">
+    <row r="217"/>
+    <row r="218" ht="110" customHeight="1">
+      <c r="A218" s="8" t="inlineStr">
         <is>
           <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 03.06.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 03.06.2026; a RETEST is dated at its own sampling day and issued on its campaign's day (sampling_dates.py, owner 15.09.2026: Tranche 1 sampled 21–24.07.2026 and issued 27.07.2026, Tranche 2 sampled 12–14.08.2026 and issued 17.08.2026, Tranche 3 sampled 19–21.08.2026 and issued 24.08.2026, each batch on the day its certificate number falls), which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. A round whose packaging date the list does not hold is numbered all the same (owner, 15.09.2026: identification A, B and foreign matter are performed on every batch) and says its testing date is not stated. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
         </is>
@@ -29303,7 +29569,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A216:AB216"/>
+    <mergeCell ref="A218:AB218"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -35526,14 +35792,12 @@
         <f>IF(ISNUMBER(F47),MAX(DATE(2026,6,6),F47+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F47" s="5" t="n">
+        <v>46065</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>031-3-ГС-26</t>
         </is>
       </c>
       <c r="H47" s="2">
@@ -35596,7 +35860,7 @@
       </c>
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -41334,15 +41598,15 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>197-4-M-26</t>
+          <t>197-5-M-26</t>
         </is>
       </c>
       <c r="H90" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050212|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060032|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I90" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050212|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060032|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -41357,12 +41621,12 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>CJ062501/2</t>
+          <t>CJ082501/2</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>P050212</t>
+          <t>P060032</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -41372,7 +41636,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>197-4-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-5-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P90" s="6" t="inlineStr">
@@ -41392,49 +41656,49 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>P050212|R</t>
+          <t>P060032|R</t>
         </is>
       </c>
       <c r="T90" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 21.07.2026; issued 17.08.2026, 7 days after 197-4-M-26 of 10.08.2026; cites iCoA-PP_26-103 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 21.07.2026; issued 17.08.2026, 7 days after 197-5-M-26 of 10.08.2026; cites iCoA-PP_26-104 of 27.07.2026</t>
         </is>
       </c>
       <c r="U90" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050212|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060032|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V90" s="9" t="n">
-        <v>18.91</v>
+        <v>18.29</v>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>197-4-К/26</t>
+          <t>197-5-К/26</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>20.00 ± 1.60 (III)</t>
+          <t>17.00 ± 1.40 (IV)</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>18.40 – 21.59 %</t>
+          <t>15.60 – 18.39 %</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>CJ_THC20 : CBD1</t>
+          <t>CJ_THC17 : CBD1</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-III_v.01</t>
+          <t>QCSP_001_CJ-IV_v.01</t>
         </is>
       </c>
       <c r="AB90" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_CJ-III_v.01 (was CJ_THC24 : CBD1, 23.00 – 25.00 %); now CJ_THC20 : CBD1 18.40 – 21.59 %</t>
+          <t>for review — replaces the issued QCSP_001_CJ-IV_v.01 (was CJ_THC20 : CBD1, 18.00 – 22.00 %); now CJ_THC17 : CBD1 15.60 – 18.39 %</t>
         </is>
       </c>
       <c r="AC90" s="11" t="inlineStr"/>
@@ -41466,20 +41730,20 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>197-5-M-26</t>
+          <t>197-7-M-26</t>
         </is>
       </c>
       <c r="H91" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060032|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060352|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I91" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060032|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060352|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -41489,22 +41753,22 @@
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>CJ082501/2</t>
+          <t>FB012602*</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>P060032</t>
+          <t>P060352</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>197-5-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-7-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P91" s="6" t="inlineStr">
@@ -41524,49 +41788,49 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>P060032|R</t>
+          <t>P060352|R</t>
         </is>
       </c>
       <c r="T91" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 21.07.2026; issued 17.08.2026, 7 days after 197-5-M-26 of 10.08.2026; cites iCoA-PP_26-104 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-7-M-26 of 10.08.2026; cites iCoA-PP_26-109 of 27.07.2026</t>
         </is>
       </c>
       <c r="U91" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060032|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060352|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V91" s="9" t="n">
-        <v>18.29</v>
+        <v>18.86</v>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>197-5-К/26</t>
+          <t>197-7-К/26</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>17.00 ± 1.40 (IV)</t>
+          <t>18.00 ± 1.80 (II)</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>15.60 – 18.39 %</t>
+          <t>16.20 – 19.79 %</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>CJ_THC17 : CBD1</t>
+          <t>FB_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_CJ-IV_v.01</t>
+          <t>QCSP_001_FB-II_v.01</t>
         </is>
       </c>
       <c r="AB91" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_CJ-IV_v.01 (was CJ_THC20 : CBD1, 18.00 – 22.00 %); now CJ_THC17 : CBD1 15.60 – 18.39 %</t>
+          <t>for review — replaces the issued QCSP_001_FB-II_v.01 (was FB_THC18 : CBD1, 17.15 – 18.85 %); now FB_THC18 : CBD1 16.20 – 19.79 %</t>
         </is>
       </c>
       <c r="AC91" s="11" t="inlineStr"/>
@@ -41598,15 +41862,15 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>197-7-M-26</t>
+          <t>197-8-M-26</t>
         </is>
       </c>
       <c r="H92" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060352|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060402|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I92" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060352|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060402|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -41621,22 +41885,22 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>FB012602*</t>
+          <t>GG012603</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060402</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>197-7-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-8-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P92" s="6" t="inlineStr">
@@ -41656,49 +41920,49 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>P060352|R</t>
+          <t>P060402|R</t>
         </is>
       </c>
       <c r="T92" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-7-M-26 of 10.08.2026; cites iCoA-PP_26-109 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-8-M-26 of 10.08.2026; cites iCoA-PP_26-110 of 27.07.2026</t>
         </is>
       </c>
       <c r="U92" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060352|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060402|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V92" s="9" t="n">
-        <v>18.86</v>
+        <v>16.7</v>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>197-7-К/26</t>
+          <t>197-8-К/26</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>18.00 ± 1.80 (II)</t>
+          <t>18.00 ± 1.77 (I)</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %</t>
+          <t>16.23 – 19.76 %</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>FB_THC18 : CBD1</t>
+          <t>GG_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-II_v.01</t>
+          <t>QCSP_001_GG-I_v.01</t>
         </is>
       </c>
       <c r="AB92" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_FB-II_v.01 (was FB_THC18 : CBD1, 17.15 – 18.85 %); now FB_THC18 : CBD1 16.20 – 19.79 %</t>
+          <t>for review — replaces the issued QCSP_001_GG-I_v.01 (was GG_THC18 : CBD1, 17.01 – 18.99 %); now GG_THC18 : CBD1 16.23 – 19.76 %</t>
         </is>
       </c>
       <c r="AC92" s="11" t="inlineStr"/>
@@ -41730,20 +41994,20 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>197-8-M-26</t>
+          <t>197-9-M-26</t>
         </is>
       </c>
       <c r="H93" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060402|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050092|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I93" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060402|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050092|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -41753,12 +42017,12 @@
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>GG1024_01</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>P060402</t>
+          <t>P050092</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -41768,7 +42032,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>197-8-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-9-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P93" s="6" t="inlineStr">
@@ -41783,29 +42047,29 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>CoQ reissue (assigned on issue)</t>
+          <t>CoQ-PP-2026-0038</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>P060402|R</t>
+          <t>P050092|R</t>
         </is>
       </c>
       <c r="T93" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-8-M-26 of 10.08.2026; cites iCoA-PP_26-110 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-9-M-26 of 10.08.2026; cites iCoA-PP_26-106 of 27.07.2026</t>
         </is>
       </c>
       <c r="U93" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060402|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050092|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V93" s="9" t="n">
-        <v>16.7</v>
+        <v>18.67</v>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>197-8-К/26</t>
+          <t>197-9-К/26</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
@@ -41862,15 +42126,15 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>197-9-M-26</t>
+          <t>197-10-M-26</t>
         </is>
       </c>
       <c r="H94" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050092|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050152|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I94" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050092|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050152|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -41885,22 +42149,22 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>GG1024_01</t>
+          <t>GP052501</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>P050092</t>
+          <t>P050152</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>197-9-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-10-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P94" s="6" t="inlineStr">
@@ -41915,54 +42179,54 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0038</t>
+          <t>CoQ reissue (assigned on issue)</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>P050092|R</t>
+          <t>P050152|R</t>
         </is>
       </c>
       <c r="T94" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-9-M-26 of 10.08.2026; cites iCoA-PP_26-106 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-10-M-26 of 10.08.2026; cites iCoA-PP_26-107 of 27.07.2026</t>
         </is>
       </c>
       <c r="U94" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050092|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050152|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V94" s="9" t="n">
-        <v>18.67</v>
+        <v>18.52</v>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>197-9-К/26</t>
+          <t>197-10-К/26</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>18.00 ± 1.77 (I)</t>
+          <t>20.00 ± 2.00 (III)</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>16.23 – 19.76 %</t>
+          <t>18.00 – 21.99 %</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>GG_THC18 : CBD1</t>
+          <t>GP_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_GG-I_v.01</t>
+          <t>QCSP_001_GP-III_v.01</t>
         </is>
       </c>
       <c r="AB94" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_GG-I_v.01 (was GG_THC18 : CBD1, 17.01 – 18.99 %); now GG_THC18 : CBD1 16.23 – 19.76 %</t>
+          <t>for review — replaces the issued QCSP_001_GP-III_v.01 (was GP_THC24 : CBD1, 22.61 – 25.39 %); now GP_THC20 : CBD1 18.00 – 21.99 %</t>
         </is>
       </c>
       <c r="AC94" s="11" t="inlineStr"/>
@@ -41994,15 +42258,15 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>197-10-M-26</t>
+          <t>197-11-M-26</t>
         </is>
       </c>
       <c r="H95" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050152|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050022|R5",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I95" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050152|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050022|R5",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -42017,12 +42281,12 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>GP052501</t>
+          <t>GP0824_02</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>P050152</t>
+          <t>P050022</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -42032,7 +42296,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>197-10-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-11-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P95" s="6" t="inlineStr">
@@ -42047,54 +42311,54 @@
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>CoQ reissue (assigned on issue)</t>
+          <t>CoQ-PP-2026-0032</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>P050152|R</t>
+          <t>P050022|R5</t>
         </is>
       </c>
       <c r="T95" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-10-M-26 of 10.08.2026; cites iCoA-PP_26-107 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-11-M-26 of 10.08.2026; cites the campaign iCoA of 27.07.2026</t>
         </is>
       </c>
       <c r="U95" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050152|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050022|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V95" s="9" t="n">
-        <v>18.52</v>
+        <v>22.61</v>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>197-10-К/26</t>
+          <t>197-11-К/26</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>20.00 ± 2.00 (III)</t>
+          <t>24.00 ± 2.00 (II)</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>18.00 – 21.99 %</t>
+          <t>22.00 – 25.99 %</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>GP_THC20 : CBD1</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-III_v.01</t>
+          <t>QCSP_001_GP-II_v.01</t>
         </is>
       </c>
       <c r="AB95" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_GP-III_v.01 (was GP_THC24 : CBD1, 22.61 – 25.39 %); now GP_THC20 : CBD1 18.00 – 21.99 %</t>
+          <t>for review — replaces the issued QCSP_001_GP-II_v.01 (was GP_THC26 : CBD1, 25.40 – 26.60 %); now GP_THC24 : CBD1 22.00 – 25.99 %</t>
         </is>
       </c>
       <c r="AC95" s="11" t="inlineStr"/>
@@ -42126,15 +42390,15 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>197-11-M-26</t>
+          <t>197-12-M-26</t>
         </is>
       </c>
       <c r="H96" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050022|R5",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050322|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I96" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050022|R5",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050322|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -42149,12 +42413,12 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>GP0824_02</t>
+          <t>GP082501/2</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>P050022</t>
+          <t>P050322</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -42164,7 +42428,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>197-11-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-12-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P96" s="6" t="inlineStr">
@@ -42179,54 +42443,54 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0032</t>
+          <t>CoQ reissue (assigned on issue)</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>P050022|R5</t>
+          <t>P050322|R</t>
         </is>
       </c>
       <c r="T96" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 22.07.2026; issued 17.08.2026, 7 days after 197-11-M-26 of 10.08.2026; cites the campaign iCoA of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-12-M-26 of 10.08.2026; cites iCoA-PP_26-111 of 27.07.2026</t>
         </is>
       </c>
       <c r="U96" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050022|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050322|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V96" s="9" t="n">
-        <v>22.61</v>
+        <v>15.7</v>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>197-11-К/26</t>
+          <t>197-12-К/26</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>24.00 ± 2.00 (II)</t>
+          <t>16.00 ± 1.60 (IV)</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>22.00 – 25.99 %</t>
+          <t>14.40 – 17.59 %</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>GP_THC24 : CBD1</t>
+          <t>GP_THC16 : CBD1</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-II_v.01</t>
+          <t>QCSP_001_GP-IV_v.01</t>
         </is>
       </c>
       <c r="AB96" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_GP-II_v.01 (was GP_THC26 : CBD1, 25.40 – 26.60 %); now GP_THC24 : CBD1 22.00 – 25.99 %</t>
+          <t>for review — replaces the issued QCSP_001_GP-IV_v.01 (was GP_THC20 : CBD1, 18.00 – 22.00 %); now GP_THC16 : CBD1 14.40 – 17.59 %</t>
         </is>
       </c>
       <c r="AC96" s="11" t="inlineStr"/>
@@ -42258,15 +42522,15 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>197-12-M-26</t>
+          <t>197-13-M-26</t>
         </is>
       </c>
       <c r="H97" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050322|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("HPA1024|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I97" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050322|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("HPA1024|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -42281,22 +42545,22 @@
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>GP082501/2</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>P050322</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>197-12-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-13-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P97" s="6" t="inlineStr">
@@ -42311,54 +42575,54 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>CoQ reissue (assigned on issue)</t>
+          <t>CoQ-PP-2026-0030</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>P050322|R</t>
+          <t>HPA1024|R</t>
         </is>
       </c>
       <c r="T97" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-12-M-26 of 10.08.2026; cites iCoA-PP_26-111 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-13-M-26 of 10.08.2026; cites iCoA-PP_26-112 of 27.07.2026</t>
         </is>
       </c>
       <c r="U97" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050322|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("HPA1024|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V97" s="9" t="n">
-        <v>15.7</v>
+        <v>17.31</v>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>197-12-К/26</t>
+          <t>197-13-К/26</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>16.00 ± 1.60 (IV)</t>
+          <t>18.00 ± 1.80 (II)</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>14.40 – 17.59 %</t>
+          <t>16.20 – 19.79 %</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>GP_THC16 : CBD1</t>
+          <t>HPA_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_GP-IV_v.01</t>
+          <t>QCSP_001_HPA-II_v.01</t>
         </is>
       </c>
       <c r="AB97" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_GP-IV_v.01 (was GP_THC20 : CBD1, 18.00 – 22.00 %); now GP_THC16 : CBD1 14.40 – 17.59 %</t>
+          <t>for review — replaces the issued QCSP_001_HPA-II_v.01 (was HPA_THC20 : CBD1, 19.01 – 20.99 %); now HPA_THC18 : CBD1 16.20 – 19.79 %</t>
         </is>
       </c>
       <c r="AC97" s="11" t="inlineStr"/>
@@ -42390,15 +42654,15 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>197-13-M-26</t>
+          <t>197-14-M-26</t>
         </is>
       </c>
       <c r="H98" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("HPA1024|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050052|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I98" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("HPA1024|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050052|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -42413,12 +42677,12 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>HPA1024_01</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P050052</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -42428,7 +42692,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>197-13-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-14-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P98" s="6" t="inlineStr">
@@ -42443,54 +42707,54 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0030</t>
+          <t>CoQ-PP-2026-0034</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>HPA1024|R</t>
+          <t>P050052|R</t>
         </is>
       </c>
       <c r="T98" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-13-M-26 of 10.08.2026; cites iCoA-PP_26-112 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-14-M-26 of 10.08.2026; cites iCoA-PP_26-113 of 27.07.2026</t>
         </is>
       </c>
       <c r="U98" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("HPA1024|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050052|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V98" s="9" t="n">
-        <v>17.31</v>
+        <v>21.61</v>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>197-13-К/26</t>
+          <t>197-14-К/26</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>18.00 ± 1.80 (II)</t>
+          <t>22.00 ± 2.20 (I)</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %</t>
+          <t>19.80 – 24.19 %</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>HPA_THC18 : CBD1</t>
+          <t>HPA_THC22 : CBD1</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_HPA-II_v.01</t>
+          <t>QCSP_001_HPA-I_v.01</t>
         </is>
       </c>
       <c r="AB98" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_HPA-II_v.01 (was HPA_THC20 : CBD1, 19.01 – 20.99 %); now HPA_THC18 : CBD1 16.20 – 19.79 %</t>
+          <t>for review — replaces the issued QCSP_001_HPA-I_v.01 (was HPA_THC22 : CBD1, 21.00 – 23.00 %); now HPA_THC22 : CBD1 19.80 – 24.19 %</t>
         </is>
       </c>
       <c r="AC98" s="11" t="inlineStr"/>
@@ -42522,15 +42786,15 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>197-14-M-26</t>
+          <t>197-16-M-26</t>
         </is>
       </c>
       <c r="H99" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050052|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060152|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I99" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050052|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060152|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -42545,22 +42809,22 @@
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>HPA1024_01</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>P050052</t>
+          <t>P060152</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>197-14-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-16-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P99" s="6" t="inlineStr">
@@ -42575,54 +42839,54 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0034</t>
+          <t>CoQ reissue (assigned on issue)</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>P050052|R</t>
+          <t>P060152|R</t>
         </is>
       </c>
       <c r="T99" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-14-M-26 of 10.08.2026; cites iCoA-PP_26-113 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-16-M-26 of 10.08.2026; cites iCoA-PP_26-114 of 27.07.2026</t>
         </is>
       </c>
       <c r="U99" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050052|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060152|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V99" s="9" t="n">
-        <v>21.61</v>
+        <v>17.32</v>
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>197-14-К/26</t>
+          <t>197-16-К/26</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>22.00 ± 2.20 (I)</t>
+          <t>18.00 ± 1.80 (III)</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>19.80 – 24.19 %</t>
+          <t>16.20 – 19.79 %</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>HPA_THC22 : CBD1</t>
+          <t>J31_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_HPA-I_v.01</t>
-        </is>
-      </c>
-      <c r="AB99" s="10" t="inlineStr">
-        <is>
-          <t>for review — replaces the issued QCSP_001_HPA-I_v.01 (was HPA_THC22 : CBD1, 21.00 – 23.00 %); now HPA_THC22 : CBD1 19.80 – 24.19 %</t>
+          <t>QCSP_001_J31-III_v.01</t>
+        </is>
+      </c>
+      <c r="AB99" s="11" t="inlineStr">
+        <is>
+          <t>for review — new</t>
         </is>
       </c>
       <c r="AC99" s="11" t="inlineStr"/>
@@ -42654,15 +42918,15 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>197-16-M-26</t>
+          <t>197-15-M-26</t>
         </is>
       </c>
       <c r="H100" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060152|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060212|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I100" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060152|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060212|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -42677,22 +42941,22 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>P060152</t>
+          <t>P060212</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>197-16-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-15-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P100" s="6" t="inlineStr">
@@ -42712,49 +42976,49 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>P060152|R</t>
+          <t>P060212|R</t>
         </is>
       </c>
       <c r="T100" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-16-M-26 of 10.08.2026; cites iCoA-PP_26-114 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-15-M-26 of 10.08.2026; cites iCoA-PP_26-115 of 27.07.2026</t>
         </is>
       </c>
       <c r="U100" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060152|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060212|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V100" s="9" t="n">
-        <v>17.32</v>
+        <v>20.32</v>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>197-16-К/26</t>
+          <t>197-15-К/26</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>18.00 ± 1.80 (III)</t>
+          <t>22.00 ± 2.20 (I)</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %</t>
+          <t>19.80 – 24.19 %</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>J31_THC18 : CBD1</t>
+          <t>JD_THC22 : CBD1</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_J31-III_v.01</t>
-        </is>
-      </c>
-      <c r="AB100" s="11" t="inlineStr">
-        <is>
-          <t>for review — new</t>
+          <t>QCSP_001_JD-I_v.01</t>
+        </is>
+      </c>
+      <c r="AB100" s="10" t="inlineStr">
+        <is>
+          <t>for review — replaces the issued QCSP_001_JD-I_v.01 (was JD_THC20 : CBD1, 18.00 – 22.00 %); now JD_THC22 : CBD1 19.80 – 24.19 %</t>
         </is>
       </c>
       <c r="AC100" s="11" t="inlineStr"/>
@@ -42786,15 +43050,15 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>197-15-M-26</t>
+          <t>197-17-M-26</t>
         </is>
       </c>
       <c r="H101" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060212|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("OPM1024|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I101" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060212|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("OPM1024|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -42809,22 +43073,22 @@
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>JD112501</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>197-15-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-17-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P101" s="6" t="inlineStr">
@@ -42839,54 +43103,54 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>CoQ reissue (assigned on issue)</t>
+          <t>CoQ-PP-2026-0031</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>P060212|R</t>
+          <t>OPM1024|R</t>
         </is>
       </c>
       <c r="T101" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 23.07.2026; issued 17.08.2026, 7 days after 197-15-M-26 of 10.08.2026; cites iCoA-PP_26-115 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-17-M-26 of 10.08.2026; cites iCoA-PP_26-116 of 27.07.2026</t>
         </is>
       </c>
       <c r="U101" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060212|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("OPM1024|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V101" s="9" t="n">
-        <v>20.32</v>
+        <v>20.03</v>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>197-15-К/26</t>
+          <t>197-17-К/26</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>22.00 ± 2.20 (I)</t>
+          <t>20.00 ± 1.40 (I)</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>19.80 – 24.19 %</t>
+          <t>18.60 – 21.39 %</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
         <is>
-          <t>JD_THC22 : CBD1</t>
+          <t>OPM_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_JD-I_v.01</t>
+          <t>QCSP_001_OPM-I_v.01</t>
         </is>
       </c>
       <c r="AB101" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_JD-I_v.01 (was JD_THC20 : CBD1, 18.00 – 22.00 %); now JD_THC22 : CBD1 19.80 – 24.19 %</t>
+          <t>for review — replaces the issued QCSP_001_OPM-I_v.01 (was OPM_THC22 : CBD1, 19.81 – 24.19 %); now OPM_THC20 : CBD1 18.60 – 21.39 %</t>
         </is>
       </c>
       <c r="AC101" s="11" t="inlineStr"/>
@@ -42918,15 +43182,15 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>197-17-M-26</t>
+          <t>197-18-M-26</t>
         </is>
       </c>
       <c r="H102" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("OPM1024|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050062|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I102" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("OPM1024|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050062|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -42941,12 +43205,12 @@
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>OPM1024_02</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P050062</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -42956,7 +43220,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>197-17-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-18-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P102" s="6" t="inlineStr">
@@ -42971,54 +43235,54 @@
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0031</t>
+          <t>CoQ-PP-2026-0035</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>OPM1024|R</t>
+          <t>P050062|R</t>
         </is>
       </c>
       <c r="T102" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-17-M-26 of 10.08.2026; cites iCoA-PP_26-116 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-18-M-26 of 10.08.2026; cites iCoA-PP_26-117 of 27.07.2026</t>
         </is>
       </c>
       <c r="U102" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("OPM1024|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050062|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V102" s="9" t="n">
-        <v>20.03</v>
+        <v>18.04</v>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>197-17-К/26</t>
+          <t>197-18-К/26</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>20.00 ± 1.40 (I)</t>
+          <t>17.00 ± 1.60 (II)</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>18.60 – 21.39 %</t>
+          <t>15.40 – 18.59 %</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>OPM_THC20 : CBD1</t>
+          <t>OPM_THC17 : CBD1</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-I_v.01</t>
+          <t>QCSP_001_OPM-II_v.01</t>
         </is>
       </c>
       <c r="AB102" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_OPM-I_v.01 (was OPM_THC22 : CBD1, 19.81 – 24.19 %); now OPM_THC20 : CBD1 18.60 – 21.39 %</t>
+          <t>for review — replaces the issued QCSP_001_OPM-II_v.01 (was OPM_THC18 : CBD1, 16.20 – 19.80 %); now OPM_THC17 : CBD1 15.40 – 18.59 %</t>
         </is>
       </c>
       <c r="AC102" s="11" t="inlineStr"/>
@@ -43050,15 +43314,15 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>197-18-M-26</t>
+          <t>197-19-M-26</t>
         </is>
       </c>
       <c r="H103" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050062|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060242|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I103" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050062|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060242|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -43073,12 +43337,12 @@
       </c>
       <c r="L103" s="3" t="inlineStr">
         <is>
-          <t>OPM1024_02</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>P050062</t>
+          <t>P060242</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -43088,7 +43352,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>197-18-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-19-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P103" s="6" t="inlineStr">
@@ -43103,54 +43367,54 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0035</t>
+          <t>CoQ reissue (assigned on issue)</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>P050062|R</t>
+          <t>P060242|R</t>
         </is>
       </c>
       <c r="T103" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-18-M-26 of 10.08.2026; cites iCoA-PP_26-117 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-19-M-26 of 10.08.2026; cites iCoA-PP_26-118 of 27.07.2026</t>
         </is>
       </c>
       <c r="U103" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050062|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060242|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V103" s="9" t="n">
-        <v>18.04</v>
+        <v>7.91</v>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>197-18-К/26</t>
+          <t>197-19-К/26</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>17.00 ± 1.60 (II)</t>
+          <t>8.00 ± 0.80 (V)</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>15.40 – 18.59 %</t>
+          <t>7.20 – 8.79 %</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
         <is>
-          <t>OPM_THC17 : CBD1</t>
+          <t>OPM_THC8 : CBD1</t>
         </is>
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-II_v.01</t>
+          <t>QCSP_001_OPM-V_v.01</t>
         </is>
       </c>
       <c r="AB103" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_OPM-II_v.01 (was OPM_THC18 : CBD1, 16.20 – 19.80 %); now OPM_THC17 : CBD1 15.40 – 18.59 %</t>
+          <t>for review — replaces the issued QCSP_001_OPM-V_v.01 (was OPM_THC8 : CBD1, 7.20 – 8.80 %); now OPM_THC8 : CBD1 7.20 – 8.79 %</t>
         </is>
       </c>
       <c r="AC103" s="11" t="inlineStr"/>
@@ -43182,15 +43446,15 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>197-19-M-26</t>
+          <t>197-20-M-26</t>
         </is>
       </c>
       <c r="H104" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060242|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060062|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I104" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060242|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060062|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -43205,22 +43469,22 @@
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>OPM122501</t>
+          <t>PM092501</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P060062</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Permanent Market</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>197-19-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-20-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P104" s="6" t="inlineStr">
@@ -43240,49 +43504,49 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>P060242|R</t>
+          <t>P060062|R</t>
         </is>
       </c>
       <c r="T104" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-19-M-26 of 10.08.2026; cites iCoA-PP_26-118 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-20-M-26 of 10.08.2026; cites iCoA-PP_26-120 of 27.07.2026</t>
         </is>
       </c>
       <c r="U104" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060242|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060062|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V104" s="9" t="n">
-        <v>7.91</v>
+        <v>12.25</v>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>197-19-К/26</t>
+          <t>197-20-К/26</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>8.00 ± 0.80 (V)</t>
+          <t>12.00 ± 1.00 (II)</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>7.20 – 8.79 %</t>
+          <t>11.00 – 12.99 %</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
         <is>
-          <t>OPM_THC8 : CBD1</t>
+          <t>PM_THC12 : CBD1</t>
         </is>
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_OPM-V_v.01</t>
+          <t>QCSP_001_PM-II_v.01</t>
         </is>
       </c>
       <c r="AB104" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_OPM-V_v.01 (was OPM_THC8 : CBD1, 7.20 – 8.80 %); now OPM_THC8 : CBD1 7.20 – 8.79 %</t>
+          <t>for review — replaces the issued QCSP_001_PM-II_v.01 (was PM_THC10 : CBD1, 9.00 – 11.00 %); now PM_THC12 : CBD1 11.00 – 12.99 %</t>
         </is>
       </c>
       <c r="AC104" s="11" t="inlineStr"/>
@@ -43314,20 +43578,20 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>197-20-M-26</t>
+          <t>197-21-M-26</t>
         </is>
       </c>
       <c r="H105" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060062|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060382|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I105" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060062|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060382|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -43337,22 +43601,22 @@
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>PM092501</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>P060062</t>
+          <t>P060382</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>197-20-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-21-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P105" s="6" t="inlineStr">
@@ -43372,49 +43636,49 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>P060062|R</t>
+          <t>P060382|R</t>
         </is>
       </c>
       <c r="T105" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-20-M-26 of 10.08.2026; cites iCoA-PP_26-120 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-21-M-26 of 10.08.2026; cites iCoA-PP_26-119 of 27.07.2026</t>
         </is>
       </c>
       <c r="U105" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060062|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060382|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V105" s="9" t="n">
-        <v>12.25</v>
+        <v>17.84</v>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>197-20-К/26</t>
+          <t>197-21-К/26</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>12.00 ± 1.00 (II)</t>
+          <t>18.00 ± 1.80 (II)</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>11.00 – 12.99 %</t>
+          <t>16.20 – 19.79 %</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
         <is>
-          <t>PM_THC12 : CBD1</t>
+          <t>SCR_THC18 : CBD1</t>
         </is>
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_PM-II_v.01</t>
+          <t>QCSP_001_SCR-II_v.01</t>
         </is>
       </c>
       <c r="AB105" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_PM-II_v.01 (was PM_THC10 : CBD1, 9.00 – 11.00 %); now PM_THC12 : CBD1 11.00 – 12.99 %</t>
+          <t>for review — replaces the issued QCSP_001_SCR-II_v.01 (was SCR_THC18 : CBD1, 16.20 – 19.80 %); now SCR_THC18 : CBD1 16.20 – 19.79 %</t>
         </is>
       </c>
       <c r="AC105" s="11" t="inlineStr"/>
@@ -43442,24 +43706,24 @@
         <v/>
       </c>
       <c r="F106" s="5" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>197-21-M-26</t>
+          <t>534-1065-26</t>
         </is>
       </c>
       <c r="H106" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060382|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050212|R2",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I106" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060382|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050212|R2",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -43469,22 +43733,22 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>CJ062501/2</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>P060382</t>
+          <t>P050212</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>197-21-K-26, (07.08.2026) [FHM-K]</t>
+          <t>197-4-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P106" s="6" t="inlineStr">
@@ -43504,49 +43768,49 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>P060382|R</t>
+          <t>P050212|R2</t>
         </is>
       </c>
       <c r="T106" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 24.07.2026; issued 17.08.2026, 7 days after 197-21-M-26 of 10.08.2026; cites iCoA-PP_26-119 of 27.07.2026</t>
+          <t>registered — retest, Tranche 1 (sampled 21–24.07.2026), sampled 21.07.2026; issued 07.09.2026, 7 days after 534-1065-26 of 31.08.2026; cites the campaign iCoA of 27.07.2026</t>
         </is>
       </c>
       <c r="U106" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060382|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050212|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
         <v/>
       </c>
       <c r="V106" s="9" t="n">
-        <v>17.84</v>
+        <v>18.91</v>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>197-21-К/26</t>
+          <t>197-4-К/26</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>18.00 ± 1.80 (II)</t>
+          <t>20.00 ± 1.60 (III)</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>16.20 – 19.79 %</t>
+          <t>18.40 – 21.59 %</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
         <is>
-          <t>SCR_THC18 : CBD1</t>
+          <t>CJ_THC20 : CBD1</t>
         </is>
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_SCR-II_v.01</t>
+          <t>QCSP_001_CJ-III_v.01</t>
         </is>
       </c>
       <c r="AB106" s="10" t="inlineStr">
         <is>
-          <t>for review — replaces the issued QCSP_001_SCR-II_v.01 (was SCR_THC18 : CBD1, 16.20 – 19.80 %); now SCR_THC18 : CBD1 16.20 – 19.79 %</t>
+          <t>for review — replaces the issued QCSP_001_CJ-III_v.01 (was CJ_THC24 : CBD1, 23.00 – 25.00 %); now CJ_THC20 : CBD1 18.40 – 21.59 %</t>
         </is>
       </c>
       <c r="AC106" s="11" t="inlineStr"/>
@@ -44110,11 +44374,11 @@
         </is>
       </c>
       <c r="H111" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050222|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P050222|R2",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I111" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050222|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P050222|R2",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -44164,12 +44428,12 @@
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>P050222|R</t>
+          <t>P050222|R2</t>
         </is>
       </c>
       <c r="T111" s="7" t="inlineStr">
         <is>
-          <t>registered — retest, Tranche 2 (sampled 12–14.08.2026), sampled 12.08.2026; issued 18.09.2026, 7 days after 220-3-M-26 of 11.09.2026; cites iCoA-PP_26-126 of 17.08.2026</t>
+          <t>registered — retest, Tranche 2 (sampled 12–14.08.2026), sampled 12.08.2026; issued 18.09.2026, 7 days after 220-3-M-26 of 11.09.2026; cites the campaign iCoA of 17.08.2026</t>
         </is>
       </c>
       <c r="U111" s="2">
@@ -55791,7 +56055,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v42 on 17.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v43 on 17.09.2026</t>
         </is>
       </c>
     </row>
@@ -55812,7 +56076,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v42.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v43.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -56055,7 +56055,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v43 on 17.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v44 on 17.09.2026</t>
         </is>
       </c>
     </row>
@@ -56076,7 +56076,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v43.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v44.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="D2" s="5">
-        <f>IF(A2="","",IF(ISNUMBER(E2),MAX(DATE(2026,6,3),E2),DATE(2026,6,3)))</f>
+        <f>IF(A2="","",IF(ISNUMBER(E2),MAX(DATE(2026,5,15),E2),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E2" s="5">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <f>IF(A3="","",IF(ISNUMBER(E3),MAX(DATE(2026,6,3),E3),DATE(2026,6,3)))</f>
+        <f>IF(A3="","",IF(ISNUMBER(E3),MAX(DATE(2026,5,15),E3),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E3" s="5">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D4" s="5">
-        <f>IF(A4="","",IF(ISNUMBER(E4),MAX(DATE(2026,6,3),E4),DATE(2026,6,3)))</f>
+        <f>IF(A4="","",IF(ISNUMBER(E4),MAX(DATE(2026,5,15),E4),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E4" s="5">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="D5" s="5">
-        <f>IF(A5="","",IF(ISNUMBER(E5),MAX(DATE(2026,6,3),E5),DATE(2026,6,3)))</f>
+        <f>IF(A5="","",IF(ISNUMBER(E5),MAX(DATE(2026,5,15),E5),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="D6" s="5">
-        <f>IF(A6="","",IF(ISNUMBER(E6),MAX(DATE(2026,6,3),E6),DATE(2026,6,3)))</f>
+        <f>IF(A6="","",IF(ISNUMBER(E6),MAX(DATE(2026,5,15),E6),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="D7" s="5">
-        <f>IF(A7="","",IF(ISNUMBER(E7),MAX(DATE(2026,6,3),E7),DATE(2026,6,3)))</f>
+        <f>IF(A7="","",IF(ISNUMBER(E7),MAX(DATE(2026,5,15),E7),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <f>IF(A9="","",IF(ISNUMBER(E9),MAX(DATE(2026,6,3),E9),DATE(2026,6,3)))</f>
+        <f>IF(A9="","",IF(ISNUMBER(E9),MAX(DATE(2026,5,15),E9),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <f>IF(A10="","",IF(ISNUMBER(E10),MAX(DATE(2026,6,3),E10),DATE(2026,6,3)))</f>
+        <f>IF(A10="","",IF(ISNUMBER(E10),MAX(DATE(2026,5,15),E10),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <f>IF(A11="","",IF(ISNUMBER(E11),MAX(DATE(2026,6,3),E11),DATE(2026,6,3)))</f>
+        <f>IF(A11="","",IF(ISNUMBER(E11),MAX(DATE(2026,5,15),E11),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="D12" s="5">
-        <f>IF(A12="","",IF(ISNUMBER(E12),MAX(DATE(2026,6,3),E12),DATE(2026,6,3)))</f>
+        <f>IF(A12="","",IF(ISNUMBER(E12),MAX(DATE(2026,5,15),E12),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <f>IF(A13="","",IF(ISNUMBER(E13),MAX(DATE(2026,6,3),E13),DATE(2026,6,3)))</f>
+        <f>IF(A13="","",IF(ISNUMBER(E13),MAX(DATE(2026,5,15),E13),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>IF(A14="","",IF(ISNUMBER(E14),MAX(DATE(2026,6,3),E14),DATE(2026,6,3)))</f>
+        <f>IF(A14="","",IF(ISNUMBER(E14),MAX(DATE(2026,5,15),E14),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <f>IF(A15="","",IF(ISNUMBER(E15),MAX(DATE(2026,6,3),E15),DATE(2026,6,3)))</f>
+        <f>IF(A15="","",IF(ISNUMBER(E15),MAX(DATE(2026,5,15),E15),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <f>IF(A16="","",IF(ISNUMBER(E16),MAX(DATE(2026,6,3),E16),DATE(2026,6,3)))</f>
+        <f>IF(A16="","",IF(ISNUMBER(E16),MAX(DATE(2026,5,15),E16),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <f>IF(A17="","",IF(ISNUMBER(E17),MAX(DATE(2026,6,3),E17),DATE(2026,6,3)))</f>
+        <f>IF(A17="","",IF(ISNUMBER(E17),MAX(DATE(2026,5,15),E17),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <f>IF(A18="","",IF(ISNUMBER(E18),MAX(DATE(2026,6,3),E18),DATE(2026,6,3)))</f>
+        <f>IF(A18="","",IF(ISNUMBER(E18),MAX(DATE(2026,5,15),E18),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="D19" s="5">
-        <f>IF(A19="","",IF(ISNUMBER(E19),MAX(DATE(2026,6,3),E19),DATE(2026,6,3)))</f>
+        <f>IF(A19="","",IF(ISNUMBER(E19),MAX(DATE(2026,5,15),E19),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D20" s="5">
-        <f>IF(A20="","",IF(ISNUMBER(E20),MAX(DATE(2026,6,3),E20),DATE(2026,6,3)))</f>
+        <f>IF(A20="","",IF(ISNUMBER(E20),MAX(DATE(2026,5,15),E20),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E20" s="5">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="D21" s="5">
-        <f>IF(A21="","",IF(ISNUMBER(E21),MAX(DATE(2026,6,3),E21),DATE(2026,6,3)))</f>
+        <f>IF(A21="","",IF(ISNUMBER(E21),MAX(DATE(2026,5,15),E21),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E21" s="5">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <f>IF(A22="","",IF(ISNUMBER(E22),MAX(DATE(2026,6,3),E22),DATE(2026,6,3)))</f>
+        <f>IF(A22="","",IF(ISNUMBER(E22),MAX(DATE(2026,5,15),E22),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E22" s="5">
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="D23" s="5">
-        <f>IF(A23="","",IF(ISNUMBER(E23),MAX(DATE(2026,6,3),E23),DATE(2026,6,3)))</f>
+        <f>IF(A23="","",IF(ISNUMBER(E23),MAX(DATE(2026,5,15),E23),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E23" s="5">
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <f>IF(A24="","",IF(ISNUMBER(E24),MAX(DATE(2026,6,3),E24),DATE(2026,6,3)))</f>
+        <f>IF(A24="","",IF(ISNUMBER(E24),MAX(DATE(2026,5,15),E24),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E24" s="5">
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>IF(A25="","",IF(ISNUMBER(E25),MAX(DATE(2026,6,3),E25),DATE(2026,6,3)))</f>
+        <f>IF(A25="","",IF(ISNUMBER(E25),MAX(DATE(2026,5,15),E25),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E25" s="5">
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="D26" s="5">
-        <f>IF(A26="","",IF(ISNUMBER(E26),MAX(DATE(2026,6,3),E26),DATE(2026,6,3)))</f>
+        <f>IF(A26="","",IF(ISNUMBER(E26),MAX(DATE(2026,5,15),E26),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E26" s="5">
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <f>IF(A27="","",IF(ISNUMBER(E27),MAX(DATE(2026,6,3),E27),DATE(2026,6,3)))</f>
+        <f>IF(A27="","",IF(ISNUMBER(E27),MAX(DATE(2026,5,15),E27),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E27" s="5">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <f>IF(A28="","",IF(ISNUMBER(E28),MAX(DATE(2026,6,3),E28),DATE(2026,6,3)))</f>
+        <f>IF(A28="","",IF(ISNUMBER(E28),MAX(DATE(2026,5,15),E28),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E28" s="5">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>IF(A29="","",IF(ISNUMBER(E29),MAX(DATE(2026,6,3),E29),DATE(2026,6,3)))</f>
+        <f>IF(A29="","",IF(ISNUMBER(E29),MAX(DATE(2026,5,15),E29),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E29" s="5">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>IF(A30="","",IF(ISNUMBER(E30),MAX(DATE(2026,6,3),E30),DATE(2026,6,3)))</f>
+        <f>IF(A30="","",IF(ISNUMBER(E30),MAX(DATE(2026,5,15),E30),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E30" s="5">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="D31" s="5">
-        <f>IF(A31="","",IF(ISNUMBER(E31),MAX(DATE(2026,6,3),E31),DATE(2026,6,3)))</f>
+        <f>IF(A31="","",IF(ISNUMBER(E31),MAX(DATE(2026,5,15),E31),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E31" s="5">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="D32" s="5">
-        <f>IF(A32="","",IF(ISNUMBER(E32),MAX(DATE(2026,6,3),E32),DATE(2026,6,3)))</f>
+        <f>IF(A32="","",IF(ISNUMBER(E32),MAX(DATE(2026,5,15),E32),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E32" s="5">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Clemosa A Bud</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>IF(A33="","",IF(ISNUMBER(E33),MAX(DATE(2026,6,3),E33),DATE(2026,6,3)))</f>
+        <f>IF(A33="","",IF(ISNUMBER(E33),MAX(DATE(2026,5,15),E33),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E33" s="5">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <f>IF(A34="","",IF(ISNUMBER(E34),MAX(DATE(2026,6,3),E34),DATE(2026,6,3)))</f>
+        <f>IF(A34="","",IF(ISNUMBER(E34),MAX(DATE(2026,5,15),E34),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E34" s="5">
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="D35" s="5">
-        <f>IF(A35="","",IF(ISNUMBER(E35),MAX(DATE(2026,6,3),E35),DATE(2026,6,3)))</f>
+        <f>IF(A35="","",IF(ISNUMBER(E35),MAX(DATE(2026,5,15),E35),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E35" s="5">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="D36" s="5">
-        <f>IF(A36="","",IF(ISNUMBER(E36),MAX(DATE(2026,6,3),E36),DATE(2026,6,3)))</f>
+        <f>IF(A36="","",IF(ISNUMBER(E36),MAX(DATE(2026,5,15),E36),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E36" s="5">
@@ -5524,7 +5524,7 @@
         </is>
       </c>
       <c r="D37" s="5">
-        <f>IF(A37="","",IF(ISNUMBER(E37),MAX(DATE(2026,6,3),E37),DATE(2026,6,3)))</f>
+        <f>IF(A37="","",IF(ISNUMBER(E37),MAX(DATE(2026,5,15),E37),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E37" s="5">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <f>IF(A38="","",IF(ISNUMBER(E38),MAX(DATE(2026,6,3),E38),DATE(2026,6,3)))</f>
+        <f>IF(A38="","",IF(ISNUMBER(E38),MAX(DATE(2026,5,15),E38),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E38" s="5">
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="D39" s="5">
-        <f>IF(A39="","",IF(ISNUMBER(E39),MAX(DATE(2026,6,3),E39),DATE(2026,6,3)))</f>
+        <f>IF(A39="","",IF(ISNUMBER(E39),MAX(DATE(2026,5,15),E39),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E39" s="5">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="D40" s="5">
-        <f>IF(A40="","",IF(ISNUMBER(E40),MAX(DATE(2026,6,3),E40),DATE(2026,6,3)))</f>
+        <f>IF(A40="","",IF(ISNUMBER(E40),MAX(DATE(2026,5,15),E40),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E40" s="5">
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <f>IF(A41="","",IF(ISNUMBER(E41),MAX(DATE(2026,6,3),E41),DATE(2026,6,3)))</f>
+        <f>IF(A41="","",IF(ISNUMBER(E41),MAX(DATE(2026,5,15),E41),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E41" s="5">
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="D42" s="5">
-        <f>IF(A42="","",IF(ISNUMBER(E42),MAX(DATE(2026,6,3),E42),DATE(2026,6,3)))</f>
+        <f>IF(A42="","",IF(ISNUMBER(E42),MAX(DATE(2026,5,15),E42),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E42" s="5">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="D43" s="5">
-        <f>IF(A43="","",IF(ISNUMBER(E43),MAX(DATE(2026,6,3),E43),DATE(2026,6,3)))</f>
+        <f>IF(A43="","",IF(ISNUMBER(E43),MAX(DATE(2026,5,15),E43),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E43" s="5">
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <f>IF(A44="","",IF(ISNUMBER(E44),MAX(DATE(2026,6,3),E44),DATE(2026,6,3)))</f>
+        <f>IF(A44="","",IF(ISNUMBER(E44),MAX(DATE(2026,5,15),E44),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E44" s="5">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="D45" s="5">
-        <f>IF(A45="","",IF(ISNUMBER(E45),MAX(DATE(2026,6,3),E45),DATE(2026,6,3)))</f>
+        <f>IF(A45="","",IF(ISNUMBER(E45),MAX(DATE(2026,5,15),E45),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E45" s="5">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="D46" s="5">
-        <f>IF(A46="","",IF(ISNUMBER(E46),MAX(DATE(2026,6,3),E46),DATE(2026,6,3)))</f>
+        <f>IF(A46="","",IF(ISNUMBER(E46),MAX(DATE(2026,5,15),E46),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E46" s="5">
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="D47" s="5">
-        <f>IF(A47="","",IF(ISNUMBER(E47),MAX(DATE(2026,6,3),E47),DATE(2026,6,3)))</f>
+        <f>IF(A47="","",IF(ISNUMBER(E47),MAX(DATE(2026,5,15),E47),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E47" s="5">
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="D48" s="5">
-        <f>IF(A48="","",IF(ISNUMBER(E48),MAX(DATE(2026,6,3),E48),DATE(2026,6,3)))</f>
+        <f>IF(A48="","",IF(ISNUMBER(E48),MAX(DATE(2026,5,15),E48),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E48" s="5">
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <f>IF(A49="","",IF(ISNUMBER(E49),MAX(DATE(2026,6,3),E49),DATE(2026,6,3)))</f>
+        <f>IF(A49="","",IF(ISNUMBER(E49),MAX(DATE(2026,5,15),E49),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E49" s="5">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="D50" s="5">
-        <f>IF(A50="","",IF(ISNUMBER(E50),MAX(DATE(2026,6,3),E50),DATE(2026,6,3)))</f>
+        <f>IF(A50="","",IF(ISNUMBER(E50),MAX(DATE(2026,5,15),E50),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E50" s="5">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="D54" s="5">
-        <f>IF(A54="","",IF(ISNUMBER(E54),MAX(DATE(2026,6,3),E54),DATE(2026,6,3)))</f>
+        <f>IF(A54="","",IF(ISNUMBER(E54),MAX(DATE(2026,5,15),E54),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E54" s="5">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="D56" s="5">
-        <f>IF(A56="","",IF(ISNUMBER(E56),MAX(DATE(2026,6,3),E56),DATE(2026,6,3)))</f>
+        <f>IF(A56="","",IF(ISNUMBER(E56),MAX(DATE(2026,5,15),E56),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E56" s="5">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
         </is>
       </c>
       <c r="D57" s="5">
-        <f>IF(A57="","",IF(ISNUMBER(E57),MAX(DATE(2026,6,3),E57),DATE(2026,6,3)))</f>
+        <f>IF(A57="","",IF(ISNUMBER(E57),MAX(DATE(2026,5,15),E57),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E57" s="5">
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="D58" s="5">
-        <f>IF(A58="","",IF(ISNUMBER(E58),MAX(DATE(2026,6,3),E58),DATE(2026,6,3)))</f>
+        <f>IF(A58="","",IF(ISNUMBER(E58),MAX(DATE(2026,5,15),E58),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E58" s="5">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="D59" s="5">
-        <f>IF(A59="","",IF(ISNUMBER(E59),MAX(DATE(2026,6,3),E59),DATE(2026,6,3)))</f>
+        <f>IF(A59="","",IF(ISNUMBER(E59),MAX(DATE(2026,5,15),E59),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E59" s="5">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <f>IF(A60="","",IF(ISNUMBER(E60),MAX(DATE(2026,6,3),E60),DATE(2026,6,3)))</f>
+        <f>IF(A60="","",IF(ISNUMBER(E60),MAX(DATE(2026,5,15),E60),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E60" s="5">
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="D61" s="5">
-        <f>IF(A61="","",IF(ISNUMBER(E61),MAX(DATE(2026,6,3),E61),DATE(2026,6,3)))</f>
+        <f>IF(A61="","",IF(ISNUMBER(E61),MAX(DATE(2026,5,15),E61),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E61" s="5">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <f>IF(A62="","",IF(ISNUMBER(E62),MAX(DATE(2026,6,3),E62),DATE(2026,6,3)))</f>
+        <f>IF(A62="","",IF(ISNUMBER(E62),MAX(DATE(2026,5,15),E62),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E62" s="5">
@@ -9026,7 +9026,7 @@
         </is>
       </c>
       <c r="D63" s="5">
-        <f>IF(A63="","",IF(ISNUMBER(E63),MAX(DATE(2026,6,3),E63),DATE(2026,6,3)))</f>
+        <f>IF(A63="","",IF(ISNUMBER(E63),MAX(DATE(2026,5,15),E63),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E63" s="5">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <f>IF(A64="","",IF(ISNUMBER(E64),MAX(DATE(2026,6,3),E64),DATE(2026,6,3)))</f>
+        <f>IF(A64="","",IF(ISNUMBER(E64),MAX(DATE(2026,5,15),E64),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E64" s="5">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="D65" s="5">
-        <f>IF(A65="","",IF(ISNUMBER(E65),MAX(DATE(2026,6,3),E65),DATE(2026,6,3)))</f>
+        <f>IF(A65="","",IF(ISNUMBER(E65),MAX(DATE(2026,5,15),E65),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E65" s="5">
@@ -10362,7 +10362,7 @@
         </is>
       </c>
       <c r="D73" s="5">
-        <f>IF(A73="","",IF(ISNUMBER(E73),MAX(DATE(2026,6,3),E73),DATE(2026,6,3)))</f>
+        <f>IF(A73="","",IF(ISNUMBER(E73),MAX(DATE(2026,5,15),E73),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E73" s="5">
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="D74" s="5">
-        <f>IF(A74="","",IF(ISNUMBER(E74),MAX(DATE(2026,6,3),E74),DATE(2026,6,3)))</f>
+        <f>IF(A74="","",IF(ISNUMBER(E74),MAX(DATE(2026,5,15),E74),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E74" s="5">
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="D75" s="5">
-        <f>IF(A75="","",IF(ISNUMBER(E75),MAX(DATE(2026,6,3),E75),DATE(2026,6,3)))</f>
+        <f>IF(A75="","",IF(ISNUMBER(E75),MAX(DATE(2026,5,15),E75),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E75" s="5">
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="D76" s="5">
-        <f>IF(A76="","",IF(ISNUMBER(E76),MAX(DATE(2026,6,3),E76),DATE(2026,6,3)))</f>
+        <f>IF(A76="","",IF(ISNUMBER(E76),MAX(DATE(2026,5,15),E76),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E76" s="5">
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="D77" s="5">
-        <f>IF(A77="","",IF(ISNUMBER(E77),MAX(DATE(2026,6,3),E77),DATE(2026,6,3)))</f>
+        <f>IF(A77="","",IF(ISNUMBER(E77),MAX(DATE(2026,5,15),E77),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E77" s="5">
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="D78" s="5">
-        <f>IF(A78="","",IF(ISNUMBER(E78),MAX(DATE(2026,6,3),E78),DATE(2026,6,3)))</f>
+        <f>IF(A78="","",IF(ISNUMBER(E78),MAX(DATE(2026,5,15),E78),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E78" s="5">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -11172,7 +11172,7 @@
         </is>
       </c>
       <c r="D79" s="5">
-        <f>IF(A79="","",IF(ISNUMBER(E79),MAX(DATE(2026,6,3),E79),DATE(2026,6,3)))</f>
+        <f>IF(A79="","",IF(ISNUMBER(E79),MAX(DATE(2026,5,15),E79),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E79" s="5">
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="D80" s="5">
-        <f>IF(A80="","",IF(ISNUMBER(E80),MAX(DATE(2026,6,3),E80),DATE(2026,6,3)))</f>
+        <f>IF(A80="","",IF(ISNUMBER(E80),MAX(DATE(2026,5,15),E80),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E80" s="5">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="D81" s="5">
-        <f>IF(A81="","",IF(ISNUMBER(E81),MAX(DATE(2026,6,3),E81),DATE(2026,6,3)))</f>
+        <f>IF(A81="","",IF(ISNUMBER(E81),MAX(DATE(2026,5,15),E81),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E81" s="5">
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="D82" s="5">
-        <f>IF(A82="","",IF(ISNUMBER(E82),MAX(DATE(2026,6,3),E82),DATE(2026,6,3)))</f>
+        <f>IF(A82="","",IF(ISNUMBER(E82),MAX(DATE(2026,5,15),E82),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E82" s="5">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="D83" s="5">
-        <f>IF(A83="","",IF(ISNUMBER(E83),MAX(DATE(2026,6,3),E83),DATE(2026,6,3)))</f>
+        <f>IF(A83="","",IF(ISNUMBER(E83),MAX(DATE(2026,5,15),E83),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E83" s="5">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -11847,7 +11847,7 @@
         </is>
       </c>
       <c r="D84" s="5">
-        <f>IF(A84="","",IF(ISNUMBER(E84),MAX(DATE(2026,6,3),E84),DATE(2026,6,3)))</f>
+        <f>IF(A84="","",IF(ISNUMBER(E84),MAX(DATE(2026,5,15),E84),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E84" s="5">
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="D85" s="5">
-        <f>IF(A85="","",IF(ISNUMBER(E85),MAX(DATE(2026,6,3),E85),DATE(2026,6,3)))</f>
+        <f>IF(A85="","",IF(ISNUMBER(E85),MAX(DATE(2026,5,15),E85),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E85" s="5">
@@ -12117,7 +12117,7 @@
         </is>
       </c>
       <c r="D86" s="5">
-        <f>IF(A86="","",IF(ISNUMBER(E86),MAX(DATE(2026,6,3),E86),DATE(2026,6,3)))</f>
+        <f>IF(A86="","",IF(ISNUMBER(E86),MAX(DATE(2026,5,15),E86),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E86" s="5">
@@ -12252,7 +12252,7 @@
         </is>
       </c>
       <c r="D87" s="5">
-        <f>IF(A87="","",IF(ISNUMBER(E87),MAX(DATE(2026,6,3),E87),DATE(2026,6,3)))</f>
+        <f>IF(A87="","",IF(ISNUMBER(E87),MAX(DATE(2026,5,15),E87),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E87" s="5">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="D88" s="5">
-        <f>IF(A88="","",IF(ISNUMBER(E88),MAX(DATE(2026,6,3),E88),DATE(2026,6,3)))</f>
+        <f>IF(A88="","",IF(ISNUMBER(E88),MAX(DATE(2026,5,15),E88),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E88" s="5">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <f>IF(A89="","",IF(ISNUMBER(E89),MAX(DATE(2026,6,3),E89),DATE(2026,6,3)))</f>
+        <f>IF(A89="","",IF(ISNUMBER(E89),MAX(DATE(2026,5,15),E89),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E89" s="5">
@@ -13197,7 +13197,7 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <f>IF(A94="","",IF(ISNUMBER(E94),MAX(DATE(2026,6,3),E94),DATE(2026,6,3)))</f>
+        <f>IF(A94="","",IF(ISNUMBER(E94),MAX(DATE(2026,5,15),E94),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E94" s="5">
@@ -13332,7 +13332,7 @@
         </is>
       </c>
       <c r="D95" s="5">
-        <f>IF(A95="","",IF(ISNUMBER(E95),MAX(DATE(2026,6,3),E95),DATE(2026,6,3)))</f>
+        <f>IF(A95="","",IF(ISNUMBER(E95),MAX(DATE(2026,5,15),E95),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E95" s="5">
@@ -13467,7 +13467,7 @@
         </is>
       </c>
       <c r="D96" s="5">
-        <f>IF(A96="","",IF(ISNUMBER(E96),MAX(DATE(2026,6,3),E96),DATE(2026,6,3)))</f>
+        <f>IF(A96="","",IF(ISNUMBER(E96),MAX(DATE(2026,5,15),E96),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E96" s="5">
@@ -14007,7 +14007,7 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <f>IF(A100="","",IF(ISNUMBER(E100),MAX(DATE(2026,6,3),E100),DATE(2026,6,3)))</f>
+        <f>IF(A100="","",IF(ISNUMBER(E100),MAX(DATE(2026,5,15),E100),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E100" s="5">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="D122" s="5">
-        <f>IF(A122="","",IF(ISNUMBER(E122),MAX(DATE(2026,6,3),E122),DATE(2026,6,3)))</f>
+        <f>IF(A122="","",IF(ISNUMBER(E122),MAX(DATE(2026,5,15),E122),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E122" s="5">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -17070,7 +17070,7 @@
         </is>
       </c>
       <c r="D123" s="5">
-        <f>IF(A123="","",IF(ISNUMBER(E123),MAX(DATE(2026,6,3),E123),DATE(2026,6,3)))</f>
+        <f>IF(A123="","",IF(ISNUMBER(E123),MAX(DATE(2026,5,15),E123),DATE(2026,5,15)))</f>
         <v/>
       </c>
       <c r="E123" s="5">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Clemosa A Bud</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
@@ -19231,7 +19231,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
@@ -21226,7 +21226,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr">
@@ -21891,7 +21891,7 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L163" s="2" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -23354,7 +23354,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -23753,7 +23753,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
@@ -26812,7 +26812,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
@@ -27344,7 +27344,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
@@ -28807,7 +28807,7 @@
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="L211" s="2" t="inlineStr">
@@ -29206,7 +29206,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
@@ -29339,7 +29339,7 @@
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="L215" s="2" t="inlineStr">
@@ -29563,7 +29563,7 @@
     <row r="218" ht="110" customHeight="1">
       <c r="A218" s="8" t="inlineStr">
         <is>
-          <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 03.06.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 03.06.2026; a RETEST is dated at its own sampling day and issued on its campaign's day (sampling_dates.py, owner 15.09.2026: Tranche 1 sampled 21–24.07.2026 and issued 27.07.2026, Tranche 2 sampled 12–14.08.2026 and issued 17.08.2026, Tranche 3 sampled 19–21.08.2026 and issued 24.08.2026, each batch on the day its certificate number falls), which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. A round whose packaging date the list does not hold is numbered all the same (owner, 15.09.2026: identification A, B and foreign matter are performed on every batch) and says its testing date is not stated. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
+          <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 15.05.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 15.05.2026; a RETEST is dated at its own sampling day and issued on its campaign's day (sampling_dates.py, owner 15.09.2026: Tranche 1 sampled 21–24.07.2026 and issued 27.07.2026, Tranche 2 sampled 12–14.08.2026 and issued 17.08.2026, Tranche 3 sampled 19–21.08.2026 and issued 24.08.2026, each batch on the day its certificate number falls), which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. A round whose packaging date the list does not hold is numbered all the same (owner, 15.09.2026: identification A, B and foreign matter are performed on every batch) and says its testing date is not stated. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
         </is>
       </c>
     </row>
@@ -29784,7 +29784,7 @@
         <v/>
       </c>
       <c r="E2" s="5">
-        <f>IF(ISNUMBER(F2),MAX(DATE(2026,6,6),F2+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F2),MAX(DATE(2026,5,27),F2+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F2" s="5" t="n">
@@ -29855,7 +29855,7 @@
       </c>
       <c r="T2" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -29917,7 +29917,7 @@
         <v/>
       </c>
       <c r="E3" s="5">
-        <f>IF(ISNUMBER(F3),MAX(DATE(2026,6,6),F3+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F3),MAX(DATE(2026,5,27),F3+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F3" s="5" t="n">
@@ -29988,7 +29988,7 @@
       </c>
       <c r="T3" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -30050,7 +30050,7 @@
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>IF(ISNUMBER(F4),MAX(DATE(2026,6,6),F4+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F4),MAX(DATE(2026,5,27),F4+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F4" s="5" t="n">
@@ -30121,7 +30121,7 @@
       </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -30183,7 +30183,7 @@
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>IF(ISNUMBER(F5),MAX(DATE(2026,6,6),F5+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F5),MAX(DATE(2026,5,27),F5+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -30324,7 +30324,7 @@
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>IF(ISNUMBER(F6),MAX(DATE(2026,6,6),F6+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F6),MAX(DATE(2026,5,27),F6+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -30397,7 +30397,7 @@
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -30459,7 +30459,7 @@
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>IF(ISNUMBER(F7),MAX(DATE(2026,6,6),F7+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F7),MAX(DATE(2026,5,27),F7+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -30594,7 +30594,7 @@
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>IF(ISNUMBER(F8),MAX(DATE(2026,6,6),F8+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F8),MAX(DATE(2026,5,27),F8+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F8" s="5" t="n">
@@ -30665,7 +30665,7 @@
       </c>
       <c r="T8" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -30727,7 +30727,7 @@
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>IF(ISNUMBER(F9),MAX(DATE(2026,6,6),F9+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F9),MAX(DATE(2026,5,27),F9+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F9" s="5" t="n">
@@ -30798,7 +30798,7 @@
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -30860,7 +30860,7 @@
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>IF(ISNUMBER(F10),MAX(DATE(2026,6,6),F10+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F10),MAX(DATE(2026,5,27),F10+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F10" s="5" t="n">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -30993,7 +30993,7 @@
         <v/>
       </c>
       <c r="E11" s="5">
-        <f>IF(ISNUMBER(F11),MAX(DATE(2026,6,6),F11+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F11),MAX(DATE(2026,5,27),F11+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F11" s="5" t="n">
@@ -31064,7 +31064,7 @@
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -31126,7 +31126,7 @@
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>IF(ISNUMBER(F12),MAX(DATE(2026,6,6),F12+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F12),MAX(DATE(2026,5,27),F12+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F12" s="5" t="n">
@@ -31197,7 +31197,7 @@
       </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -31259,7 +31259,7 @@
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>IF(ISNUMBER(F13),MAX(DATE(2026,6,6),F13+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F13),MAX(DATE(2026,5,27),F13+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F13" s="5" t="n">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -31392,7 +31392,7 @@
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>IF(ISNUMBER(F14),MAX(DATE(2026,6,6),F14+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F14),MAX(DATE(2026,5,27),F14+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F14" s="5" t="n">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -31525,7 +31525,7 @@
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>IF(ISNUMBER(F15),MAX(DATE(2026,6,6),F15+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F15),MAX(DATE(2026,5,27),F15+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F15" s="5" t="n">
@@ -31596,7 +31596,7 @@
       </c>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -31658,7 +31658,7 @@
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>IF(ISNUMBER(F16),MAX(DATE(2026,6,6),F16+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F16),MAX(DATE(2026,5,27),F16+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F16" s="5" t="n">
@@ -31729,7 +31729,7 @@
       </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -31791,7 +31791,7 @@
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>IF(ISNUMBER(F17),MAX(DATE(2026,6,6),F17+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F17),MAX(DATE(2026,5,27),F17+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F17" s="5" t="n">
@@ -31862,7 +31862,7 @@
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -31924,7 +31924,7 @@
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>IF(ISNUMBER(F18),MAX(DATE(2026,6,6),F18+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F18),MAX(DATE(2026,5,27),F18+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F18" s="5" t="n">
@@ -31995,7 +31995,7 @@
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -32057,7 +32057,7 @@
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>IF(ISNUMBER(F19),MAX(DATE(2026,6,6),F19+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F19),MAX(DATE(2026,5,27),F19+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F19" s="5" t="n">
@@ -32128,7 +32128,7 @@
       </c>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -32190,7 +32190,7 @@
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>IF(ISNUMBER(F20),MAX(DATE(2026,6,6),F20+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F20),MAX(DATE(2026,5,27),F20+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F20" s="5" t="n">
@@ -32261,7 +32261,7 @@
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -32323,7 +32323,7 @@
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>IF(ISNUMBER(F21),MAX(DATE(2026,6,6),F21+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F21),MAX(DATE(2026,5,27),F21+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F21" s="5" t="n">
@@ -32394,7 +32394,7 @@
       </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -32456,7 +32456,7 @@
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>IF(ISNUMBER(F22),MAX(DATE(2026,6,6),F22+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F22),MAX(DATE(2026,5,27),F22+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -32529,7 +32529,7 @@
       </c>
       <c r="T22" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -32597,7 +32597,7 @@
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>IF(ISNUMBER(F23),MAX(DATE(2026,6,6),F23+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F23),MAX(DATE(2026,5,27),F23+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F23" s="5" t="n">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -32730,7 +32730,7 @@
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>IF(ISNUMBER(F24),MAX(DATE(2026,6,6),F24+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F24),MAX(DATE(2026,5,27),F24+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F24" s="5" t="n">
@@ -32801,7 +32801,7 @@
       </c>
       <c r="T24" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -32863,7 +32863,7 @@
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>IF(ISNUMBER(F25),MAX(DATE(2026,6,6),F25+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F25),MAX(DATE(2026,5,27),F25+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n">
@@ -32934,7 +32934,7 @@
       </c>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -32996,7 +32996,7 @@
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>IF(ISNUMBER(F26),MAX(DATE(2026,6,6),F26+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F26),MAX(DATE(2026,5,27),F26+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F26" s="5" t="n">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="T26" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP_26-023</t>
+          <t>iCoA-PP_26-024</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
@@ -33129,7 +33129,7 @@
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>IF(ISNUMBER(F27),MAX(DATE(2026,6,6),F27+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F27),MAX(DATE(2026,5,27),F27+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F27" s="5" t="n">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -33213,7 +33213,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP_26-024</t>
+          <t>iCoA-PP_26-025</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
@@ -33262,7 +33262,7 @@
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>IF(ISNUMBER(F28),MAX(DATE(2026,6,6),F28+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F28),MAX(DATE(2026,5,27),F28+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F28" s="5" t="n">
@@ -33333,7 +33333,7 @@
       </c>
       <c r="T28" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -33395,7 +33395,7 @@
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>IF(ISNUMBER(F29),MAX(DATE(2026,6,6),F29+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F29),MAX(DATE(2026,5,27),F29+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F29" s="5" t="n">
@@ -33466,7 +33466,7 @@
       </c>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -33528,7 +33528,7 @@
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>IF(ISNUMBER(F30),MAX(DATE(2026,6,6),F30+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F30),MAX(DATE(2026,5,27),F30+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F30" s="5" t="n">
@@ -33599,7 +33599,7 @@
       </c>
       <c r="T30" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -33661,7 +33661,7 @@
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>IF(ISNUMBER(F31),MAX(DATE(2026,6,6),F31+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F31),MAX(DATE(2026,5,27),F31+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F31" s="5" t="n">
@@ -33732,7 +33732,7 @@
       </c>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -33794,7 +33794,7 @@
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>IF(ISNUMBER(F32),MAX(DATE(2026,6,6),F32+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F32),MAX(DATE(2026,5,27),F32+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F32" s="5" t="n">
@@ -33865,7 +33865,7 @@
       </c>
       <c r="T32" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -33927,7 +33927,7 @@
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>IF(ISNUMBER(F33),MAX(DATE(2026,6,6),F33+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F33),MAX(DATE(2026,5,27),F33+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F33" s="5" t="n">
@@ -33968,7 +33968,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Clemosa a Bud</t>
+          <t>Clemosa A Bud</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -33998,7 +33998,7 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -34060,7 +34060,7 @@
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>IF(ISNUMBER(F34),MAX(DATE(2026,6,6),F34+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F34),MAX(DATE(2026,5,27),F34+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F34" s="5" t="n">
@@ -34131,7 +34131,7 @@
       </c>
       <c r="T34" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -34193,7 +34193,7 @@
         <v/>
       </c>
       <c r="E35" s="5">
-        <f>IF(ISNUMBER(F35),MAX(DATE(2026,6,6),F35+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F35),MAX(DATE(2026,5,27),F35+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F35" s="5" t="n">
@@ -34264,7 +34264,7 @@
       </c>
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -34326,7 +34326,7 @@
         <v/>
       </c>
       <c r="E36" s="5">
-        <f>IF(ISNUMBER(F36),MAX(DATE(2026,6,6),F36+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F36),MAX(DATE(2026,5,27),F36+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F36" s="5" t="n">
@@ -34397,7 +34397,7 @@
       </c>
       <c r="T36" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -34459,7 +34459,7 @@
         <v/>
       </c>
       <c r="E37" s="5">
-        <f>IF(ISNUMBER(F37),MAX(DATE(2026,6,6),F37+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F37),MAX(DATE(2026,5,27),F37+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F37" s="5" t="n">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -34592,7 +34592,7 @@
         <v/>
       </c>
       <c r="E38" s="5">
-        <f>IF(ISNUMBER(F38),MAX(DATE(2026,6,6),F38+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F38),MAX(DATE(2026,5,27),F38+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F38" s="5" t="n">
@@ -34663,7 +34663,7 @@
       </c>
       <c r="T38" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -34725,7 +34725,7 @@
         <v/>
       </c>
       <c r="E39" s="5">
-        <f>IF(ISNUMBER(F39),MAX(DATE(2026,6,6),F39+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F39),MAX(DATE(2026,5,27),F39+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F39" s="5" t="n">
@@ -34796,7 +34796,7 @@
       </c>
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -34858,7 +34858,7 @@
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>IF(ISNUMBER(F40),MAX(DATE(2026,6,6),F40+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F40),MAX(DATE(2026,5,27),F40+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F40" s="5" t="n">
@@ -34929,7 +34929,7 @@
       </c>
       <c r="T40" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -34991,7 +34991,7 @@
         <v/>
       </c>
       <c r="E41" s="5">
-        <f>IF(ISNUMBER(F41),MAX(DATE(2026,6,6),F41+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F41),MAX(DATE(2026,5,27),F41+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F41" s="5" t="n">
@@ -35062,7 +35062,7 @@
       </c>
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -35124,7 +35124,7 @@
         <v/>
       </c>
       <c r="E42" s="5">
-        <f>IF(ISNUMBER(F42),MAX(DATE(2026,6,6),F42+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F42),MAX(DATE(2026,5,27),F42+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F42" s="5" t="n">
@@ -35195,7 +35195,7 @@
       </c>
       <c r="T42" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -35257,7 +35257,7 @@
         <v/>
       </c>
       <c r="E43" s="5">
-        <f>IF(ISNUMBER(F43),MAX(DATE(2026,6,6),F43+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F43),MAX(DATE(2026,5,27),F43+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F43" s="5" t="n">
@@ -35298,7 +35298,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -35328,7 +35328,7 @@
       </c>
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -35390,7 +35390,7 @@
         <v/>
       </c>
       <c r="E44" s="5">
-        <f>IF(ISNUMBER(F44),MAX(DATE(2026,6,6),F44+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F44),MAX(DATE(2026,5,27),F44+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F44" s="5" t="n">
@@ -35461,7 +35461,7 @@
       </c>
       <c r="T44" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -35523,7 +35523,7 @@
         <v/>
       </c>
       <c r="E45" s="5">
-        <f>IF(ISNUMBER(F45),MAX(DATE(2026,6,6),F45+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F45),MAX(DATE(2026,5,27),F45+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F45" s="5" t="n">
@@ -35594,7 +35594,7 @@
       </c>
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -35656,7 +35656,7 @@
         <v/>
       </c>
       <c r="E46" s="5">
-        <f>IF(ISNUMBER(F46),MAX(DATE(2026,6,6),F46+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F46),MAX(DATE(2026,5,27),F46+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F46" s="5" t="n">
@@ -35727,7 +35727,7 @@
       </c>
       <c r="T46" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -35789,7 +35789,7 @@
         <v/>
       </c>
       <c r="E47" s="5">
-        <f>IF(ISNUMBER(F47),MAX(DATE(2026,6,6),F47+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F47),MAX(DATE(2026,5,27),F47+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F47" s="5" t="n">
@@ -35860,7 +35860,7 @@
       </c>
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -35928,7 +35928,7 @@
         <v/>
       </c>
       <c r="E48" s="5">
-        <f>IF(ISNUMBER(F48),MAX(DATE(2026,6,6),F48+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F48),MAX(DATE(2026,5,27),F48+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -36001,7 +36001,7 @@
       </c>
       <c r="T48" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -36069,7 +36069,7 @@
         <v/>
       </c>
       <c r="E49" s="5">
-        <f>IF(ISNUMBER(F49),MAX(DATE(2026,6,6),F49+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F49),MAX(DATE(2026,5,27),F49+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -36142,7 +36142,7 @@
       </c>
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -36210,7 +36210,7 @@
         <v/>
       </c>
       <c r="E50" s="5">
-        <f>IF(ISNUMBER(F50),MAX(DATE(2026,6,6),F50+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F50),MAX(DATE(2026,5,27),F50+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -36283,7 +36283,7 @@
       </c>
       <c r="T50" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -36351,7 +36351,7 @@
         <v/>
       </c>
       <c r="E51" s="5">
-        <f>IF(ISNUMBER(F51),MAX(DATE(2026,6,6),F51+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F51),MAX(DATE(2026,5,27),F51+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -36394,7 +36394,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr">
@@ -36424,7 +36424,7 @@
       </c>
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -36492,7 +36492,7 @@
         <v/>
       </c>
       <c r="E52" s="5">
-        <f>IF(ISNUMBER(F52),MAX(DATE(2026,6,6),F52+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F52),MAX(DATE(2026,5,27),F52+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F52" s="5" t="n">
@@ -36563,7 +36563,7 @@
       </c>
       <c r="T52" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -36625,7 +36625,7 @@
         <v/>
       </c>
       <c r="E53" s="5">
-        <f>IF(ISNUMBER(F53),MAX(DATE(2026,6,6),F53+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F53),MAX(DATE(2026,5,27),F53+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F53" s="5" t="n">
@@ -36696,7 +36696,7 @@
       </c>
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -36758,7 +36758,7 @@
         <v/>
       </c>
       <c r="E54" s="5">
-        <f>IF(ISNUMBER(F54),MAX(DATE(2026,6,6),F54+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F54),MAX(DATE(2026,5,27),F54+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F54" s="5" t="n">
@@ -36829,7 +36829,7 @@
       </c>
       <c r="T54" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -36891,7 +36891,7 @@
         <v/>
       </c>
       <c r="E55" s="5">
-        <f>IF(ISNUMBER(F55),MAX(DATE(2026,6,6),F55+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F55),MAX(DATE(2026,5,27),F55+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F55" s="5" t="n">
@@ -36932,7 +36932,7 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -36962,7 +36962,7 @@
       </c>
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -37024,7 +37024,7 @@
         <v/>
       </c>
       <c r="E56" s="5">
-        <f>IF(ISNUMBER(F56),MAX(DATE(2026,6,6),F56+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F56),MAX(DATE(2026,5,27),F56+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F56" s="5" t="n">
@@ -37095,7 +37095,7 @@
       </c>
       <c r="T56" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -37157,7 +37157,7 @@
         <v/>
       </c>
       <c r="E57" s="5">
-        <f>IF(ISNUMBER(F57),MAX(DATE(2026,6,6),F57+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F57),MAX(DATE(2026,5,27),F57+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F57" s="5" t="n">
@@ -37228,7 +37228,7 @@
       </c>
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -37290,7 +37290,7 @@
         <v/>
       </c>
       <c r="E58" s="5">
-        <f>IF(ISNUMBER(F58),MAX(DATE(2026,6,6),F58+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F58),MAX(DATE(2026,5,27),F58+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F58" s="5" t="n">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -37361,7 +37361,7 @@
       </c>
       <c r="T58" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -37423,7 +37423,7 @@
         <v/>
       </c>
       <c r="E59" s="5">
-        <f>IF(ISNUMBER(F59),MAX(DATE(2026,6,6),F59+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F59),MAX(DATE(2026,5,27),F59+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F59" s="5" t="n">
@@ -37494,7 +37494,7 @@
       </c>
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -37556,7 +37556,7 @@
         <v/>
       </c>
       <c r="E60" s="5">
-        <f>IF(ISNUMBER(F60),MAX(DATE(2026,6,6),F60+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F60),MAX(DATE(2026,5,27),F60+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F60" s="5" t="n">
@@ -37627,7 +37627,7 @@
       </c>
       <c r="T60" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -37689,7 +37689,7 @@
         <v/>
       </c>
       <c r="E61" s="5">
-        <f>IF(ISNUMBER(F61),MAX(DATE(2026,6,6),F61+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F61),MAX(DATE(2026,5,27),F61+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F61" s="5" t="n">
@@ -37760,7 +37760,7 @@
       </c>
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -37822,7 +37822,7 @@
         <v/>
       </c>
       <c r="E62" s="5">
-        <f>IF(ISNUMBER(F62),MAX(DATE(2026,6,6),F62+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F62),MAX(DATE(2026,5,27),F62+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F62" s="5" t="n">
@@ -37893,7 +37893,7 @@
       </c>
       <c r="T62" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -37955,7 +37955,7 @@
         <v/>
       </c>
       <c r="E63" s="5">
-        <f>IF(ISNUMBER(F63),MAX(DATE(2026,6,6),F63+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F63),MAX(DATE(2026,5,27),F63+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F63" s="5" t="n">
@@ -38088,7 +38088,7 @@
         <v/>
       </c>
       <c r="E64" s="5">
-        <f>IF(ISNUMBER(F64),MAX(DATE(2026,6,6),F64+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F64),MAX(DATE(2026,5,27),F64+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F64" s="5" t="n">
@@ -38221,7 +38221,7 @@
         <v/>
       </c>
       <c r="E65" s="5">
-        <f>IF(ISNUMBER(F65),MAX(DATE(2026,6,6),F65+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F65),MAX(DATE(2026,5,27),F65+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F65" s="5" t="n">
@@ -38354,7 +38354,7 @@
         <v/>
       </c>
       <c r="E66" s="5">
-        <f>IF(ISNUMBER(F66),MAX(DATE(2026,6,6),F66+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F66),MAX(DATE(2026,5,27),F66+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F66" s="5" t="n">
@@ -38487,7 +38487,7 @@
         <v/>
       </c>
       <c r="E67" s="5">
-        <f>IF(ISNUMBER(F67),MAX(DATE(2026,6,6),F67+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F67),MAX(DATE(2026,5,27),F67+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F67" s="5" t="n">
@@ -38620,7 +38620,7 @@
         <v/>
       </c>
       <c r="E68" s="5">
-        <f>IF(ISNUMBER(F68),MAX(DATE(2026,6,6),F68+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F68),MAX(DATE(2026,5,27),F68+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F68" s="5" t="n">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -38753,7 +38753,7 @@
         <v/>
       </c>
       <c r="E69" s="5">
-        <f>IF(ISNUMBER(F69),MAX(DATE(2026,6,6),F69+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F69),MAX(DATE(2026,5,27),F69+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -38890,7 +38890,7 @@
         <v/>
       </c>
       <c r="E70" s="5">
-        <f>IF(ISNUMBER(F70),MAX(DATE(2026,6,6),F70+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F70),MAX(DATE(2026,5,27),F70+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F70" s="5" t="n">
@@ -39023,7 +39023,7 @@
         <v/>
       </c>
       <c r="E71" s="5">
-        <f>IF(ISNUMBER(F71),MAX(DATE(2026,6,6),F71+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F71),MAX(DATE(2026,5,27),F71+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -39164,7 +39164,7 @@
         <v/>
       </c>
       <c r="E72" s="5">
-        <f>IF(ISNUMBER(F72),MAX(DATE(2026,6,6),F72+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F72),MAX(DATE(2026,5,27),F72+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -39207,7 +39207,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr">
@@ -39305,7 +39305,7 @@
         <v/>
       </c>
       <c r="E73" s="5">
-        <f>IF(ISNUMBER(F73),MAX(DATE(2026,6,6),F73+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F73),MAX(DATE(2026,5,27),F73+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -39446,7 +39446,7 @@
         <v/>
       </c>
       <c r="E74" s="5">
-        <f>IF(ISNUMBER(F74),MAX(DATE(2026,6,6),F74+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F74),MAX(DATE(2026,5,27),F74+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -39587,7 +39587,7 @@
         <v/>
       </c>
       <c r="E75" s="5">
-        <f>IF(ISNUMBER(F75),MAX(DATE(2026,6,6),F75+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F75),MAX(DATE(2026,5,27),F75+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -39728,7 +39728,7 @@
         <v/>
       </c>
       <c r="E76" s="5">
-        <f>IF(ISNUMBER(F76),MAX(DATE(2026,6,6),F76+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F76),MAX(DATE(2026,5,27),F76+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F76" s="5" t="n">
@@ -39861,7 +39861,7 @@
         <v/>
       </c>
       <c r="E77" s="5">
-        <f>IF(ISNUMBER(F77),MAX(DATE(2026,6,6),F77+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F77),MAX(DATE(2026,5,27),F77+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F77" s="5" t="n">
@@ -39902,7 +39902,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -39994,7 +39994,7 @@
         <v/>
       </c>
       <c r="E78" s="5">
-        <f>IF(ISNUMBER(F78),MAX(DATE(2026,6,6),F78+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F78),MAX(DATE(2026,5,27),F78+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F78" s="5" t="n">
@@ -40127,7 +40127,7 @@
         <v/>
       </c>
       <c r="E79" s="5">
-        <f>IF(ISNUMBER(F79),MAX(DATE(2026,6,6),F79+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F79),MAX(DATE(2026,5,27),F79+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F79" s="5" t="n">
@@ -40168,7 +40168,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -40260,7 +40260,7 @@
         <v/>
       </c>
       <c r="E80" s="5">
-        <f>IF(ISNUMBER(F80),MAX(DATE(2026,6,6),F80+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F80),MAX(DATE(2026,5,27),F80+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F80" s="5" t="n">
@@ -40393,7 +40393,7 @@
         <v/>
       </c>
       <c r="E81" s="5">
-        <f>IF(ISNUMBER(F81),MAX(DATE(2026,6,6),F81+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F81),MAX(DATE(2026,5,27),F81+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F81" s="5" t="n">
@@ -40526,7 +40526,7 @@
         <v/>
       </c>
       <c r="E82" s="5">
-        <f>IF(ISNUMBER(F82),MAX(DATE(2026,6,6),F82+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F82),MAX(DATE(2026,5,27),F82+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F82" s="5" t="n">
@@ -40659,7 +40659,7 @@
         <v/>
       </c>
       <c r="E83" s="5">
-        <f>IF(ISNUMBER(F83),MAX(DATE(2026,6,6),F83+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F83),MAX(DATE(2026,5,27),F83+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F83" s="5" t="n">
@@ -40792,7 +40792,7 @@
         <v/>
       </c>
       <c r="E84" s="5">
-        <f>IF(ISNUMBER(F84),MAX(DATE(2026,6,6),F84+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F84),MAX(DATE(2026,5,27),F84+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F84" s="5" t="n">
@@ -40833,7 +40833,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -40925,7 +40925,7 @@
         <v/>
       </c>
       <c r="E85" s="5">
-        <f>IF(ISNUMBER(F85),MAX(DATE(2026,6,6),F85+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F85),MAX(DATE(2026,5,27),F85+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -40968,7 +40968,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O85" s="6" t="inlineStr">
@@ -41066,7 +41066,7 @@
         <v/>
       </c>
       <c r="E86" s="5">
-        <f>IF(ISNUMBER(F86),MAX(DATE(2026,6,6),F86+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F86),MAX(DATE(2026,5,27),F86+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F86" s="5" t="n">
@@ -41198,7 +41198,7 @@
         <v/>
       </c>
       <c r="E87" s="5">
-        <f>IF(ISNUMBER(F87),MAX(DATE(2026,6,6),F87+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F87),MAX(DATE(2026,5,27),F87+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F87" s="5" t="n">
@@ -41330,7 +41330,7 @@
         <v/>
       </c>
       <c r="E88" s="5">
-        <f>IF(ISNUMBER(F88),MAX(DATE(2026,6,6),F88+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F88),MAX(DATE(2026,5,27),F88+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F88" s="5" t="n">
@@ -41458,7 +41458,7 @@
         <v/>
       </c>
       <c r="E89" s="5">
-        <f>IF(ISNUMBER(F89),MAX(DATE(2026,6,6),F89+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F89),MAX(DATE(2026,5,27),F89+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F89" s="5" t="n">
@@ -41590,7 +41590,7 @@
         <v/>
       </c>
       <c r="E90" s="5">
-        <f>IF(ISNUMBER(F90),MAX(DATE(2026,6,6),F90+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F90),MAX(DATE(2026,5,27),F90+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F90" s="5" t="n">
@@ -41722,7 +41722,7 @@
         <v/>
       </c>
       <c r="E91" s="5">
-        <f>IF(ISNUMBER(F91),MAX(DATE(2026,6,6),F91+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F91),MAX(DATE(2026,5,27),F91+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F91" s="5" t="n">
@@ -41854,7 +41854,7 @@
         <v/>
       </c>
       <c r="E92" s="5">
-        <f>IF(ISNUMBER(F92),MAX(DATE(2026,6,6),F92+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F92),MAX(DATE(2026,5,27),F92+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F92" s="5" t="n">
@@ -41986,7 +41986,7 @@
         <v/>
       </c>
       <c r="E93" s="5">
-        <f>IF(ISNUMBER(F93),MAX(DATE(2026,6,6),F93+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F93),MAX(DATE(2026,5,27),F93+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F93" s="5" t="n">
@@ -42118,7 +42118,7 @@
         <v/>
       </c>
       <c r="E94" s="5">
-        <f>IF(ISNUMBER(F94),MAX(DATE(2026,6,6),F94+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F94),MAX(DATE(2026,5,27),F94+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F94" s="5" t="n">
@@ -42250,7 +42250,7 @@
         <v/>
       </c>
       <c r="E95" s="5">
-        <f>IF(ISNUMBER(F95),MAX(DATE(2026,6,6),F95+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F95),MAX(DATE(2026,5,27),F95+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F95" s="5" t="n">
@@ -42382,7 +42382,7 @@
         <v/>
       </c>
       <c r="E96" s="5">
-        <f>IF(ISNUMBER(F96),MAX(DATE(2026,6,6),F96+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F96),MAX(DATE(2026,5,27),F96+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F96" s="5" t="n">
@@ -42514,7 +42514,7 @@
         <v/>
       </c>
       <c r="E97" s="5">
-        <f>IF(ISNUMBER(F97),MAX(DATE(2026,6,6),F97+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F97),MAX(DATE(2026,5,27),F97+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F97" s="5" t="n">
@@ -42646,7 +42646,7 @@
         <v/>
       </c>
       <c r="E98" s="5">
-        <f>IF(ISNUMBER(F98),MAX(DATE(2026,6,6),F98+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F98),MAX(DATE(2026,5,27),F98+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F98" s="5" t="n">
@@ -42778,7 +42778,7 @@
         <v/>
       </c>
       <c r="E99" s="5">
-        <f>IF(ISNUMBER(F99),MAX(DATE(2026,6,6),F99+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F99),MAX(DATE(2026,5,27),F99+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F99" s="5" t="n">
@@ -42910,7 +42910,7 @@
         <v/>
       </c>
       <c r="E100" s="5">
-        <f>IF(ISNUMBER(F100),MAX(DATE(2026,6,6),F100+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F100),MAX(DATE(2026,5,27),F100+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F100" s="5" t="n">
@@ -42951,7 +42951,7 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
@@ -43042,7 +43042,7 @@
         <v/>
       </c>
       <c r="E101" s="5">
-        <f>IF(ISNUMBER(F101),MAX(DATE(2026,6,6),F101+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F101),MAX(DATE(2026,5,27),F101+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F101" s="5" t="n">
@@ -43174,7 +43174,7 @@
         <v/>
       </c>
       <c r="E102" s="5">
-        <f>IF(ISNUMBER(F102),MAX(DATE(2026,6,6),F102+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F102),MAX(DATE(2026,5,27),F102+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F102" s="5" t="n">
@@ -43306,7 +43306,7 @@
         <v/>
       </c>
       <c r="E103" s="5">
-        <f>IF(ISNUMBER(F103),MAX(DATE(2026,6,6),F103+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F103),MAX(DATE(2026,5,27),F103+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F103" s="5" t="n">
@@ -43438,7 +43438,7 @@
         <v/>
       </c>
       <c r="E104" s="5">
-        <f>IF(ISNUMBER(F104),MAX(DATE(2026,6,6),F104+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F104),MAX(DATE(2026,5,27),F104+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F104" s="5" t="n">
@@ -43479,7 +43479,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
@@ -43570,7 +43570,7 @@
         <v/>
       </c>
       <c r="E105" s="5">
-        <f>IF(ISNUMBER(F105),MAX(DATE(2026,6,6),F105+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F105),MAX(DATE(2026,5,27),F105+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F105" s="5" t="n">
@@ -43702,7 +43702,7 @@
         <v/>
       </c>
       <c r="E106" s="5">
-        <f>IF(ISNUMBER(F106),MAX(DATE(2026,6,6),F106+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F106),MAX(DATE(2026,5,27),F106+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F106" s="5" t="n">
@@ -43834,7 +43834,7 @@
         <v/>
       </c>
       <c r="E107" s="5">
-        <f>IF(ISNUMBER(F107),MAX(DATE(2026,6,6),F107+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F107),MAX(DATE(2026,5,27),F107+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F107" s="5" t="n">
@@ -43966,7 +43966,7 @@
         <v/>
       </c>
       <c r="E108" s="5">
-        <f>IF(ISNUMBER(F108),MAX(DATE(2026,6,6),F108+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F108),MAX(DATE(2026,5,27),F108+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F108" s="5" t="n">
@@ -44098,7 +44098,7 @@
         <v/>
       </c>
       <c r="E109" s="5">
-        <f>IF(ISNUMBER(F109),MAX(DATE(2026,6,6),F109+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F109),MAX(DATE(2026,5,27),F109+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F109" s="5" t="n">
@@ -44230,7 +44230,7 @@
         <v/>
       </c>
       <c r="E110" s="5">
-        <f>IF(ISNUMBER(F110),MAX(DATE(2026,6,6),F110+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F110),MAX(DATE(2026,5,27),F110+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F110" s="5" t="n">
@@ -44362,7 +44362,7 @@
         <v/>
       </c>
       <c r="E111" s="5">
-        <f>IF(ISNUMBER(F111),MAX(DATE(2026,6,6),F111+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F111),MAX(DATE(2026,5,27),F111+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F111" s="5" t="n">
@@ -44494,7 +44494,7 @@
         <v/>
       </c>
       <c r="E112" s="5">
-        <f>IF(ISNUMBER(F112),MAX(DATE(2026,6,6),F112+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F112),MAX(DATE(2026,5,27),F112+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F112" s="5" t="n">
@@ -44626,7 +44626,7 @@
         <v/>
       </c>
       <c r="E113" s="5">
-        <f>IF(ISNUMBER(F113),MAX(DATE(2026,6,6),F113+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F113),MAX(DATE(2026,5,27),F113+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F113" s="5" t="n">
@@ -44758,7 +44758,7 @@
         <v/>
       </c>
       <c r="E114" s="5">
-        <f>IF(ISNUMBER(F114),MAX(DATE(2026,6,6),F114+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F114),MAX(DATE(2026,5,27),F114+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F114" s="5" t="n">
@@ -44799,7 +44799,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Clemosa a Bud</t>
+          <t>Clemosa A Bud</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
@@ -44890,7 +44890,7 @@
         <v/>
       </c>
       <c r="E115" s="5">
-        <f>IF(ISNUMBER(F115),MAX(DATE(2026,6,6),F115+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F115),MAX(DATE(2026,5,27),F115+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F115" s="5" t="n">
@@ -45022,7 +45022,7 @@
         <v/>
       </c>
       <c r="E116" s="5">
-        <f>IF(ISNUMBER(F116),MAX(DATE(2026,6,6),F116+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F116),MAX(DATE(2026,5,27),F116+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F116" s="5" t="n">
@@ -45154,7 +45154,7 @@
         <v/>
       </c>
       <c r="E117" s="5">
-        <f>IF(ISNUMBER(F117),MAX(DATE(2026,6,6),F117+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F117),MAX(DATE(2026,5,27),F117+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F117" s="5" t="n">
@@ -45286,7 +45286,7 @@
         <v/>
       </c>
       <c r="E118" s="5">
-        <f>IF(ISNUMBER(F118),MAX(DATE(2026,6,6),F118+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F118),MAX(DATE(2026,5,27),F118+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F118" s="5" t="n">
@@ -45418,7 +45418,7 @@
         <v/>
       </c>
       <c r="E119" s="5">
-        <f>IF(ISNUMBER(F119),MAX(DATE(2026,6,6),F119+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F119),MAX(DATE(2026,5,27),F119+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F119" s="5" t="n">
@@ -45550,7 +45550,7 @@
         <v/>
       </c>
       <c r="E120" s="5">
-        <f>IF(ISNUMBER(F120),MAX(DATE(2026,6,6),F120+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F120),MAX(DATE(2026,5,27),F120+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F120" s="5" t="n">
@@ -45682,7 +45682,7 @@
         <v/>
       </c>
       <c r="E121" s="5">
-        <f>IF(ISNUMBER(F121),MAX(DATE(2026,6,6),F121+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F121),MAX(DATE(2026,5,27),F121+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F121" s="5" t="n">
@@ -45723,7 +45723,7 @@
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
@@ -45814,7 +45814,7 @@
         <v/>
       </c>
       <c r="E122" s="5">
-        <f>IF(ISNUMBER(F122),MAX(DATE(2026,6,6),F122+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F122),MAX(DATE(2026,5,27),F122+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F122" s="5" t="n">
@@ -45946,7 +45946,7 @@
         <v/>
       </c>
       <c r="E123" s="5">
-        <f>IF(ISNUMBER(F123),MAX(DATE(2026,6,6),F123+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F123),MAX(DATE(2026,5,27),F123+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F123" s="5" t="n">
@@ -45987,7 +45987,7 @@
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
@@ -46078,7 +46078,7 @@
         <v/>
       </c>
       <c r="E124" s="5">
-        <f>IF(ISNUMBER(F124),MAX(DATE(2026,6,6),F124+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F124),MAX(DATE(2026,5,27),F124+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F124" s="5" t="n">
@@ -46119,7 +46119,7 @@
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
@@ -46210,7 +46210,7 @@
         <v/>
       </c>
       <c r="E125" s="5">
-        <f>IF(ISNUMBER(F125),MAX(DATE(2026,6,6),F125+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F125),MAX(DATE(2026,5,27),F125+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F125" s="5" t="n">
@@ -46251,7 +46251,7 @@
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
@@ -46342,7 +46342,7 @@
         <v/>
       </c>
       <c r="E126" s="5">
-        <f>IF(ISNUMBER(F126),MAX(DATE(2026,6,6),F126+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F126),MAX(DATE(2026,5,27),F126+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F126" s="5" t="n">
@@ -46383,7 +46383,7 @@
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
@@ -46474,7 +46474,7 @@
         <v/>
       </c>
       <c r="E127" s="5">
-        <f>IF(ISNUMBER(F127),MAX(DATE(2026,6,6),F127+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F127),MAX(DATE(2026,5,27),F127+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F127" s="5" t="n">
@@ -46606,7 +46606,7 @@
         <v/>
       </c>
       <c r="E128" s="5">
-        <f>IF(ISNUMBER(F128),MAX(DATE(2026,6,6),F128+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F128),MAX(DATE(2026,5,27),F128+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F128" s="5" t="n">
@@ -46738,7 +46738,7 @@
         <v/>
       </c>
       <c r="E129" s="5">
-        <f>IF(ISNUMBER(F129),MAX(DATE(2026,6,6),F129+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F129),MAX(DATE(2026,5,27),F129+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F129" s="5" t="n">
@@ -46870,7 +46870,7 @@
         <v/>
       </c>
       <c r="E130" s="5">
-        <f>IF(ISNUMBER(F130),MAX(DATE(2026,6,6),F130+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F130),MAX(DATE(2026,5,27),F130+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F130" s="5" t="n">
@@ -47002,7 +47002,7 @@
         <v/>
       </c>
       <c r="E131" s="5">
-        <f>IF(ISNUMBER(F131),MAX(DATE(2026,6,6),F131+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F131),MAX(DATE(2026,5,27),F131+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F131" s="5" t="n">
@@ -47134,7 +47134,7 @@
         <v/>
       </c>
       <c r="E132" s="5">
-        <f>IF(ISNUMBER(F132),MAX(DATE(2026,6,6),F132+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F132),MAX(DATE(2026,5,27),F132+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F132" s="5" t="n">
@@ -47266,7 +47266,7 @@
         <v/>
       </c>
       <c r="E133" s="5">
-        <f>IF(ISNUMBER(F133),MAX(DATE(2026,6,6),F133+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F133),MAX(DATE(2026,5,27),F133+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F133" s="5" t="n">
@@ -47398,7 +47398,7 @@
         <v/>
       </c>
       <c r="E134" s="5">
-        <f>IF(ISNUMBER(F134),MAX(DATE(2026,6,6),F134+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F134),MAX(DATE(2026,5,27),F134+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F134" s="5" t="n">
@@ -47530,7 +47530,7 @@
         <v/>
       </c>
       <c r="E135" s="5">
-        <f>IF(ISNUMBER(F135),MAX(DATE(2026,6,6),F135+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F135),MAX(DATE(2026,5,27),F135+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F135" s="5" t="n">
@@ -47662,7 +47662,7 @@
         <v/>
       </c>
       <c r="E136" s="5">
-        <f>IF(ISNUMBER(F136),MAX(DATE(2026,6,6),F136+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F136),MAX(DATE(2026,5,27),F136+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F136" s="5" t="n">
@@ -47789,9 +47789,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D137" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D137" s="5" t="inlineStr"/>
       <c r="E137" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47865,7 +47863,7 @@
       </c>
       <c r="T137" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-30-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-30-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U137" s="2">
@@ -47921,9 +47919,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D138" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D138" s="5" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47997,7 +47993,7 @@
       </c>
       <c r="T138" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-29-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-29-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U138" s="2">
@@ -48053,9 +48049,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D139" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D139" s="5" t="inlineStr"/>
       <c r="E139" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48129,7 +48123,7 @@
       </c>
       <c r="T139" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-1-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-1-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U139" s="2">
@@ -48185,9 +48179,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D140" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D140" s="5" t="inlineStr"/>
       <c r="E140" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48261,7 +48253,7 @@
       </c>
       <c r="T140" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-25-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-25-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U140" s="2">
@@ -48317,9 +48309,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D141" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D141" s="5" t="inlineStr"/>
       <c r="E141" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48393,7 +48383,7 @@
       </c>
       <c r="T141" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-28-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-28-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U141" s="2">
@@ -48449,9 +48439,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D142" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D142" s="5" t="inlineStr"/>
       <c r="E142" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48525,7 +48513,7 @@
       </c>
       <c r="T142" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-27-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-27-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U142" s="2">
@@ -48581,9 +48569,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D143" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D143" s="5" t="inlineStr"/>
       <c r="E143" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48657,7 +48643,7 @@
       </c>
       <c r="T143" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-26-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-26-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U143" s="2">
@@ -48713,9 +48699,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D144" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D144" s="5" t="inlineStr"/>
       <c r="E144" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48789,7 +48773,7 @@
       </c>
       <c r="T144" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-24-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-24-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U144" s="2">
@@ -48845,9 +48829,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D145" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D145" s="5" t="inlineStr"/>
       <c r="E145" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48921,7 +48903,7 @@
       </c>
       <c r="T145" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-23-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-23-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U145" s="2">
@@ -48977,9 +48959,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D146" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D146" s="5" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49053,7 +49033,7 @@
       </c>
       <c r="T146" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-22-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-22-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U146" s="2">
@@ -49109,9 +49089,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D147" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D147" s="5" t="inlineStr"/>
       <c r="E147" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49185,7 +49163,7 @@
       </c>
       <c r="T147" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-21-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-21-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U147" s="2">
@@ -49241,9 +49219,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D148" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D148" s="5" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49317,7 +49293,7 @@
       </c>
       <c r="T148" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-19-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-19-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U148" s="2">
@@ -49373,9 +49349,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D149" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D149" s="5" t="inlineStr"/>
       <c r="E149" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49449,7 +49423,7 @@
       </c>
       <c r="T149" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-20-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-20-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U149" s="2">
@@ -49505,9 +49479,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D150" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D150" s="5" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49581,7 +49553,7 @@
       </c>
       <c r="T150" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-18-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-18-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U150" s="2">
@@ -49637,9 +49609,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D151" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D151" s="5" t="inlineStr"/>
       <c r="E151" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49713,7 +49683,7 @@
       </c>
       <c r="T151" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-17-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-17-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U151" s="2">
@@ -49769,9 +49739,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D152" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D152" s="5" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49845,7 +49813,7 @@
       </c>
       <c r="T152" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-2-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-2-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U152" s="2">
@@ -49901,9 +49869,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D153" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D153" s="5" t="inlineStr"/>
       <c r="E153" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49947,7 +49913,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -49977,7 +49943,7 @@
       </c>
       <c r="T153" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-16-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-16-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U153" s="2">
@@ -50033,9 +49999,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D154" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D154" s="5" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50109,7 +50073,7 @@
       </c>
       <c r="T154" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-14-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-14-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U154" s="2">
@@ -50165,9 +50129,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D155" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D155" s="5" t="inlineStr"/>
       <c r="E155" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50241,7 +50203,7 @@
       </c>
       <c r="T155" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay — pending — on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay — pending — on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U155" s="2">
@@ -50297,9 +50259,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D156" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D156" s="5" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50343,7 +50303,7 @@
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
@@ -50373,7 +50333,7 @@
       </c>
       <c r="T156" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-15-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-15-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U156" s="2">
@@ -50429,9 +50389,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D157" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D157" s="5" t="inlineStr"/>
       <c r="E157" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50505,7 +50463,7 @@
       </c>
       <c r="T157" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-12-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-12-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U157" s="2">
@@ -50561,9 +50519,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D158" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D158" s="5" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50637,7 +50593,7 @@
       </c>
       <c r="T158" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-11-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-11-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U158" s="2">
@@ -50693,9 +50649,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D159" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D159" s="5" t="inlineStr"/>
       <c r="E159" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50769,7 +50723,7 @@
       </c>
       <c r="T159" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-10-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-10-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U159" s="2">
@@ -50825,9 +50779,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D160" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D160" s="5" t="inlineStr"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50901,7 +50853,7 @@
       </c>
       <c r="T160" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-9-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-9-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U160" s="2">
@@ -50957,9 +50909,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D161" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D161" s="5" t="inlineStr"/>
       <c r="E161" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51033,7 +50983,7 @@
       </c>
       <c r="T161" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-8-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-8-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U161" s="2">
@@ -51089,9 +51039,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D162" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D162" s="5" t="inlineStr"/>
       <c r="E162" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51165,7 +51113,7 @@
       </c>
       <c r="T162" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-7-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-7-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U162" s="2">
@@ -51221,9 +51169,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D163" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D163" s="5" t="inlineStr"/>
       <c r="E163" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51297,7 +51243,7 @@
       </c>
       <c r="T163" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-6-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-6-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U163" s="2">
@@ -51353,9 +51299,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D164" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D164" s="5" t="inlineStr"/>
       <c r="E164" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51429,7 +51373,7 @@
       </c>
       <c r="T164" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-5-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites iCoA-PP_26-162 of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-5-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites iCoA-PP_26-162 of 24.08.2026</t>
         </is>
       </c>
       <c r="U164" s="2">
@@ -51485,9 +51429,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D165" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D165" s="5" t="inlineStr"/>
       <c r="E165" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51561,7 +51503,7 @@
       </c>
       <c r="T165" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-3-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-3-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U165" s="2">
@@ -51617,9 +51559,7 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D166" s="5" t="n">
-        <v>46286</v>
-      </c>
+      <c r="D166" s="5" t="inlineStr"/>
       <c r="E166" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51693,7 +51633,7 @@
       </c>
       <c r="T166" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-4-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-4-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U166" s="2">
@@ -51754,7 +51694,7 @@
         <v/>
       </c>
       <c r="E167" s="5">
-        <f>IF(ISNUMBER(F167),MAX(DATE(2026,6,6),F167+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F167),MAX(DATE(2026,5,27),F167+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F167" s="5" t="n">
@@ -51887,7 +51827,7 @@
         <v/>
       </c>
       <c r="E168" s="5">
-        <f>IF(ISNUMBER(F168),MAX(DATE(2026,6,6),F168+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F168),MAX(DATE(2026,5,27),F168+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F168" s="5" t="n">
@@ -52020,7 +51960,7 @@
         <v/>
       </c>
       <c r="E169" s="5">
-        <f>IF(ISNUMBER(F169),MAX(DATE(2026,6,6),F169+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F169),MAX(DATE(2026,5,27),F169+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F169" s="5" t="n">
@@ -52153,7 +52093,7 @@
         <v/>
       </c>
       <c r="E170" s="5">
-        <f>IF(ISNUMBER(F170),MAX(DATE(2026,6,6),F170+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F170),MAX(DATE(2026,5,27),F170+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F170" s="5" t="inlineStr">
@@ -52294,7 +52234,7 @@
         <v/>
       </c>
       <c r="E171" s="5">
-        <f>IF(ISNUMBER(F171),MAX(DATE(2026,6,6),F171+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F171),MAX(DATE(2026,5,27),F171+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F171" s="5" t="n">
@@ -52426,7 +52366,7 @@
         <v/>
       </c>
       <c r="E172" s="5">
-        <f>IF(ISNUMBER(F172),MAX(DATE(2026,6,6),F172+7),DATE(2026,6,6))</f>
+        <f>IF(ISNUMBER(F172),MAX(DATE(2026,5,27),F172+7),DATE(2026,5,27))</f>
         <v/>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -52567,7 +52507,7 @@
         <v/>
       </c>
       <c r="E173" s="5">
-        <f>IF(ISNUMBER(F173),MAX(DATE(2026,6,6),F173+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F173),MAX(DATE(2026,5,27),F173+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F173" s="5" t="n">
@@ -52684,7 +52624,7 @@
     <row r="175" ht="150" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
@@ -56055,28 +55995,28 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v44 on 17.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v45 on 06.09.2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 03.06.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 03.06.2026; a RETEST is dated at its own sampling day and issued on its campaign's day (sampling_dates.py, owner 15.09.2026: Tranche 1 sampled 21–24.07.2026 and issued 27.07.2026, Tranche 2 sampled 12–14.08.2026 and issued 17.08.2026, Tranche 3 sampled 19–21.08.2026 and issued 24.08.2026, each batch on the day its certificate number falls), which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. A round whose packaging date the list does not hold is numbered all the same (owner, 15.09.2026: identification A, B and foreign matter are performed on every batch) and says its testing date is not stated. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
+          <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 15.05.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 15.05.2026; a RETEST is dated at its own sampling day and issued on its campaign's day (sampling_dates.py, owner 15.09.2026: Tranche 1 sampled 21–24.07.2026 and issued 27.07.2026, Tranche 2 sampled 12–14.08.2026 and issued 17.08.2026, Tranche 3 sampled 19–21.08.2026 and issued 24.08.2026, each batch on the day its certificate number falls), which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. A round whose packaging date the list does not hold is numbered all the same (owner, 15.09.2026: identification A, B and foreign matter are performed on every batch) and says its testing date is not stated. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="190" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v44.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v45.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="D2" s="5">
-        <f>IF(A2="","",IF(ISNUMBER(E2),MAX(DATE(2026,5,15),E2),DATE(2026,5,15)))</f>
+        <f>IF(A2="","",IF(ISNUMBER(E2),MAX(DATE(2026,6,3),E2),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E2" s="5">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <f>IF(A3="","",IF(ISNUMBER(E3),MAX(DATE(2026,5,15),E3),DATE(2026,5,15)))</f>
+        <f>IF(A3="","",IF(ISNUMBER(E3),MAX(DATE(2026,6,3),E3),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E3" s="5">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D4" s="5">
-        <f>IF(A4="","",IF(ISNUMBER(E4),MAX(DATE(2026,5,15),E4),DATE(2026,5,15)))</f>
+        <f>IF(A4="","",IF(ISNUMBER(E4),MAX(DATE(2026,6,3),E4),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E4" s="5">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="D5" s="5">
-        <f>IF(A5="","",IF(ISNUMBER(E5),MAX(DATE(2026,5,15),E5),DATE(2026,5,15)))</f>
+        <f>IF(A5="","",IF(ISNUMBER(E5),MAX(DATE(2026,6,3),E5),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="D6" s="5">
-        <f>IF(A6="","",IF(ISNUMBER(E6),MAX(DATE(2026,5,15),E6),DATE(2026,5,15)))</f>
+        <f>IF(A6="","",IF(ISNUMBER(E6),MAX(DATE(2026,6,3),E6),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="D7" s="5">
-        <f>IF(A7="","",IF(ISNUMBER(E7),MAX(DATE(2026,5,15),E7),DATE(2026,5,15)))</f>
+        <f>IF(A7="","",IF(ISNUMBER(E7),MAX(DATE(2026,6,3),E7),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <f>IF(A9="","",IF(ISNUMBER(E9),MAX(DATE(2026,5,15),E9),DATE(2026,5,15)))</f>
+        <f>IF(A9="","",IF(ISNUMBER(E9),MAX(DATE(2026,6,3),E9),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <f>IF(A10="","",IF(ISNUMBER(E10),MAX(DATE(2026,5,15),E10),DATE(2026,5,15)))</f>
+        <f>IF(A10="","",IF(ISNUMBER(E10),MAX(DATE(2026,6,3),E10),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <f>IF(A11="","",IF(ISNUMBER(E11),MAX(DATE(2026,5,15),E11),DATE(2026,5,15)))</f>
+        <f>IF(A11="","",IF(ISNUMBER(E11),MAX(DATE(2026,6,3),E11),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="D12" s="5">
-        <f>IF(A12="","",IF(ISNUMBER(E12),MAX(DATE(2026,5,15),E12),DATE(2026,5,15)))</f>
+        <f>IF(A12="","",IF(ISNUMBER(E12),MAX(DATE(2026,6,3),E12),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <f>IF(A13="","",IF(ISNUMBER(E13),MAX(DATE(2026,5,15),E13),DATE(2026,5,15)))</f>
+        <f>IF(A13="","",IF(ISNUMBER(E13),MAX(DATE(2026,6,3),E13),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>IF(A14="","",IF(ISNUMBER(E14),MAX(DATE(2026,5,15),E14),DATE(2026,5,15)))</f>
+        <f>IF(A14="","",IF(ISNUMBER(E14),MAX(DATE(2026,6,3),E14),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <f>IF(A15="","",IF(ISNUMBER(E15),MAX(DATE(2026,5,15),E15),DATE(2026,5,15)))</f>
+        <f>IF(A15="","",IF(ISNUMBER(E15),MAX(DATE(2026,6,3),E15),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <f>IF(A16="","",IF(ISNUMBER(E16),MAX(DATE(2026,5,15),E16),DATE(2026,5,15)))</f>
+        <f>IF(A16="","",IF(ISNUMBER(E16),MAX(DATE(2026,6,3),E16),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <f>IF(A17="","",IF(ISNUMBER(E17),MAX(DATE(2026,5,15),E17),DATE(2026,5,15)))</f>
+        <f>IF(A17="","",IF(ISNUMBER(E17),MAX(DATE(2026,6,3),E17),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <f>IF(A18="","",IF(ISNUMBER(E18),MAX(DATE(2026,5,15),E18),DATE(2026,5,15)))</f>
+        <f>IF(A18="","",IF(ISNUMBER(E18),MAX(DATE(2026,6,3),E18),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="D19" s="5">
-        <f>IF(A19="","",IF(ISNUMBER(E19),MAX(DATE(2026,5,15),E19),DATE(2026,5,15)))</f>
+        <f>IF(A19="","",IF(ISNUMBER(E19),MAX(DATE(2026,6,3),E19),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D20" s="5">
-        <f>IF(A20="","",IF(ISNUMBER(E20),MAX(DATE(2026,5,15),E20),DATE(2026,5,15)))</f>
+        <f>IF(A20="","",IF(ISNUMBER(E20),MAX(DATE(2026,6,3),E20),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E20" s="5">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="D21" s="5">
-        <f>IF(A21="","",IF(ISNUMBER(E21),MAX(DATE(2026,5,15),E21),DATE(2026,5,15)))</f>
+        <f>IF(A21="","",IF(ISNUMBER(E21),MAX(DATE(2026,6,3),E21),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E21" s="5">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <f>IF(A22="","",IF(ISNUMBER(E22),MAX(DATE(2026,5,15),E22),DATE(2026,5,15)))</f>
+        <f>IF(A22="","",IF(ISNUMBER(E22),MAX(DATE(2026,6,3),E22),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E22" s="5">
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="D23" s="5">
-        <f>IF(A23="","",IF(ISNUMBER(E23),MAX(DATE(2026,5,15),E23),DATE(2026,5,15)))</f>
+        <f>IF(A23="","",IF(ISNUMBER(E23),MAX(DATE(2026,6,3),E23),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E23" s="5">
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <f>IF(A24="","",IF(ISNUMBER(E24),MAX(DATE(2026,5,15),E24),DATE(2026,5,15)))</f>
+        <f>IF(A24="","",IF(ISNUMBER(E24),MAX(DATE(2026,6,3),E24),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E24" s="5">
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>IF(A25="","",IF(ISNUMBER(E25),MAX(DATE(2026,5,15),E25),DATE(2026,5,15)))</f>
+        <f>IF(A25="","",IF(ISNUMBER(E25),MAX(DATE(2026,6,3),E25),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E25" s="5">
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="D26" s="5">
-        <f>IF(A26="","",IF(ISNUMBER(E26),MAX(DATE(2026,5,15),E26),DATE(2026,5,15)))</f>
+        <f>IF(A26="","",IF(ISNUMBER(E26),MAX(DATE(2026,6,3),E26),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E26" s="5">
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <f>IF(A27="","",IF(ISNUMBER(E27),MAX(DATE(2026,5,15),E27),DATE(2026,5,15)))</f>
+        <f>IF(A27="","",IF(ISNUMBER(E27),MAX(DATE(2026,6,3),E27),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E27" s="5">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <f>IF(A28="","",IF(ISNUMBER(E28),MAX(DATE(2026,5,15),E28),DATE(2026,5,15)))</f>
+        <f>IF(A28="","",IF(ISNUMBER(E28),MAX(DATE(2026,6,3),E28),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E28" s="5">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>IF(A29="","",IF(ISNUMBER(E29),MAX(DATE(2026,5,15),E29),DATE(2026,5,15)))</f>
+        <f>IF(A29="","",IF(ISNUMBER(E29),MAX(DATE(2026,6,3),E29),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E29" s="5">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>IF(A30="","",IF(ISNUMBER(E30),MAX(DATE(2026,5,15),E30),DATE(2026,5,15)))</f>
+        <f>IF(A30="","",IF(ISNUMBER(E30),MAX(DATE(2026,6,3),E30),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E30" s="5">
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="D31" s="5">
-        <f>IF(A31="","",IF(ISNUMBER(E31),MAX(DATE(2026,5,15),E31),DATE(2026,5,15)))</f>
+        <f>IF(A31="","",IF(ISNUMBER(E31),MAX(DATE(2026,6,3),E31),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E31" s="5">
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="D32" s="5">
-        <f>IF(A32="","",IF(ISNUMBER(E32),MAX(DATE(2026,5,15),E32),DATE(2026,5,15)))</f>
+        <f>IF(A32="","",IF(ISNUMBER(E32),MAX(DATE(2026,6,3),E32),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E32" s="5">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>IF(A33="","",IF(ISNUMBER(E33),MAX(DATE(2026,5,15),E33),DATE(2026,5,15)))</f>
+        <f>IF(A33="","",IF(ISNUMBER(E33),MAX(DATE(2026,6,3),E33),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E33" s="5">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <f>IF(A34="","",IF(ISNUMBER(E34),MAX(DATE(2026,5,15),E34),DATE(2026,5,15)))</f>
+        <f>IF(A34="","",IF(ISNUMBER(E34),MAX(DATE(2026,6,3),E34),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E34" s="5">
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="D35" s="5">
-        <f>IF(A35="","",IF(ISNUMBER(E35),MAX(DATE(2026,5,15),E35),DATE(2026,5,15)))</f>
+        <f>IF(A35="","",IF(ISNUMBER(E35),MAX(DATE(2026,6,3),E35),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E35" s="5">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="D36" s="5">
-        <f>IF(A36="","",IF(ISNUMBER(E36),MAX(DATE(2026,5,15),E36),DATE(2026,5,15)))</f>
+        <f>IF(A36="","",IF(ISNUMBER(E36),MAX(DATE(2026,6,3),E36),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E36" s="5">
@@ -5524,7 +5524,7 @@
         </is>
       </c>
       <c r="D37" s="5">
-        <f>IF(A37="","",IF(ISNUMBER(E37),MAX(DATE(2026,5,15),E37),DATE(2026,5,15)))</f>
+        <f>IF(A37="","",IF(ISNUMBER(E37),MAX(DATE(2026,6,3),E37),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E37" s="5">
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <f>IF(A38="","",IF(ISNUMBER(E38),MAX(DATE(2026,5,15),E38),DATE(2026,5,15)))</f>
+        <f>IF(A38="","",IF(ISNUMBER(E38),MAX(DATE(2026,6,3),E38),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E38" s="5">
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="D39" s="5">
-        <f>IF(A39="","",IF(ISNUMBER(E39),MAX(DATE(2026,5,15),E39),DATE(2026,5,15)))</f>
+        <f>IF(A39="","",IF(ISNUMBER(E39),MAX(DATE(2026,6,3),E39),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E39" s="5">
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="D40" s="5">
-        <f>IF(A40="","",IF(ISNUMBER(E40),MAX(DATE(2026,5,15),E40),DATE(2026,5,15)))</f>
+        <f>IF(A40="","",IF(ISNUMBER(E40),MAX(DATE(2026,6,3),E40),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E40" s="5">
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <f>IF(A41="","",IF(ISNUMBER(E41),MAX(DATE(2026,5,15),E41),DATE(2026,5,15)))</f>
+        <f>IF(A41="","",IF(ISNUMBER(E41),MAX(DATE(2026,6,3),E41),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E41" s="5">
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="D42" s="5">
-        <f>IF(A42="","",IF(ISNUMBER(E42),MAX(DATE(2026,5,15),E42),DATE(2026,5,15)))</f>
+        <f>IF(A42="","",IF(ISNUMBER(E42),MAX(DATE(2026,6,3),E42),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E42" s="5">
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="D43" s="5">
-        <f>IF(A43="","",IF(ISNUMBER(E43),MAX(DATE(2026,5,15),E43),DATE(2026,5,15)))</f>
+        <f>IF(A43="","",IF(ISNUMBER(E43),MAX(DATE(2026,6,3),E43),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E43" s="5">
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <f>IF(A44="","",IF(ISNUMBER(E44),MAX(DATE(2026,5,15),E44),DATE(2026,5,15)))</f>
+        <f>IF(A44="","",IF(ISNUMBER(E44),MAX(DATE(2026,6,3),E44),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E44" s="5">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="D45" s="5">
-        <f>IF(A45="","",IF(ISNUMBER(E45),MAX(DATE(2026,5,15),E45),DATE(2026,5,15)))</f>
+        <f>IF(A45="","",IF(ISNUMBER(E45),MAX(DATE(2026,6,3),E45),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E45" s="5">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="D46" s="5">
-        <f>IF(A46="","",IF(ISNUMBER(E46),MAX(DATE(2026,5,15),E46),DATE(2026,5,15)))</f>
+        <f>IF(A46="","",IF(ISNUMBER(E46),MAX(DATE(2026,6,3),E46),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E46" s="5">
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="D47" s="5">
-        <f>IF(A47="","",IF(ISNUMBER(E47),MAX(DATE(2026,5,15),E47),DATE(2026,5,15)))</f>
+        <f>IF(A47="","",IF(ISNUMBER(E47),MAX(DATE(2026,6,3),E47),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E47" s="5">
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="D48" s="5">
-        <f>IF(A48="","",IF(ISNUMBER(E48),MAX(DATE(2026,5,15),E48),DATE(2026,5,15)))</f>
+        <f>IF(A48="","",IF(ISNUMBER(E48),MAX(DATE(2026,6,3),E48),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E48" s="5">
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <f>IF(A49="","",IF(ISNUMBER(E49),MAX(DATE(2026,5,15),E49),DATE(2026,5,15)))</f>
+        <f>IF(A49="","",IF(ISNUMBER(E49),MAX(DATE(2026,6,3),E49),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E49" s="5">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="D50" s="5">
-        <f>IF(A50="","",IF(ISNUMBER(E50),MAX(DATE(2026,5,15),E50),DATE(2026,5,15)))</f>
+        <f>IF(A50="","",IF(ISNUMBER(E50),MAX(DATE(2026,6,3),E50),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E50" s="5">
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="D54" s="5">
-        <f>IF(A54="","",IF(ISNUMBER(E54),MAX(DATE(2026,5,15),E54),DATE(2026,5,15)))</f>
+        <f>IF(A54="","",IF(ISNUMBER(E54),MAX(DATE(2026,6,3),E54),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E54" s="5">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="D56" s="5">
-        <f>IF(A56="","",IF(ISNUMBER(E56),MAX(DATE(2026,5,15),E56),DATE(2026,5,15)))</f>
+        <f>IF(A56="","",IF(ISNUMBER(E56),MAX(DATE(2026,6,3),E56),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E56" s="5">
@@ -8216,7 +8216,7 @@
         </is>
       </c>
       <c r="D57" s="5">
-        <f>IF(A57="","",IF(ISNUMBER(E57),MAX(DATE(2026,5,15),E57),DATE(2026,5,15)))</f>
+        <f>IF(A57="","",IF(ISNUMBER(E57),MAX(DATE(2026,6,3),E57),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E57" s="5">
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="D58" s="5">
-        <f>IF(A58="","",IF(ISNUMBER(E58),MAX(DATE(2026,5,15),E58),DATE(2026,5,15)))</f>
+        <f>IF(A58="","",IF(ISNUMBER(E58),MAX(DATE(2026,6,3),E58),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E58" s="5">
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="D59" s="5">
-        <f>IF(A59="","",IF(ISNUMBER(E59),MAX(DATE(2026,5,15),E59),DATE(2026,5,15)))</f>
+        <f>IF(A59="","",IF(ISNUMBER(E59),MAX(DATE(2026,6,3),E59),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E59" s="5">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <f>IF(A60="","",IF(ISNUMBER(E60),MAX(DATE(2026,5,15),E60),DATE(2026,5,15)))</f>
+        <f>IF(A60="","",IF(ISNUMBER(E60),MAX(DATE(2026,6,3),E60),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E60" s="5">
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="D61" s="5">
-        <f>IF(A61="","",IF(ISNUMBER(E61),MAX(DATE(2026,5,15),E61),DATE(2026,5,15)))</f>
+        <f>IF(A61="","",IF(ISNUMBER(E61),MAX(DATE(2026,6,3),E61),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E61" s="5">
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <f>IF(A62="","",IF(ISNUMBER(E62),MAX(DATE(2026,5,15),E62),DATE(2026,5,15)))</f>
+        <f>IF(A62="","",IF(ISNUMBER(E62),MAX(DATE(2026,6,3),E62),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E62" s="5">
@@ -9026,7 +9026,7 @@
         </is>
       </c>
       <c r="D63" s="5">
-        <f>IF(A63="","",IF(ISNUMBER(E63),MAX(DATE(2026,5,15),E63),DATE(2026,5,15)))</f>
+        <f>IF(A63="","",IF(ISNUMBER(E63),MAX(DATE(2026,6,3),E63),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E63" s="5">
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <f>IF(A64="","",IF(ISNUMBER(E64),MAX(DATE(2026,5,15),E64),DATE(2026,5,15)))</f>
+        <f>IF(A64="","",IF(ISNUMBER(E64),MAX(DATE(2026,6,3),E64),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E64" s="5">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="D65" s="5">
-        <f>IF(A65="","",IF(ISNUMBER(E65),MAX(DATE(2026,5,15),E65),DATE(2026,5,15)))</f>
+        <f>IF(A65="","",IF(ISNUMBER(E65),MAX(DATE(2026,6,3),E65),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E65" s="5">
@@ -10362,7 +10362,7 @@
         </is>
       </c>
       <c r="D73" s="5">
-        <f>IF(A73="","",IF(ISNUMBER(E73),MAX(DATE(2026,5,15),E73),DATE(2026,5,15)))</f>
+        <f>IF(A73="","",IF(ISNUMBER(E73),MAX(DATE(2026,6,3),E73),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E73" s="5">
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="D74" s="5">
-        <f>IF(A74="","",IF(ISNUMBER(E74),MAX(DATE(2026,5,15),E74),DATE(2026,5,15)))</f>
+        <f>IF(A74="","",IF(ISNUMBER(E74),MAX(DATE(2026,6,3),E74),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E74" s="5">
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="D75" s="5">
-        <f>IF(A75="","",IF(ISNUMBER(E75),MAX(DATE(2026,5,15),E75),DATE(2026,5,15)))</f>
+        <f>IF(A75="","",IF(ISNUMBER(E75),MAX(DATE(2026,6,3),E75),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E75" s="5">
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="D76" s="5">
-        <f>IF(A76="","",IF(ISNUMBER(E76),MAX(DATE(2026,5,15),E76),DATE(2026,5,15)))</f>
+        <f>IF(A76="","",IF(ISNUMBER(E76),MAX(DATE(2026,6,3),E76),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E76" s="5">
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="D77" s="5">
-        <f>IF(A77="","",IF(ISNUMBER(E77),MAX(DATE(2026,5,15),E77),DATE(2026,5,15)))</f>
+        <f>IF(A77="","",IF(ISNUMBER(E77),MAX(DATE(2026,6,3),E77),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E77" s="5">
@@ -11037,7 +11037,7 @@
         </is>
       </c>
       <c r="D78" s="5">
-        <f>IF(A78="","",IF(ISNUMBER(E78),MAX(DATE(2026,5,15),E78),DATE(2026,5,15)))</f>
+        <f>IF(A78="","",IF(ISNUMBER(E78),MAX(DATE(2026,6,3),E78),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E78" s="5">
@@ -11172,7 +11172,7 @@
         </is>
       </c>
       <c r="D79" s="5">
-        <f>IF(A79="","",IF(ISNUMBER(E79),MAX(DATE(2026,5,15),E79),DATE(2026,5,15)))</f>
+        <f>IF(A79="","",IF(ISNUMBER(E79),MAX(DATE(2026,6,3),E79),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E79" s="5">
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="D80" s="5">
-        <f>IF(A80="","",IF(ISNUMBER(E80),MAX(DATE(2026,5,15),E80),DATE(2026,5,15)))</f>
+        <f>IF(A80="","",IF(ISNUMBER(E80),MAX(DATE(2026,6,3),E80),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E80" s="5">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="D81" s="5">
-        <f>IF(A81="","",IF(ISNUMBER(E81),MAX(DATE(2026,5,15),E81),DATE(2026,5,15)))</f>
+        <f>IF(A81="","",IF(ISNUMBER(E81),MAX(DATE(2026,6,3),E81),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E81" s="5">
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="D82" s="5">
-        <f>IF(A82="","",IF(ISNUMBER(E82),MAX(DATE(2026,5,15),E82),DATE(2026,5,15)))</f>
+        <f>IF(A82="","",IF(ISNUMBER(E82),MAX(DATE(2026,6,3),E82),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E82" s="5">
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="D83" s="5">
-        <f>IF(A83="","",IF(ISNUMBER(E83),MAX(DATE(2026,5,15),E83),DATE(2026,5,15)))</f>
+        <f>IF(A83="","",IF(ISNUMBER(E83),MAX(DATE(2026,6,3),E83),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E83" s="5">
@@ -11847,7 +11847,7 @@
         </is>
       </c>
       <c r="D84" s="5">
-        <f>IF(A84="","",IF(ISNUMBER(E84),MAX(DATE(2026,5,15),E84),DATE(2026,5,15)))</f>
+        <f>IF(A84="","",IF(ISNUMBER(E84),MAX(DATE(2026,6,3),E84),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E84" s="5">
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="D85" s="5">
-        <f>IF(A85="","",IF(ISNUMBER(E85),MAX(DATE(2026,5,15),E85),DATE(2026,5,15)))</f>
+        <f>IF(A85="","",IF(ISNUMBER(E85),MAX(DATE(2026,6,3),E85),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E85" s="5">
@@ -12117,7 +12117,7 @@
         </is>
       </c>
       <c r="D86" s="5">
-        <f>IF(A86="","",IF(ISNUMBER(E86),MAX(DATE(2026,5,15),E86),DATE(2026,5,15)))</f>
+        <f>IF(A86="","",IF(ISNUMBER(E86),MAX(DATE(2026,6,3),E86),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E86" s="5">
@@ -12252,7 +12252,7 @@
         </is>
       </c>
       <c r="D87" s="5">
-        <f>IF(A87="","",IF(ISNUMBER(E87),MAX(DATE(2026,5,15),E87),DATE(2026,5,15)))</f>
+        <f>IF(A87="","",IF(ISNUMBER(E87),MAX(DATE(2026,6,3),E87),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E87" s="5">
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="D88" s="5">
-        <f>IF(A88="","",IF(ISNUMBER(E88),MAX(DATE(2026,5,15),E88),DATE(2026,5,15)))</f>
+        <f>IF(A88="","",IF(ISNUMBER(E88),MAX(DATE(2026,6,3),E88),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E88" s="5">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <f>IF(A89="","",IF(ISNUMBER(E89),MAX(DATE(2026,5,15),E89),DATE(2026,5,15)))</f>
+        <f>IF(A89="","",IF(ISNUMBER(E89),MAX(DATE(2026,6,3),E89),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E89" s="5">
@@ -13197,7 +13197,7 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <f>IF(A94="","",IF(ISNUMBER(E94),MAX(DATE(2026,5,15),E94),DATE(2026,5,15)))</f>
+        <f>IF(A94="","",IF(ISNUMBER(E94),MAX(DATE(2026,6,3),E94),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E94" s="5">
@@ -13332,7 +13332,7 @@
         </is>
       </c>
       <c r="D95" s="5">
-        <f>IF(A95="","",IF(ISNUMBER(E95),MAX(DATE(2026,5,15),E95),DATE(2026,5,15)))</f>
+        <f>IF(A95="","",IF(ISNUMBER(E95),MAX(DATE(2026,6,3),E95),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E95" s="5">
@@ -13467,7 +13467,7 @@
         </is>
       </c>
       <c r="D96" s="5">
-        <f>IF(A96="","",IF(ISNUMBER(E96),MAX(DATE(2026,5,15),E96),DATE(2026,5,15)))</f>
+        <f>IF(A96="","",IF(ISNUMBER(E96),MAX(DATE(2026,6,3),E96),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E96" s="5">
@@ -14007,7 +14007,7 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <f>IF(A100="","",IF(ISNUMBER(E100),MAX(DATE(2026,5,15),E100),DATE(2026,5,15)))</f>
+        <f>IF(A100="","",IF(ISNUMBER(E100),MAX(DATE(2026,6,3),E100),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E100" s="5">
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="D122" s="5">
-        <f>IF(A122="","",IF(ISNUMBER(E122),MAX(DATE(2026,5,15),E122),DATE(2026,5,15)))</f>
+        <f>IF(A122="","",IF(ISNUMBER(E122),MAX(DATE(2026,6,3),E122),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E122" s="5">
@@ -17070,7 +17070,7 @@
         </is>
       </c>
       <c r="D123" s="5">
-        <f>IF(A123="","",IF(ISNUMBER(E123),MAX(DATE(2026,5,15),E123),DATE(2026,5,15)))</f>
+        <f>IF(A123="","",IF(ISNUMBER(E123),MAX(DATE(2026,6,3),E123),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E123" s="5">
@@ -29563,7 +29563,7 @@
     <row r="218" ht="110" customHeight="1">
       <c r="A218" s="8" t="inlineStr">
         <is>
-          <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 15.05.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 15.05.2026; a RETEST is dated at its own sampling day and issued on its campaign's day (sampling_dates.py, owner 15.09.2026: Tranche 1 sampled 21–24.07.2026 and issued 27.07.2026, Tranche 2 sampled 12–14.08.2026 and issued 17.08.2026, Tranche 3 sampled 19–21.08.2026 and issued 24.08.2026, each batch on the day its certificate number falls), which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. A round whose packaging date the list does not hold is numbered all the same (owner, 15.09.2026: identification A, B and foreign matter are performed on every batch) and says its testing date is not stated. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
+          <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 03.06.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 03.06.2026; a RETEST is dated at its own sampling day and issued on its campaign's day (sampling_dates.py, owner 15.09.2026: Tranche 1 sampled 21–24.07.2026 and issued 27.07.2026, Tranche 2 sampled 12–14.08.2026 and issued 17.08.2026, Tranche 3 sampled 19–21.08.2026 and issued 24.08.2026, each batch on the day its certificate number falls), which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. A round whose packaging date the list does not hold is numbered all the same (owner, 15.09.2026: identification A, B and foreign matter are performed on every batch) and says its testing date is not stated. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
         </is>
       </c>
     </row>
@@ -29784,7 +29784,7 @@
         <v/>
       </c>
       <c r="E2" s="5">
-        <f>IF(ISNUMBER(F2),MAX(DATE(2026,5,27),F2+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F2),MAX(DATE(2026,6,6),F2+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F2" s="5" t="n">
@@ -29855,7 +29855,7 @@
       </c>
       <c r="T2" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -29917,7 +29917,7 @@
         <v/>
       </c>
       <c r="E3" s="5">
-        <f>IF(ISNUMBER(F3),MAX(DATE(2026,5,27),F3+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F3),MAX(DATE(2026,6,6),F3+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F3" s="5" t="n">
@@ -29988,7 +29988,7 @@
       </c>
       <c r="T3" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -30050,7 +30050,7 @@
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>IF(ISNUMBER(F4),MAX(DATE(2026,5,27),F4+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F4),MAX(DATE(2026,6,6),F4+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F4" s="5" t="n">
@@ -30121,7 +30121,7 @@
       </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -30183,7 +30183,7 @@
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>IF(ISNUMBER(F5),MAX(DATE(2026,5,27),F5+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F5),MAX(DATE(2026,6,6),F5+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -30324,7 +30324,7 @@
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>IF(ISNUMBER(F6),MAX(DATE(2026,5,27),F6+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F6),MAX(DATE(2026,6,6),F6+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -30397,7 +30397,7 @@
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -30459,7 +30459,7 @@
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>IF(ISNUMBER(F7),MAX(DATE(2026,5,27),F7+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F7),MAX(DATE(2026,6,6),F7+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -30594,7 +30594,7 @@
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>IF(ISNUMBER(F8),MAX(DATE(2026,5,27),F8+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F8),MAX(DATE(2026,6,6),F8+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F8" s="5" t="n">
@@ -30665,7 +30665,7 @@
       </c>
       <c r="T8" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -30727,7 +30727,7 @@
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>IF(ISNUMBER(F9),MAX(DATE(2026,5,27),F9+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F9),MAX(DATE(2026,6,6),F9+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F9" s="5" t="n">
@@ -30798,7 +30798,7 @@
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -30860,7 +30860,7 @@
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>IF(ISNUMBER(F10),MAX(DATE(2026,5,27),F10+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F10),MAX(DATE(2026,6,6),F10+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F10" s="5" t="n">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -30993,7 +30993,7 @@
         <v/>
       </c>
       <c r="E11" s="5">
-        <f>IF(ISNUMBER(F11),MAX(DATE(2026,5,27),F11+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F11),MAX(DATE(2026,6,6),F11+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F11" s="5" t="n">
@@ -31064,7 +31064,7 @@
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -31126,7 +31126,7 @@
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>IF(ISNUMBER(F12),MAX(DATE(2026,5,27),F12+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F12),MAX(DATE(2026,6,6),F12+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F12" s="5" t="n">
@@ -31197,7 +31197,7 @@
       </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -31259,7 +31259,7 @@
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>IF(ISNUMBER(F13),MAX(DATE(2026,5,27),F13+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F13),MAX(DATE(2026,6,6),F13+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F13" s="5" t="n">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -31392,7 +31392,7 @@
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>IF(ISNUMBER(F14),MAX(DATE(2026,5,27),F14+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F14),MAX(DATE(2026,6,6),F14+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F14" s="5" t="n">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -31525,7 +31525,7 @@
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>IF(ISNUMBER(F15),MAX(DATE(2026,5,27),F15+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F15),MAX(DATE(2026,6,6),F15+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F15" s="5" t="n">
@@ -31596,7 +31596,7 @@
       </c>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -31658,7 +31658,7 @@
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>IF(ISNUMBER(F16),MAX(DATE(2026,5,27),F16+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F16),MAX(DATE(2026,6,6),F16+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F16" s="5" t="n">
@@ -31729,7 +31729,7 @@
       </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -31791,7 +31791,7 @@
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>IF(ISNUMBER(F17),MAX(DATE(2026,5,27),F17+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F17),MAX(DATE(2026,6,6),F17+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F17" s="5" t="n">
@@ -31862,7 +31862,7 @@
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -31924,7 +31924,7 @@
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>IF(ISNUMBER(F18),MAX(DATE(2026,5,27),F18+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F18),MAX(DATE(2026,6,6),F18+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F18" s="5" t="n">
@@ -31995,7 +31995,7 @@
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -32057,7 +32057,7 @@
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>IF(ISNUMBER(F19),MAX(DATE(2026,5,27),F19+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F19),MAX(DATE(2026,6,6),F19+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F19" s="5" t="n">
@@ -32128,7 +32128,7 @@
       </c>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -32190,7 +32190,7 @@
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>IF(ISNUMBER(F20),MAX(DATE(2026,5,27),F20+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F20),MAX(DATE(2026,6,6),F20+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F20" s="5" t="n">
@@ -32261,7 +32261,7 @@
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -32323,7 +32323,7 @@
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>IF(ISNUMBER(F21),MAX(DATE(2026,5,27),F21+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F21),MAX(DATE(2026,6,6),F21+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F21" s="5" t="n">
@@ -32394,7 +32394,7 @@
       </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -32456,7 +32456,7 @@
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>IF(ISNUMBER(F22),MAX(DATE(2026,5,27),F22+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F22),MAX(DATE(2026,6,6),F22+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -32529,7 +32529,7 @@
       </c>
       <c r="T22" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -32597,7 +32597,7 @@
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>IF(ISNUMBER(F23),MAX(DATE(2026,5,27),F23+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F23),MAX(DATE(2026,6,6),F23+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F23" s="5" t="n">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -32730,7 +32730,7 @@
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>IF(ISNUMBER(F24),MAX(DATE(2026,5,27),F24+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F24),MAX(DATE(2026,6,6),F24+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F24" s="5" t="n">
@@ -32801,7 +32801,7 @@
       </c>
       <c r="T24" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -32863,7 +32863,7 @@
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>IF(ISNUMBER(F25),MAX(DATE(2026,5,27),F25+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F25),MAX(DATE(2026,6,6),F25+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n">
@@ -32934,7 +32934,7 @@
       </c>
       <c r="T25" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -32996,7 +32996,7 @@
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>IF(ISNUMBER(F26),MAX(DATE(2026,5,27),F26+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F26),MAX(DATE(2026,6,6),F26+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F26" s="5" t="n">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="T26" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -33129,7 +33129,7 @@
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>IF(ISNUMBER(F27),MAX(DATE(2026,5,27),F27+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F27),MAX(DATE(2026,6,6),F27+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F27" s="5" t="n">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="T27" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -33262,7 +33262,7 @@
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>IF(ISNUMBER(F28),MAX(DATE(2026,5,27),F28+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F28),MAX(DATE(2026,6,6),F28+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F28" s="5" t="n">
@@ -33333,7 +33333,7 @@
       </c>
       <c r="T28" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -33395,7 +33395,7 @@
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>IF(ISNUMBER(F29),MAX(DATE(2026,5,27),F29+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F29),MAX(DATE(2026,6,6),F29+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F29" s="5" t="n">
@@ -33466,7 +33466,7 @@
       </c>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -33528,7 +33528,7 @@
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>IF(ISNUMBER(F30),MAX(DATE(2026,5,27),F30+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F30),MAX(DATE(2026,6,6),F30+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F30" s="5" t="n">
@@ -33599,7 +33599,7 @@
       </c>
       <c r="T30" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -33661,7 +33661,7 @@
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>IF(ISNUMBER(F31),MAX(DATE(2026,5,27),F31+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F31),MAX(DATE(2026,6,6),F31+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F31" s="5" t="n">
@@ -33732,7 +33732,7 @@
       </c>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -33794,7 +33794,7 @@
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>IF(ISNUMBER(F32),MAX(DATE(2026,5,27),F32+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F32),MAX(DATE(2026,6,6),F32+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F32" s="5" t="n">
@@ -33865,7 +33865,7 @@
       </c>
       <c r="T32" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -33927,7 +33927,7 @@
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>IF(ISNUMBER(F33),MAX(DATE(2026,5,27),F33+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F33),MAX(DATE(2026,6,6),F33+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F33" s="5" t="n">
@@ -33998,7 +33998,7 @@
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -34060,7 +34060,7 @@
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>IF(ISNUMBER(F34),MAX(DATE(2026,5,27),F34+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F34),MAX(DATE(2026,6,6),F34+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F34" s="5" t="n">
@@ -34131,7 +34131,7 @@
       </c>
       <c r="T34" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -34193,7 +34193,7 @@
         <v/>
       </c>
       <c r="E35" s="5">
-        <f>IF(ISNUMBER(F35),MAX(DATE(2026,5,27),F35+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F35),MAX(DATE(2026,6,6),F35+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F35" s="5" t="n">
@@ -34264,7 +34264,7 @@
       </c>
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -34326,7 +34326,7 @@
         <v/>
       </c>
       <c r="E36" s="5">
-        <f>IF(ISNUMBER(F36),MAX(DATE(2026,5,27),F36+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F36),MAX(DATE(2026,6,6),F36+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F36" s="5" t="n">
@@ -34397,7 +34397,7 @@
       </c>
       <c r="T36" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -34459,7 +34459,7 @@
         <v/>
       </c>
       <c r="E37" s="5">
-        <f>IF(ISNUMBER(F37),MAX(DATE(2026,5,27),F37+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F37),MAX(DATE(2026,6,6),F37+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F37" s="5" t="n">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -34592,7 +34592,7 @@
         <v/>
       </c>
       <c r="E38" s="5">
-        <f>IF(ISNUMBER(F38),MAX(DATE(2026,5,27),F38+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F38),MAX(DATE(2026,6,6),F38+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F38" s="5" t="n">
@@ -34663,7 +34663,7 @@
       </c>
       <c r="T38" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -34725,7 +34725,7 @@
         <v/>
       </c>
       <c r="E39" s="5">
-        <f>IF(ISNUMBER(F39),MAX(DATE(2026,5,27),F39+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F39),MAX(DATE(2026,6,6),F39+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F39" s="5" t="n">
@@ -34796,7 +34796,7 @@
       </c>
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -34858,7 +34858,7 @@
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>IF(ISNUMBER(F40),MAX(DATE(2026,5,27),F40+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F40),MAX(DATE(2026,6,6),F40+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F40" s="5" t="n">
@@ -34929,7 +34929,7 @@
       </c>
       <c r="T40" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -34991,7 +34991,7 @@
         <v/>
       </c>
       <c r="E41" s="5">
-        <f>IF(ISNUMBER(F41),MAX(DATE(2026,5,27),F41+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F41),MAX(DATE(2026,6,6),F41+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F41" s="5" t="n">
@@ -35062,7 +35062,7 @@
       </c>
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -35124,7 +35124,7 @@
         <v/>
       </c>
       <c r="E42" s="5">
-        <f>IF(ISNUMBER(F42),MAX(DATE(2026,5,27),F42+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F42),MAX(DATE(2026,6,6),F42+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F42" s="5" t="n">
@@ -35195,7 +35195,7 @@
       </c>
       <c r="T42" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -35257,7 +35257,7 @@
         <v/>
       </c>
       <c r="E43" s="5">
-        <f>IF(ISNUMBER(F43),MAX(DATE(2026,5,27),F43+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F43),MAX(DATE(2026,6,6),F43+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F43" s="5" t="n">
@@ -35328,7 +35328,7 @@
       </c>
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -35390,7 +35390,7 @@
         <v/>
       </c>
       <c r="E44" s="5">
-        <f>IF(ISNUMBER(F44),MAX(DATE(2026,5,27),F44+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F44),MAX(DATE(2026,6,6),F44+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F44" s="5" t="n">
@@ -35461,7 +35461,7 @@
       </c>
       <c r="T44" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -35523,7 +35523,7 @@
         <v/>
       </c>
       <c r="E45" s="5">
-        <f>IF(ISNUMBER(F45),MAX(DATE(2026,5,27),F45+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F45),MAX(DATE(2026,6,6),F45+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F45" s="5" t="n">
@@ -35594,7 +35594,7 @@
       </c>
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -35656,7 +35656,7 @@
         <v/>
       </c>
       <c r="E46" s="5">
-        <f>IF(ISNUMBER(F46),MAX(DATE(2026,5,27),F46+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F46),MAX(DATE(2026,6,6),F46+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F46" s="5" t="n">
@@ -35727,7 +35727,7 @@
       </c>
       <c r="T46" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -35789,7 +35789,7 @@
         <v/>
       </c>
       <c r="E47" s="5">
-        <f>IF(ISNUMBER(F47),MAX(DATE(2026,5,27),F47+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F47),MAX(DATE(2026,6,6),F47+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F47" s="5" t="n">
@@ -35860,7 +35860,7 @@
       </c>
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -35928,7 +35928,7 @@
         <v/>
       </c>
       <c r="E48" s="5">
-        <f>IF(ISNUMBER(F48),MAX(DATE(2026,5,27),F48+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F48),MAX(DATE(2026,6,6),F48+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -36001,7 +36001,7 @@
       </c>
       <c r="T48" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -36069,7 +36069,7 @@
         <v/>
       </c>
       <c r="E49" s="5">
-        <f>IF(ISNUMBER(F49),MAX(DATE(2026,5,27),F49+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F49),MAX(DATE(2026,6,6),F49+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -36142,7 +36142,7 @@
       </c>
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -36210,7 +36210,7 @@
         <v/>
       </c>
       <c r="E50" s="5">
-        <f>IF(ISNUMBER(F50),MAX(DATE(2026,5,27),F50+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F50),MAX(DATE(2026,6,6),F50+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -36283,7 +36283,7 @@
       </c>
       <c r="T50" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -36351,7 +36351,7 @@
         <v/>
       </c>
       <c r="E51" s="5">
-        <f>IF(ISNUMBER(F51),MAX(DATE(2026,5,27),F51+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F51),MAX(DATE(2026,6,6),F51+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -36424,7 +36424,7 @@
       </c>
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -36492,7 +36492,7 @@
         <v/>
       </c>
       <c r="E52" s="5">
-        <f>IF(ISNUMBER(F52),MAX(DATE(2026,5,27),F52+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F52),MAX(DATE(2026,6,6),F52+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F52" s="5" t="n">
@@ -36563,7 +36563,7 @@
       </c>
       <c r="T52" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -36625,7 +36625,7 @@
         <v/>
       </c>
       <c r="E53" s="5">
-        <f>IF(ISNUMBER(F53),MAX(DATE(2026,5,27),F53+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F53),MAX(DATE(2026,6,6),F53+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F53" s="5" t="n">
@@ -36696,7 +36696,7 @@
       </c>
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -36758,7 +36758,7 @@
         <v/>
       </c>
       <c r="E54" s="5">
-        <f>IF(ISNUMBER(F54),MAX(DATE(2026,5,27),F54+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F54),MAX(DATE(2026,6,6),F54+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F54" s="5" t="n">
@@ -36829,7 +36829,7 @@
       </c>
       <c r="T54" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -36891,7 +36891,7 @@
         <v/>
       </c>
       <c r="E55" s="5">
-        <f>IF(ISNUMBER(F55),MAX(DATE(2026,5,27),F55+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F55),MAX(DATE(2026,6,6),F55+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F55" s="5" t="n">
@@ -36962,7 +36962,7 @@
       </c>
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -37024,7 +37024,7 @@
         <v/>
       </c>
       <c r="E56" s="5">
-        <f>IF(ISNUMBER(F56),MAX(DATE(2026,5,27),F56+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F56),MAX(DATE(2026,6,6),F56+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F56" s="5" t="n">
@@ -37095,7 +37095,7 @@
       </c>
       <c r="T56" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -37157,7 +37157,7 @@
         <v/>
       </c>
       <c r="E57" s="5">
-        <f>IF(ISNUMBER(F57),MAX(DATE(2026,5,27),F57+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F57),MAX(DATE(2026,6,6),F57+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F57" s="5" t="n">
@@ -37228,7 +37228,7 @@
       </c>
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -37290,7 +37290,7 @@
         <v/>
       </c>
       <c r="E58" s="5">
-        <f>IF(ISNUMBER(F58),MAX(DATE(2026,5,27),F58+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F58),MAX(DATE(2026,6,6),F58+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F58" s="5" t="n">
@@ -37361,7 +37361,7 @@
       </c>
       <c r="T58" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -37423,7 +37423,7 @@
         <v/>
       </c>
       <c r="E59" s="5">
-        <f>IF(ISNUMBER(F59),MAX(DATE(2026,5,27),F59+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F59),MAX(DATE(2026,6,6),F59+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F59" s="5" t="n">
@@ -37494,7 +37494,7 @@
       </c>
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -37556,7 +37556,7 @@
         <v/>
       </c>
       <c r="E60" s="5">
-        <f>IF(ISNUMBER(F60),MAX(DATE(2026,5,27),F60+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F60),MAX(DATE(2026,6,6),F60+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F60" s="5" t="n">
@@ -37627,7 +37627,7 @@
       </c>
       <c r="T60" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -37689,7 +37689,7 @@
         <v/>
       </c>
       <c r="E61" s="5">
-        <f>IF(ISNUMBER(F61),MAX(DATE(2026,5,27),F61+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F61),MAX(DATE(2026,6,6),F61+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F61" s="5" t="n">
@@ -37760,7 +37760,7 @@
       </c>
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -37822,7 +37822,7 @@
         <v/>
       </c>
       <c r="E62" s="5">
-        <f>IF(ISNUMBER(F62),MAX(DATE(2026,5,27),F62+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F62),MAX(DATE(2026,6,6),F62+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F62" s="5" t="n">
@@ -37893,7 +37893,7 @@
       </c>
       <c r="T62" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -37955,7 +37955,7 @@
         <v/>
       </c>
       <c r="E63" s="5">
-        <f>IF(ISNUMBER(F63),MAX(DATE(2026,5,27),F63+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F63),MAX(DATE(2026,6,6),F63+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F63" s="5" t="n">
@@ -38088,7 +38088,7 @@
         <v/>
       </c>
       <c r="E64" s="5">
-        <f>IF(ISNUMBER(F64),MAX(DATE(2026,5,27),F64+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F64),MAX(DATE(2026,6,6),F64+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F64" s="5" t="n">
@@ -38221,7 +38221,7 @@
         <v/>
       </c>
       <c r="E65" s="5">
-        <f>IF(ISNUMBER(F65),MAX(DATE(2026,5,27),F65+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F65),MAX(DATE(2026,6,6),F65+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F65" s="5" t="n">
@@ -38354,7 +38354,7 @@
         <v/>
       </c>
       <c r="E66" s="5">
-        <f>IF(ISNUMBER(F66),MAX(DATE(2026,5,27),F66+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F66),MAX(DATE(2026,6,6),F66+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F66" s="5" t="n">
@@ -38487,7 +38487,7 @@
         <v/>
       </c>
       <c r="E67" s="5">
-        <f>IF(ISNUMBER(F67),MAX(DATE(2026,5,27),F67+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F67),MAX(DATE(2026,6,6),F67+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F67" s="5" t="n">
@@ -38620,7 +38620,7 @@
         <v/>
       </c>
       <c r="E68" s="5">
-        <f>IF(ISNUMBER(F68),MAX(DATE(2026,5,27),F68+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F68),MAX(DATE(2026,6,6),F68+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F68" s="5" t="n">
@@ -38753,7 +38753,7 @@
         <v/>
       </c>
       <c r="E69" s="5">
-        <f>IF(ISNUMBER(F69),MAX(DATE(2026,5,27),F69+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F69),MAX(DATE(2026,6,6),F69+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -38890,7 +38890,7 @@
         <v/>
       </c>
       <c r="E70" s="5">
-        <f>IF(ISNUMBER(F70),MAX(DATE(2026,5,27),F70+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F70),MAX(DATE(2026,6,6),F70+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F70" s="5" t="n">
@@ -39023,7 +39023,7 @@
         <v/>
       </c>
       <c r="E71" s="5">
-        <f>IF(ISNUMBER(F71),MAX(DATE(2026,5,27),F71+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F71),MAX(DATE(2026,6,6),F71+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -39164,7 +39164,7 @@
         <v/>
       </c>
       <c r="E72" s="5">
-        <f>IF(ISNUMBER(F72),MAX(DATE(2026,5,27),F72+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F72),MAX(DATE(2026,6,6),F72+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -39305,7 +39305,7 @@
         <v/>
       </c>
       <c r="E73" s="5">
-        <f>IF(ISNUMBER(F73),MAX(DATE(2026,5,27),F73+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F73),MAX(DATE(2026,6,6),F73+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -39446,7 +39446,7 @@
         <v/>
       </c>
       <c r="E74" s="5">
-        <f>IF(ISNUMBER(F74),MAX(DATE(2026,5,27),F74+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F74),MAX(DATE(2026,6,6),F74+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -39587,7 +39587,7 @@
         <v/>
       </c>
       <c r="E75" s="5">
-        <f>IF(ISNUMBER(F75),MAX(DATE(2026,5,27),F75+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F75),MAX(DATE(2026,6,6),F75+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -39728,7 +39728,7 @@
         <v/>
       </c>
       <c r="E76" s="5">
-        <f>IF(ISNUMBER(F76),MAX(DATE(2026,5,27),F76+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F76),MAX(DATE(2026,6,6),F76+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F76" s="5" t="n">
@@ -39861,7 +39861,7 @@
         <v/>
       </c>
       <c r="E77" s="5">
-        <f>IF(ISNUMBER(F77),MAX(DATE(2026,5,27),F77+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F77),MAX(DATE(2026,6,6),F77+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F77" s="5" t="n">
@@ -39994,7 +39994,7 @@
         <v/>
       </c>
       <c r="E78" s="5">
-        <f>IF(ISNUMBER(F78),MAX(DATE(2026,5,27),F78+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F78),MAX(DATE(2026,6,6),F78+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F78" s="5" t="n">
@@ -40127,7 +40127,7 @@
         <v/>
       </c>
       <c r="E79" s="5">
-        <f>IF(ISNUMBER(F79),MAX(DATE(2026,5,27),F79+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F79),MAX(DATE(2026,6,6),F79+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F79" s="5" t="n">
@@ -40260,7 +40260,7 @@
         <v/>
       </c>
       <c r="E80" s="5">
-        <f>IF(ISNUMBER(F80),MAX(DATE(2026,5,27),F80+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F80),MAX(DATE(2026,6,6),F80+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F80" s="5" t="n">
@@ -40393,7 +40393,7 @@
         <v/>
       </c>
       <c r="E81" s="5">
-        <f>IF(ISNUMBER(F81),MAX(DATE(2026,5,27),F81+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F81),MAX(DATE(2026,6,6),F81+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F81" s="5" t="n">
@@ -40526,7 +40526,7 @@
         <v/>
       </c>
       <c r="E82" s="5">
-        <f>IF(ISNUMBER(F82),MAX(DATE(2026,5,27),F82+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F82),MAX(DATE(2026,6,6),F82+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F82" s="5" t="n">
@@ -40659,7 +40659,7 @@
         <v/>
       </c>
       <c r="E83" s="5">
-        <f>IF(ISNUMBER(F83),MAX(DATE(2026,5,27),F83+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F83),MAX(DATE(2026,6,6),F83+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F83" s="5" t="n">
@@ -40792,7 +40792,7 @@
         <v/>
       </c>
       <c r="E84" s="5">
-        <f>IF(ISNUMBER(F84),MAX(DATE(2026,5,27),F84+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F84),MAX(DATE(2026,6,6),F84+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F84" s="5" t="n">
@@ -40925,7 +40925,7 @@
         <v/>
       </c>
       <c r="E85" s="5">
-        <f>IF(ISNUMBER(F85),MAX(DATE(2026,5,27),F85+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F85),MAX(DATE(2026,6,6),F85+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -41066,7 +41066,7 @@
         <v/>
       </c>
       <c r="E86" s="5">
-        <f>IF(ISNUMBER(F86),MAX(DATE(2026,5,27),F86+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F86),MAX(DATE(2026,6,6),F86+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F86" s="5" t="n">
@@ -41198,7 +41198,7 @@
         <v/>
       </c>
       <c r="E87" s="5">
-        <f>IF(ISNUMBER(F87),MAX(DATE(2026,5,27),F87+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F87),MAX(DATE(2026,6,6),F87+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F87" s="5" t="n">
@@ -41330,7 +41330,7 @@
         <v/>
       </c>
       <c r="E88" s="5">
-        <f>IF(ISNUMBER(F88),MAX(DATE(2026,5,27),F88+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F88),MAX(DATE(2026,6,6),F88+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F88" s="5" t="n">
@@ -41458,7 +41458,7 @@
         <v/>
       </c>
       <c r="E89" s="5">
-        <f>IF(ISNUMBER(F89),MAX(DATE(2026,5,27),F89+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F89),MAX(DATE(2026,6,6),F89+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F89" s="5" t="n">
@@ -41590,7 +41590,7 @@
         <v/>
       </c>
       <c r="E90" s="5">
-        <f>IF(ISNUMBER(F90),MAX(DATE(2026,5,27),F90+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F90),MAX(DATE(2026,6,6),F90+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F90" s="5" t="n">
@@ -41722,7 +41722,7 @@
         <v/>
       </c>
       <c r="E91" s="5">
-        <f>IF(ISNUMBER(F91),MAX(DATE(2026,5,27),F91+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F91),MAX(DATE(2026,6,6),F91+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F91" s="5" t="n">
@@ -41854,7 +41854,7 @@
         <v/>
       </c>
       <c r="E92" s="5">
-        <f>IF(ISNUMBER(F92),MAX(DATE(2026,5,27),F92+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F92),MAX(DATE(2026,6,6),F92+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F92" s="5" t="n">
@@ -41986,7 +41986,7 @@
         <v/>
       </c>
       <c r="E93" s="5">
-        <f>IF(ISNUMBER(F93),MAX(DATE(2026,5,27),F93+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F93),MAX(DATE(2026,6,6),F93+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F93" s="5" t="n">
@@ -42118,7 +42118,7 @@
         <v/>
       </c>
       <c r="E94" s="5">
-        <f>IF(ISNUMBER(F94),MAX(DATE(2026,5,27),F94+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F94),MAX(DATE(2026,6,6),F94+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F94" s="5" t="n">
@@ -42250,7 +42250,7 @@
         <v/>
       </c>
       <c r="E95" s="5">
-        <f>IF(ISNUMBER(F95),MAX(DATE(2026,5,27),F95+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F95),MAX(DATE(2026,6,6),F95+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F95" s="5" t="n">
@@ -42382,7 +42382,7 @@
         <v/>
       </c>
       <c r="E96" s="5">
-        <f>IF(ISNUMBER(F96),MAX(DATE(2026,5,27),F96+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F96),MAX(DATE(2026,6,6),F96+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F96" s="5" t="n">
@@ -42514,7 +42514,7 @@
         <v/>
       </c>
       <c r="E97" s="5">
-        <f>IF(ISNUMBER(F97),MAX(DATE(2026,5,27),F97+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F97),MAX(DATE(2026,6,6),F97+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F97" s="5" t="n">
@@ -42646,7 +42646,7 @@
         <v/>
       </c>
       <c r="E98" s="5">
-        <f>IF(ISNUMBER(F98),MAX(DATE(2026,5,27),F98+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F98),MAX(DATE(2026,6,6),F98+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F98" s="5" t="n">
@@ -42778,7 +42778,7 @@
         <v/>
       </c>
       <c r="E99" s="5">
-        <f>IF(ISNUMBER(F99),MAX(DATE(2026,5,27),F99+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F99),MAX(DATE(2026,6,6),F99+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F99" s="5" t="n">
@@ -42910,7 +42910,7 @@
         <v/>
       </c>
       <c r="E100" s="5">
-        <f>IF(ISNUMBER(F100),MAX(DATE(2026,5,27),F100+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F100),MAX(DATE(2026,6,6),F100+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F100" s="5" t="n">
@@ -43042,7 +43042,7 @@
         <v/>
       </c>
       <c r="E101" s="5">
-        <f>IF(ISNUMBER(F101),MAX(DATE(2026,5,27),F101+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F101),MAX(DATE(2026,6,6),F101+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F101" s="5" t="n">
@@ -43174,7 +43174,7 @@
         <v/>
       </c>
       <c r="E102" s="5">
-        <f>IF(ISNUMBER(F102),MAX(DATE(2026,5,27),F102+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F102),MAX(DATE(2026,6,6),F102+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F102" s="5" t="n">
@@ -43306,7 +43306,7 @@
         <v/>
       </c>
       <c r="E103" s="5">
-        <f>IF(ISNUMBER(F103),MAX(DATE(2026,5,27),F103+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F103),MAX(DATE(2026,6,6),F103+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F103" s="5" t="n">
@@ -43438,7 +43438,7 @@
         <v/>
       </c>
       <c r="E104" s="5">
-        <f>IF(ISNUMBER(F104),MAX(DATE(2026,5,27),F104+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F104),MAX(DATE(2026,6,6),F104+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F104" s="5" t="n">
@@ -43570,7 +43570,7 @@
         <v/>
       </c>
       <c r="E105" s="5">
-        <f>IF(ISNUMBER(F105),MAX(DATE(2026,5,27),F105+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F105),MAX(DATE(2026,6,6),F105+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F105" s="5" t="n">
@@ -43702,7 +43702,7 @@
         <v/>
       </c>
       <c r="E106" s="5">
-        <f>IF(ISNUMBER(F106),MAX(DATE(2026,5,27),F106+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F106),MAX(DATE(2026,6,6),F106+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F106" s="5" t="n">
@@ -43834,7 +43834,7 @@
         <v/>
       </c>
       <c r="E107" s="5">
-        <f>IF(ISNUMBER(F107),MAX(DATE(2026,5,27),F107+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F107),MAX(DATE(2026,6,6),F107+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F107" s="5" t="n">
@@ -43966,7 +43966,7 @@
         <v/>
       </c>
       <c r="E108" s="5">
-        <f>IF(ISNUMBER(F108),MAX(DATE(2026,5,27),F108+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F108),MAX(DATE(2026,6,6),F108+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F108" s="5" t="n">
@@ -44098,7 +44098,7 @@
         <v/>
       </c>
       <c r="E109" s="5">
-        <f>IF(ISNUMBER(F109),MAX(DATE(2026,5,27),F109+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F109),MAX(DATE(2026,6,6),F109+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F109" s="5" t="n">
@@ -44230,7 +44230,7 @@
         <v/>
       </c>
       <c r="E110" s="5">
-        <f>IF(ISNUMBER(F110),MAX(DATE(2026,5,27),F110+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F110),MAX(DATE(2026,6,6),F110+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F110" s="5" t="n">
@@ -44362,7 +44362,7 @@
         <v/>
       </c>
       <c r="E111" s="5">
-        <f>IF(ISNUMBER(F111),MAX(DATE(2026,5,27),F111+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F111),MAX(DATE(2026,6,6),F111+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F111" s="5" t="n">
@@ -44494,7 +44494,7 @@
         <v/>
       </c>
       <c r="E112" s="5">
-        <f>IF(ISNUMBER(F112),MAX(DATE(2026,5,27),F112+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F112),MAX(DATE(2026,6,6),F112+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F112" s="5" t="n">
@@ -44626,7 +44626,7 @@
         <v/>
       </c>
       <c r="E113" s="5">
-        <f>IF(ISNUMBER(F113),MAX(DATE(2026,5,27),F113+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F113),MAX(DATE(2026,6,6),F113+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F113" s="5" t="n">
@@ -44758,7 +44758,7 @@
         <v/>
       </c>
       <c r="E114" s="5">
-        <f>IF(ISNUMBER(F114),MAX(DATE(2026,5,27),F114+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F114),MAX(DATE(2026,6,6),F114+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F114" s="5" t="n">
@@ -44890,7 +44890,7 @@
         <v/>
       </c>
       <c r="E115" s="5">
-        <f>IF(ISNUMBER(F115),MAX(DATE(2026,5,27),F115+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F115),MAX(DATE(2026,6,6),F115+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F115" s="5" t="n">
@@ -45022,7 +45022,7 @@
         <v/>
       </c>
       <c r="E116" s="5">
-        <f>IF(ISNUMBER(F116),MAX(DATE(2026,5,27),F116+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F116),MAX(DATE(2026,6,6),F116+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F116" s="5" t="n">
@@ -45154,7 +45154,7 @@
         <v/>
       </c>
       <c r="E117" s="5">
-        <f>IF(ISNUMBER(F117),MAX(DATE(2026,5,27),F117+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F117),MAX(DATE(2026,6,6),F117+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F117" s="5" t="n">
@@ -45286,7 +45286,7 @@
         <v/>
       </c>
       <c r="E118" s="5">
-        <f>IF(ISNUMBER(F118),MAX(DATE(2026,5,27),F118+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F118),MAX(DATE(2026,6,6),F118+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F118" s="5" t="n">
@@ -45418,7 +45418,7 @@
         <v/>
       </c>
       <c r="E119" s="5">
-        <f>IF(ISNUMBER(F119),MAX(DATE(2026,5,27),F119+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F119),MAX(DATE(2026,6,6),F119+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F119" s="5" t="n">
@@ -45550,7 +45550,7 @@
         <v/>
       </c>
       <c r="E120" s="5">
-        <f>IF(ISNUMBER(F120),MAX(DATE(2026,5,27),F120+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F120),MAX(DATE(2026,6,6),F120+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F120" s="5" t="n">
@@ -45682,7 +45682,7 @@
         <v/>
       </c>
       <c r="E121" s="5">
-        <f>IF(ISNUMBER(F121),MAX(DATE(2026,5,27),F121+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F121),MAX(DATE(2026,6,6),F121+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F121" s="5" t="n">
@@ -45814,7 +45814,7 @@
         <v/>
       </c>
       <c r="E122" s="5">
-        <f>IF(ISNUMBER(F122),MAX(DATE(2026,5,27),F122+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F122),MAX(DATE(2026,6,6),F122+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F122" s="5" t="n">
@@ -45946,7 +45946,7 @@
         <v/>
       </c>
       <c r="E123" s="5">
-        <f>IF(ISNUMBER(F123),MAX(DATE(2026,5,27),F123+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F123),MAX(DATE(2026,6,6),F123+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F123" s="5" t="n">
@@ -46078,7 +46078,7 @@
         <v/>
       </c>
       <c r="E124" s="5">
-        <f>IF(ISNUMBER(F124),MAX(DATE(2026,5,27),F124+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F124),MAX(DATE(2026,6,6),F124+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F124" s="5" t="n">
@@ -46210,7 +46210,7 @@
         <v/>
       </c>
       <c r="E125" s="5">
-        <f>IF(ISNUMBER(F125),MAX(DATE(2026,5,27),F125+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F125),MAX(DATE(2026,6,6),F125+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F125" s="5" t="n">
@@ -46342,7 +46342,7 @@
         <v/>
       </c>
       <c r="E126" s="5">
-        <f>IF(ISNUMBER(F126),MAX(DATE(2026,5,27),F126+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F126),MAX(DATE(2026,6,6),F126+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F126" s="5" t="n">
@@ -46474,7 +46474,7 @@
         <v/>
       </c>
       <c r="E127" s="5">
-        <f>IF(ISNUMBER(F127),MAX(DATE(2026,5,27),F127+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F127),MAX(DATE(2026,6,6),F127+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F127" s="5" t="n">
@@ -46606,7 +46606,7 @@
         <v/>
       </c>
       <c r="E128" s="5">
-        <f>IF(ISNUMBER(F128),MAX(DATE(2026,5,27),F128+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F128),MAX(DATE(2026,6,6),F128+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F128" s="5" t="n">
@@ -46738,7 +46738,7 @@
         <v/>
       </c>
       <c r="E129" s="5">
-        <f>IF(ISNUMBER(F129),MAX(DATE(2026,5,27),F129+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F129),MAX(DATE(2026,6,6),F129+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F129" s="5" t="n">
@@ -46870,7 +46870,7 @@
         <v/>
       </c>
       <c r="E130" s="5">
-        <f>IF(ISNUMBER(F130),MAX(DATE(2026,5,27),F130+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F130),MAX(DATE(2026,6,6),F130+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F130" s="5" t="n">
@@ -47002,7 +47002,7 @@
         <v/>
       </c>
       <c r="E131" s="5">
-        <f>IF(ISNUMBER(F131),MAX(DATE(2026,5,27),F131+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F131),MAX(DATE(2026,6,6),F131+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F131" s="5" t="n">
@@ -47134,7 +47134,7 @@
         <v/>
       </c>
       <c r="E132" s="5">
-        <f>IF(ISNUMBER(F132),MAX(DATE(2026,5,27),F132+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F132),MAX(DATE(2026,6,6),F132+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F132" s="5" t="n">
@@ -47266,7 +47266,7 @@
         <v/>
       </c>
       <c r="E133" s="5">
-        <f>IF(ISNUMBER(F133),MAX(DATE(2026,5,27),F133+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F133),MAX(DATE(2026,6,6),F133+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F133" s="5" t="n">
@@ -47398,7 +47398,7 @@
         <v/>
       </c>
       <c r="E134" s="5">
-        <f>IF(ISNUMBER(F134),MAX(DATE(2026,5,27),F134+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F134),MAX(DATE(2026,6,6),F134+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F134" s="5" t="n">
@@ -47530,7 +47530,7 @@
         <v/>
       </c>
       <c r="E135" s="5">
-        <f>IF(ISNUMBER(F135),MAX(DATE(2026,5,27),F135+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F135),MAX(DATE(2026,6,6),F135+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F135" s="5" t="n">
@@ -47662,7 +47662,7 @@
         <v/>
       </c>
       <c r="E136" s="5">
-        <f>IF(ISNUMBER(F136),MAX(DATE(2026,5,27),F136+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F136),MAX(DATE(2026,6,6),F136+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F136" s="5" t="n">
@@ -51694,7 +51694,7 @@
         <v/>
       </c>
       <c r="E167" s="5">
-        <f>IF(ISNUMBER(F167),MAX(DATE(2026,5,27),F167+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F167),MAX(DATE(2026,6,6),F167+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F167" s="5" t="n">
@@ -51827,7 +51827,7 @@
         <v/>
       </c>
       <c r="E168" s="5">
-        <f>IF(ISNUMBER(F168),MAX(DATE(2026,5,27),F168+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F168),MAX(DATE(2026,6,6),F168+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F168" s="5" t="n">
@@ -51960,7 +51960,7 @@
         <v/>
       </c>
       <c r="E169" s="5">
-        <f>IF(ISNUMBER(F169),MAX(DATE(2026,5,27),F169+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F169),MAX(DATE(2026,6,6),F169+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F169" s="5" t="n">
@@ -52093,7 +52093,7 @@
         <v/>
       </c>
       <c r="E170" s="5">
-        <f>IF(ISNUMBER(F170),MAX(DATE(2026,5,27),F170+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F170),MAX(DATE(2026,6,6),F170+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F170" s="5" t="inlineStr">
@@ -52234,7 +52234,7 @@
         <v/>
       </c>
       <c r="E171" s="5">
-        <f>IF(ISNUMBER(F171),MAX(DATE(2026,5,27),F171+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F171),MAX(DATE(2026,6,6),F171+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F171" s="5" t="n">
@@ -52366,7 +52366,7 @@
         <v/>
       </c>
       <c r="E172" s="5">
-        <f>IF(ISNUMBER(F172),MAX(DATE(2026,5,27),F172+7),DATE(2026,5,27))</f>
+        <f>IF(ISNUMBER(F172),MAX(DATE(2026,6,6),F172+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -52507,7 +52507,7 @@
         <v/>
       </c>
       <c r="E173" s="5">
-        <f>IF(ISNUMBER(F173),MAX(DATE(2026,5,27),F173+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F173),MAX(DATE(2026,6,6),F173+7),"— awaiting the retest certificates —")</f>
         <v/>
       </c>
       <c r="F173" s="5" t="n">
@@ -52624,7 +52624,7 @@
     <row r="175" ht="150" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
@@ -55995,21 +55995,21 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v45 on 06.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v45 on 18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 15.05.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 15.05.2026; a RETEST is dated at its own sampling day and issued on its campaign's day (sampling_dates.py, owner 15.09.2026: Tranche 1 sampled 21–24.07.2026 and issued 27.07.2026, Tranche 2 sampled 12–14.08.2026 and issued 17.08.2026, Tranche 3 sampled 19–21.08.2026 and issued 24.08.2026, each batch on the day its certificate number falls), which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. A round whose packaging date the list does not hold is numbered all the same (owner, 15.09.2026: identification A, B and foreign matter are performed on every batch) and says its testing date is not stated. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
+          <t>THE STANDING REGISTER OF INTERNAL CERTIFICATES OF ANALYSIS. Head of QC, 10.09.2026: "the register encompasses every internal certificate that exists or ever will" — ONE PER TESTING ROUND, not one per lot and not only the ones the drafted certificates happen to need. Each carries identification A, identification B and foreign matter ALWAYS (performed in house, on the first day of packaging for the release round and at its own sampling for a retest), plus any determination whose only result in that round is an in-house record. Codes iCoA-PP_26-nnn, one series for the year of issue, in the order of issue: by issue date, then by when the work was done, then by batch — 03.06.2026 for anything that would otherwise predate the specification SOP, so the backlog shares one date and orders by packaging, as the CoQ series does. THE ROWS, THE NUMBER AND THE CODE ARE NOT COMPUTED HERE (11.09.2026): this sheet RENDERS icoa_register.py, which is the series, and writes its numbers as literal values. Two things were being decided twice and disagreed. The number used to be a formula over this sheet's own row order, so the first physical row took iCoA-PP_26-001 while its own certificate cited iCoA-PP_26-066 and none of the 49 comparable rows agreed; and the ROW SET was this sheet's issuance planning, so it printed 60 of the series' 95 codes, showed no retest certificate at all where the series issues 26 (its retest rows are one per lot per tranche — a lot with four retest rounds had one row standing for four certificates), and withheld nine more under "where a CNP certificate reports all three, no iCoA is needed", the note of 05.09.2026 that the ruling of 10.09.2026 replaced: the in-house laboratory performs those three whatever an external laboratory also reports, so the certificate exists and is registered. Which document the CERTIFICATE OF QUALITY cites for them is a separate question and is unchanged. Rows below the series are lots it does not carry — a retest that is planned but not yet sampled, a lot with no production record, and the starred lots, whose star batch_id.batch_key deliberately keeps because whether GG012601＊ is GG012601 is the Head of QC's to rule. They are unnumbered and say why. Inserting a row renumbers nothing. verify_workbook.py compares sheet and series on every run. FORMULAS remaining: a release round's testing date and packaging-complete date are looked up on Batch Dates by P batch (else by the batch as listed) and its issue date is the later of that testing date and 03.06.2026; a RETEST is dated at its own sampling day and issued on its campaign's day (sampling_dates.py, owner 15.09.2026: Tranche 1 sampled 21–24.07.2026 and issued 27.07.2026, Tranche 2 sampled 12–14.08.2026 and issued 17.08.2026, Tranche 3 sampled 19–21.08.2026 and issued 24.08.2026, each batch on the day its certificate number falls), which no sheet holds, so the series' dates are written as literals rather than guessed by a formula. A round whose packaging date the list does not hold is numbered all the same (owner, 15.09.2026: identification A, B and foreign matter are performed on every batch) and says its testing date is not stated. CoQ (register) is looked up on the CoQ Register by Key — the tracker's in-house cells cite this register by Key, so they follow it. Working days are Monday to Friday; public holidays are not applied.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="190" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -36150,46 +36150,40 @@
           <t>n/a — initial certificate</t>
         </is>
       </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="V49" s="9" t="n">
+        <v>12.91</v>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>031-5-К/26</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.00 ± 1.20 (I)</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.80 – 13.19 %</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACC_THC12 : CBD1</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB49" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC49" s="10" t="inlineStr">
-        <is>
-          <t>no Total THC result on this certificate</t>
-        </is>
-      </c>
+          <t>QCSP_001_ACC-I_v.01</t>
+        </is>
+      </c>
+      <c r="AB49" s="10" t="inlineStr">
+        <is>
+          <t>for review — replaces the issued QCSP_001_ACC-I_v.01 (was ACC_THC12 : CBD1, 10.80 – 13.20 %); now ACC_THC12 : CBD1 10.80 – 13.19 %</t>
+        </is>
+      </c>
+      <c r="AC49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
@@ -36291,46 +36285,40 @@
           <t>n/a — initial certificate</t>
         </is>
       </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="V50" s="9" t="n">
+        <v>9.83</v>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>031-4-К/26</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.00 ± 1.00 (I)</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.00 – 10.99 %</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CF_THC10 : CBD1</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB50" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC50" s="10" t="inlineStr">
-        <is>
-          <t>no Total THC result on this certificate</t>
-        </is>
-      </c>
+          <t>QCSP_001_CF-I_v.01</t>
+        </is>
+      </c>
+      <c r="AB50" s="10" t="inlineStr">
+        <is>
+          <t>for review — replaces the issued QCSP_001_CF-I_v.01 (was CF_THC10 : CBD1, 9.00 – 11.00 %); now CF_THC10 : CBD1 9.00 – 10.99 %</t>
+        </is>
+      </c>
+      <c r="AC50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
@@ -47789,7 +47777,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr"/>
+      <c r="D137" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47863,7 +47853,7 @@
       </c>
       <c r="T137" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-30-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-30-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U137" s="2">
@@ -47919,7 +47909,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D138" s="5" t="inlineStr"/>
+      <c r="D138" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47993,7 +47985,7 @@
       </c>
       <c r="T138" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-29-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-29-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U138" s="2">
@@ -48049,7 +48041,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr"/>
+      <c r="D139" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48123,7 +48117,7 @@
       </c>
       <c r="T139" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-1-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-1-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U139" s="2">
@@ -48179,7 +48173,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr"/>
+      <c r="D140" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48253,7 +48249,7 @@
       </c>
       <c r="T140" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-25-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-25-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U140" s="2">
@@ -48309,7 +48305,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D141" s="5" t="inlineStr"/>
+      <c r="D141" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48383,7 +48381,7 @@
       </c>
       <c r="T141" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-28-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-28-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U141" s="2">
@@ -48439,7 +48437,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr"/>
+      <c r="D142" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48513,7 +48513,7 @@
       </c>
       <c r="T142" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-27-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-27-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U142" s="2">
@@ -48569,7 +48569,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr"/>
+      <c r="D143" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48643,7 +48645,7 @@
       </c>
       <c r="T143" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-26-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-26-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U143" s="2">
@@ -48699,7 +48701,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr"/>
+      <c r="D144" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48773,7 +48777,7 @@
       </c>
       <c r="T144" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-24-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-24-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U144" s="2">
@@ -48829,7 +48833,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr"/>
+      <c r="D145" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48903,7 +48909,7 @@
       </c>
       <c r="T145" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-23-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-23-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U145" s="2">
@@ -48959,7 +48965,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D146" s="5" t="inlineStr"/>
+      <c r="D146" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49033,7 +49041,7 @@
       </c>
       <c r="T146" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-22-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-22-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U146" s="2">
@@ -49089,7 +49097,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr"/>
+      <c r="D147" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49163,7 +49173,7 @@
       </c>
       <c r="T147" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-21-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-21-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U147" s="2">
@@ -49219,7 +49229,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D148" s="5" t="inlineStr"/>
+      <c r="D148" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49293,7 +49305,7 @@
       </c>
       <c r="T148" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-19-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-19-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U148" s="2">
@@ -49349,7 +49361,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr"/>
+      <c r="D149" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49423,7 +49437,7 @@
       </c>
       <c r="T149" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-20-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-20-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U149" s="2">
@@ -49479,7 +49493,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr"/>
+      <c r="D150" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49553,7 +49569,7 @@
       </c>
       <c r="T150" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-18-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-18-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U150" s="2">
@@ -49609,7 +49625,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr"/>
+      <c r="D151" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49683,7 +49701,7 @@
       </c>
       <c r="T151" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-17-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-17-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U151" s="2">
@@ -49739,7 +49757,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D152" s="5" t="inlineStr"/>
+      <c r="D152" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49813,7 +49833,7 @@
       </c>
       <c r="T152" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-2-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-2-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U152" s="2">
@@ -49869,7 +49889,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D153" s="5" t="inlineStr"/>
+      <c r="D153" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49943,7 +49965,7 @@
       </c>
       <c r="T153" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-16-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-16-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U153" s="2">
@@ -49999,7 +50021,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D154" s="5" t="inlineStr"/>
+      <c r="D154" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50073,7 +50097,7 @@
       </c>
       <c r="T154" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-14-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-14-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U154" s="2">
@@ -50129,7 +50153,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D155" s="5" t="inlineStr"/>
+      <c r="D155" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50203,7 +50229,7 @@
       </c>
       <c r="T155" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay — pending — on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay — pending — on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U155" s="2">
@@ -50259,7 +50285,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D156" s="5" t="inlineStr"/>
+      <c r="D156" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50333,7 +50361,7 @@
       </c>
       <c r="T156" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-15-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-15-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U156" s="2">
@@ -50389,7 +50417,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D157" s="5" t="inlineStr"/>
+      <c r="D157" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50463,7 +50493,7 @@
       </c>
       <c r="T157" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-12-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-12-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U157" s="2">
@@ -50519,7 +50549,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D158" s="5" t="inlineStr"/>
+      <c r="D158" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50593,7 +50625,7 @@
       </c>
       <c r="T158" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-11-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-11-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U158" s="2">
@@ -50649,7 +50681,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr"/>
+      <c r="D159" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50723,7 +50757,7 @@
       </c>
       <c r="T159" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-10-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-10-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U159" s="2">
@@ -50779,7 +50813,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D160" s="5" t="inlineStr"/>
+      <c r="D160" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50853,7 +50889,7 @@
       </c>
       <c r="T160" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-9-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-9-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U160" s="2">
@@ -50909,7 +50945,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D161" s="5" t="inlineStr"/>
+      <c r="D161" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50983,7 +51021,7 @@
       </c>
       <c r="T161" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-8-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-8-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U161" s="2">
@@ -51039,7 +51077,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D162" s="5" t="inlineStr"/>
+      <c r="D162" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51113,7 +51153,7 @@
       </c>
       <c r="T162" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-7-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-7-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U162" s="2">
@@ -51169,7 +51209,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D163" s="5" t="inlineStr"/>
+      <c r="D163" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51243,7 +51285,7 @@
       </c>
       <c r="T163" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-6-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-6-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U163" s="2">
@@ -51299,7 +51341,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D164" s="5" t="inlineStr"/>
+      <c r="D164" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51373,7 +51417,7 @@
       </c>
       <c r="T164" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-5-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites iCoA-PP_26-162 of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-5-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites iCoA-PP_26-162 of 24.08.2026</t>
         </is>
       </c>
       <c r="U164" s="2">
@@ -51429,7 +51473,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D165" s="5" t="inlineStr"/>
+      <c r="D165" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51503,7 +51549,7 @@
       </c>
       <c r="T165" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-3-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-3-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U165" s="2">
@@ -51559,7 +51605,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D166" s="5" t="inlineStr"/>
+      <c r="D166" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -51633,7 +51681,7 @@
       </c>
       <c r="T166" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-4-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-4-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U166" s="2">
@@ -52624,7 +52672,7 @@
     <row r="175" ht="150" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
@@ -55995,7 +56043,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v45 on 18.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v46 on 18.09.2026</t>
         </is>
       </c>
     </row>
@@ -56009,14 +56057,14 @@
     <row r="3" ht="190" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v45.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v46.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -29767,7 +29767,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <f>IF(OR(C2="yes",C2="allocated"),COUNT(A$1:A1)+1,"")</f>
+        <f>IF(OR(C2="yes",C2="allocated",C2="ruled"),COUNT(A$1:A1)+1,"")</f>
         <v/>
       </c>
       <c r="B2" s="3">
@@ -29780,7 +29780,7 @@
         </is>
       </c>
       <c r="D2" s="5">
-        <f>IF(OR(A2="",C2="allocated"),"",MAX(E2,IF(ISNUMBER(I2),I2,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S2,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S2,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A2="",C2="allocated",C2="ruled"),"",MAX(E2,IF(ISNUMBER(I2),I2,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S2,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S2,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E2" s="5">
@@ -29900,7 +29900,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <f>IF(OR(C3="yes",C3="allocated"),COUNT(A$1:A2)+1,"")</f>
+        <f>IF(OR(C3="yes",C3="allocated",C3="ruled"),COUNT(A$1:A2)+1,"")</f>
         <v/>
       </c>
       <c r="B3" s="3">
@@ -29913,7 +29913,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <f>IF(OR(A3="",C3="allocated"),"",MAX(E3,IF(ISNUMBER(I3),I3,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S3,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S3,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A3="",C3="allocated",C3="ruled"),"",MAX(E3,IF(ISNUMBER(I3),I3,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S3,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S3,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E3" s="5">
@@ -30033,7 +30033,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <f>IF(OR(C4="yes",C4="allocated"),COUNT(A$1:A3)+1,"")</f>
+        <f>IF(OR(C4="yes",C4="allocated",C4="ruled"),COUNT(A$1:A3)+1,"")</f>
         <v/>
       </c>
       <c r="B4" s="3">
@@ -30046,7 +30046,7 @@
         </is>
       </c>
       <c r="D4" s="5">
-        <f>IF(OR(A4="",C4="allocated"),"",MAX(E4,IF(ISNUMBER(I4),I4,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S4,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S4,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A4="",C4="allocated",C4="ruled"),"",MAX(E4,IF(ISNUMBER(I4),I4,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S4,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S4,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E4" s="5">
@@ -30166,7 +30166,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <f>IF(OR(C5="yes",C5="allocated"),COUNT(A$1:A4)+1,"")</f>
+        <f>IF(OR(C5="yes",C5="allocated",C5="ruled"),COUNT(A$1:A4)+1,"")</f>
         <v/>
       </c>
       <c r="B5" s="3">
@@ -30179,7 +30179,7 @@
         </is>
       </c>
       <c r="D5" s="5">
-        <f>IF(OR(A5="",C5="allocated"),"",MAX(E5,IF(ISNUMBER(I5),I5,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S5,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S5,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A5="",C5="allocated",C5="ruled"),"",MAX(E5,IF(ISNUMBER(I5),I5,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S5,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S5,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -30307,7 +30307,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <f>IF(OR(C6="yes",C6="allocated"),COUNT(A$1:A5)+1,"")</f>
+        <f>IF(OR(C6="yes",C6="allocated",C6="ruled"),COUNT(A$1:A5)+1,"")</f>
         <v/>
       </c>
       <c r="B6" s="3">
@@ -30320,7 +30320,7 @@
         </is>
       </c>
       <c r="D6" s="5">
-        <f>IF(OR(A6="",C6="allocated"),"",MAX(E6,IF(ISNUMBER(I6),I6,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S6,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S6,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A6="",C6="allocated",C6="ruled"),"",MAX(E6,IF(ISNUMBER(I6),I6,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S6,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S6,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -30442,7 +30442,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <f>IF(OR(C7="yes",C7="allocated"),COUNT(A$1:A6)+1,"")</f>
+        <f>IF(OR(C7="yes",C7="allocated",C7="ruled"),COUNT(A$1:A6)+1,"")</f>
         <v/>
       </c>
       <c r="B7" s="3">
@@ -30455,7 +30455,7 @@
         </is>
       </c>
       <c r="D7" s="5">
-        <f>IF(OR(A7="",C7="allocated"),"",MAX(E7,IF(ISNUMBER(I7),I7,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S7,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S7,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A7="",C7="allocated",C7="ruled"),"",MAX(E7,IF(ISNUMBER(I7),I7,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S7,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S7,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -30577,7 +30577,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <f>IF(OR(C8="yes",C8="allocated"),COUNT(A$1:A7)+1,"")</f>
+        <f>IF(OR(C8="yes",C8="allocated",C8="ruled"),COUNT(A$1:A7)+1,"")</f>
         <v/>
       </c>
       <c r="B8" s="3">
@@ -30590,7 +30590,7 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <f>IF(OR(A8="",C8="allocated"),"",MAX(E8,IF(ISNUMBER(I8),I8,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S8,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S8,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A8="",C8="allocated",C8="ruled"),"",MAX(E8,IF(ISNUMBER(I8),I8,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S8,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S8,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -30710,7 +30710,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <f>IF(OR(C9="yes",C9="allocated"),COUNT(A$1:A8)+1,"")</f>
+        <f>IF(OR(C9="yes",C9="allocated",C9="ruled"),COUNT(A$1:A8)+1,"")</f>
         <v/>
       </c>
       <c r="B9" s="3">
@@ -30723,7 +30723,7 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <f>IF(OR(A9="",C9="allocated"),"",MAX(E9,IF(ISNUMBER(I9),I9,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S9,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S9,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A9="",C9="allocated",C9="ruled"),"",MAX(E9,IF(ISNUMBER(I9),I9,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S9,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S9,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -30843,7 +30843,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <f>IF(OR(C10="yes",C10="allocated"),COUNT(A$1:A9)+1,"")</f>
+        <f>IF(OR(C10="yes",C10="allocated",C10="ruled"),COUNT(A$1:A9)+1,"")</f>
         <v/>
       </c>
       <c r="B10" s="3">
@@ -30856,7 +30856,7 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <f>IF(OR(A10="",C10="allocated"),"",MAX(E10,IF(ISNUMBER(I10),I10,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S10,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S10,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A10="",C10="allocated",C10="ruled"),"",MAX(E10,IF(ISNUMBER(I10),I10,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S10,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S10,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -30976,7 +30976,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <f>IF(OR(C11="yes",C11="allocated"),COUNT(A$1:A10)+1,"")</f>
+        <f>IF(OR(C11="yes",C11="allocated",C11="ruled"),COUNT(A$1:A10)+1,"")</f>
         <v/>
       </c>
       <c r="B11" s="3">
@@ -30989,7 +30989,7 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <f>IF(OR(A11="",C11="allocated"),"",MAX(E11,IF(ISNUMBER(I11),I11,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S11,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S11,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A11="",C11="allocated",C11="ruled"),"",MAX(E11,IF(ISNUMBER(I11),I11,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S11,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S11,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -31109,7 +31109,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <f>IF(OR(C12="yes",C12="allocated"),COUNT(A$1:A11)+1,"")</f>
+        <f>IF(OR(C12="yes",C12="allocated",C12="ruled"),COUNT(A$1:A11)+1,"")</f>
         <v/>
       </c>
       <c r="B12" s="3">
@@ -31122,7 +31122,7 @@
         </is>
       </c>
       <c r="D12" s="5">
-        <f>IF(OR(A12="",C12="allocated"),"",MAX(E12,IF(ISNUMBER(I12),I12,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S12,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S12,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A12="",C12="allocated",C12="ruled"),"",MAX(E12,IF(ISNUMBER(I12),I12,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S12,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S12,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -31242,7 +31242,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <f>IF(OR(C13="yes",C13="allocated"),COUNT(A$1:A12)+1,"")</f>
+        <f>IF(OR(C13="yes",C13="allocated",C13="ruled"),COUNT(A$1:A12)+1,"")</f>
         <v/>
       </c>
       <c r="B13" s="3">
@@ -31255,7 +31255,7 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <f>IF(OR(A13="",C13="allocated"),"",MAX(E13,IF(ISNUMBER(I13),I13,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S13,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S13,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A13="",C13="allocated",C13="ruled"),"",MAX(E13,IF(ISNUMBER(I13),I13,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S13,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S13,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -31375,7 +31375,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <f>IF(OR(C14="yes",C14="allocated"),COUNT(A$1:A13)+1,"")</f>
+        <f>IF(OR(C14="yes",C14="allocated",C14="ruled"),COUNT(A$1:A13)+1,"")</f>
         <v/>
       </c>
       <c r="B14" s="3">
@@ -31388,7 +31388,7 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>IF(OR(A14="",C14="allocated"),"",MAX(E14,IF(ISNUMBER(I14),I14,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S14,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S14,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A14="",C14="allocated",C14="ruled"),"",MAX(E14,IF(ISNUMBER(I14),I14,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S14,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S14,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -31508,7 +31508,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <f>IF(OR(C15="yes",C15="allocated"),COUNT(A$1:A14)+1,"")</f>
+        <f>IF(OR(C15="yes",C15="allocated",C15="ruled"),COUNT(A$1:A14)+1,"")</f>
         <v/>
       </c>
       <c r="B15" s="3">
@@ -31521,7 +31521,7 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <f>IF(OR(A15="",C15="allocated"),"",MAX(E15,IF(ISNUMBER(I15),I15,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S15,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S15,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A15="",C15="allocated",C15="ruled"),"",MAX(E15,IF(ISNUMBER(I15),I15,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S15,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S15,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -31641,7 +31641,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <f>IF(OR(C16="yes",C16="allocated"),COUNT(A$1:A15)+1,"")</f>
+        <f>IF(OR(C16="yes",C16="allocated",C16="ruled"),COUNT(A$1:A15)+1,"")</f>
         <v/>
       </c>
       <c r="B16" s="3">
@@ -31654,7 +31654,7 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <f>IF(OR(A16="",C16="allocated"),"",MAX(E16,IF(ISNUMBER(I16),I16,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S16,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S16,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A16="",C16="allocated",C16="ruled"),"",MAX(E16,IF(ISNUMBER(I16),I16,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S16,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S16,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -31774,7 +31774,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <f>IF(OR(C17="yes",C17="allocated"),COUNT(A$1:A16)+1,"")</f>
+        <f>IF(OR(C17="yes",C17="allocated",C17="ruled"),COUNT(A$1:A16)+1,"")</f>
         <v/>
       </c>
       <c r="B17" s="3">
@@ -31787,7 +31787,7 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <f>IF(OR(A17="",C17="allocated"),"",MAX(E17,IF(ISNUMBER(I17),I17,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S17,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S17,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A17="",C17="allocated",C17="ruled"),"",MAX(E17,IF(ISNUMBER(I17),I17,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S17,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S17,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -31907,7 +31907,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <f>IF(OR(C18="yes",C18="allocated"),COUNT(A$1:A17)+1,"")</f>
+        <f>IF(OR(C18="yes",C18="allocated",C18="ruled"),COUNT(A$1:A17)+1,"")</f>
         <v/>
       </c>
       <c r="B18" s="3">
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <f>IF(OR(A18="",C18="allocated"),"",MAX(E18,IF(ISNUMBER(I18),I18,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S18,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S18,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A18="",C18="allocated",C18="ruled"),"",MAX(E18,IF(ISNUMBER(I18),I18,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S18,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S18,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -32040,7 +32040,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <f>IF(OR(C19="yes",C19="allocated"),COUNT(A$1:A18)+1,"")</f>
+        <f>IF(OR(C19="yes",C19="allocated",C19="ruled"),COUNT(A$1:A18)+1,"")</f>
         <v/>
       </c>
       <c r="B19" s="3">
@@ -32053,7 +32053,7 @@
         </is>
       </c>
       <c r="D19" s="5">
-        <f>IF(OR(A19="",C19="allocated"),"",MAX(E19,IF(ISNUMBER(I19),I19,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S19,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S19,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A19="",C19="allocated",C19="ruled"),"",MAX(E19,IF(ISNUMBER(I19),I19,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S19,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S19,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -32173,7 +32173,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <f>IF(OR(C20="yes",C20="allocated"),COUNT(A$1:A19)+1,"")</f>
+        <f>IF(OR(C20="yes",C20="allocated",C20="ruled"),COUNT(A$1:A19)+1,"")</f>
         <v/>
       </c>
       <c r="B20" s="3">
@@ -32186,7 +32186,7 @@
         </is>
       </c>
       <c r="D20" s="5">
-        <f>IF(OR(A20="",C20="allocated"),"",MAX(E20,IF(ISNUMBER(I20),I20,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S20,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S20,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A20="",C20="allocated",C20="ruled"),"",MAX(E20,IF(ISNUMBER(I20),I20,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S20,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S20,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E20" s="5">
@@ -32306,7 +32306,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <f>IF(OR(C21="yes",C21="allocated"),COUNT(A$1:A20)+1,"")</f>
+        <f>IF(OR(C21="yes",C21="allocated",C21="ruled"),COUNT(A$1:A20)+1,"")</f>
         <v/>
       </c>
       <c r="B21" s="3">
@@ -32319,7 +32319,7 @@
         </is>
       </c>
       <c r="D21" s="5">
-        <f>IF(OR(A21="",C21="allocated"),"",MAX(E21,IF(ISNUMBER(I21),I21,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S21,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S21,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A21="",C21="allocated",C21="ruled"),"",MAX(E21,IF(ISNUMBER(I21),I21,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S21,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S21,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E21" s="5">
@@ -32439,7 +32439,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <f>IF(OR(C22="yes",C22="allocated"),COUNT(A$1:A21)+1,"")</f>
+        <f>IF(OR(C22="yes",C22="allocated",C22="ruled"),COUNT(A$1:A21)+1,"")</f>
         <v/>
       </c>
       <c r="B22" s="3">
@@ -32452,7 +32452,7 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <f>IF(OR(A22="",C22="allocated"),"",MAX(E22,IF(ISNUMBER(I22),I22,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S22,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S22,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A22="",C22="allocated",C22="ruled"),"",MAX(E22,IF(ISNUMBER(I22),I22,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S22,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S22,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E22" s="5">
@@ -32580,7 +32580,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <f>IF(OR(C23="yes",C23="allocated"),COUNT(A$1:A22)+1,"")</f>
+        <f>IF(OR(C23="yes",C23="allocated",C23="ruled"),COUNT(A$1:A22)+1,"")</f>
         <v/>
       </c>
       <c r="B23" s="3">
@@ -32593,7 +32593,7 @@
         </is>
       </c>
       <c r="D23" s="5">
-        <f>IF(OR(A23="",C23="allocated"),"",MAX(E23,IF(ISNUMBER(I23),I23,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S23,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S23,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A23="",C23="allocated",C23="ruled"),"",MAX(E23,IF(ISNUMBER(I23),I23,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S23,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S23,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E23" s="5">
@@ -32713,7 +32713,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <f>IF(OR(C24="yes",C24="allocated"),COUNT(A$1:A23)+1,"")</f>
+        <f>IF(OR(C24="yes",C24="allocated",C24="ruled"),COUNT(A$1:A23)+1,"")</f>
         <v/>
       </c>
       <c r="B24" s="3">
@@ -32726,7 +32726,7 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <f>IF(OR(A24="",C24="allocated"),"",MAX(E24,IF(ISNUMBER(I24),I24,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S24,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S24,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A24="",C24="allocated",C24="ruled"),"",MAX(E24,IF(ISNUMBER(I24),I24,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S24,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S24,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E24" s="5">
@@ -32846,7 +32846,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <f>IF(OR(C25="yes",C25="allocated"),COUNT(A$1:A24)+1,"")</f>
+        <f>IF(OR(C25="yes",C25="allocated",C25="ruled"),COUNT(A$1:A24)+1,"")</f>
         <v/>
       </c>
       <c r="B25" s="3">
@@ -32859,7 +32859,7 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>IF(OR(A25="",C25="allocated"),"",MAX(E25,IF(ISNUMBER(I25),I25,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S25,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S25,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A25="",C25="allocated",C25="ruled"),"",MAX(E25,IF(ISNUMBER(I25),I25,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S25,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S25,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E25" s="5">
@@ -32979,7 +32979,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <f>IF(OR(C26="yes",C26="allocated"),COUNT(A$1:A25)+1,"")</f>
+        <f>IF(OR(C26="yes",C26="allocated",C26="ruled"),COUNT(A$1:A25)+1,"")</f>
         <v/>
       </c>
       <c r="B26" s="3">
@@ -32992,7 +32992,7 @@
         </is>
       </c>
       <c r="D26" s="5">
-        <f>IF(OR(A26="",C26="allocated"),"",MAX(E26,IF(ISNUMBER(I26),I26,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S26,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S26,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A26="",C26="allocated",C26="ruled"),"",MAX(E26,IF(ISNUMBER(I26),I26,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S26,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S26,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E26" s="5">
@@ -33112,7 +33112,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <f>IF(OR(C27="yes",C27="allocated"),COUNT(A$1:A26)+1,"")</f>
+        <f>IF(OR(C27="yes",C27="allocated",C27="ruled"),COUNT(A$1:A26)+1,"")</f>
         <v/>
       </c>
       <c r="B27" s="3">
@@ -33125,7 +33125,7 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <f>IF(OR(A27="",C27="allocated"),"",MAX(E27,IF(ISNUMBER(I27),I27,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S27,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S27,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A27="",C27="allocated",C27="ruled"),"",MAX(E27,IF(ISNUMBER(I27),I27,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S27,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S27,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E27" s="5">
@@ -33245,7 +33245,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <f>IF(OR(C28="yes",C28="allocated"),COUNT(A$1:A27)+1,"")</f>
+        <f>IF(OR(C28="yes",C28="allocated",C28="ruled"),COUNT(A$1:A27)+1,"")</f>
         <v/>
       </c>
       <c r="B28" s="3">
@@ -33258,7 +33258,7 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <f>IF(OR(A28="",C28="allocated"),"",MAX(E28,IF(ISNUMBER(I28),I28,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S28,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S28,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A28="",C28="allocated",C28="ruled"),"",MAX(E28,IF(ISNUMBER(I28),I28,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S28,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S28,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E28" s="5">
@@ -33378,7 +33378,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <f>IF(OR(C29="yes",C29="allocated"),COUNT(A$1:A28)+1,"")</f>
+        <f>IF(OR(C29="yes",C29="allocated",C29="ruled"),COUNT(A$1:A28)+1,"")</f>
         <v/>
       </c>
       <c r="B29" s="3">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>IF(OR(A29="",C29="allocated"),"",MAX(E29,IF(ISNUMBER(I29),I29,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S29,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S29,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A29="",C29="allocated",C29="ruled"),"",MAX(E29,IF(ISNUMBER(I29),I29,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S29,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S29,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E29" s="5">
@@ -33511,7 +33511,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <f>IF(OR(C30="yes",C30="allocated"),COUNT(A$1:A29)+1,"")</f>
+        <f>IF(OR(C30="yes",C30="allocated",C30="ruled"),COUNT(A$1:A29)+1,"")</f>
         <v/>
       </c>
       <c r="B30" s="3">
@@ -33524,7 +33524,7 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>IF(OR(A30="",C30="allocated"),"",MAX(E30,IF(ISNUMBER(I30),I30,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S30,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S30,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A30="",C30="allocated",C30="ruled"),"",MAX(E30,IF(ISNUMBER(I30),I30,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S30,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S30,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E30" s="5">
@@ -33644,7 +33644,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <f>IF(OR(C31="yes",C31="allocated"),COUNT(A$1:A30)+1,"")</f>
+        <f>IF(OR(C31="yes",C31="allocated",C31="ruled"),COUNT(A$1:A30)+1,"")</f>
         <v/>
       </c>
       <c r="B31" s="3">
@@ -33657,7 +33657,7 @@
         </is>
       </c>
       <c r="D31" s="5">
-        <f>IF(OR(A31="",C31="allocated"),"",MAX(E31,IF(ISNUMBER(I31),I31,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S31,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S31,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A31="",C31="allocated",C31="ruled"),"",MAX(E31,IF(ISNUMBER(I31),I31,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S31,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S31,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E31" s="5">
@@ -33777,7 +33777,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <f>IF(OR(C32="yes",C32="allocated"),COUNT(A$1:A31)+1,"")</f>
+        <f>IF(OR(C32="yes",C32="allocated",C32="ruled"),COUNT(A$1:A31)+1,"")</f>
         <v/>
       </c>
       <c r="B32" s="3">
@@ -33790,7 +33790,7 @@
         </is>
       </c>
       <c r="D32" s="5">
-        <f>IF(OR(A32="",C32="allocated"),"",MAX(E32,IF(ISNUMBER(I32),I32,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S32,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S32,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A32="",C32="allocated",C32="ruled"),"",MAX(E32,IF(ISNUMBER(I32),I32,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S32,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S32,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E32" s="5">
@@ -33910,7 +33910,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <f>IF(OR(C33="yes",C33="allocated"),COUNT(A$1:A32)+1,"")</f>
+        <f>IF(OR(C33="yes",C33="allocated",C33="ruled"),COUNT(A$1:A32)+1,"")</f>
         <v/>
       </c>
       <c r="B33" s="3">
@@ -33923,7 +33923,7 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>IF(OR(A33="",C33="allocated"),"",MAX(E33,IF(ISNUMBER(I33),I33,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S33,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S33,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A33="",C33="allocated",C33="ruled"),"",MAX(E33,IF(ISNUMBER(I33),I33,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S33,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S33,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E33" s="5">
@@ -34043,7 +34043,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <f>IF(OR(C34="yes",C34="allocated"),COUNT(A$1:A33)+1,"")</f>
+        <f>IF(OR(C34="yes",C34="allocated",C34="ruled"),COUNT(A$1:A33)+1,"")</f>
         <v/>
       </c>
       <c r="B34" s="3">
@@ -34056,7 +34056,7 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <f>IF(OR(A34="",C34="allocated"),"",MAX(E34,IF(ISNUMBER(I34),I34,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S34,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S34,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A34="",C34="allocated",C34="ruled"),"",MAX(E34,IF(ISNUMBER(I34),I34,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S34,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S34,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E34" s="5">
@@ -34176,7 +34176,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <f>IF(OR(C35="yes",C35="allocated"),COUNT(A$1:A34)+1,"")</f>
+        <f>IF(OR(C35="yes",C35="allocated",C35="ruled"),COUNT(A$1:A34)+1,"")</f>
         <v/>
       </c>
       <c r="B35" s="3">
@@ -34189,7 +34189,7 @@
         </is>
       </c>
       <c r="D35" s="5">
-        <f>IF(OR(A35="",C35="allocated"),"",MAX(E35,IF(ISNUMBER(I35),I35,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S35,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S35,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A35="",C35="allocated",C35="ruled"),"",MAX(E35,IF(ISNUMBER(I35),I35,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S35,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S35,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E35" s="5">
@@ -34309,7 +34309,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <f>IF(OR(C36="yes",C36="allocated"),COUNT(A$1:A35)+1,"")</f>
+        <f>IF(OR(C36="yes",C36="allocated",C36="ruled"),COUNT(A$1:A35)+1,"")</f>
         <v/>
       </c>
       <c r="B36" s="3">
@@ -34322,7 +34322,7 @@
         </is>
       </c>
       <c r="D36" s="5">
-        <f>IF(OR(A36="",C36="allocated"),"",MAX(E36,IF(ISNUMBER(I36),I36,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S36,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S36,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A36="",C36="allocated",C36="ruled"),"",MAX(E36,IF(ISNUMBER(I36),I36,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S36,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S36,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E36" s="5">
@@ -34442,7 +34442,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <f>IF(OR(C37="yes",C37="allocated"),COUNT(A$1:A36)+1,"")</f>
+        <f>IF(OR(C37="yes",C37="allocated",C37="ruled"),COUNT(A$1:A36)+1,"")</f>
         <v/>
       </c>
       <c r="B37" s="3">
@@ -34455,7 +34455,7 @@
         </is>
       </c>
       <c r="D37" s="5">
-        <f>IF(OR(A37="",C37="allocated"),"",MAX(E37,IF(ISNUMBER(I37),I37,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S37,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S37,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A37="",C37="allocated",C37="ruled"),"",MAX(E37,IF(ISNUMBER(I37),I37,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S37,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S37,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E37" s="5">
@@ -34575,7 +34575,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <f>IF(OR(C38="yes",C38="allocated"),COUNT(A$1:A37)+1,"")</f>
+        <f>IF(OR(C38="yes",C38="allocated",C38="ruled"),COUNT(A$1:A37)+1,"")</f>
         <v/>
       </c>
       <c r="B38" s="3">
@@ -34588,7 +34588,7 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <f>IF(OR(A38="",C38="allocated"),"",MAX(E38,IF(ISNUMBER(I38),I38,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S38,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S38,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A38="",C38="allocated",C38="ruled"),"",MAX(E38,IF(ISNUMBER(I38),I38,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S38,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S38,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E38" s="5">
@@ -34708,7 +34708,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <f>IF(OR(C39="yes",C39="allocated"),COUNT(A$1:A38)+1,"")</f>
+        <f>IF(OR(C39="yes",C39="allocated",C39="ruled"),COUNT(A$1:A38)+1,"")</f>
         <v/>
       </c>
       <c r="B39" s="3">
@@ -34721,7 +34721,7 @@
         </is>
       </c>
       <c r="D39" s="5">
-        <f>IF(OR(A39="",C39="allocated"),"",MAX(E39,IF(ISNUMBER(I39),I39,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S39,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S39,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A39="",C39="allocated",C39="ruled"),"",MAX(E39,IF(ISNUMBER(I39),I39,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S39,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S39,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E39" s="5">
@@ -34841,7 +34841,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <f>IF(OR(C40="yes",C40="allocated"),COUNT(A$1:A39)+1,"")</f>
+        <f>IF(OR(C40="yes",C40="allocated",C40="ruled"),COUNT(A$1:A39)+1,"")</f>
         <v/>
       </c>
       <c r="B40" s="3">
@@ -34854,7 +34854,7 @@
         </is>
       </c>
       <c r="D40" s="5">
-        <f>IF(OR(A40="",C40="allocated"),"",MAX(E40,IF(ISNUMBER(I40),I40,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S40,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S40,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A40="",C40="allocated",C40="ruled"),"",MAX(E40,IF(ISNUMBER(I40),I40,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S40,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S40,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E40" s="5">
@@ -34974,7 +34974,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <f>IF(OR(C41="yes",C41="allocated"),COUNT(A$1:A40)+1,"")</f>
+        <f>IF(OR(C41="yes",C41="allocated",C41="ruled"),COUNT(A$1:A40)+1,"")</f>
         <v/>
       </c>
       <c r="B41" s="3">
@@ -34987,7 +34987,7 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <f>IF(OR(A41="",C41="allocated"),"",MAX(E41,IF(ISNUMBER(I41),I41,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S41,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S41,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A41="",C41="allocated",C41="ruled"),"",MAX(E41,IF(ISNUMBER(I41),I41,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S41,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S41,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E41" s="5">
@@ -35107,7 +35107,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <f>IF(OR(C42="yes",C42="allocated"),COUNT(A$1:A41)+1,"")</f>
+        <f>IF(OR(C42="yes",C42="allocated",C42="ruled"),COUNT(A$1:A41)+1,"")</f>
         <v/>
       </c>
       <c r="B42" s="3">
@@ -35120,7 +35120,7 @@
         </is>
       </c>
       <c r="D42" s="5">
-        <f>IF(OR(A42="",C42="allocated"),"",MAX(E42,IF(ISNUMBER(I42),I42,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S42,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S42,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A42="",C42="allocated",C42="ruled"),"",MAX(E42,IF(ISNUMBER(I42),I42,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S42,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S42,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E42" s="5">
@@ -35240,7 +35240,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <f>IF(OR(C43="yes",C43="allocated"),COUNT(A$1:A42)+1,"")</f>
+        <f>IF(OR(C43="yes",C43="allocated",C43="ruled"),COUNT(A$1:A42)+1,"")</f>
         <v/>
       </c>
       <c r="B43" s="3">
@@ -35253,7 +35253,7 @@
         </is>
       </c>
       <c r="D43" s="5">
-        <f>IF(OR(A43="",C43="allocated"),"",MAX(E43,IF(ISNUMBER(I43),I43,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S43,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S43,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A43="",C43="allocated",C43="ruled"),"",MAX(E43,IF(ISNUMBER(I43),I43,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S43,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S43,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E43" s="5">
@@ -35373,7 +35373,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <f>IF(OR(C44="yes",C44="allocated"),COUNT(A$1:A43)+1,"")</f>
+        <f>IF(OR(C44="yes",C44="allocated",C44="ruled"),COUNT(A$1:A43)+1,"")</f>
         <v/>
       </c>
       <c r="B44" s="3">
@@ -35386,7 +35386,7 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <f>IF(OR(A44="",C44="allocated"),"",MAX(E44,IF(ISNUMBER(I44),I44,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S44,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S44,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A44="",C44="allocated",C44="ruled"),"",MAX(E44,IF(ISNUMBER(I44),I44,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S44,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S44,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E44" s="5">
@@ -35506,7 +35506,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <f>IF(OR(C45="yes",C45="allocated"),COUNT(A$1:A44)+1,"")</f>
+        <f>IF(OR(C45="yes",C45="allocated",C45="ruled"),COUNT(A$1:A44)+1,"")</f>
         <v/>
       </c>
       <c r="B45" s="3">
@@ -35519,7 +35519,7 @@
         </is>
       </c>
       <c r="D45" s="5">
-        <f>IF(OR(A45="",C45="allocated"),"",MAX(E45,IF(ISNUMBER(I45),I45,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S45,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S45,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A45="",C45="allocated",C45="ruled"),"",MAX(E45,IF(ISNUMBER(I45),I45,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S45,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S45,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E45" s="5">
@@ -35639,7 +35639,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <f>IF(OR(C46="yes",C46="allocated"),COUNT(A$1:A45)+1,"")</f>
+        <f>IF(OR(C46="yes",C46="allocated",C46="ruled"),COUNT(A$1:A45)+1,"")</f>
         <v/>
       </c>
       <c r="B46" s="3">
@@ -35652,7 +35652,7 @@
         </is>
       </c>
       <c r="D46" s="5">
-        <f>IF(OR(A46="",C46="allocated"),"",MAX(E46,IF(ISNUMBER(I46),I46,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S46,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S46,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A46="",C46="allocated",C46="ruled"),"",MAX(E46,IF(ISNUMBER(I46),I46,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S46,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S46,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E46" s="5">
@@ -35772,7 +35772,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <f>IF(OR(C47="yes",C47="allocated"),COUNT(A$1:A46)+1,"")</f>
+        <f>IF(OR(C47="yes",C47="allocated",C47="ruled"),COUNT(A$1:A46)+1,"")</f>
         <v/>
       </c>
       <c r="B47" s="3">
@@ -35785,7 +35785,7 @@
         </is>
       </c>
       <c r="D47" s="5">
-        <f>IF(OR(A47="",C47="allocated"),"",MAX(E47,IF(ISNUMBER(I47),I47,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S47,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S47,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A47="",C47="allocated",C47="ruled"),"",MAX(E47,IF(ISNUMBER(I47),I47,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S47,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S47,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E47" s="5">
@@ -35911,7 +35911,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <f>IF(OR(C48="yes",C48="allocated"),COUNT(A$1:A47)+1,"")</f>
+        <f>IF(OR(C48="yes",C48="allocated",C48="ruled"),COUNT(A$1:A47)+1,"")</f>
         <v/>
       </c>
       <c r="B48" s="3">
@@ -35924,7 +35924,7 @@
         </is>
       </c>
       <c r="D48" s="5">
-        <f>IF(OR(A48="",C48="allocated"),"",MAX(E48,IF(ISNUMBER(I48),I48,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S48,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S48,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A48="",C48="allocated",C48="ruled"),"",MAX(E48,IF(ISNUMBER(I48),I48,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S48,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S48,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E48" s="5">
@@ -36052,7 +36052,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <f>IF(OR(C49="yes",C49="allocated"),COUNT(A$1:A48)+1,"")</f>
+        <f>IF(OR(C49="yes",C49="allocated",C49="ruled"),COUNT(A$1:A48)+1,"")</f>
         <v/>
       </c>
       <c r="B49" s="3">
@@ -36065,7 +36065,7 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <f>IF(OR(A49="",C49="allocated"),"",MAX(E49,IF(ISNUMBER(I49),I49,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S49,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S49,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A49="",C49="allocated",C49="ruled"),"",MAX(E49,IF(ISNUMBER(I49),I49,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S49,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S49,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E49" s="5">
@@ -36187,7 +36187,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <f>IF(OR(C50="yes",C50="allocated"),COUNT(A$1:A49)+1,"")</f>
+        <f>IF(OR(C50="yes",C50="allocated",C50="ruled"),COUNT(A$1:A49)+1,"")</f>
         <v/>
       </c>
       <c r="B50" s="3">
@@ -36200,7 +36200,7 @@
         </is>
       </c>
       <c r="D50" s="5">
-        <f>IF(OR(A50="",C50="allocated"),"",MAX(E50,IF(ISNUMBER(I50),I50,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S50,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S50,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A50="",C50="allocated",C50="ruled"),"",MAX(E50,IF(ISNUMBER(I50),I50,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S50,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S50,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E50" s="5">
@@ -36322,7 +36322,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <f>IF(OR(C51="yes",C51="allocated"),COUNT(A$1:A50)+1,"")</f>
+        <f>IF(OR(C51="yes",C51="allocated",C51="ruled"),COUNT(A$1:A50)+1,"")</f>
         <v/>
       </c>
       <c r="B51" s="3">
@@ -36335,7 +36335,7 @@
         </is>
       </c>
       <c r="D51" s="5">
-        <f>IF(OR(A51="",C51="allocated"),"",MAX(E51,IF(ISNUMBER(I51),I51,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S51,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S51,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A51="",C51="allocated",C51="ruled"),"",MAX(E51,IF(ISNUMBER(I51),I51,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S51,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S51,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E51" s="5">
@@ -36463,7 +36463,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <f>IF(OR(C52="yes",C52="allocated"),COUNT(A$1:A51)+1,"")</f>
+        <f>IF(OR(C52="yes",C52="allocated",C52="ruled"),COUNT(A$1:A51)+1,"")</f>
         <v/>
       </c>
       <c r="B52" s="3">
@@ -36476,7 +36476,7 @@
         </is>
       </c>
       <c r="D52" s="5">
-        <f>IF(OR(A52="",C52="allocated"),"",MAX(E52,IF(ISNUMBER(I52),I52,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S52,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S52,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A52="",C52="allocated",C52="ruled"),"",MAX(E52,IF(ISNUMBER(I52),I52,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S52,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S52,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E52" s="5">
@@ -36596,7 +36596,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <f>IF(OR(C53="yes",C53="allocated"),COUNT(A$1:A52)+1,"")</f>
+        <f>IF(OR(C53="yes",C53="allocated",C53="ruled"),COUNT(A$1:A52)+1,"")</f>
         <v/>
       </c>
       <c r="B53" s="3">
@@ -36609,7 +36609,7 @@
         </is>
       </c>
       <c r="D53" s="5">
-        <f>IF(OR(A53="",C53="allocated"),"",MAX(E53,IF(ISNUMBER(I53),I53,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S53,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S53,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A53="",C53="allocated",C53="ruled"),"",MAX(E53,IF(ISNUMBER(I53),I53,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S53,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S53,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E53" s="5">
@@ -36729,7 +36729,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <f>IF(OR(C54="yes",C54="allocated"),COUNT(A$1:A53)+1,"")</f>
+        <f>IF(OR(C54="yes",C54="allocated",C54="ruled"),COUNT(A$1:A53)+1,"")</f>
         <v/>
       </c>
       <c r="B54" s="3">
@@ -36742,7 +36742,7 @@
         </is>
       </c>
       <c r="D54" s="5">
-        <f>IF(OR(A54="",C54="allocated"),"",MAX(E54,IF(ISNUMBER(I54),I54,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S54,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S54,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A54="",C54="allocated",C54="ruled"),"",MAX(E54,IF(ISNUMBER(I54),I54,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S54,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S54,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E54" s="5">
@@ -36862,7 +36862,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <f>IF(OR(C55="yes",C55="allocated"),COUNT(A$1:A54)+1,"")</f>
+        <f>IF(OR(C55="yes",C55="allocated",C55="ruled"),COUNT(A$1:A54)+1,"")</f>
         <v/>
       </c>
       <c r="B55" s="3">
@@ -36875,7 +36875,7 @@
         </is>
       </c>
       <c r="D55" s="5">
-        <f>IF(OR(A55="",C55="allocated"),"",MAX(E55,IF(ISNUMBER(I55),I55,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S55,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S55,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A55="",C55="allocated",C55="ruled"),"",MAX(E55,IF(ISNUMBER(I55),I55,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S55,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S55,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E55" s="5">
@@ -36995,7 +36995,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <f>IF(OR(C56="yes",C56="allocated"),COUNT(A$1:A55)+1,"")</f>
+        <f>IF(OR(C56="yes",C56="allocated",C56="ruled"),COUNT(A$1:A55)+1,"")</f>
         <v/>
       </c>
       <c r="B56" s="3">
@@ -37008,7 +37008,7 @@
         </is>
       </c>
       <c r="D56" s="5">
-        <f>IF(OR(A56="",C56="allocated"),"",MAX(E56,IF(ISNUMBER(I56),I56,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S56,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S56,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A56="",C56="allocated",C56="ruled"),"",MAX(E56,IF(ISNUMBER(I56),I56,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S56,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S56,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E56" s="5">
@@ -37128,7 +37128,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <f>IF(OR(C57="yes",C57="allocated"),COUNT(A$1:A56)+1,"")</f>
+        <f>IF(OR(C57="yes",C57="allocated",C57="ruled"),COUNT(A$1:A56)+1,"")</f>
         <v/>
       </c>
       <c r="B57" s="3">
@@ -37141,7 +37141,7 @@
         </is>
       </c>
       <c r="D57" s="5">
-        <f>IF(OR(A57="",C57="allocated"),"",MAX(E57,IF(ISNUMBER(I57),I57,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S57,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S57,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A57="",C57="allocated",C57="ruled"),"",MAX(E57,IF(ISNUMBER(I57),I57,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S57,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S57,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E57" s="5">
@@ -37261,7 +37261,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <f>IF(OR(C58="yes",C58="allocated"),COUNT(A$1:A57)+1,"")</f>
+        <f>IF(OR(C58="yes",C58="allocated",C58="ruled"),COUNT(A$1:A57)+1,"")</f>
         <v/>
       </c>
       <c r="B58" s="3">
@@ -37274,7 +37274,7 @@
         </is>
       </c>
       <c r="D58" s="5">
-        <f>IF(OR(A58="",C58="allocated"),"",MAX(E58,IF(ISNUMBER(I58),I58,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S58,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S58,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A58="",C58="allocated",C58="ruled"),"",MAX(E58,IF(ISNUMBER(I58),I58,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S58,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S58,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E58" s="5">
@@ -37394,7 +37394,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <f>IF(OR(C59="yes",C59="allocated"),COUNT(A$1:A58)+1,"")</f>
+        <f>IF(OR(C59="yes",C59="allocated",C59="ruled"),COUNT(A$1:A58)+1,"")</f>
         <v/>
       </c>
       <c r="B59" s="3">
@@ -37407,7 +37407,7 @@
         </is>
       </c>
       <c r="D59" s="5">
-        <f>IF(OR(A59="",C59="allocated"),"",MAX(E59,IF(ISNUMBER(I59),I59,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S59,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S59,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A59="",C59="allocated",C59="ruled"),"",MAX(E59,IF(ISNUMBER(I59),I59,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S59,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S59,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E59" s="5">
@@ -37527,7 +37527,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <f>IF(OR(C60="yes",C60="allocated"),COUNT(A$1:A59)+1,"")</f>
+        <f>IF(OR(C60="yes",C60="allocated",C60="ruled"),COUNT(A$1:A59)+1,"")</f>
         <v/>
       </c>
       <c r="B60" s="3">
@@ -37540,7 +37540,7 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <f>IF(OR(A60="",C60="allocated"),"",MAX(E60,IF(ISNUMBER(I60),I60,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S60,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S60,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A60="",C60="allocated",C60="ruled"),"",MAX(E60,IF(ISNUMBER(I60),I60,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S60,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S60,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E60" s="5">
@@ -37660,7 +37660,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <f>IF(OR(C61="yes",C61="allocated"),COUNT(A$1:A60)+1,"")</f>
+        <f>IF(OR(C61="yes",C61="allocated",C61="ruled"),COUNT(A$1:A60)+1,"")</f>
         <v/>
       </c>
       <c r="B61" s="3">
@@ -37673,7 +37673,7 @@
         </is>
       </c>
       <c r="D61" s="5">
-        <f>IF(OR(A61="",C61="allocated"),"",MAX(E61,IF(ISNUMBER(I61),I61,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S61,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S61,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A61="",C61="allocated",C61="ruled"),"",MAX(E61,IF(ISNUMBER(I61),I61,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S61,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S61,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E61" s="5">
@@ -37793,7 +37793,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <f>IF(OR(C62="yes",C62="allocated"),COUNT(A$1:A61)+1,"")</f>
+        <f>IF(OR(C62="yes",C62="allocated",C62="ruled"),COUNT(A$1:A61)+1,"")</f>
         <v/>
       </c>
       <c r="B62" s="3">
@@ -37806,7 +37806,7 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <f>IF(OR(A62="",C62="allocated"),"",MAX(E62,IF(ISNUMBER(I62),I62,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S62,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S62,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A62="",C62="allocated",C62="ruled"),"",MAX(E62,IF(ISNUMBER(I62),I62,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S62,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S62,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E62" s="5">
@@ -37926,7 +37926,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <f>IF(OR(C63="yes",C63="allocated"),COUNT(A$1:A62)+1,"")</f>
+        <f>IF(OR(C63="yes",C63="allocated",C63="ruled"),COUNT(A$1:A62)+1,"")</f>
         <v/>
       </c>
       <c r="B63" s="3">
@@ -37939,7 +37939,7 @@
         </is>
       </c>
       <c r="D63" s="5">
-        <f>IF(OR(A63="",C63="allocated"),"",MAX(E63,IF(ISNUMBER(I63),I63,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S63,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S63,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A63="",C63="allocated",C63="ruled"),"",MAX(E63,IF(ISNUMBER(I63),I63,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S63,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S63,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E63" s="5">
@@ -38059,7 +38059,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <f>IF(OR(C64="yes",C64="allocated"),COUNT(A$1:A63)+1,"")</f>
+        <f>IF(OR(C64="yes",C64="allocated",C64="ruled"),COUNT(A$1:A63)+1,"")</f>
         <v/>
       </c>
       <c r="B64" s="3">
@@ -38072,7 +38072,7 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <f>IF(OR(A64="",C64="allocated"),"",MAX(E64,IF(ISNUMBER(I64),I64,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S64,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S64,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A64="",C64="allocated",C64="ruled"),"",MAX(E64,IF(ISNUMBER(I64),I64,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S64,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S64,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E64" s="5">
@@ -38192,7 +38192,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <f>IF(OR(C65="yes",C65="allocated"),COUNT(A$1:A64)+1,"")</f>
+        <f>IF(OR(C65="yes",C65="allocated",C65="ruled"),COUNT(A$1:A64)+1,"")</f>
         <v/>
       </c>
       <c r="B65" s="3">
@@ -38205,7 +38205,7 @@
         </is>
       </c>
       <c r="D65" s="5">
-        <f>IF(OR(A65="",C65="allocated"),"",MAX(E65,IF(ISNUMBER(I65),I65,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S65,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S65,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A65="",C65="allocated",C65="ruled"),"",MAX(E65,IF(ISNUMBER(I65),I65,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S65,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S65,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E65" s="5">
@@ -38325,7 +38325,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <f>IF(OR(C66="yes",C66="allocated"),COUNT(A$1:A65)+1,"")</f>
+        <f>IF(OR(C66="yes",C66="allocated",C66="ruled"),COUNT(A$1:A65)+1,"")</f>
         <v/>
       </c>
       <c r="B66" s="3">
@@ -38338,7 +38338,7 @@
         </is>
       </c>
       <c r="D66" s="5">
-        <f>IF(OR(A66="",C66="allocated"),"",MAX(E66,IF(ISNUMBER(I66),I66,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S66,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S66,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A66="",C66="allocated",C66="ruled"),"",MAX(E66,IF(ISNUMBER(I66),I66,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S66,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S66,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E66" s="5">
@@ -38458,7 +38458,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <f>IF(OR(C67="yes",C67="allocated"),COUNT(A$1:A66)+1,"")</f>
+        <f>IF(OR(C67="yes",C67="allocated",C67="ruled"),COUNT(A$1:A66)+1,"")</f>
         <v/>
       </c>
       <c r="B67" s="3">
@@ -38471,7 +38471,7 @@
         </is>
       </c>
       <c r="D67" s="5">
-        <f>IF(OR(A67="",C67="allocated"),"",MAX(E67,IF(ISNUMBER(I67),I67,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S67,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S67,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A67="",C67="allocated",C67="ruled"),"",MAX(E67,IF(ISNUMBER(I67),I67,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S67,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S67,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E67" s="5">
@@ -38591,7 +38591,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <f>IF(OR(C68="yes",C68="allocated"),COUNT(A$1:A67)+1,"")</f>
+        <f>IF(OR(C68="yes",C68="allocated",C68="ruled"),COUNT(A$1:A67)+1,"")</f>
         <v/>
       </c>
       <c r="B68" s="3">
@@ -38604,7 +38604,7 @@
         </is>
       </c>
       <c r="D68" s="5">
-        <f>IF(OR(A68="",C68="allocated"),"",MAX(E68,IF(ISNUMBER(I68),I68,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S68,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S68,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A68="",C68="allocated",C68="ruled"),"",MAX(E68,IF(ISNUMBER(I68),I68,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S68,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S68,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E68" s="5">
@@ -38724,7 +38724,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <f>IF(OR(C69="yes",C69="allocated"),COUNT(A$1:A68)+1,"")</f>
+        <f>IF(OR(C69="yes",C69="allocated",C69="ruled"),COUNT(A$1:A68)+1,"")</f>
         <v/>
       </c>
       <c r="B69" s="3">
@@ -38737,7 +38737,7 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <f>IF(OR(A69="",C69="allocated"),"",MAX(E69,IF(ISNUMBER(I69),I69,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S69,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S69,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A69="",C69="allocated",C69="ruled"),"",MAX(E69,IF(ISNUMBER(I69),I69,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S69,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S69,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E69" s="5">
@@ -38861,7 +38861,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <f>IF(OR(C70="yes",C70="allocated"),COUNT(A$1:A69)+1,"")</f>
+        <f>IF(OR(C70="yes",C70="allocated",C70="ruled"),COUNT(A$1:A69)+1,"")</f>
         <v/>
       </c>
       <c r="B70" s="3">
@@ -38874,7 +38874,7 @@
         </is>
       </c>
       <c r="D70" s="5">
-        <f>IF(OR(A70="",C70="allocated"),"",MAX(E70,IF(ISNUMBER(I70),I70,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S70,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S70,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A70="",C70="allocated",C70="ruled"),"",MAX(E70,IF(ISNUMBER(I70),I70,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S70,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S70,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E70" s="5">
@@ -38994,7 +38994,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <f>IF(OR(C71="yes",C71="allocated"),COUNT(A$1:A70)+1,"")</f>
+        <f>IF(OR(C71="yes",C71="allocated",C71="ruled"),COUNT(A$1:A70)+1,"")</f>
         <v/>
       </c>
       <c r="B71" s="3">
@@ -39007,7 +39007,7 @@
         </is>
       </c>
       <c r="D71" s="5">
-        <f>IF(OR(A71="",C71="allocated"),"",MAX(E71,IF(ISNUMBER(I71),I71,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S71,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S71,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A71="",C71="allocated",C71="ruled"),"",MAX(E71,IF(ISNUMBER(I71),I71,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S71,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S71,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E71" s="5">
@@ -39135,7 +39135,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <f>IF(OR(C72="yes",C72="allocated"),COUNT(A$1:A71)+1,"")</f>
+        <f>IF(OR(C72="yes",C72="allocated",C72="ruled"),COUNT(A$1:A71)+1,"")</f>
         <v/>
       </c>
       <c r="B72" s="3">
@@ -39148,7 +39148,7 @@
         </is>
       </c>
       <c r="D72" s="5">
-        <f>IF(OR(A72="",C72="allocated"),"",MAX(E72,IF(ISNUMBER(I72),I72,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S72,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S72,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A72="",C72="allocated",C72="ruled"),"",MAX(E72,IF(ISNUMBER(I72),I72,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S72,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S72,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E72" s="5">
@@ -39276,7 +39276,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <f>IF(OR(C73="yes",C73="allocated"),COUNT(A$1:A72)+1,"")</f>
+        <f>IF(OR(C73="yes",C73="allocated",C73="ruled"),COUNT(A$1:A72)+1,"")</f>
         <v/>
       </c>
       <c r="B73" s="3">
@@ -39289,7 +39289,7 @@
         </is>
       </c>
       <c r="D73" s="5">
-        <f>IF(OR(A73="",C73="allocated"),"",MAX(E73,IF(ISNUMBER(I73),I73,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S73,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S73,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A73="",C73="allocated",C73="ruled"),"",MAX(E73,IF(ISNUMBER(I73),I73,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S73,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S73,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E73" s="5">
@@ -39417,7 +39417,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <f>IF(OR(C74="yes",C74="allocated"),COUNT(A$1:A73)+1,"")</f>
+        <f>IF(OR(C74="yes",C74="allocated",C74="ruled"),COUNT(A$1:A73)+1,"")</f>
         <v/>
       </c>
       <c r="B74" s="3">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="D74" s="5">
-        <f>IF(OR(A74="",C74="allocated"),"",MAX(E74,IF(ISNUMBER(I74),I74,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S74,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S74,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A74="",C74="allocated",C74="ruled"),"",MAX(E74,IF(ISNUMBER(I74),I74,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S74,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S74,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E74" s="5">
@@ -39558,7 +39558,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <f>IF(OR(C75="yes",C75="allocated"),COUNT(A$1:A74)+1,"")</f>
+        <f>IF(OR(C75="yes",C75="allocated",C75="ruled"),COUNT(A$1:A74)+1,"")</f>
         <v/>
       </c>
       <c r="B75" s="3">
@@ -39571,7 +39571,7 @@
         </is>
       </c>
       <c r="D75" s="5">
-        <f>IF(OR(A75="",C75="allocated"),"",MAX(E75,IF(ISNUMBER(I75),I75,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S75,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S75,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A75="",C75="allocated",C75="ruled"),"",MAX(E75,IF(ISNUMBER(I75),I75,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S75,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S75,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E75" s="5">
@@ -39699,7 +39699,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <f>IF(OR(C76="yes",C76="allocated"),COUNT(A$1:A75)+1,"")</f>
+        <f>IF(OR(C76="yes",C76="allocated",C76="ruled"),COUNT(A$1:A75)+1,"")</f>
         <v/>
       </c>
       <c r="B76" s="3">
@@ -39712,7 +39712,7 @@
         </is>
       </c>
       <c r="D76" s="5">
-        <f>IF(OR(A76="",C76="allocated"),"",MAX(E76,IF(ISNUMBER(I76),I76,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S76,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S76,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A76="",C76="allocated",C76="ruled"),"",MAX(E76,IF(ISNUMBER(I76),I76,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S76,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S76,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E76" s="5">
@@ -39832,7 +39832,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <f>IF(OR(C77="yes",C77="allocated"),COUNT(A$1:A76)+1,"")</f>
+        <f>IF(OR(C77="yes",C77="allocated",C77="ruled"),COUNT(A$1:A76)+1,"")</f>
         <v/>
       </c>
       <c r="B77" s="3">
@@ -39845,7 +39845,7 @@
         </is>
       </c>
       <c r="D77" s="5">
-        <f>IF(OR(A77="",C77="allocated"),"",MAX(E77,IF(ISNUMBER(I77),I77,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S77,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S77,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A77="",C77="allocated",C77="ruled"),"",MAX(E77,IF(ISNUMBER(I77),I77,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S77,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S77,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E77" s="5">
@@ -39965,7 +39965,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <f>IF(OR(C78="yes",C78="allocated"),COUNT(A$1:A77)+1,"")</f>
+        <f>IF(OR(C78="yes",C78="allocated",C78="ruled"),COUNT(A$1:A77)+1,"")</f>
         <v/>
       </c>
       <c r="B78" s="3">
@@ -39978,7 +39978,7 @@
         </is>
       </c>
       <c r="D78" s="5">
-        <f>IF(OR(A78="",C78="allocated"),"",MAX(E78,IF(ISNUMBER(I78),I78,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S78,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S78,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A78="",C78="allocated",C78="ruled"),"",MAX(E78,IF(ISNUMBER(I78),I78,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S78,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S78,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E78" s="5">
@@ -40098,7 +40098,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <f>IF(OR(C79="yes",C79="allocated"),COUNT(A$1:A78)+1,"")</f>
+        <f>IF(OR(C79="yes",C79="allocated",C79="ruled"),COUNT(A$1:A78)+1,"")</f>
         <v/>
       </c>
       <c r="B79" s="3">
@@ -40111,7 +40111,7 @@
         </is>
       </c>
       <c r="D79" s="5">
-        <f>IF(OR(A79="",C79="allocated"),"",MAX(E79,IF(ISNUMBER(I79),I79,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S79,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S79,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A79="",C79="allocated",C79="ruled"),"",MAX(E79,IF(ISNUMBER(I79),I79,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S79,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S79,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E79" s="5">
@@ -40231,7 +40231,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <f>IF(OR(C80="yes",C80="allocated"),COUNT(A$1:A79)+1,"")</f>
+        <f>IF(OR(C80="yes",C80="allocated",C80="ruled"),COUNT(A$1:A79)+1,"")</f>
         <v/>
       </c>
       <c r="B80" s="3">
@@ -40244,7 +40244,7 @@
         </is>
       </c>
       <c r="D80" s="5">
-        <f>IF(OR(A80="",C80="allocated"),"",MAX(E80,IF(ISNUMBER(I80),I80,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S80,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S80,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A80="",C80="allocated",C80="ruled"),"",MAX(E80,IF(ISNUMBER(I80),I80,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S80,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S80,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E80" s="5">
@@ -40364,7 +40364,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <f>IF(OR(C81="yes",C81="allocated"),COUNT(A$1:A80)+1,"")</f>
+        <f>IF(OR(C81="yes",C81="allocated",C81="ruled"),COUNT(A$1:A80)+1,"")</f>
         <v/>
       </c>
       <c r="B81" s="3">
@@ -40377,7 +40377,7 @@
         </is>
       </c>
       <c r="D81" s="5">
-        <f>IF(OR(A81="",C81="allocated"),"",MAX(E81,IF(ISNUMBER(I81),I81,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S81,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S81,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A81="",C81="allocated",C81="ruled"),"",MAX(E81,IF(ISNUMBER(I81),I81,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S81,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S81,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E81" s="5">
@@ -40497,7 +40497,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <f>IF(OR(C82="yes",C82="allocated"),COUNT(A$1:A81)+1,"")</f>
+        <f>IF(OR(C82="yes",C82="allocated",C82="ruled"),COUNT(A$1:A81)+1,"")</f>
         <v/>
       </c>
       <c r="B82" s="3">
@@ -40510,7 +40510,7 @@
         </is>
       </c>
       <c r="D82" s="5">
-        <f>IF(OR(A82="",C82="allocated"),"",MAX(E82,IF(ISNUMBER(I82),I82,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S82,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S82,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A82="",C82="allocated",C82="ruled"),"",MAX(E82,IF(ISNUMBER(I82),I82,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S82,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S82,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E82" s="5">
@@ -40630,7 +40630,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <f>IF(OR(C83="yes",C83="allocated"),COUNT(A$1:A82)+1,"")</f>
+        <f>IF(OR(C83="yes",C83="allocated",C83="ruled"),COUNT(A$1:A82)+1,"")</f>
         <v/>
       </c>
       <c r="B83" s="3">
@@ -40643,7 +40643,7 @@
         </is>
       </c>
       <c r="D83" s="5">
-        <f>IF(OR(A83="",C83="allocated"),"",MAX(E83,IF(ISNUMBER(I83),I83,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S83,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S83,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A83="",C83="allocated",C83="ruled"),"",MAX(E83,IF(ISNUMBER(I83),I83,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S83,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S83,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E83" s="5">
@@ -40763,7 +40763,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <f>IF(OR(C84="yes",C84="allocated"),COUNT(A$1:A83)+1,"")</f>
+        <f>IF(OR(C84="yes",C84="allocated",C84="ruled"),COUNT(A$1:A83)+1,"")</f>
         <v/>
       </c>
       <c r="B84" s="3">
@@ -40776,7 +40776,7 @@
         </is>
       </c>
       <c r="D84" s="5">
-        <f>IF(OR(A84="",C84="allocated"),"",MAX(E84,IF(ISNUMBER(I84),I84,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S84,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S84,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A84="",C84="allocated",C84="ruled"),"",MAX(E84,IF(ISNUMBER(I84),I84,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S84,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S84,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E84" s="5">
@@ -40896,7 +40896,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <f>IF(OR(C85="yes",C85="allocated"),COUNT(A$1:A84)+1,"")</f>
+        <f>IF(OR(C85="yes",C85="allocated",C85="ruled"),COUNT(A$1:A84)+1,"")</f>
         <v/>
       </c>
       <c r="B85" s="3">
@@ -40909,7 +40909,7 @@
         </is>
       </c>
       <c r="D85" s="5">
-        <f>IF(OR(A85="",C85="allocated"),"",MAX(E85,IF(ISNUMBER(I85),I85,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S85,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S85,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A85="",C85="allocated",C85="ruled"),"",MAX(E85,IF(ISNUMBER(I85),I85,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S85,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S85,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E85" s="5">
@@ -41037,7 +41037,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <f>IF(OR(C86="yes",C86="allocated"),COUNT(A$1:A85)+1,"")</f>
+        <f>IF(OR(C86="yes",C86="allocated",C86="ruled"),COUNT(A$1:A85)+1,"")</f>
         <v/>
       </c>
       <c r="B86" s="3">
@@ -41050,7 +41050,7 @@
         </is>
       </c>
       <c r="D86" s="5">
-        <f>IF(OR(A86="",C86="allocated"),"",MAX(E86,IF(ISNUMBER(I86),I86,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S86,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S86,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A86="",C86="allocated",C86="ruled"),"",MAX(E86,IF(ISNUMBER(I86),I86,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S86,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S86,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E86" s="5">
@@ -41169,7 +41169,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <f>IF(OR(C87="yes",C87="allocated"),COUNT(A$1:A86)+1,"")</f>
+        <f>IF(OR(C87="yes",C87="allocated",C87="ruled"),COUNT(A$1:A86)+1,"")</f>
         <v/>
       </c>
       <c r="B87" s="3">
@@ -41182,7 +41182,7 @@
         </is>
       </c>
       <c r="D87" s="5">
-        <f>IF(OR(A87="",C87="allocated"),"",MAX(E87,IF(ISNUMBER(I87),I87,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S87,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S87,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A87="",C87="allocated",C87="ruled"),"",MAX(E87,IF(ISNUMBER(I87),I87,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S87,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S87,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E87" s="5">
@@ -41301,7 +41301,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <f>IF(OR(C88="yes",C88="allocated"),COUNT(A$1:A87)+1,"")</f>
+        <f>IF(OR(C88="yes",C88="allocated",C88="ruled"),COUNT(A$1:A87)+1,"")</f>
         <v/>
       </c>
       <c r="B88" s="3">
@@ -41314,7 +41314,7 @@
         </is>
       </c>
       <c r="D88" s="5">
-        <f>IF(OR(A88="",C88="allocated"),"",MAX(E88,IF(ISNUMBER(I88),I88,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S88,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S88,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A88="",C88="allocated",C88="ruled"),"",MAX(E88,IF(ISNUMBER(I88),I88,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S88,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S88,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E88" s="5">
@@ -41429,7 +41429,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <f>IF(OR(C89="yes",C89="allocated"),COUNT(A$1:A88)+1,"")</f>
+        <f>IF(OR(C89="yes",C89="allocated",C89="ruled"),COUNT(A$1:A88)+1,"")</f>
         <v/>
       </c>
       <c r="B89" s="3">
@@ -41442,7 +41442,7 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <f>IF(OR(A89="",C89="allocated"),"",MAX(E89,IF(ISNUMBER(I89),I89,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S89,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S89,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A89="",C89="allocated",C89="ruled"),"",MAX(E89,IF(ISNUMBER(I89),I89,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S89,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S89,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E89" s="5">
@@ -41561,7 +41561,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <f>IF(OR(C90="yes",C90="allocated"),COUNT(A$1:A89)+1,"")</f>
+        <f>IF(OR(C90="yes",C90="allocated",C90="ruled"),COUNT(A$1:A89)+1,"")</f>
         <v/>
       </c>
       <c r="B90" s="3">
@@ -41574,7 +41574,7 @@
         </is>
       </c>
       <c r="D90" s="5">
-        <f>IF(OR(A90="",C90="allocated"),"",MAX(E90,IF(ISNUMBER(I90),I90,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S90,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S90,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A90="",C90="allocated",C90="ruled"),"",MAX(E90,IF(ISNUMBER(I90),I90,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S90,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S90,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E90" s="5">
@@ -41693,7 +41693,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <f>IF(OR(C91="yes",C91="allocated"),COUNT(A$1:A90)+1,"")</f>
+        <f>IF(OR(C91="yes",C91="allocated",C91="ruled"),COUNT(A$1:A90)+1,"")</f>
         <v/>
       </c>
       <c r="B91" s="3">
@@ -41706,7 +41706,7 @@
         </is>
       </c>
       <c r="D91" s="5">
-        <f>IF(OR(A91="",C91="allocated"),"",MAX(E91,IF(ISNUMBER(I91),I91,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S91,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S91,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A91="",C91="allocated",C91="ruled"),"",MAX(E91,IF(ISNUMBER(I91),I91,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S91,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S91,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E91" s="5">
@@ -41825,7 +41825,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <f>IF(OR(C92="yes",C92="allocated"),COUNT(A$1:A91)+1,"")</f>
+        <f>IF(OR(C92="yes",C92="allocated",C92="ruled"),COUNT(A$1:A91)+1,"")</f>
         <v/>
       </c>
       <c r="B92" s="3">
@@ -41838,7 +41838,7 @@
         </is>
       </c>
       <c r="D92" s="5">
-        <f>IF(OR(A92="",C92="allocated"),"",MAX(E92,IF(ISNUMBER(I92),I92,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S92,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S92,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A92="",C92="allocated",C92="ruled"),"",MAX(E92,IF(ISNUMBER(I92),I92,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S92,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S92,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E92" s="5">
@@ -41957,7 +41957,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <f>IF(OR(C93="yes",C93="allocated"),COUNT(A$1:A92)+1,"")</f>
+        <f>IF(OR(C93="yes",C93="allocated",C93="ruled"),COUNT(A$1:A92)+1,"")</f>
         <v/>
       </c>
       <c r="B93" s="3">
@@ -41970,7 +41970,7 @@
         </is>
       </c>
       <c r="D93" s="5">
-        <f>IF(OR(A93="",C93="allocated"),"",MAX(E93,IF(ISNUMBER(I93),I93,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S93,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S93,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A93="",C93="allocated",C93="ruled"),"",MAX(E93,IF(ISNUMBER(I93),I93,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S93,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S93,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E93" s="5">
@@ -42089,7 +42089,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <f>IF(OR(C94="yes",C94="allocated"),COUNT(A$1:A93)+1,"")</f>
+        <f>IF(OR(C94="yes",C94="allocated",C94="ruled"),COUNT(A$1:A93)+1,"")</f>
         <v/>
       </c>
       <c r="B94" s="3">
@@ -42102,7 +42102,7 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <f>IF(OR(A94="",C94="allocated"),"",MAX(E94,IF(ISNUMBER(I94),I94,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S94,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S94,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A94="",C94="allocated",C94="ruled"),"",MAX(E94,IF(ISNUMBER(I94),I94,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S94,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S94,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E94" s="5">
@@ -42221,7 +42221,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <f>IF(OR(C95="yes",C95="allocated"),COUNT(A$1:A94)+1,"")</f>
+        <f>IF(OR(C95="yes",C95="allocated",C95="ruled"),COUNT(A$1:A94)+1,"")</f>
         <v/>
       </c>
       <c r="B95" s="3">
@@ -42234,7 +42234,7 @@
         </is>
       </c>
       <c r="D95" s="5">
-        <f>IF(OR(A95="",C95="allocated"),"",MAX(E95,IF(ISNUMBER(I95),I95,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S95,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S95,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A95="",C95="allocated",C95="ruled"),"",MAX(E95,IF(ISNUMBER(I95),I95,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S95,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S95,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E95" s="5">
@@ -42353,7 +42353,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <f>IF(OR(C96="yes",C96="allocated"),COUNT(A$1:A95)+1,"")</f>
+        <f>IF(OR(C96="yes",C96="allocated",C96="ruled"),COUNT(A$1:A95)+1,"")</f>
         <v/>
       </c>
       <c r="B96" s="3">
@@ -42366,7 +42366,7 @@
         </is>
       </c>
       <c r="D96" s="5">
-        <f>IF(OR(A96="",C96="allocated"),"",MAX(E96,IF(ISNUMBER(I96),I96,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S96,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S96,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A96="",C96="allocated",C96="ruled"),"",MAX(E96,IF(ISNUMBER(I96),I96,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S96,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S96,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E96" s="5">
@@ -42485,7 +42485,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <f>IF(OR(C97="yes",C97="allocated"),COUNT(A$1:A96)+1,"")</f>
+        <f>IF(OR(C97="yes",C97="allocated",C97="ruled"),COUNT(A$1:A96)+1,"")</f>
         <v/>
       </c>
       <c r="B97" s="3">
@@ -42498,7 +42498,7 @@
         </is>
       </c>
       <c r="D97" s="5">
-        <f>IF(OR(A97="",C97="allocated"),"",MAX(E97,IF(ISNUMBER(I97),I97,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S97,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S97,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A97="",C97="allocated",C97="ruled"),"",MAX(E97,IF(ISNUMBER(I97),I97,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S97,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S97,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E97" s="5">
@@ -42617,7 +42617,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <f>IF(OR(C98="yes",C98="allocated"),COUNT(A$1:A97)+1,"")</f>
+        <f>IF(OR(C98="yes",C98="allocated",C98="ruled"),COUNT(A$1:A97)+1,"")</f>
         <v/>
       </c>
       <c r="B98" s="3">
@@ -42630,7 +42630,7 @@
         </is>
       </c>
       <c r="D98" s="5">
-        <f>IF(OR(A98="",C98="allocated"),"",MAX(E98,IF(ISNUMBER(I98),I98,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S98,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S98,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A98="",C98="allocated",C98="ruled"),"",MAX(E98,IF(ISNUMBER(I98),I98,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S98,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S98,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E98" s="5">
@@ -42749,7 +42749,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <f>IF(OR(C99="yes",C99="allocated"),COUNT(A$1:A98)+1,"")</f>
+        <f>IF(OR(C99="yes",C99="allocated",C99="ruled"),COUNT(A$1:A98)+1,"")</f>
         <v/>
       </c>
       <c r="B99" s="3">
@@ -42762,7 +42762,7 @@
         </is>
       </c>
       <c r="D99" s="5">
-        <f>IF(OR(A99="",C99="allocated"),"",MAX(E99,IF(ISNUMBER(I99),I99,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S99,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S99,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A99="",C99="allocated",C99="ruled"),"",MAX(E99,IF(ISNUMBER(I99),I99,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S99,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S99,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E99" s="5">
@@ -42881,7 +42881,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <f>IF(OR(C100="yes",C100="allocated"),COUNT(A$1:A99)+1,"")</f>
+        <f>IF(OR(C100="yes",C100="allocated",C100="ruled"),COUNT(A$1:A99)+1,"")</f>
         <v/>
       </c>
       <c r="B100" s="3">
@@ -42894,7 +42894,7 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <f>IF(OR(A100="",C100="allocated"),"",MAX(E100,IF(ISNUMBER(I100),I100,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S100,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S100,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A100="",C100="allocated",C100="ruled"),"",MAX(E100,IF(ISNUMBER(I100),I100,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S100,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S100,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E100" s="5">
@@ -43013,7 +43013,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <f>IF(OR(C101="yes",C101="allocated"),COUNT(A$1:A100)+1,"")</f>
+        <f>IF(OR(C101="yes",C101="allocated",C101="ruled"),COUNT(A$1:A100)+1,"")</f>
         <v/>
       </c>
       <c r="B101" s="3">
@@ -43026,7 +43026,7 @@
         </is>
       </c>
       <c r="D101" s="5">
-        <f>IF(OR(A101="",C101="allocated"),"",MAX(E101,IF(ISNUMBER(I101),I101,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S101,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S101,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A101="",C101="allocated",C101="ruled"),"",MAX(E101,IF(ISNUMBER(I101),I101,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S101,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S101,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E101" s="5">
@@ -43145,7 +43145,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <f>IF(OR(C102="yes",C102="allocated"),COUNT(A$1:A101)+1,"")</f>
+        <f>IF(OR(C102="yes",C102="allocated",C102="ruled"),COUNT(A$1:A101)+1,"")</f>
         <v/>
       </c>
       <c r="B102" s="3">
@@ -43158,7 +43158,7 @@
         </is>
       </c>
       <c r="D102" s="5">
-        <f>IF(OR(A102="",C102="allocated"),"",MAX(E102,IF(ISNUMBER(I102),I102,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S102,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S102,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A102="",C102="allocated",C102="ruled"),"",MAX(E102,IF(ISNUMBER(I102),I102,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S102,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S102,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E102" s="5">
@@ -43277,7 +43277,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <f>IF(OR(C103="yes",C103="allocated"),COUNT(A$1:A102)+1,"")</f>
+        <f>IF(OR(C103="yes",C103="allocated",C103="ruled"),COUNT(A$1:A102)+1,"")</f>
         <v/>
       </c>
       <c r="B103" s="3">
@@ -43290,7 +43290,7 @@
         </is>
       </c>
       <c r="D103" s="5">
-        <f>IF(OR(A103="",C103="allocated"),"",MAX(E103,IF(ISNUMBER(I103),I103,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S103,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S103,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A103="",C103="allocated",C103="ruled"),"",MAX(E103,IF(ISNUMBER(I103),I103,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S103,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S103,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E103" s="5">
@@ -43409,7 +43409,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <f>IF(OR(C104="yes",C104="allocated"),COUNT(A$1:A103)+1,"")</f>
+        <f>IF(OR(C104="yes",C104="allocated",C104="ruled"),COUNT(A$1:A103)+1,"")</f>
         <v/>
       </c>
       <c r="B104" s="3">
@@ -43422,7 +43422,7 @@
         </is>
       </c>
       <c r="D104" s="5">
-        <f>IF(OR(A104="",C104="allocated"),"",MAX(E104,IF(ISNUMBER(I104),I104,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S104,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S104,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A104="",C104="allocated",C104="ruled"),"",MAX(E104,IF(ISNUMBER(I104),I104,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S104,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S104,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E104" s="5">
@@ -43541,7 +43541,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <f>IF(OR(C105="yes",C105="allocated"),COUNT(A$1:A104)+1,"")</f>
+        <f>IF(OR(C105="yes",C105="allocated",C105="ruled"),COUNT(A$1:A104)+1,"")</f>
         <v/>
       </c>
       <c r="B105" s="3">
@@ -43554,7 +43554,7 @@
         </is>
       </c>
       <c r="D105" s="5">
-        <f>IF(OR(A105="",C105="allocated"),"",MAX(E105,IF(ISNUMBER(I105),I105,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S105,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S105,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A105="",C105="allocated",C105="ruled"),"",MAX(E105,IF(ISNUMBER(I105),I105,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S105,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S105,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E105" s="5">
@@ -43673,7 +43673,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <f>IF(OR(C106="yes",C106="allocated"),COUNT(A$1:A105)+1,"")</f>
+        <f>IF(OR(C106="yes",C106="allocated",C106="ruled"),COUNT(A$1:A105)+1,"")</f>
         <v/>
       </c>
       <c r="B106" s="3">
@@ -43686,7 +43686,7 @@
         </is>
       </c>
       <c r="D106" s="5">
-        <f>IF(OR(A106="",C106="allocated"),"",MAX(E106,IF(ISNUMBER(I106),I106,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S106,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S106,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A106="",C106="allocated",C106="ruled"),"",MAX(E106,IF(ISNUMBER(I106),I106,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S106,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S106,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E106" s="5">
@@ -43805,7 +43805,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <f>IF(OR(C107="yes",C107="allocated"),COUNT(A$1:A106)+1,"")</f>
+        <f>IF(OR(C107="yes",C107="allocated",C107="ruled"),COUNT(A$1:A106)+1,"")</f>
         <v/>
       </c>
       <c r="B107" s="3">
@@ -43818,7 +43818,7 @@
         </is>
       </c>
       <c r="D107" s="5">
-        <f>IF(OR(A107="",C107="allocated"),"",MAX(E107,IF(ISNUMBER(I107),I107,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S107,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S107,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A107="",C107="allocated",C107="ruled"),"",MAX(E107,IF(ISNUMBER(I107),I107,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S107,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S107,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E107" s="5">
@@ -43937,7 +43937,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <f>IF(OR(C108="yes",C108="allocated"),COUNT(A$1:A107)+1,"")</f>
+        <f>IF(OR(C108="yes",C108="allocated",C108="ruled"),COUNT(A$1:A107)+1,"")</f>
         <v/>
       </c>
       <c r="B108" s="3">
@@ -43950,7 +43950,7 @@
         </is>
       </c>
       <c r="D108" s="5">
-        <f>IF(OR(A108="",C108="allocated"),"",MAX(E108,IF(ISNUMBER(I108),I108,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S108,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S108,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A108="",C108="allocated",C108="ruled"),"",MAX(E108,IF(ISNUMBER(I108),I108,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S108,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S108,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E108" s="5">
@@ -44069,7 +44069,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <f>IF(OR(C109="yes",C109="allocated"),COUNT(A$1:A108)+1,"")</f>
+        <f>IF(OR(C109="yes",C109="allocated",C109="ruled"),COUNT(A$1:A108)+1,"")</f>
         <v/>
       </c>
       <c r="B109" s="3">
@@ -44082,7 +44082,7 @@
         </is>
       </c>
       <c r="D109" s="5">
-        <f>IF(OR(A109="",C109="allocated"),"",MAX(E109,IF(ISNUMBER(I109),I109,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S109,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S109,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A109="",C109="allocated",C109="ruled"),"",MAX(E109,IF(ISNUMBER(I109),I109,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S109,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S109,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E109" s="5">
@@ -44201,7 +44201,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <f>IF(OR(C110="yes",C110="allocated"),COUNT(A$1:A109)+1,"")</f>
+        <f>IF(OR(C110="yes",C110="allocated",C110="ruled"),COUNT(A$1:A109)+1,"")</f>
         <v/>
       </c>
       <c r="B110" s="3">
@@ -44214,7 +44214,7 @@
         </is>
       </c>
       <c r="D110" s="5">
-        <f>IF(OR(A110="",C110="allocated"),"",MAX(E110,IF(ISNUMBER(I110),I110,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S110,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S110,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A110="",C110="allocated",C110="ruled"),"",MAX(E110,IF(ISNUMBER(I110),I110,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S110,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S110,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E110" s="5">
@@ -44333,7 +44333,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <f>IF(OR(C111="yes",C111="allocated"),COUNT(A$1:A110)+1,"")</f>
+        <f>IF(OR(C111="yes",C111="allocated",C111="ruled"),COUNT(A$1:A110)+1,"")</f>
         <v/>
       </c>
       <c r="B111" s="3">
@@ -44346,7 +44346,7 @@
         </is>
       </c>
       <c r="D111" s="5">
-        <f>IF(OR(A111="",C111="allocated"),"",MAX(E111,IF(ISNUMBER(I111),I111,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S111,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S111,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A111="",C111="allocated",C111="ruled"),"",MAX(E111,IF(ISNUMBER(I111),I111,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S111,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S111,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E111" s="5">
@@ -44465,7 +44465,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <f>IF(OR(C112="yes",C112="allocated"),COUNT(A$1:A111)+1,"")</f>
+        <f>IF(OR(C112="yes",C112="allocated",C112="ruled"),COUNT(A$1:A111)+1,"")</f>
         <v/>
       </c>
       <c r="B112" s="3">
@@ -44478,7 +44478,7 @@
         </is>
       </c>
       <c r="D112" s="5">
-        <f>IF(OR(A112="",C112="allocated"),"",MAX(E112,IF(ISNUMBER(I112),I112,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S112,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S112,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A112="",C112="allocated",C112="ruled"),"",MAX(E112,IF(ISNUMBER(I112),I112,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S112,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S112,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E112" s="5">
@@ -44597,7 +44597,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <f>IF(OR(C113="yes",C113="allocated"),COUNT(A$1:A112)+1,"")</f>
+        <f>IF(OR(C113="yes",C113="allocated",C113="ruled"),COUNT(A$1:A112)+1,"")</f>
         <v/>
       </c>
       <c r="B113" s="3">
@@ -44610,7 +44610,7 @@
         </is>
       </c>
       <c r="D113" s="5">
-        <f>IF(OR(A113="",C113="allocated"),"",MAX(E113,IF(ISNUMBER(I113),I113,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S113,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S113,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A113="",C113="allocated",C113="ruled"),"",MAX(E113,IF(ISNUMBER(I113),I113,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S113,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S113,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E113" s="5">
@@ -44729,7 +44729,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <f>IF(OR(C114="yes",C114="allocated"),COUNT(A$1:A113)+1,"")</f>
+        <f>IF(OR(C114="yes",C114="allocated",C114="ruled"),COUNT(A$1:A113)+1,"")</f>
         <v/>
       </c>
       <c r="B114" s="3">
@@ -44742,7 +44742,7 @@
         </is>
       </c>
       <c r="D114" s="5">
-        <f>IF(OR(A114="",C114="allocated"),"",MAX(E114,IF(ISNUMBER(I114),I114,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S114,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S114,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A114="",C114="allocated",C114="ruled"),"",MAX(E114,IF(ISNUMBER(I114),I114,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S114,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S114,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E114" s="5">
@@ -44861,7 +44861,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <f>IF(OR(C115="yes",C115="allocated"),COUNT(A$1:A114)+1,"")</f>
+        <f>IF(OR(C115="yes",C115="allocated",C115="ruled"),COUNT(A$1:A114)+1,"")</f>
         <v/>
       </c>
       <c r="B115" s="3">
@@ -44874,7 +44874,7 @@
         </is>
       </c>
       <c r="D115" s="5">
-        <f>IF(OR(A115="",C115="allocated"),"",MAX(E115,IF(ISNUMBER(I115),I115,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S115,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S115,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A115="",C115="allocated",C115="ruled"),"",MAX(E115,IF(ISNUMBER(I115),I115,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S115,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S115,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E115" s="5">
@@ -44993,7 +44993,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <f>IF(OR(C116="yes",C116="allocated"),COUNT(A$1:A115)+1,"")</f>
+        <f>IF(OR(C116="yes",C116="allocated",C116="ruled"),COUNT(A$1:A115)+1,"")</f>
         <v/>
       </c>
       <c r="B116" s="3">
@@ -45006,7 +45006,7 @@
         </is>
       </c>
       <c r="D116" s="5">
-        <f>IF(OR(A116="",C116="allocated"),"",MAX(E116,IF(ISNUMBER(I116),I116,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S116,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S116,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A116="",C116="allocated",C116="ruled"),"",MAX(E116,IF(ISNUMBER(I116),I116,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S116,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S116,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E116" s="5">
@@ -45125,7 +45125,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <f>IF(OR(C117="yes",C117="allocated"),COUNT(A$1:A116)+1,"")</f>
+        <f>IF(OR(C117="yes",C117="allocated",C117="ruled"),COUNT(A$1:A116)+1,"")</f>
         <v/>
       </c>
       <c r="B117" s="3">
@@ -45138,7 +45138,7 @@
         </is>
       </c>
       <c r="D117" s="5">
-        <f>IF(OR(A117="",C117="allocated"),"",MAX(E117,IF(ISNUMBER(I117),I117,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S117,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S117,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A117="",C117="allocated",C117="ruled"),"",MAX(E117,IF(ISNUMBER(I117),I117,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S117,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S117,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E117" s="5">
@@ -45257,7 +45257,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <f>IF(OR(C118="yes",C118="allocated"),COUNT(A$1:A117)+1,"")</f>
+        <f>IF(OR(C118="yes",C118="allocated",C118="ruled"),COUNT(A$1:A117)+1,"")</f>
         <v/>
       </c>
       <c r="B118" s="3">
@@ -45270,7 +45270,7 @@
         </is>
       </c>
       <c r="D118" s="5">
-        <f>IF(OR(A118="",C118="allocated"),"",MAX(E118,IF(ISNUMBER(I118),I118,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S118,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S118,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A118="",C118="allocated",C118="ruled"),"",MAX(E118,IF(ISNUMBER(I118),I118,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S118,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S118,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E118" s="5">
@@ -45389,7 +45389,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <f>IF(OR(C119="yes",C119="allocated"),COUNT(A$1:A118)+1,"")</f>
+        <f>IF(OR(C119="yes",C119="allocated",C119="ruled"),COUNT(A$1:A118)+1,"")</f>
         <v/>
       </c>
       <c r="B119" s="3">
@@ -45402,7 +45402,7 @@
         </is>
       </c>
       <c r="D119" s="5">
-        <f>IF(OR(A119="",C119="allocated"),"",MAX(E119,IF(ISNUMBER(I119),I119,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S119,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S119,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A119="",C119="allocated",C119="ruled"),"",MAX(E119,IF(ISNUMBER(I119),I119,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S119,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S119,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E119" s="5">
@@ -45521,7 +45521,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2">
-        <f>IF(OR(C120="yes",C120="allocated"),COUNT(A$1:A119)+1,"")</f>
+        <f>IF(OR(C120="yes",C120="allocated",C120="ruled"),COUNT(A$1:A119)+1,"")</f>
         <v/>
       </c>
       <c r="B120" s="3">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="D120" s="5">
-        <f>IF(OR(A120="",C120="allocated"),"",MAX(E120,IF(ISNUMBER(I120),I120,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S120,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S120,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A120="",C120="allocated",C120="ruled"),"",MAX(E120,IF(ISNUMBER(I120),I120,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S120,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S120,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E120" s="5">
@@ -45653,7 +45653,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2">
-        <f>IF(OR(C121="yes",C121="allocated"),COUNT(A$1:A120)+1,"")</f>
+        <f>IF(OR(C121="yes",C121="allocated",C121="ruled"),COUNT(A$1:A120)+1,"")</f>
         <v/>
       </c>
       <c r="B121" s="3">
@@ -45666,7 +45666,7 @@
         </is>
       </c>
       <c r="D121" s="5">
-        <f>IF(OR(A121="",C121="allocated"),"",MAX(E121,IF(ISNUMBER(I121),I121,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S121,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S121,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A121="",C121="allocated",C121="ruled"),"",MAX(E121,IF(ISNUMBER(I121),I121,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S121,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S121,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E121" s="5">
@@ -45785,7 +45785,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2">
-        <f>IF(OR(C122="yes",C122="allocated"),COUNT(A$1:A121)+1,"")</f>
+        <f>IF(OR(C122="yes",C122="allocated",C122="ruled"),COUNT(A$1:A121)+1,"")</f>
         <v/>
       </c>
       <c r="B122" s="3">
@@ -45798,7 +45798,7 @@
         </is>
       </c>
       <c r="D122" s="5">
-        <f>IF(OR(A122="",C122="allocated"),"",MAX(E122,IF(ISNUMBER(I122),I122,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S122,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S122,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A122="",C122="allocated",C122="ruled"),"",MAX(E122,IF(ISNUMBER(I122),I122,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S122,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S122,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E122" s="5">
@@ -45917,7 +45917,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2">
-        <f>IF(OR(C123="yes",C123="allocated"),COUNT(A$1:A122)+1,"")</f>
+        <f>IF(OR(C123="yes",C123="allocated",C123="ruled"),COUNT(A$1:A122)+1,"")</f>
         <v/>
       </c>
       <c r="B123" s="3">
@@ -45930,7 +45930,7 @@
         </is>
       </c>
       <c r="D123" s="5">
-        <f>IF(OR(A123="",C123="allocated"),"",MAX(E123,IF(ISNUMBER(I123),I123,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S123,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S123,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A123="",C123="allocated",C123="ruled"),"",MAX(E123,IF(ISNUMBER(I123),I123,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S123,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S123,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E123" s="5">
@@ -46049,7 +46049,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2">
-        <f>IF(OR(C124="yes",C124="allocated"),COUNT(A$1:A123)+1,"")</f>
+        <f>IF(OR(C124="yes",C124="allocated",C124="ruled"),COUNT(A$1:A123)+1,"")</f>
         <v/>
       </c>
       <c r="B124" s="3">
@@ -46062,7 +46062,7 @@
         </is>
       </c>
       <c r="D124" s="5">
-        <f>IF(OR(A124="",C124="allocated"),"",MAX(E124,IF(ISNUMBER(I124),I124,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S124,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S124,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A124="",C124="allocated",C124="ruled"),"",MAX(E124,IF(ISNUMBER(I124),I124,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S124,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S124,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E124" s="5">
@@ -46181,7 +46181,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2">
-        <f>IF(OR(C125="yes",C125="allocated"),COUNT(A$1:A124)+1,"")</f>
+        <f>IF(OR(C125="yes",C125="allocated",C125="ruled"),COUNT(A$1:A124)+1,"")</f>
         <v/>
       </c>
       <c r="B125" s="3">
@@ -46194,7 +46194,7 @@
         </is>
       </c>
       <c r="D125" s="5">
-        <f>IF(OR(A125="",C125="allocated"),"",MAX(E125,IF(ISNUMBER(I125),I125,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S125,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S125,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A125="",C125="allocated",C125="ruled"),"",MAX(E125,IF(ISNUMBER(I125),I125,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S125,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S125,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E125" s="5">
@@ -46313,7 +46313,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2">
-        <f>IF(OR(C126="yes",C126="allocated"),COUNT(A$1:A125)+1,"")</f>
+        <f>IF(OR(C126="yes",C126="allocated",C126="ruled"),COUNT(A$1:A125)+1,"")</f>
         <v/>
       </c>
       <c r="B126" s="3">
@@ -46326,7 +46326,7 @@
         </is>
       </c>
       <c r="D126" s="5">
-        <f>IF(OR(A126="",C126="allocated"),"",MAX(E126,IF(ISNUMBER(I126),I126,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S126,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S126,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A126="",C126="allocated",C126="ruled"),"",MAX(E126,IF(ISNUMBER(I126),I126,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S126,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S126,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E126" s="5">
@@ -46445,7 +46445,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2">
-        <f>IF(OR(C127="yes",C127="allocated"),COUNT(A$1:A126)+1,"")</f>
+        <f>IF(OR(C127="yes",C127="allocated",C127="ruled"),COUNT(A$1:A126)+1,"")</f>
         <v/>
       </c>
       <c r="B127" s="3">
@@ -46458,7 +46458,7 @@
         </is>
       </c>
       <c r="D127" s="5">
-        <f>IF(OR(A127="",C127="allocated"),"",MAX(E127,IF(ISNUMBER(I127),I127,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S127,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S127,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A127="",C127="allocated",C127="ruled"),"",MAX(E127,IF(ISNUMBER(I127),I127,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S127,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S127,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E127" s="5">
@@ -46577,7 +46577,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2">
-        <f>IF(OR(C128="yes",C128="allocated"),COUNT(A$1:A127)+1,"")</f>
+        <f>IF(OR(C128="yes",C128="allocated",C128="ruled"),COUNT(A$1:A127)+1,"")</f>
         <v/>
       </c>
       <c r="B128" s="3">
@@ -46590,7 +46590,7 @@
         </is>
       </c>
       <c r="D128" s="5">
-        <f>IF(OR(A128="",C128="allocated"),"",MAX(E128,IF(ISNUMBER(I128),I128,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S128,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S128,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A128="",C128="allocated",C128="ruled"),"",MAX(E128,IF(ISNUMBER(I128),I128,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S128,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S128,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E128" s="5">
@@ -46709,7 +46709,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2">
-        <f>IF(OR(C129="yes",C129="allocated"),COUNT(A$1:A128)+1,"")</f>
+        <f>IF(OR(C129="yes",C129="allocated",C129="ruled"),COUNT(A$1:A128)+1,"")</f>
         <v/>
       </c>
       <c r="B129" s="3">
@@ -46722,7 +46722,7 @@
         </is>
       </c>
       <c r="D129" s="5">
-        <f>IF(OR(A129="",C129="allocated"),"",MAX(E129,IF(ISNUMBER(I129),I129,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S129,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S129,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A129="",C129="allocated",C129="ruled"),"",MAX(E129,IF(ISNUMBER(I129),I129,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S129,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S129,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E129" s="5">
@@ -46841,7 +46841,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2">
-        <f>IF(OR(C130="yes",C130="allocated"),COUNT(A$1:A129)+1,"")</f>
+        <f>IF(OR(C130="yes",C130="allocated",C130="ruled"),COUNT(A$1:A129)+1,"")</f>
         <v/>
       </c>
       <c r="B130" s="3">
@@ -46854,7 +46854,7 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <f>IF(OR(A130="",C130="allocated"),"",MAX(E130,IF(ISNUMBER(I130),I130,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S130,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S130,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A130="",C130="allocated",C130="ruled"),"",MAX(E130,IF(ISNUMBER(I130),I130,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S130,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S130,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E130" s="5">
@@ -46973,7 +46973,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2">
-        <f>IF(OR(C131="yes",C131="allocated"),COUNT(A$1:A130)+1,"")</f>
+        <f>IF(OR(C131="yes",C131="allocated",C131="ruled"),COUNT(A$1:A130)+1,"")</f>
         <v/>
       </c>
       <c r="B131" s="3">
@@ -46986,7 +46986,7 @@
         </is>
       </c>
       <c r="D131" s="5">
-        <f>IF(OR(A131="",C131="allocated"),"",MAX(E131,IF(ISNUMBER(I131),I131,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S131,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S131,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A131="",C131="allocated",C131="ruled"),"",MAX(E131,IF(ISNUMBER(I131),I131,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S131,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S131,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E131" s="5">
@@ -47105,7 +47105,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2">
-        <f>IF(OR(C132="yes",C132="allocated"),COUNT(A$1:A131)+1,"")</f>
+        <f>IF(OR(C132="yes",C132="allocated",C132="ruled"),COUNT(A$1:A131)+1,"")</f>
         <v/>
       </c>
       <c r="B132" s="3">
@@ -47118,7 +47118,7 @@
         </is>
       </c>
       <c r="D132" s="5">
-        <f>IF(OR(A132="",C132="allocated"),"",MAX(E132,IF(ISNUMBER(I132),I132,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S132,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S132,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A132="",C132="allocated",C132="ruled"),"",MAX(E132,IF(ISNUMBER(I132),I132,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S132,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S132,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E132" s="5">
@@ -47237,7 +47237,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2">
-        <f>IF(OR(C133="yes",C133="allocated"),COUNT(A$1:A132)+1,"")</f>
+        <f>IF(OR(C133="yes",C133="allocated",C133="ruled"),COUNT(A$1:A132)+1,"")</f>
         <v/>
       </c>
       <c r="B133" s="3">
@@ -47250,7 +47250,7 @@
         </is>
       </c>
       <c r="D133" s="5">
-        <f>IF(OR(A133="",C133="allocated"),"",MAX(E133,IF(ISNUMBER(I133),I133,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S133,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S133,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A133="",C133="allocated",C133="ruled"),"",MAX(E133,IF(ISNUMBER(I133),I133,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S133,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S133,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E133" s="5">
@@ -47369,7 +47369,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2">
-        <f>IF(OR(C134="yes",C134="allocated"),COUNT(A$1:A133)+1,"")</f>
+        <f>IF(OR(C134="yes",C134="allocated",C134="ruled"),COUNT(A$1:A133)+1,"")</f>
         <v/>
       </c>
       <c r="B134" s="3">
@@ -47382,7 +47382,7 @@
         </is>
       </c>
       <c r="D134" s="5">
-        <f>IF(OR(A134="",C134="allocated"),"",MAX(E134,IF(ISNUMBER(I134),I134,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S134,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S134,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A134="",C134="allocated",C134="ruled"),"",MAX(E134,IF(ISNUMBER(I134),I134,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S134,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S134,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E134" s="5">
@@ -47501,7 +47501,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2">
-        <f>IF(OR(C135="yes",C135="allocated"),COUNT(A$1:A134)+1,"")</f>
+        <f>IF(OR(C135="yes",C135="allocated",C135="ruled"),COUNT(A$1:A134)+1,"")</f>
         <v/>
       </c>
       <c r="B135" s="3">
@@ -47514,7 +47514,7 @@
         </is>
       </c>
       <c r="D135" s="5">
-        <f>IF(OR(A135="",C135="allocated"),"",MAX(E135,IF(ISNUMBER(I135),I135,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S135,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S135,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A135="",C135="allocated",C135="ruled"),"",MAX(E135,IF(ISNUMBER(I135),I135,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S135,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S135,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E135" s="5">
@@ -47633,7 +47633,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2">
-        <f>IF(OR(C136="yes",C136="allocated"),COUNT(A$1:A135)+1,"")</f>
+        <f>IF(OR(C136="yes",C136="allocated",C136="ruled"),COUNT(A$1:A135)+1,"")</f>
         <v/>
       </c>
       <c r="B136" s="3">
@@ -47646,7 +47646,7 @@
         </is>
       </c>
       <c r="D136" s="5">
-        <f>IF(OR(A136="",C136="allocated"),"",MAX(E136,IF(ISNUMBER(I136),I136,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S136,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S136,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A136="",C136="allocated",C136="ruled"),"",MAX(E136,IF(ISNUMBER(I136),I136,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S136,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S136,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E136" s="5">
@@ -47765,7 +47765,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2">
-        <f>IF(OR(C137="yes",C137="allocated"),COUNT(A$1:A136)+1,"")</f>
+        <f>IF(OR(C137="yes",C137="allocated",C137="ruled"),COUNT(A$1:A136)+1,"")</f>
         <v/>
       </c>
       <c r="B137" s="3">
@@ -47897,7 +47897,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2">
-        <f>IF(OR(C138="yes",C138="allocated"),COUNT(A$1:A137)+1,"")</f>
+        <f>IF(OR(C138="yes",C138="allocated",C138="ruled"),COUNT(A$1:A137)+1,"")</f>
         <v/>
       </c>
       <c r="B138" s="3">
@@ -48029,7 +48029,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <f>IF(OR(C139="yes",C139="allocated"),COUNT(A$1:A138)+1,"")</f>
+        <f>IF(OR(C139="yes",C139="allocated",C139="ruled"),COUNT(A$1:A138)+1,"")</f>
         <v/>
       </c>
       <c r="B139" s="3">
@@ -48161,7 +48161,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <f>IF(OR(C140="yes",C140="allocated"),COUNT(A$1:A139)+1,"")</f>
+        <f>IF(OR(C140="yes",C140="allocated",C140="ruled"),COUNT(A$1:A139)+1,"")</f>
         <v/>
       </c>
       <c r="B140" s="3">
@@ -48293,7 +48293,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <f>IF(OR(C141="yes",C141="allocated"),COUNT(A$1:A140)+1,"")</f>
+        <f>IF(OR(C141="yes",C141="allocated",C141="ruled"),COUNT(A$1:A140)+1,"")</f>
         <v/>
       </c>
       <c r="B141" s="3">
@@ -48425,7 +48425,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <f>IF(OR(C142="yes",C142="allocated"),COUNT(A$1:A141)+1,"")</f>
+        <f>IF(OR(C142="yes",C142="allocated",C142="ruled"),COUNT(A$1:A141)+1,"")</f>
         <v/>
       </c>
       <c r="B142" s="3">
@@ -48557,7 +48557,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <f>IF(OR(C143="yes",C143="allocated"),COUNT(A$1:A142)+1,"")</f>
+        <f>IF(OR(C143="yes",C143="allocated",C143="ruled"),COUNT(A$1:A142)+1,"")</f>
         <v/>
       </c>
       <c r="B143" s="3">
@@ -48689,7 +48689,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2">
-        <f>IF(OR(C144="yes",C144="allocated"),COUNT(A$1:A143)+1,"")</f>
+        <f>IF(OR(C144="yes",C144="allocated",C144="ruled"),COUNT(A$1:A143)+1,"")</f>
         <v/>
       </c>
       <c r="B144" s="3">
@@ -48821,7 +48821,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2">
-        <f>IF(OR(C145="yes",C145="allocated"),COUNT(A$1:A144)+1,"")</f>
+        <f>IF(OR(C145="yes",C145="allocated",C145="ruled"),COUNT(A$1:A144)+1,"")</f>
         <v/>
       </c>
       <c r="B145" s="3">
@@ -48953,7 +48953,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2">
-        <f>IF(OR(C146="yes",C146="allocated"),COUNT(A$1:A145)+1,"")</f>
+        <f>IF(OR(C146="yes",C146="allocated",C146="ruled"),COUNT(A$1:A145)+1,"")</f>
         <v/>
       </c>
       <c r="B146" s="3">
@@ -49085,7 +49085,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2">
-        <f>IF(OR(C147="yes",C147="allocated"),COUNT(A$1:A146)+1,"")</f>
+        <f>IF(OR(C147="yes",C147="allocated",C147="ruled"),COUNT(A$1:A146)+1,"")</f>
         <v/>
       </c>
       <c r="B147" s="3">
@@ -49217,7 +49217,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2">
-        <f>IF(OR(C148="yes",C148="allocated"),COUNT(A$1:A147)+1,"")</f>
+        <f>IF(OR(C148="yes",C148="allocated",C148="ruled"),COUNT(A$1:A147)+1,"")</f>
         <v/>
       </c>
       <c r="B148" s="3">
@@ -49349,7 +49349,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2">
-        <f>IF(OR(C149="yes",C149="allocated"),COUNT(A$1:A148)+1,"")</f>
+        <f>IF(OR(C149="yes",C149="allocated",C149="ruled"),COUNT(A$1:A148)+1,"")</f>
         <v/>
       </c>
       <c r="B149" s="3">
@@ -49481,7 +49481,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2">
-        <f>IF(OR(C150="yes",C150="allocated"),COUNT(A$1:A149)+1,"")</f>
+        <f>IF(OR(C150="yes",C150="allocated",C150="ruled"),COUNT(A$1:A149)+1,"")</f>
         <v/>
       </c>
       <c r="B150" s="3">
@@ -49613,7 +49613,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2">
-        <f>IF(OR(C151="yes",C151="allocated"),COUNT(A$1:A150)+1,"")</f>
+        <f>IF(OR(C151="yes",C151="allocated",C151="ruled"),COUNT(A$1:A150)+1,"")</f>
         <v/>
       </c>
       <c r="B151" s="3">
@@ -49745,7 +49745,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2">
-        <f>IF(OR(C152="yes",C152="allocated"),COUNT(A$1:A151)+1,"")</f>
+        <f>IF(OR(C152="yes",C152="allocated",C152="ruled"),COUNT(A$1:A151)+1,"")</f>
         <v/>
       </c>
       <c r="B152" s="3">
@@ -49877,7 +49877,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2">
-        <f>IF(OR(C153="yes",C153="allocated"),COUNT(A$1:A152)+1,"")</f>
+        <f>IF(OR(C153="yes",C153="allocated",C153="ruled"),COUNT(A$1:A152)+1,"")</f>
         <v/>
       </c>
       <c r="B153" s="3">
@@ -50009,7 +50009,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2">
-        <f>IF(OR(C154="yes",C154="allocated"),COUNT(A$1:A153)+1,"")</f>
+        <f>IF(OR(C154="yes",C154="allocated",C154="ruled"),COUNT(A$1:A153)+1,"")</f>
         <v/>
       </c>
       <c r="B154" s="3">
@@ -50141,7 +50141,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2">
-        <f>IF(OR(C155="yes",C155="allocated"),COUNT(A$1:A154)+1,"")</f>
+        <f>IF(OR(C155="yes",C155="allocated",C155="ruled"),COUNT(A$1:A154)+1,"")</f>
         <v/>
       </c>
       <c r="B155" s="3">
@@ -50273,7 +50273,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2">
-        <f>IF(OR(C156="yes",C156="allocated"),COUNT(A$1:A155)+1,"")</f>
+        <f>IF(OR(C156="yes",C156="allocated",C156="ruled"),COUNT(A$1:A155)+1,"")</f>
         <v/>
       </c>
       <c r="B156" s="3">
@@ -50405,7 +50405,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2">
-        <f>IF(OR(C157="yes",C157="allocated"),COUNT(A$1:A156)+1,"")</f>
+        <f>IF(OR(C157="yes",C157="allocated",C157="ruled"),COUNT(A$1:A156)+1,"")</f>
         <v/>
       </c>
       <c r="B157" s="3">
@@ -50537,7 +50537,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2">
-        <f>IF(OR(C158="yes",C158="allocated"),COUNT(A$1:A157)+1,"")</f>
+        <f>IF(OR(C158="yes",C158="allocated",C158="ruled"),COUNT(A$1:A157)+1,"")</f>
         <v/>
       </c>
       <c r="B158" s="3">
@@ -50669,7 +50669,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2">
-        <f>IF(OR(C159="yes",C159="allocated"),COUNT(A$1:A158)+1,"")</f>
+        <f>IF(OR(C159="yes",C159="allocated",C159="ruled"),COUNT(A$1:A158)+1,"")</f>
         <v/>
       </c>
       <c r="B159" s="3">
@@ -50801,7 +50801,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2">
-        <f>IF(OR(C160="yes",C160="allocated"),COUNT(A$1:A159)+1,"")</f>
+        <f>IF(OR(C160="yes",C160="allocated",C160="ruled"),COUNT(A$1:A159)+1,"")</f>
         <v/>
       </c>
       <c r="B160" s="3">
@@ -50933,7 +50933,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2">
-        <f>IF(OR(C161="yes",C161="allocated"),COUNT(A$1:A160)+1,"")</f>
+        <f>IF(OR(C161="yes",C161="allocated",C161="ruled"),COUNT(A$1:A160)+1,"")</f>
         <v/>
       </c>
       <c r="B161" s="3">
@@ -51065,7 +51065,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2">
-        <f>IF(OR(C162="yes",C162="allocated"),COUNT(A$1:A161)+1,"")</f>
+        <f>IF(OR(C162="yes",C162="allocated",C162="ruled"),COUNT(A$1:A161)+1,"")</f>
         <v/>
       </c>
       <c r="B162" s="3">
@@ -51197,7 +51197,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2">
-        <f>IF(OR(C163="yes",C163="allocated"),COUNT(A$1:A162)+1,"")</f>
+        <f>IF(OR(C163="yes",C163="allocated",C163="ruled"),COUNT(A$1:A162)+1,"")</f>
         <v/>
       </c>
       <c r="B163" s="3">
@@ -51329,7 +51329,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2">
-        <f>IF(OR(C164="yes",C164="allocated"),COUNT(A$1:A163)+1,"")</f>
+        <f>IF(OR(C164="yes",C164="allocated",C164="ruled"),COUNT(A$1:A163)+1,"")</f>
         <v/>
       </c>
       <c r="B164" s="3">
@@ -51461,7 +51461,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2">
-        <f>IF(OR(C165="yes",C165="allocated"),COUNT(A$1:A164)+1,"")</f>
+        <f>IF(OR(C165="yes",C165="allocated",C165="ruled"),COUNT(A$1:A164)+1,"")</f>
         <v/>
       </c>
       <c r="B165" s="3">
@@ -51593,7 +51593,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2">
-        <f>IF(OR(C166="yes",C166="allocated"),COUNT(A$1:A165)+1,"")</f>
+        <f>IF(OR(C166="yes",C166="allocated",C166="ruled"),COUNT(A$1:A165)+1,"")</f>
         <v/>
       </c>
       <c r="B166" s="3">
@@ -51725,40 +51725,42 @@
     </row>
     <row r="167">
       <c r="A167" s="2">
-        <f>IF(OR(C167="yes",C167="allocated"),COUNT(A$1:A166)+1,"")</f>
+        <f>IF(OR(C167="yes",C167="allocated",C167="ruled"),COUNT(A$1:A166)+1,"")</f>
         <v/>
       </c>
       <c r="B167" s="3">
         <f>IF(A167&lt;&gt;"","CoQ-PP_26-"&amp;TEXT(A167,"000"),"— at issue —")</f>
         <v/>
       </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>ruled</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <f>IF(OR(A167="",C167="allocated"),"",MAX(E167,IF(ISNUMBER(I167),I167,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S167,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S167,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A167="",C167="allocated",C167="ruled"),"",MAX(E167,IF(ISNUMBER(I167),I167,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S167,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S167,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E167" s="5">
         <f>IF(ISNUMBER(F167),MAX(DATE(2026,6,6),F167+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F167" s="5" t="n">
-        <v>46209</v>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>ППК26117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H167" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P160012|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("CC042601|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I167" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P160012|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("CC042601|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -51773,23 +51775,27 @@
       </c>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>— not recorded — (P160012)</t>
+          <t>CC042601</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="N167" s="2" t="inlineStr"/>
-      <c r="O167" s="2" t="inlineStr">
-        <is>
-          <t>ППК26117, (06.07.2026) [CNP]</t>
-        </is>
-      </c>
-      <c r="P167" s="2" t="inlineStr">
-        <is>
-          <t>A: ППК26117 / B: ППК26117 / FM: ППК26117</t>
+          <t>N/A — no P batch assigned</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="O167" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
+        </is>
+      </c>
+      <c r="P167" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -51804,12 +51810,12 @@
       </c>
       <c r="S167" s="2" t="inlineStr">
         <is>
-          <t>P160012|I</t>
-        </is>
-      </c>
-      <c r="T167" s="10" t="inlineStr">
-        <is>
-          <t>not yet issuable — no packaging date on the list</t>
+          <t>CC042601|I</t>
+        </is>
+      </c>
+      <c r="T167" s="13" t="inlineStr">
+        <is>
+          <t>ruled — numbered on the Head of QC's instruction of 18.09.2026 ("assign codes if they're missing"); the list holds no packaging date for the lot, so the register could not date the certificate and had withheld the number; the date follows the packaging date once the list carries it</t>
         </is>
       </c>
       <c r="U167" s="2" t="inlineStr">
@@ -51817,12 +51823,14 @@
           <t>n/a — initial certificate</t>
         </is>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>26.32</v>
+      <c r="V167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W167" s="2" t="inlineStr">
         <is>
-          <t>ППК26117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="X167" s="2" t="inlineStr">
@@ -51852,46 +51860,48 @@
       </c>
       <c r="AC167" s="10" t="inlineStr">
         <is>
-          <t>strain not in the potency specification of 15.09.2026</t>
+          <t>no Total THC result on this certificate</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2">
-        <f>IF(OR(C168="yes",C168="allocated"),COUNT(A$1:A167)+1,"")</f>
+        <f>IF(OR(C168="yes",C168="allocated",C168="ruled"),COUNT(A$1:A167)+1,"")</f>
         <v/>
       </c>
       <c r="B168" s="3">
         <f>IF(A168&lt;&gt;"","CoQ-PP_26-"&amp;TEXT(A168,"000"),"— at issue —")</f>
         <v/>
       </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="C168" s="12" t="inlineStr">
+        <is>
+          <t>ruled</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <f>IF(OR(A168="",C168="allocated"),"",MAX(E168,IF(ISNUMBER(I168),I168,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S168,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S168,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A168="",C168="allocated",C168="ruled"),"",MAX(E168,IF(ISNUMBER(I168),I168,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S168,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S168,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E168" s="5">
         <f>IF(ISNUMBER(F168),MAX(DATE(2026,6,6),F168+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F168" s="5" t="n">
-        <v>46209</v>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>ППК26118</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H168" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P160022|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("FB042601|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I168" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P160022|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("FB042601|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -51906,23 +51916,27 @@
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>— not recorded — (P160022)</t>
+          <t>FB042601</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>P160022</t>
-        </is>
-      </c>
-      <c r="N168" s="2" t="inlineStr"/>
-      <c r="O168" s="2" t="inlineStr">
-        <is>
-          <t>ППК26118, (06.07.2026) [CNP]</t>
-        </is>
-      </c>
-      <c r="P168" s="2" t="inlineStr">
-        <is>
-          <t>A: ППК26118 / B: ППК26118 / FM: ППК26118</t>
+          <t>N/A — no P batch assigned</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="O168" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
+        </is>
+      </c>
+      <c r="P168" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -51937,12 +51951,12 @@
       </c>
       <c r="S168" s="2" t="inlineStr">
         <is>
-          <t>P160022|I</t>
-        </is>
-      </c>
-      <c r="T168" s="10" t="inlineStr">
-        <is>
-          <t>not yet issuable — no packaging date on the list</t>
+          <t>FB042601|I</t>
+        </is>
+      </c>
+      <c r="T168" s="13" t="inlineStr">
+        <is>
+          <t>ruled — numbered on the Head of QC's instruction of 18.09.2026 ("assign codes if they're missing"); the list holds no packaging date for the lot, so the register could not date the certificate and had withheld the number; the date follows the packaging date once the list carries it</t>
         </is>
       </c>
       <c r="U168" s="2" t="inlineStr">
@@ -51950,12 +51964,14 @@
           <t>n/a — initial certificate</t>
         </is>
       </c>
-      <c r="V168" s="9" t="n">
-        <v>25.72</v>
+      <c r="V168" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W168" s="2" t="inlineStr">
         <is>
-          <t>ППК26118</t>
+          <t>—</t>
         </is>
       </c>
       <c r="X168" s="2" t="inlineStr">
@@ -51985,26 +52001,26 @@
       </c>
       <c r="AC168" s="10" t="inlineStr">
         <is>
-          <t>strain not in the potency specification of 15.09.2026</t>
+          <t>no Total THC result on this certificate</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2">
-        <f>IF(OR(C169="yes",C169="allocated"),COUNT(A$1:A168)+1,"")</f>
+        <f>IF(OR(C169="yes",C169="allocated",C169="ruled"),COUNT(A$1:A168)+1,"")</f>
         <v/>
       </c>
       <c r="B169" s="3">
         <f>IF(A169&lt;&gt;"","CoQ-PP_26-"&amp;TEXT(A169,"000"),"— at issue —")</f>
         <v/>
       </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="C169" s="12" t="inlineStr">
+        <is>
+          <t>ruled</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <f>IF(OR(A169="",C169="allocated"),"",MAX(E169,IF(ISNUMBER(I169),I169,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S169,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S169,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A169="",C169="allocated",C169="ruled"),"",MAX(E169,IF(ISNUMBER(I169),I169,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S169,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S169,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E169" s="5">
@@ -52016,15 +52032,15 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>ППК26119</t>
+          <t>ППК26117</t>
         </is>
       </c>
       <c r="H169" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P160032|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P160012|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I169" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P160032|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P160012|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -52039,23 +52055,23 @@
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>— not recorded — (P160032)</t>
+          <t>— not recorded — (P160012)</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr"/>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>ППК26119, (06.07.2026) [CNP]</t>
+          <t>ППК26117, (06.07.2026) [CNP]</t>
         </is>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26119 / B: ППК26119 / FM: ППК26119</t>
+          <t>A: ППК26117 / B: ППК26117 / FM: ППК26117</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -52070,12 +52086,12 @@
       </c>
       <c r="S169" s="2" t="inlineStr">
         <is>
-          <t>P160032|I</t>
-        </is>
-      </c>
-      <c r="T169" s="10" t="inlineStr">
-        <is>
-          <t>not yet issuable — no packaging date on the list</t>
+          <t>P160012|I</t>
+        </is>
+      </c>
+      <c r="T169" s="13" t="inlineStr">
+        <is>
+          <t>ruled — numbered on the Head of QC's instruction of 18.09.2026 ("assign codes if they're missing"); the list holds no packaging date for the lot, so the register could not date the certificate and had withheld the number; the date follows the packaging date once the list carries it</t>
         </is>
       </c>
       <c r="U169" s="2" t="inlineStr">
@@ -52084,11 +52100,11 @@
         </is>
       </c>
       <c r="V169" s="9" t="n">
-        <v>24.78</v>
+        <v>26.32</v>
       </c>
       <c r="W169" s="2" t="inlineStr">
         <is>
-          <t>ППК26119</t>
+          <t>ППК26117</t>
         </is>
       </c>
       <c r="X169" s="2" t="inlineStr">
@@ -52124,42 +52140,40 @@
     </row>
     <row r="170">
       <c r="A170" s="2">
-        <f>IF(OR(C170="yes",C170="allocated"),COUNT(A$1:A169)+1,"")</f>
+        <f>IF(OR(C170="yes",C170="allocated",C170="ruled"),COUNT(A$1:A169)+1,"")</f>
         <v/>
       </c>
       <c r="B170" s="3">
         <f>IF(A170&lt;&gt;"","CoQ-PP_26-"&amp;TEXT(A170,"000"),"— at issue —")</f>
         <v/>
       </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>ruled</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <f>IF(OR(A170="",C170="allocated"),"",MAX(E170,IF(ISNUMBER(I170),I170,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S170,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S170,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A170="",C170="allocated",C170="ruled"),"",MAX(E170,IF(ISNUMBER(I170),I170,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S170,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S170,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E170" s="5">
         <f>IF(ISNUMBER(F170),MAX(DATE(2026,6,6),F170+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F170" s="5" t="n">
+        <v>46209</v>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ППК26118</t>
         </is>
       </c>
       <c r="H170" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("CC042601|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P160022|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I170" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("CC042601|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P160022|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -52174,27 +52188,23 @@
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>CC042601</t>
+          <t>— not recorded — (P160022)</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
-        </is>
-      </c>
-      <c r="N170" s="2" t="inlineStr">
-        <is>
-          <t>Cash Cow</t>
-        </is>
-      </c>
-      <c r="O170" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
-        </is>
-      </c>
-      <c r="P170" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>P160022</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>ППК26118, (06.07.2026) [CNP]</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>A: ППК26118 / B: ППК26118 / FM: ППК26118</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -52209,12 +52219,12 @@
       </c>
       <c r="S170" s="2" t="inlineStr">
         <is>
-          <t>CC042601|I</t>
-        </is>
-      </c>
-      <c r="T170" s="10" t="inlineStr">
-        <is>
-          <t>not yet issuable — no packaging date on the list</t>
+          <t>P160022|I</t>
+        </is>
+      </c>
+      <c r="T170" s="13" t="inlineStr">
+        <is>
+          <t>ruled — numbered on the Head of QC's instruction of 18.09.2026 ("assign codes if they're missing"); the list holds no packaging date for the lot, so the register could not date the certificate and had withheld the number; the date follows the packaging date once the list carries it</t>
         </is>
       </c>
       <c r="U170" s="2" t="inlineStr">
@@ -52222,14 +52232,12 @@
           <t>n/a — initial certificate</t>
         </is>
       </c>
-      <c r="V170" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="V170" s="9" t="n">
+        <v>25.72</v>
       </c>
       <c r="W170" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ППК26118</t>
         </is>
       </c>
       <c r="X170" s="2" t="inlineStr">
@@ -52259,46 +52267,46 @@
       </c>
       <c r="AC170" s="10" t="inlineStr">
         <is>
-          <t>no Total THC result on this certificate</t>
+          <t>strain not in the potency specification of 15.09.2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2">
-        <f>IF(OR(C171="yes",C171="allocated"),COUNT(A$1:A170)+1,"")</f>
+        <f>IF(OR(C171="yes",C171="allocated",C171="ruled"),COUNT(A$1:A170)+1,"")</f>
         <v/>
       </c>
       <c r="B171" s="3">
         <f>IF(A171&lt;&gt;"","CoQ-PP_26-"&amp;TEXT(A171,"000"),"— at issue —")</f>
         <v/>
       </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>ruled</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <f>IF(OR(A171="",C171="allocated"),"",MAX(E171,IF(ISNUMBER(I171),I171,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S171,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S171,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A171="",C171="allocated",C171="ruled"),"",MAX(E171,IF(ISNUMBER(I171),I171,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S171,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S171,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E171" s="5">
-        <f>IF(ISNUMBER(F171),MAX(DATE(2026,6,6),F171+7),"— awaiting the retest certificates —")</f>
+        <f>IF(ISNUMBER(F171),MAX(DATE(2026,6,6),F171+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F171" s="5" t="n">
-        <v>46276</v>
+        <v>46209</v>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>220-32-M-26</t>
+          <t>ППК26119</t>
         </is>
       </c>
       <c r="H171" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("CC042601|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P160032|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I171" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("CC042601|R",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P160032|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -52308,32 +52316,28 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>retest — Tranche 2 (sampled 12–14.08.2026)</t>
+          <t>initial release</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>CC042601</t>
+          <t>— not recorded — (P160032)</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>Cash Cow</t>
-        </is>
-      </c>
+          <t>P160032</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr"/>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>220-32-K-26, (26.08.2026) [FHM-K]</t>
-        </is>
-      </c>
-      <c r="P171" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ППК26119, (06.07.2026) [CNP]</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>A: ППК26119 / B: ППК26119 / FM: ППК26119</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -52343,96 +52347,99 @@
       </c>
       <c r="R171" s="2" t="inlineStr">
         <is>
-          <t>CoQ reissue (assigned on issue)</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S171" s="2" t="inlineStr">
         <is>
-          <t>CC042601|R</t>
-        </is>
-      </c>
-      <c r="T171" s="10" t="inlineStr">
-        <is>
-          <t>not yet issuable — initial certificate withheld — due — retest assay and mycotoxins on file; iCoA tested 14.08.2026, issued 17.08.2026 · issued 7 days after the latest retest certificate once the assay, the mycotoxins and the iCoA exist</t>
-        </is>
-      </c>
-      <c r="U171" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("CC042601|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
-        <v/>
+          <t>P160032|I</t>
+        </is>
+      </c>
+      <c r="T171" s="13" t="inlineStr">
+        <is>
+          <t>ruled — numbered on the Head of QC's instruction of 18.09.2026 ("assign codes if they're missing"); the list holds no packaging date for the lot, so the register could not date the certificate and had withheld the number; the date follows the packaging date once the list carries it</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>n/a — initial certificate</t>
+        </is>
       </c>
       <c r="V171" s="9" t="n">
-        <v>14.9</v>
+        <v>24.78</v>
       </c>
       <c r="W171" s="2" t="inlineStr">
         <is>
-          <t>220-32-К/26</t>
+          <t>ППК26119</t>
         </is>
       </c>
       <c r="X171" s="2" t="inlineStr">
         <is>
-          <t>14.00 ± 1.35 (II)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Y171" s="2" t="inlineStr">
         <is>
-          <t>12.65 – 15.34 %</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Z171" s="2" t="inlineStr">
         <is>
-          <t>CC_THC14 : CBD1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA171" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_CC-II_v.01</t>
-        </is>
-      </c>
-      <c r="AB171" s="10" t="inlineStr">
-        <is>
-          <t>for review — replaces the issued QCSP_001_CC-II_v.01 (was CC_THC14 : CBD1, 12.60 – 15.40 %); now CC_THC14 : CBD1 12.65 – 15.34 %</t>
-        </is>
-      </c>
-      <c r="AC171" s="11" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB171" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC171" s="10" t="inlineStr">
+        <is>
+          <t>strain not in the potency specification of 15.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2">
-        <f>IF(OR(C172="yes",C172="allocated"),COUNT(A$1:A171)+1,"")</f>
+        <f>IF(OR(C172="yes",C172="allocated",C172="ruled"),COUNT(A$1:A171)+1,"")</f>
         <v/>
       </c>
       <c r="B172" s="3">
         <f>IF(A172&lt;&gt;"","CoQ-PP_26-"&amp;TEXT(A172,"000"),"— at issue —")</f>
         <v/>
       </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>ruled</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <f>IF(OR(A172="",C172="allocated"),"",MAX(E172,IF(ISNUMBER(I172),I172,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S172,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S172,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A172="",C172="allocated",C172="ruled"),"",MAX(E172,IF(ISNUMBER(I172),I172,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S172,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S172,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E172" s="5">
-        <f>IF(ISNUMBER(F172),MAX(DATE(2026,6,6),F172+7),DATE(2026,6,6))</f>
-        <v/>
-      </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <f>IF(ISNUMBER(F172),MAX(DATE(2026,6,6),F172+7),"— awaiting the retest certificates —")</f>
+        <v/>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>46276</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220-32-M-26</t>
         </is>
       </c>
       <c r="H172" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("FB042601|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("CC042601|R",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I172" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("FB042601|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("CC042601|R",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -52442,12 +52449,12 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>initial release</t>
+          <t>retest — Tranche 2 (sampled 12–14.08.2026)</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>FB042601</t>
+          <t>CC042601</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
@@ -52457,12 +52464,12 @@
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
-      <c r="O172" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>220-32-K-26, (26.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P172" s="6" t="inlineStr">
@@ -52477,81 +52484,74 @@
       </c>
       <c r="R172" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ reissue (assigned on issue)</t>
         </is>
       </c>
       <c r="S172" s="2" t="inlineStr">
         <is>
-          <t>FB042601|I</t>
-        </is>
-      </c>
-      <c r="T172" s="10" t="inlineStr">
-        <is>
-          <t>not yet issuable — no packaging date on the list</t>
-        </is>
-      </c>
-      <c r="U172" s="2" t="inlineStr">
-        <is>
-          <t>n/a — initial certificate</t>
-        </is>
-      </c>
-      <c r="V172" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>CC042601|R</t>
+        </is>
+      </c>
+      <c r="T172" s="13" t="inlineStr">
+        <is>
+          <t>ruled — numbered on the Head of QC's instruction of 18.09.2026 ("assign codes if they're missing"); the list holds no packaging date for the lot, so the register could not date the certificate and had withheld the number; the date follows the packaging date once the list carries it; a reissue, numbered after its release certificate — initial certificate withheld — due — retest assay and mycotoxins on file; iCoA tested 14.08.2026, issued 17.08.2026</t>
+        </is>
+      </c>
+      <c r="U172" s="2">
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("CC042601|I",'CoQ Register'!$S:$S,0)),"— initial certificate not on the register —")</f>
+        <v/>
+      </c>
+      <c r="V172" s="9" t="n">
+        <v>14.9</v>
       </c>
       <c r="W172" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220-32-К/26</t>
         </is>
       </c>
       <c r="X172" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.00 ± 1.35 (II)</t>
         </is>
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.65 – 15.34 %</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CC_THC14 : CBD1</t>
         </is>
       </c>
       <c r="AA172" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB172" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC172" s="10" t="inlineStr">
-        <is>
-          <t>no Total THC result on this certificate</t>
-        </is>
-      </c>
+          <t>QCSP_001_CC-II_v.01</t>
+        </is>
+      </c>
+      <c r="AB172" s="10" t="inlineStr">
+        <is>
+          <t>for review — replaces the issued QCSP_001_CC-II_v.01 (was CC_THC14 : CBD1, 12.60 – 15.40 %); now CC_THC14 : CBD1 12.65 – 15.34 %</t>
+        </is>
+      </c>
+      <c r="AC172" s="11" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2">
-        <f>IF(OR(C173="yes",C173="allocated"),COUNT(A$1:A172)+1,"")</f>
+        <f>IF(OR(C173="yes",C173="allocated",C173="ruled"),COUNT(A$1:A172)+1,"")</f>
         <v/>
       </c>
       <c r="B173" s="3">
         <f>IF(A173&lt;&gt;"","CoQ-PP_26-"&amp;TEXT(A173,"000"),"— at issue —")</f>
         <v/>
       </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>ruled</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <f>IF(OR(A173="",C173="allocated"),"",MAX(E173,IF(ISNUMBER(I173),I173,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S173,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S173,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
+        <f>IF(OR(A173="",C173="allocated",C173="ruled"),"",MAX(E173,IF(ISNUMBER(I173),I173,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S173,'iCoA Register'!$AA:$AA,0))),INDEX('iCoA Register'!$F:$F,MATCH(S173,'iCoA Register'!$AA:$AA,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E173" s="5">
@@ -52624,9 +52624,9 @@
           <t>FB042601|R</t>
         </is>
       </c>
-      <c r="T173" s="10" t="inlineStr">
-        <is>
-          <t>not yet issuable — initial certificate withheld — due — retest assay and mycotoxins on file; iCoA tested 14.08.2026, issued 17.08.2026 · issued 7 days after the latest retest certificate once the assay, the mycotoxins and the iCoA exist</t>
+      <c r="T173" s="13" t="inlineStr">
+        <is>
+          <t>ruled — numbered on the Head of QC's instruction of 18.09.2026 ("assign codes if they're missing"); the list holds no packaging date for the lot, so the register could not date the certificate and had withheld the number; the date follows the packaging date once the list carries it; a reissue, numbered after its release certificate — initial certificate withheld — due — retest assay and mycotoxins on file; iCoA tested 14.08.2026, issued 17.08.2026</t>
         </is>
       </c>
       <c r="U173" s="2">
@@ -52672,7 +52672,7 @@
     <row r="175" ht="150" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
@@ -56043,7 +56043,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v46 on 18.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v47 on 18.09.2026</t>
         </is>
       </c>
     </row>
@@ -56057,14 +56057,14 @@
     <row r="3" ht="190" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). FORMULAS: No. counts the rows whose Issuable is 'yes' or 'allocated'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v46.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v47.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -56043,7 +56043,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v47 on 18.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v48 on 18.09.2026</t>
         </is>
       </c>
     </row>
@@ -56064,7 +56064,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v47.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v48.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -32051,7 +32051,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP_26-024</t>
+          <t>iCoA-PP_26-023</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
@@ -32184,7 +32184,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP_26-025</t>
+          <t>iCoA-PP_26-024</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
@@ -54954,7 +54954,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v49 on 20.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v50 on 20.09.2026</t>
         </is>
       </c>
     </row>
@@ -54975,7 +54975,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v49.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v50.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -54954,7 +54954,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v50 on 20.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v51 on 20.09.2026</t>
         </is>
       </c>
     </row>
@@ -54975,7 +54975,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v50.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v51.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -46748,7 +46748,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr"/>
+      <c r="D137" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -46822,7 +46824,7 @@
       </c>
       <c r="T137" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-30-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-30-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U137" s="2">
@@ -46878,7 +46880,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D138" s="5" t="inlineStr"/>
+      <c r="D138" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -46952,7 +46956,7 @@
       </c>
       <c r="T138" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-29-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-29-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U138" s="2">
@@ -47008,7 +47012,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr"/>
+      <c r="D139" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47082,7 +47088,7 @@
       </c>
       <c r="T139" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-1-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-1-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U139" s="2">
@@ -47138,7 +47144,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr"/>
+      <c r="D140" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47212,7 +47220,7 @@
       </c>
       <c r="T140" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-25-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-25-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U140" s="2">
@@ -47268,7 +47276,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D141" s="5" t="inlineStr"/>
+      <c r="D141" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47342,7 +47352,7 @@
       </c>
       <c r="T141" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-28-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-28-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U141" s="2">
@@ -47398,7 +47408,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr"/>
+      <c r="D142" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47472,7 +47484,7 @@
       </c>
       <c r="T142" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-27-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-27-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U142" s="2">
@@ -47528,7 +47540,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr"/>
+      <c r="D143" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47602,7 +47616,7 @@
       </c>
       <c r="T143" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-26-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-26-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U143" s="2">
@@ -47658,7 +47672,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr"/>
+      <c r="D144" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47732,7 +47748,7 @@
       </c>
       <c r="T144" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-24-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-24-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U144" s="2">
@@ -47788,7 +47804,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr"/>
+      <c r="D145" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47862,7 +47880,7 @@
       </c>
       <c r="T145" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-23-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-23-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U145" s="2">
@@ -47918,7 +47936,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D146" s="5" t="inlineStr"/>
+      <c r="D146" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -47992,7 +48012,7 @@
       </c>
       <c r="T146" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-22-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-22-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U146" s="2">
@@ -48048,7 +48068,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr"/>
+      <c r="D147" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48122,7 +48144,7 @@
       </c>
       <c r="T147" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-21-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 21.08.2026, retest assay 227-21-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U147" s="2">
@@ -48178,7 +48200,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D148" s="5" t="inlineStr"/>
+      <c r="D148" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48252,7 +48276,7 @@
       </c>
       <c r="T148" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-19-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-19-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U148" s="2">
@@ -48308,7 +48332,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr"/>
+      <c r="D149" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48382,7 +48408,7 @@
       </c>
       <c r="T149" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-20-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-20-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U149" s="2">
@@ -48438,7 +48464,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr"/>
+      <c r="D150" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48512,7 +48540,7 @@
       </c>
       <c r="T150" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-18-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-18-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U150" s="2">
@@ -48568,7 +48596,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr"/>
+      <c r="D151" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48642,7 +48672,7 @@
       </c>
       <c r="T151" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-17-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-17-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U151" s="2">
@@ -48698,7 +48728,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D152" s="5" t="inlineStr"/>
+      <c r="D152" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48772,7 +48804,7 @@
       </c>
       <c r="T152" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-2-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-2-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U152" s="2">
@@ -48828,7 +48860,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D153" s="5" t="inlineStr"/>
+      <c r="D153" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -48902,7 +48936,7 @@
       </c>
       <c r="T153" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-16-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-16-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U153" s="2">
@@ -48958,7 +48992,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D154" s="5" t="inlineStr"/>
+      <c r="D154" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49032,7 +49068,7 @@
       </c>
       <c r="T154" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-14-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-14-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U154" s="2">
@@ -49088,7 +49124,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D155" s="5" t="inlineStr"/>
+      <c r="D155" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49162,7 +49200,7 @@
       </c>
       <c r="T155" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay — pending — on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay — pending — on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U155" s="2">
@@ -49218,7 +49256,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D156" s="5" t="inlineStr"/>
+      <c r="D156" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49292,7 +49332,7 @@
       </c>
       <c r="T156" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-15-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-15-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U156" s="2">
@@ -49348,7 +49388,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D157" s="5" t="inlineStr"/>
+      <c r="D157" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49422,7 +49464,7 @@
       </c>
       <c r="T157" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-12-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-12-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U157" s="2">
@@ -49478,7 +49520,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D158" s="5" t="inlineStr"/>
+      <c r="D158" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49552,7 +49596,7 @@
       </c>
       <c r="T158" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-11-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 20.08.2026, retest assay 227-11-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U158" s="2">
@@ -49608,7 +49652,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr"/>
+      <c r="D159" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49682,7 +49728,7 @@
       </c>
       <c r="T159" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-10-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-10-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U159" s="2">
@@ -49738,7 +49784,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D160" s="5" t="inlineStr"/>
+      <c r="D160" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49812,7 +49860,7 @@
       </c>
       <c r="T160" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-9-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-9-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U160" s="2">
@@ -49868,7 +49916,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D161" s="5" t="inlineStr"/>
+      <c r="D161" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -49942,7 +49992,7 @@
       </c>
       <c r="T161" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-8-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-8-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U161" s="2">
@@ -49998,7 +50048,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D162" s="5" t="inlineStr"/>
+      <c r="D162" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50072,7 +50124,7 @@
       </c>
       <c r="T162" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-7-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-7-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U162" s="2">
@@ -50128,7 +50180,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D163" s="5" t="inlineStr"/>
+      <c r="D163" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50202,7 +50256,7 @@
       </c>
       <c r="T163" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-6-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-6-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U163" s="2">
@@ -50258,7 +50312,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D164" s="5" t="inlineStr"/>
+      <c r="D164" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50332,7 +50388,7 @@
       </c>
       <c r="T164" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-5-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites iCoA-PP_26-150 of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-5-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites iCoA-PP_26-150 of 24.08.2026</t>
         </is>
       </c>
       <c r="U164" s="2">
@@ -50388,7 +50444,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D165" s="5" t="inlineStr"/>
+      <c r="D165" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50462,7 +50520,7 @@
       </c>
       <c r="T165" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-3-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-3-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U165" s="2">
@@ -50518,7 +50576,9 @@
           <t>allocated</t>
         </is>
       </c>
-      <c r="D166" s="5" t="inlineStr"/>
+      <c r="D166" s="5" t="n">
+        <v>46286</v>
+      </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
           <t>— the owner's date for all of Tranche 3 (15.09.2026), the 227-М certificates expected by 18.09.2026; provisional —</t>
@@ -50592,7 +50652,7 @@
       </c>
       <c r="T166" s="13" t="inlineStr">
         <is>
-          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-4-K-26 on file, mycotoxins pending; issued on the owner's date once the 227-М certificate exists, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
+          <t>allocated — code reserved 15.09.2026 for the Tranche 3 (sampled 19–21.08.2026) reissue (owner: every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date); sampled 19.08.2026, retest assay 227-4-K-26 on file, mycotoxins pending; planned 21.09.2026 — the owner's date of 15.09.2026 for all of Tranche 3, the 227-М certificates expected by 18.09.2026, provisional until they exist, after every Tranche 2 reissue; cites the campaign iCoA of 24.08.2026</t>
         </is>
       </c>
       <c r="U166" s="2">
@@ -51583,7 +51643,7 @@
     <row r="175" ht="150" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
@@ -54954,7 +55014,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v51 on 20.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v52 on 20.09.2026</t>
         </is>
       </c>
     </row>
@@ -54968,14 +55028,14 @@
     <row r="3" ht="190" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: not yet set, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v51.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v52.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -55014,7 +55014,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v52 on 20.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v53 on 20.09.2026</t>
         </is>
       </c>
     </row>
@@ -55035,7 +55035,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v52.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v53.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -6697,7 +6697,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+          <t>031-3-К-26, (10.02.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+          <t>031-2-К-26, (10.02.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+          <t>031-5-К-26, (10.02.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+          <t>031-4-К-26, (10.02.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
@@ -29157,14 +29157,12 @@
         <f>IF(ISNUMBER(F5),MAX(DATE(2026,6,6),F5+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F5" s="5" t="n">
+        <v>45720</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>748-2025</t>
         </is>
       </c>
       <c r="H5" s="2">
@@ -29227,7 +29225,7 @@
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP)</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -34804,9 +34802,9 @@
           <t>Wedding Cake</t>
         </is>
       </c>
-      <c r="O47" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>031-3-К-26, (10.02.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
@@ -34831,7 +34829,7 @@
       </c>
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ)</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -34839,14 +34837,12 @@
           <t>n/a — initial certificate</t>
         </is>
       </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="V47" s="10" t="n">
+        <v>22.05</v>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>031-3-К/26</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
@@ -34866,17 +34862,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>QCSP_001_WED-II_v.01</t>
         </is>
       </c>
       <c r="AB47" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>for review — new specification required</t>
         </is>
       </c>
       <c r="AC47" s="8" t="inlineStr">
         <is>
-          <t>no Total THC result on this certificate</t>
+          <t>new specification required — 22.05 % is in no window of WED (nearest 23.40 – 28.59); nominal and tolerance to define, numeral II</t>
         </is>
       </c>
     </row>
@@ -34902,14 +34898,12 @@
         <f>IF(ISNUMBER(F48),MAX(DATE(2026,6,6),F48+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F48" s="5" t="n">
+        <v>46064</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>031-2-ГС-26</t>
         </is>
       </c>
       <c r="H48" s="2">
@@ -34945,9 +34939,9 @@
           <t>Pure Michigen</t>
         </is>
       </c>
-      <c r="O48" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>031-2-К-26, (10.02.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P48" s="6" t="inlineStr">
@@ -34972,7 +34966,7 @@
       </c>
       <c r="T48" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #4 (CNP)</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -35043,14 +35037,12 @@
         <f>IF(ISNUMBER(F49),MAX(DATE(2026,6,6),F49+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F49" s="5" t="n">
+        <v>46065</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>031-5-ГС-26</t>
         </is>
       </c>
       <c r="H49" s="2">
@@ -35086,9 +35078,9 @@
           <t>Amnesia Core Cut</t>
         </is>
       </c>
-      <c r="O49" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>031-5-К-26, (10.02.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
@@ -35113,7 +35105,7 @@
       </c>
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -35178,14 +35170,12 @@
         <f>IF(ISNUMBER(F50),MAX(DATE(2026,6,6),F50+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F50" s="5" t="n">
+        <v>46065</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>031-4-ГС-26</t>
         </is>
       </c>
       <c r="H50" s="2">
@@ -35221,9 +35211,9 @@
           <t>Chem Flyer</t>
         </is>
       </c>
-      <c r="O50" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>031-4-К-26, (10.02.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
@@ -35248,7 +35238,7 @@
       </c>
       <c r="T50" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -35455,11 +35445,11 @@
         <v/>
       </c>
       <c r="F52" s="5" t="n">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>051-1-LoD-26</t>
+          <t>1056-2026</t>
         </is>
       </c>
       <c r="H52" s="2">
@@ -35522,7 +35512,7 @@
       </c>
       <c r="T52" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -35588,11 +35578,11 @@
         <v/>
       </c>
       <c r="F53" s="5" t="n">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>051-3-LoD-26</t>
+          <t>1065-2026</t>
         </is>
       </c>
       <c r="H53" s="2">
@@ -35655,7 +35645,7 @@
       </c>
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP)</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -35721,11 +35711,11 @@
         <v/>
       </c>
       <c r="F54" s="5" t="n">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>051-4-LoD-26</t>
+          <t>1058-2026</t>
         </is>
       </c>
       <c r="H54" s="2">
@@ -35788,7 +35778,7 @@
       </c>
       <c r="T54" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -35854,11 +35844,11 @@
         <v/>
       </c>
       <c r="F55" s="5" t="n">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>051-6-LoD-26</t>
+          <t>1060-2026</t>
         </is>
       </c>
       <c r="H55" s="2">
@@ -35921,7 +35911,7 @@
       </c>
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ)</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -35987,11 +35977,11 @@
         <v/>
       </c>
       <c r="F56" s="5" t="n">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>051-2-LoD-26</t>
+          <t>1061-2026</t>
         </is>
       </c>
       <c r="H56" s="2">
@@ -36054,7 +36044,7 @@
       </c>
       <c r="T56" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -36120,11 +36110,11 @@
         <v/>
       </c>
       <c r="F57" s="5" t="n">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>051-5-LoD-26</t>
+          <t>1057-2026</t>
         </is>
       </c>
       <c r="H57" s="2">
@@ -36187,7 +36177,7 @@
       </c>
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ)</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -36386,11 +36376,11 @@
         <v/>
       </c>
       <c r="F59" s="5" t="n">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>ППК26031</t>
+          <t>1062-2026</t>
         </is>
       </c>
       <c r="H59" s="2">
@@ -36453,7 +36443,7 @@
       </c>
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ)</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -36519,11 +36509,11 @@
         <v/>
       </c>
       <c r="F60" s="5" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>ППК26030</t>
+          <t>1059-2026</t>
         </is>
       </c>
       <c r="H60" s="2">
@@ -36586,7 +36576,7 @@
       </c>
       <c r="T60" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 06.06.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 06.06.2026</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -37715,22 +37705,20 @@
         <f>IF(ISNUMBER(F69),MAX(DATE(2026,6,6),F69+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F69" s="5" t="n">
+        <v>46153</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ППК26067</t>
         </is>
       </c>
       <c r="H69" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060332|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060322|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I69" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060332|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060322|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -37745,18 +37733,22 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>FB012601_1</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>P060332</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+          <t>P060322</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>ППК26067, (11.05.2026) [CNP]</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
@@ -37771,17 +37763,17 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ-PP-2026-0019</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>P060332|I</t>
+          <t>P060322|I</t>
         </is>
       </c>
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — rule date 18.05.2026 held to the legacy series day</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -37789,46 +37781,40 @@
           <t>n/a — initial certificate</t>
         </is>
       </c>
-      <c r="V69" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="V69" s="10" t="n">
+        <v>14.68</v>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ППК26067</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.00 ± 1.20 (III)</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.80 – 16.19 %</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FB_THC15 : CBD1</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC69" s="8" t="inlineStr">
-        <is>
-          <t>no Total THC result on this certificate</t>
-        </is>
-      </c>
+          <t>QCSP_001_FB-III_v.01</t>
+        </is>
+      </c>
+      <c r="AB69" s="8" t="inlineStr">
+        <is>
+          <t>for review — replaces the issued QCSP_001_FB-III_v.01 (was FB_THC16 : CBD1, 14.86 – 17.14 %); now FB_THC15 : CBD1 13.80 – 16.19 %</t>
+        </is>
+      </c>
+      <c r="AC69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
@@ -37852,20 +37838,22 @@
         <f>IF(ISNUMBER(F70),MAX(DATE(2026,6,6),F70+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F70" s="5" t="n">
-        <v>46153</v>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>ППК26067</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060322|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060342|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I70" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060322|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060342|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -37880,22 +37868,22 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>SCR012601*</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060342</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>ППК26067, (11.05.2026) [CNP]</t>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P70" s="6" t="inlineStr">
@@ -37910,17 +37898,17 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0019</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>P060322|I</t>
+          <t>P060342|I</t>
         </is>
       </c>
       <c r="T70" s="7" t="inlineStr">
         <is>
-          <t>registered — rule date 18.05.2026 held to the legacy series day</t>
+          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -37928,40 +37916,46 @@
           <t>n/a — initial certificate</t>
         </is>
       </c>
-      <c r="V70" s="10" t="n">
-        <v>14.68</v>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>ППК26067</t>
+          <t>—</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>15.00 ± 1.20 (III)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>13.80 – 16.19 %</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>FB_THC15 : CBD1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>QCSP_001_FB-III_v.01</t>
-        </is>
-      </c>
-      <c r="AB70" s="8" t="inlineStr">
-        <is>
-          <t>for review — replaces the issued QCSP_001_FB-III_v.01 (was FB_THC16 : CBD1, 14.86 – 17.14 %); now FB_THC15 : CBD1 13.80 – 16.19 %</t>
-        </is>
-      </c>
-      <c r="AC70" s="11" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB70" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC70" s="8" t="inlineStr">
+        <is>
+          <t>no Total THC result on this certificate</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2">
@@ -37985,22 +37979,20 @@
         <f>IF(ISNUMBER(F71),MAX(DATE(2026,6,6),F71+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F71" s="5" t="n">
+        <v>46174</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>361-0691-26</t>
         </is>
       </c>
       <c r="H71" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060352|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060332|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I71" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060352|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060332|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -38015,17 +38007,17 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>FB012602*</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060332</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr">
@@ -38045,17 +38037,17 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0021</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>P060352|I</t>
+          <t>P060332|I</t>
         </is>
       </c>
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -38126,22 +38118,20 @@
         <f>IF(ISNUMBER(F72),MAX(DATE(2026,6,6),F72+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F72" s="5" t="n">
+        <v>46174</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>366-0696-26</t>
         </is>
       </c>
       <c r="H72" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060362|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060352|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I72" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060362|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060352|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -38156,17 +38146,17 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>FB012602*</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>P060362</t>
+          <t>P060352</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr">
@@ -38174,9 +38164,9 @@
           <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -38186,17 +38176,17 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0020</t>
+          <t>CoQ-PP-2026-0021</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>P060362|I</t>
+          <t>P060352|I</t>
         </is>
       </c>
       <c r="T72" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #1 (CNP), #2 (CNP), #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #7 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -38267,22 +38257,20 @@
         <f>IF(ISNUMBER(F73),MAX(DATE(2026,6,6),F73+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F73" s="5" t="n">
+        <v>46174</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>365-0695-26</t>
         </is>
       </c>
       <c r="H73" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060372|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060362|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I73" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060372|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060362|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -38297,17 +38285,17 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>CC012603</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>P060372</t>
+          <t>P060362</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr">
@@ -38315,9 +38303,9 @@
           <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
-      <c r="P73" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -38327,17 +38315,17 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0024</t>
+          <t>CoQ-PP-2026-0020</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>P060372|I</t>
+          <t>P060362|I</t>
         </is>
       </c>
       <c r="T73" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #1 (CNP), #2 (CNP), #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #7 (CNP), #8 (CNP), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -38408,22 +38396,20 @@
         <f>IF(ISNUMBER(F74),MAX(DATE(2026,6,6),F74+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F74" s="5" t="n">
+        <v>46174</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>363-0693-26</t>
         </is>
       </c>
       <c r="H74" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060342|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060372|I",'iCoA Register'!$AA:$AA,0)),"—")</f>
         <v/>
       </c>
       <c r="I74" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060342|I",'iCoA Register'!$AA:$AA,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060372|I",'iCoA Register'!$AA:$AA,0)),"")</f>
         <v/>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -38438,17 +38424,17 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>SCR012601*</t>
+          <t>CC012603</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>P060342</t>
+          <t>P060372</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr">
@@ -38468,17 +38454,17 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ-PP-2026-0024</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>P060342|I</t>
+          <t>P060372|I</t>
         </is>
       </c>
       <c r="T74" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -38549,14 +38535,12 @@
         <f>IF(ISNUMBER(F75),MAX(DATE(2026,6,6),F75+7),DATE(2026,6,6))</f>
         <v/>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F75" s="5" t="n">
+        <v>46174</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>364-0694-26</t>
         </is>
       </c>
       <c r="H75" s="2">
@@ -38619,7 +38603,7 @@
       </c>
       <c r="T75" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -38758,7 +38742,7 @@
       </c>
       <c r="T76" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ)</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -38891,7 +38875,7 @@
       </c>
       <c r="T77" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -39024,7 +39008,7 @@
       </c>
       <c r="T78" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -39157,7 +39141,7 @@
       </c>
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #1 (CNP), #7 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #1 (CNP), #7 (CNP)</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -39290,7 +39274,7 @@
       </c>
       <c r="T80" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ)</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -39423,7 +39407,7 @@
       </c>
       <c r="T81" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ)</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -39556,7 +39540,7 @@
       </c>
       <c r="T82" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -39689,7 +39673,7 @@
       </c>
       <c r="T83" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #11 (CNP)</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -39822,7 +39806,7 @@
       </c>
       <c r="T84" s="7" t="inlineStr">
         <is>
-          <t>registered — held to the packaging date · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — held to the packaging date</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -40328,7 +40312,11 @@
           <t>P060332</t>
         </is>
       </c>
-      <c r="N88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
           <t>197-6-K-26, (07.08.2026) [FHM-K]</t>
@@ -51034,7 +51022,11 @@
           <t>P160012</t>
         </is>
       </c>
-      <c r="N169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
           <t>ППК26117, (06.07.2026) [CNP]</t>
@@ -51080,34 +51072,30 @@
       </c>
       <c r="X169" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28.00 ± 2.00 (I)</t>
         </is>
       </c>
       <c r="Y169" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26.00 – 29.99 %</t>
         </is>
       </c>
       <c r="Z169" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GP_THC28 : CBD1</t>
         </is>
       </c>
       <c r="AA169" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB169" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC169" s="8" t="inlineStr">
-        <is>
-          <t>strain not in the potency specification of 15.09.2026</t>
-        </is>
-      </c>
+          <t>QCSP_001_GP-I_v.01</t>
+        </is>
+      </c>
+      <c r="AB169" s="8" t="inlineStr">
+        <is>
+          <t>for review — replaces the issued QCSP_001_GP-I_v.01 (was GP_THC28 : CBD1, 26.61 – 29.39 %); now GP_THC28 : CBD1 26.00 – 29.99 %</t>
+        </is>
+      </c>
+      <c r="AC169" s="11" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2">
@@ -51167,7 +51155,11 @@
           <t>P160022</t>
         </is>
       </c>
-      <c r="N170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
           <t>ППК26118, (06.07.2026) [CNP]</t>
@@ -51213,34 +51205,30 @@
       </c>
       <c r="X170" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24.00 ± 2.00 (II)</t>
         </is>
       </c>
       <c r="Y170" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22.00 – 25.99 %</t>
         </is>
       </c>
       <c r="Z170" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AA170" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB170" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC170" s="8" t="inlineStr">
-        <is>
-          <t>strain not in the potency specification of 15.09.2026</t>
-        </is>
-      </c>
+          <t>QCSP_001_GP-II_v.01</t>
+        </is>
+      </c>
+      <c r="AB170" s="8" t="inlineStr">
+        <is>
+          <t>for review — replaces the issued QCSP_001_GP-II_v.01 (was GP_THC26 : CBD1, 25.40 – 26.60 %); now GP_THC24 : CBD1 22.00 – 25.99 %</t>
+        </is>
+      </c>
+      <c r="AC170" s="11" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2">
@@ -51300,7 +51288,11 @@
           <t>P160032</t>
         </is>
       </c>
-      <c r="N171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
           <t>ППК26119, (06.07.2026) [CNP]</t>
@@ -51346,34 +51338,30 @@
       </c>
       <c r="X171" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24.00 ± 2.00 (II)</t>
         </is>
       </c>
       <c r="Y171" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22.00 – 25.99 %</t>
         </is>
       </c>
       <c r="Z171" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GP_THC24 : CBD1</t>
         </is>
       </c>
       <c r="AA171" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB171" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC171" s="8" t="inlineStr">
-        <is>
-          <t>strain not in the potency specification of 15.09.2026</t>
-        </is>
-      </c>
+          <t>QCSP_001_GP-II_v.01</t>
+        </is>
+      </c>
+      <c r="AB171" s="8" t="inlineStr">
+        <is>
+          <t>for review — replaces the issued QCSP_001_GP-II_v.01 (was GP_THC26 : CBD1, 25.40 – 26.60 %); now GP_THC24 : CBD1 22.00 – 25.99 %</t>
+        </is>
+      </c>
+      <c r="AC171" s="11" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2">
@@ -51643,7 +51631,7 @@
     <row r="175" ht="150" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | GG1024: no initial certificate for #3, #4, #5, #6 — only the retest 220-9-K-26 of 25.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #4 — only the retest 220-25-K-26 of 26.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
@@ -55014,7 +55002,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v53 on 20.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v54 on 21.09.2026</t>
         </is>
       </c>
     </row>
@@ -55028,14 +55016,14 @@
     <row r="3" ht="190" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | GG1024: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-9-K-26 of 25.08.2026 / 220-9-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #10 — only the retest 220-14-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060412: no initial certificate for #10 — only the retest 220-17-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060422: no initial certificate for #10 — only the retest 220-18-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | P060172: no initial certificate for #10 — only the retest 220-19-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060232: no initial certificate for #10 — only the retest 220-24-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-4-K-26 of 11.09.2026 / 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060122: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-1-K-26 of 25.08.2026 / 220-1-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060132: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-6-K-26 of 25.08.2026 / 220-6-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-25-K-26 of 26.08.2026 / 220-25-M-26 of 11.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 06.06.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 06.06.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 06.06.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins) and, for every determination not retested, the initial certificate's result and document (owner, 15.09.2026); its rule date is 7 days after the latest retest certificate it cites, and it is numbered, in date order with the release series, once the retest assay, the mycotoxins and the campaign's internal certificate (sampled and issued per sampling_dates.py) all exist — Tranche 1 and Tranche 2 in this build (Tranche 2 since v30, its potency certificates of 25/26.08.2026 taken in on 15.09.2026). TRANCHE 3 (owner, 15.09.2026, evening): every Tranche 3 retest parameter is tested at Farmahem and its certificates all issue on one date, so the Tranche 3 reissues take their codes now — after the last Tranche 2 reissue, in the order the series gives them — with Issuable reading 'allocated' and the planned date the owner's: 21.09.2026, all Tranche 3 certificates on one day, the 227-М mycotoxin certificates expected by 18.09.2026, provisional until they exist; the one code computed in advance, by the owner's ruling. After the numbered and the allocated rows, the batches the tranches do not cover — under production, under testing, or on no tranche list — are listed lot by lot; such a batch carries its release certificate and no retest row, because only the tranche batches are for sale and only they were retested at the QP's request (owner, 15.09.2026). RULED (Head of QC, 18.09.2026, "assign codes if they're missing"): the rows the register had withheld only for want of a packaging date on the list — CC042601 and FB042601, release and reissue, and P160012, P160022, P160032 — take their codes after the last allocated one, release certificates first, with Issuable reading 'ruled' and no planned date until the list carries the packaging date. FORMULAS: No. counts the rows whose Issuable is 'yes', 'allocated' or 'ruled'; No. and the code as on the iCoA Register; Rule date is 06.06.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 06.06.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. SUPERSEDES (initial CoQ): a reissue names the initial certificate of the same lot by the register's own code, looked up by Key, so it follows a renumbering; n/a on an initial certificate. POTENCY GRADING (owner, 15.09.2026): the Total THC result the certificate prints, the certificate it comes from, the grade of the Head of QC's potency specification of 15.09.2026 (Potency Grades tab) whose window it falls in — nominal ± tolerance, with the strain's grade numeral — and the product code {ABBR}_THC{nominal} : CBD1 and specification document code QCSP_001_{ABBR}-{numeral}_v.01 that follow — always v.01 (owner, 15.09.2026: the initially issued specifications were wrong and this is not the official issuing; the set goes for review), the status recording what the issued v.01 of the same strain and numeral printed. The numeral is SEQUENTIAL within the strain (owner, 15.09.2026): the grades of the specification of 15.09.2026 are numbered as that table lists them, frozen in potency_grades_2026-09-15.csv, and a grade defined later takes the strain's next numeral whatever its nominal — so -II is not lower or higher than -I, only later. A result in no window of its strain needs a specification of its own: the row says 'new specification required', names the nearest window and reserves the strain's next numeral for it; no grade is guessed. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | GG1024: no initial certificate for #3, #4, #5, #6 — only the retest 220-9-K-26 of 25.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-16-K-26 of 11.09.2026 / 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060362: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-16-K-26 of 25.08.2026 / 220-16-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-1-K-26 of 11.09.2026 / 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #3, #4, #5, #6, #9 — only the retest 227-8-K-26 of 11.09.2026 / 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060112: no initial certificate for #4 — only the retest 220-25-K-26 of 26.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060372: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-29-K-26 of 26.08.2026 / 220-29-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060492: no initial certificate on file — the CoQ keeps its planned number with a provisional date 13.08.2026 | P060492: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-30-K-26 of 26.08.2026 / 220-30-M-26 of 11.09.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | FB042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-31-K-26 of 26.08.2026 / 220-31-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | CC042601: no initial certificate for #3, #4, #5, #6, #10 — only the retest 220-32-K-26 of 26.08.2026 / 220-32-M-26 of 11.09.2026; the — CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v53.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v54.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -55002,7 +55002,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v54 on 21.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v55 on 21.09.2026</t>
         </is>
       </c>
     </row>
@@ -55023,7 +55023,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v54.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v55.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -55002,7 +55002,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v55 on 21.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v56 on 21.09.2026</t>
         </is>
       </c>
     </row>
@@ -55023,7 +55023,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v55.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v56.xlsx, sheets iCoA Register and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>
